--- a/data/schemas/data_investigation.xlsx
+++ b/data/schemas/data_investigation.xlsx
@@ -4,13 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="21942" windowHeight="9017" activeTab="3"/>
+    <workbookView windowWidth="21942" windowHeight="9737" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="Record Count" sheetId="1" r:id="rId1"/>
-    <sheet name="Entities" sheetId="2" r:id="rId2"/>
-    <sheet name="Provenance Metadata" sheetId="3" r:id="rId3"/>
-    <sheet name="Array Complexity" sheetId="4" r:id="rId4"/>
+    <sheet name="bronze.record_count" sheetId="1" r:id="rId1"/>
+    <sheet name="bronze.entities" sheetId="2" r:id="rId2"/>
+    <sheet name="bronze.provenance_metadata" sheetId="3" r:id="rId3"/>
+    <sheet name="bronze.array_complexity" sheetId="4" r:id="rId4"/>
+    <sheet name="silver.flattened_notes" sheetId="5" r:id="rId5"/>
+    <sheet name="silver.data_quality" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="99">
   <si>
     <t>total_records</t>
   </si>
@@ -210,6 +212,131 @@
   </si>
   <si>
     <t>max_notes_per_entity</t>
+  </si>
+  <si>
+    <t>entity_id</t>
+  </si>
+  <si>
+    <t>entity_name</t>
+  </si>
+  <si>
+    <t>entity_type</t>
+  </si>
+  <si>
+    <t>primary_jurisdiction</t>
+  </si>
+  <si>
+    <t>provenance_sources</t>
+  </si>
+  <si>
+    <t>sanction_reason</t>
+  </si>
+  <si>
+    <t>sanction_program</t>
+  </si>
+  <si>
+    <t>entity_notes</t>
+  </si>
+  <si>
+    <t>Q7680491</t>
+  </si>
+  <si>
+    <t>Tam Yiu-chung</t>
+  </si>
+  <si>
+    <t>hk</t>
+  </si>
+  <si>
+    <t>everypolitician, wd_categories, us_ofac_sdn, us_sam_exclusions, ann_pep_positions, wikidata, wd_peps, us_trade_csl</t>
+  </si>
+  <si>
+    <t>2019-05-21T00:00:00</t>
+  </si>
+  <si>
+    <t>Executive Order 13936 (HK)</t>
+  </si>
+  <si>
+    <t>HK-EO13936</t>
+  </si>
+  <si>
+    <t>(also YAOZONG TAN) 
+ (also YIU-CHUNG TAM) 
+ Hong Kong politician</t>
+  </si>
+  <si>
+    <t>Q7690322</t>
+  </si>
+  <si>
+    <t>Tayseer Qala Awwad</t>
+  </si>
+  <si>
+    <t>sy</t>
+  </si>
+  <si>
+    <t>fr_tresor_gels_avoir, wd_categories, be_fod_sanctions, eu_fsf, ann_pep_positions, ch_seco_sanctions, ca_dfatd_sema_sanctions, mc_fund_freezes, gb_hmt_sanctions, wikidata, wd_peps, eu_travel_bans, gb_coh_disqualified, au_dfat_sanctions, gb_fcdo_sanctions, eu_journal_sanctions</t>
+  </si>
+  <si>
+    <t>2022-04-27T18:12:14</t>
+  </si>
+  <si>
+    <t>2020/716 (OJ L168)</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>Last known position: Minister of Justice 
+ Former Minister of Justice under the former al-Assad regime. Associated with the former al-Assad regime and its violent repression of the civilian population. Former Head of Military Court. Member of the High Judicial Council. 
+ Syrian minister of justice 
+ The Director Disqualification Sanction was imposed on 09/04/2025. 
+ (Date of UN designation: 2011-09-23) 
+ Disqualified 
+ Lié à l’ancien régime d’al-Assad et impliqué dans la répression violente exercée contre la population civile. Ancien président de tribunal militaire. Membre du Haut Conseil de la justice.</t>
+  </si>
+  <si>
+    <t>Part 2</t>
+  </si>
+  <si>
+    <t>Syria / Syrie</t>
+  </si>
+  <si>
+    <t>SYR</t>
+  </si>
+  <si>
+    <t>Council Decision concerning restrictive measures against Syria</t>
+  </si>
+  <si>
+    <t>Lié à l’ancien régime d’al-Assad et impliqué dans la répression violente exercée contre la population civile. Ancien président de tribunal militaire. Membre du Haut Conseil de la justice.</t>
+  </si>
+  <si>
+    <t>(UE) 2018/774 du 28/05/2018 (UE Syrie - R (UE) 36/2012 ), (UE) 2020/716 du 28/05/2020 (UE Syrie - R (UE) 36/2012 ), (UE) 950/2011 du 23/09/2011 (UE Syrie - R (UE) 36/2012 ), (UE) 2025/1094 du 27/05/2025 (UE Syrie - R (UE) 36/2012 )</t>
+  </si>
+  <si>
+    <t>act: sanctions anti money laundering act 2018 | section: 3A | description_identifier: disqualification under sanctions regulation</t>
+  </si>
+  <si>
+    <t>There are reasonable grounds to suspect that they are an involved person under the Syria (Sanctions) (EU Exit) Regulations 2019 because they are or have been involved in activities carried out on behalf of the Assad regime, implementing or connected to the repressive police of that regime and/or involved in supporting or benefitting from the Assad regime.</t>
+  </si>
+  <si>
+    <t>The Syria (Sanctions) (EU Exit) Regulations 2019</t>
+  </si>
+  <si>
+    <t>There are reasonable grounds to suspect that they are an involved person under the Syria (Sanctions) (EU Exit) Regulations 2019 because they are or have been involved in activities carried out on behalf of the Assad regime, implementing or connected to the repressive police of that regime and/or involved in supporting or benefitting from the Assad regime.</t>
+  </si>
+  <si>
+    <t>Syria</t>
+  </si>
+  <si>
+    <t>Ancien ministre de la justice sous l’ancien régime d’al-Assad. Lié à l’ancien régime d’al-Assad et impliqué dans la répression violente exercée contre la population civile. Ancien président de tribunal militaire. Membre du Haut Conseil de la justice.</t>
+  </si>
+  <si>
+    <t>total_rows</t>
+  </si>
+  <si>
+    <t>valid_reasons</t>
+  </si>
+  <si>
+    <t>valid_notes</t>
   </si>
 </sst>
 </file>
@@ -861,7 +988,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -869,6 +996,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -880,12 +1022,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1279,24 +1415,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="8">
+      <c r="A2" s="7">
         <v>1245058</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>446542</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <v>326001</v>
       </c>
     </row>
@@ -1320,98 +1456,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="11" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="10">
         <v>1003458</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="10">
         <v>108502</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="10">
         <v>71939</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="10">
         <v>20367</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="10">
         <v>18469</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="10">
         <v>13674</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="10">
         <v>8264</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="10">
         <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="10">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="10">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="10">
         <v>1</v>
       </c>
     </row>
@@ -1434,169 +1570,169 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="4"/>
+      <c r="E1" s="9"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="4"/>
+      <c r="E2" s="9"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="9"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="4"/>
+      <c r="E4" s="9"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="9"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="9"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="9"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="9"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="9"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="9"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="4"/>
+      <c r="E11" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1615,19 +1751,400 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
+      <c r="A1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="7">
+        <v>102</v>
+      </c>
+      <c r="B2" s="7">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultColWidth="9.1" defaultRowHeight="15.85"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12.7166666666667" customWidth="1"/>
+    <col min="3" max="3" width="10.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="17.6416666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.3583333333333" customWidth="1"/>
+    <col min="6" max="6" width="10.7833333333333" customWidth="1"/>
+    <col min="7" max="7" width="16.075" customWidth="1"/>
+    <col min="8" max="8" width="18.0666666666667" customWidth="1"/>
+    <col min="9" max="9" width="27.15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" ht="111" spans="1:9">
+      <c r="A2" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" ht="409.5" spans="1:9">
+      <c r="A3" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" ht="409.5" spans="1:9">
+      <c r="A4" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" ht="409.5" spans="1:9">
+      <c r="A5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" ht="409.5" spans="1:9">
+      <c r="A6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" ht="409.5" spans="1:9">
+      <c r="A7" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" ht="409.5" spans="1:9">
+      <c r="A8" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" ht="409.5" spans="1:9">
+      <c r="A9" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" ht="409.5" spans="1:9">
+      <c r="A10" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" ht="409.5" spans="1:9">
+      <c r="A11" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="9.1" defaultRowHeight="15.85" outlineLevelRow="1" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="10.2" customWidth="1"/>
+    <col min="2" max="2" width="12.9166666666667" customWidth="1"/>
+    <col min="3" max="3" width="10.9166666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>97</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="2">
-        <v>102</v>
+        <v>1520592</v>
       </c>
       <c r="B2" s="2">
-        <v>100</v>
+        <v>224537</v>
+      </c>
+      <c r="C2" s="2">
+        <v>570521</v>
       </c>
     </row>
   </sheetData>

--- a/data/schemas/data_investigation.xlsx
+++ b/data/schemas/data_investigation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="21942" windowHeight="9737" firstSheet="1" activeTab="5"/>
+    <workbookView windowWidth="21942" windowHeight="9737" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="bronze.record_count" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="bronze.array_complexity" sheetId="4" r:id="rId4"/>
     <sheet name="silver.flattened_notes" sheetId="5" r:id="rId5"/>
     <sheet name="silver.data_quality" sheetId="6" r:id="rId6"/>
+    <sheet name="gold.chunked_df" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="117">
   <si>
     <t>total_records</t>
   </si>
@@ -337,6 +338,60 @@
   </si>
   <si>
     <t>valid_notes</t>
+  </si>
+  <si>
+    <t>gold_text</t>
+  </si>
+  <si>
+    <t>NK-BzkLKSJByLmXCxMvzVrXwb</t>
+  </si>
+  <si>
+    <t>Anton Sergeevich Urusov</t>
+  </si>
+  <si>
+    <t>Entity Name: Anton Sergeevich Urusov | Type: Person | Jurisdiction: ru | Risk Context: Executive Order 14024 (Russia) | (also ANTON SERGEYEVICH URUSOV) General Director of Perspective Industrial and Infrastructure Technologies (also ANTON SERGEEVICH URUSOV)</t>
+  </si>
+  <si>
+    <t>Entity Name: Anton Sergeevich Urusov | Type: Person | Jurisdiction: ru | Risk Context: (also ANTON SERGEYEVICH URUSOV) General Director of Perspective Industrial and Infrastructure Technologies (also ANTON SERGEEVICH URUSOV)</t>
+  </si>
+  <si>
+    <t>NK-BzmyxXH2ubH6ZPBeoQ76Nx</t>
+  </si>
+  <si>
+    <t>Priscilla Conner</t>
+  </si>
+  <si>
+    <t>Entity Name: Priscilla Conner | Type: Person | Jurisdiction: us | Risk Context: 1128b4</t>
+  </si>
+  <si>
+    <t>NK-Bzp3cVcUErdtrJ9KUo5aHy</t>
+  </si>
+  <si>
+    <t>OOO BLM SINERZHI</t>
+  </si>
+  <si>
+    <t>Entity Name: OOO BLM SINERZHI | Type: Company | Jurisdiction: ru | Risk Context: Executive Order 14024 (Russia) | (also OOO BLM SINERZHI) (also BLM SYNERGY LLC)</t>
+  </si>
+  <si>
+    <t>Entity Name: OOO BLM SINERZHI | Type: Company | Jurisdiction: ru | Risk Context: (also OOO BLM SINERZHI) (also BLM SYNERGY LLC)</t>
+  </si>
+  <si>
+    <t>NK-Bzrjd3pB3Uju2XZ6vK6yno</t>
+  </si>
+  <si>
+    <t>HOJO</t>
+  </si>
+  <si>
+    <t>Entity Name: HOJO | Type: Vessel | Jurisdiction: Unknown | Risk Context: 07114 - FIRE SAFETY - Remote Means of control (opening,pumps,ventilation,etc.) Machinery spaces (no responsibility of RO)07114 - FIRE SAFETY - Remote Means of control (opening,pumps,ventilation,etc.) Machinery spaces (no responsibility of RO) | 07114 - FIRE SAFETY - Remote Means of control (opening,pumps,ventilation,etc.) Machinery spaces (no responsibility of RO) | 07103 - FIRE SAFETY - Division - decks,bulkheads and penetrations (no responsibility of RO) | 07116 - FIRE SAFETY - Ventilation (no responsibility of RO)</t>
+  </si>
+  <si>
+    <t>NK-Bzy6mZ2F8ZVQtQstUaej84</t>
+  </si>
+  <si>
+    <t>Munzir Jamil AL ASAD</t>
+  </si>
+  <si>
+    <t>Entity Name: Munzir Jamil AL ASAD | Type: Person | Jurisdiction: sy | Risk Context: Involved in violence against the civilian population as part of the Shabiha militia under the former al-Assad regime. Last known position: Member of the Shabiha militia. Passport No.: a) 86449, b) 842781. Impliqué dans les violences exercées contre la population civile en tant que membre de la milice Shabiha sous l'ancien régime d'al-Assad. (Date of UN designation: 2011-05-09) (Date of listing: 9.5.2011) Cousin of President Bashar al Asad Cousin of President Bashar al Asad The Director Disqualification Sanction was imposed on 09/04/2025. N° Passeport : 86449 et 842781 Date of listing: 9.5.2011 Disqualified</t>
   </si>
 </sst>
 </file>
@@ -988,8 +1043,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1004,12 +1066,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1415,24 +1471,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="7">
+      <c r="A2" s="5">
         <v>1245058</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="5">
         <v>446542</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="5">
         <v>326001</v>
       </c>
     </row>
@@ -1456,98 +1512,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>1003458</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="11">
         <v>108502</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="11">
         <v>71939</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="11">
         <v>20367</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="11">
         <v>18469</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="11">
         <v>13674</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="11">
         <v>8264</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="11">
         <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="11">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="11">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1570,169 +1626,169 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="9"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="9"/>
+      <c r="E2" s="10"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="9"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="9"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="9"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="9"/>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="9"/>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="9"/>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="9"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="9"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="9"/>
+      <c r="E11" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1751,18 +1807,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="7">
+      <c r="A2" s="5">
         <v>102</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="5">
         <v>100</v>
       </c>
     </row>
@@ -1790,321 +1846,321 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="8" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="2" ht="111" spans="1:9">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" ht="409.5" spans="1:9">
-      <c r="A3" s="4" t="s">
+    <row r="3" ht="380.55" spans="1:9">
+      <c r="A3" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="4" ht="409.5" spans="1:9">
-      <c r="A4" s="4" t="s">
+    <row r="4" ht="380.55" spans="1:9">
+      <c r="A4" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="5" ht="409.5" spans="1:9">
-      <c r="A5" s="4" t="s">
+    <row r="5" ht="380.55" spans="1:9">
+      <c r="A5" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="6" ht="409.5" spans="1:9">
-      <c r="A6" s="4" t="s">
+    <row r="6" ht="380.55" spans="1:9">
+      <c r="A6" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" ht="409.5" spans="1:9">
-      <c r="A7" s="4" t="s">
+    <row r="7" ht="380.55" spans="1:9">
+      <c r="A7" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="8" ht="409.5" spans="1:9">
-      <c r="A8" s="4" t="s">
+    <row r="8" ht="380.55" spans="1:9">
+      <c r="A8" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="9" ht="409.5" spans="1:9">
-      <c r="A9" s="4" t="s">
+    <row r="9" ht="380.55" spans="1:9">
+      <c r="A9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" ht="409.5" spans="1:9">
-      <c r="A10" s="4" t="s">
+    <row r="10" ht="380.55" spans="1:9">
+      <c r="A10" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" ht="409.5" spans="1:9">
-      <c r="A11" s="4" t="s">
+    <row r="11" ht="380.55" spans="1:9">
+      <c r="A11" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="7" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2126,25 +2182,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
+      <c r="A1" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="5">
+        <v>1520592</v>
+      </c>
+      <c r="B2" s="5">
+        <v>224537</v>
+      </c>
+      <c r="C2" s="5">
+        <v>570521</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultColWidth="9.1" defaultRowHeight="15.85" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="29.9416666666667" customWidth="1"/>
+    <col min="2" max="2" width="23.4166666666667" customWidth="1"/>
+    <col min="3" max="3" width="97.5666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2">
-        <v>1520592</v>
-      </c>
-      <c r="B2" s="2">
-        <v>224537</v>
-      </c>
-      <c r="C2" s="2">
-        <v>570521</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" ht="31.7" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" ht="31.7" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" ht="31.7" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" ht="31.7" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" ht="63.45" spans="1:3">
+      <c r="A10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" ht="63.45" spans="1:3">
+      <c r="A11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/data/schemas/data_investigation.xlsx
+++ b/data/schemas/data_investigation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="21942" windowHeight="9737" firstSheet="2" activeTab="6"/>
+    <workbookView windowWidth="21942" windowHeight="9737" firstSheet="3" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="bronze.record_count" sheetId="1" r:id="rId1"/>
@@ -14,6 +14,7 @@
     <sheet name="silver.flattened_notes" sheetId="5" r:id="rId5"/>
     <sheet name="silver.data_quality" sheetId="6" r:id="rId6"/>
     <sheet name="gold.chunked_df" sheetId="7" r:id="rId7"/>
+    <sheet name="gold_vectors" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="514">
   <si>
     <t>total_records</t>
   </si>
@@ -392,6 +393,1197 @@
   </si>
   <si>
     <t>Entity Name: Munzir Jamil AL ASAD | Type: Person | Jurisdiction: sy | Risk Context: Involved in violence against the civilian population as part of the Shabiha militia under the former al-Assad regime. Last known position: Member of the Shabiha militia. Passport No.: a) 86449, b) 842781. Impliqué dans les violences exercées contre la population civile en tant que membre de la milice Shabiha sous l'ancien régime d'al-Assad. (Date of UN designation: 2011-05-09) (Date of listing: 9.5.2011) Cousin of President Bashar al Asad Cousin of President Bashar al Asad The Director Disqualification Sanction was imposed on 09/04/2025. N° Passeport : 86449 et 842781 Date of listing: 9.5.2011 Disqualified</t>
+  </si>
+  <si>
+    <t>vector</t>
+  </si>
+  <si>
+    <t>NK-24z4UVg9JvWi5NmRkpmv2d</t>
+  </si>
+  <si>
+    <t>FELICITY HOME HEALTH SERVICE</t>
+  </si>
+  <si>
+    <t>Entity Name: FELICITY HOME HEALTH SERVICE | Type: LegalEntity | Jurisdiction: us | Risk Context: BAD DEBT</t>
+  </si>
+  <si>
+    <t>["0.012693095","-0.014630492","-0.055746954","0.0106992135","-0.052692037","0.03415667","0.03564547","-0.031600885","0.014019628","-0.06011081","0.028509561","0.008956576","-0.009141288","-0.046466418","-0.031217419","-0.045822736","0.067213036","0.0073083276","-0.026054146","0.03671668","3.7878173E-4","0.105717145","0.033971682","0.031248823","0.004825897","-0.03587025","-0.02573852","-0.0077515747","-0.01026007","-0.048175674","0.033612538","0.053347807","0.049260806","0.07017189","0.064789295","0.009917055","-0.03066348","0.019106528","-0.005576642","-0.01237328","0.055328716","-0.07837","0.042099454","0.0010881486","-0.011305036","-0.025684519","-0.021586651","0.008864796","0.012733814","0.08770769","-0.059238948","-0.039708402","-0.039478827","0.09081863","0.026219213","0.018187597","-0.019663699","-0.00260926","-0.08172978","-0.047699783","0.06973523","0.06565175","0.0127679445","0.04523393","-0.029992063","0.03837841","0.038997717","0.069938324","0.013231777","-0.078432515","0.020517316","-0.06398859","-0.07409534","0.07470745","0.009122199","0.015782857","0.044717573","0.036451284","0.07952074","-0.06235854","0.002414411","0.044777323","0.034993086","0.069640025","-0.10997196","0.08120397","-0.023187019","-0.037183736","0.016412593","-0.071403116","0.015207686","-0.034750655","0.14170124","-0.050799668","0.042872015","-0.004091648","-0.013933382","-0.13326538","-0.06874297","0.06691742","-0.04925296","0.015504827","0.06138078","0.058020856","0.030925253","0.025993042","-0.010770809","0.012288564","0.028467555","0.002736002","0.013476052","0.05091552","-0.016475903","-0.11853064","0.07018139","0.020196956","-0.06144965","-0.012682699","0.091305204","-0.07384881","0.028560905","-0.024205491","-0.09209742","-0.06739867","-0.041724674","0.025458982","-0.03035923","-7.73156E-34","0.03168839","0.00558569","0.089269035","0.021045608","0.035336178","-0.025407884","0.0047855577","-0.012468703","-0.07037857","0.051072016","0.05545911","-0.004477584","-0.018211834","-0.06653126","0.008021813","0.06418832","-0.08340951","0.051015694","0.03264806","0.09914353","-0.029718136","-0.0019644853","-0.0055318726","0.013613663","-0.064609155","-0.080280624","0.02009085","-0.058559213","0.06975205","0.005491624","0.06355219","0.06796256","0.124465264","-0.030085463","-0.02830427","0.077403106","-0.049646538","-0.029356591","-0.043903254","-0.0014894757","0.02970402","0.046430953","0.0545733","0.082341015","0.06032456","-0.0654068","0.007004205","-0.074222855","0.006560274","0.07014088","-0.022794293","0.0077688303","-0.041122973","0.0179059","-0.017148962","0.0141711105","0.005040078","0.05180685","-0.0062978286","-0.06963178","-0.015139113","-0.10878778","-0.025754973","0.019611124","-0.0144003","-0.03987264","0.014170423","-0.06547497","-0.02187408","-0.0099758115","-0.016651573","0.028893825","0.007512579","0.02655714","-0.0111658955","4.9150677E-4","-0.03599738","-0.052726377","0.005197739","0.01449404","-0.084078215","0.01266425","0.023807267","0.119154245","0.04063518","0.016895669","0.008116375","-0.10107198","-0.04819774","-3.8426515E-4","-0.07746421","0.06408727","0.03696573","0.073277146","0.032256916","-5.810555E-34","-0.06526247","-0.08851128","-0.09021307","0.032728728","0.039513305","-0.08253953","-0.05498247","0.016758805","1.6406504E-4","0.03463454","-0.0097615","-0.045722034","-0.072642475","0.029340222","0.083705455","0.005552741","0.010443322","-0.018579578","-0.025890507","0.08203715","0.020069733","0.028227983","0.0011677537","0.07932459","0.016944898","0.059554145","2.4237845E-4","-4.2690477E-5","-0.0117612425","-0.09815118","0.011634282","0.029717973","0.0022702194","0.094275616","-0.12408892","-0.061934277","0.00446946","-0.097057186","-0.0571923","-0.11014388","0.09741386","5.038637E-4","-0.054822866","-0.013541019","-0.0036785507","-0.032801718","0.025508866","-0.014251278","0.0925368","-0.032859236","0.0116474265","-0.048640214","-0.033434846","0.089766845","0.023202186","0.0685748","0.11163862","-0.0068772626","0.0091973","-0.017540278","0.0022178518","0.11611668","-0.038142044","0.094215415","0.06923124","-0.08889579","-0.04111716","-0.03942838","-0.07863971","-0.0494322","-0.08234366","-0.053147037","-0.033245444","-0.01994036","0.041803762","-0.008728302","-0.0052175582","-0.08115061","-0.08534106","-0.0073377974","0.040366214","-0.061491862","-0.009011648","0.081766635","-0.03510929","-0.026126394","0.058272813","0.025975484","0.02938275","0.09995297","-0.01631186","-0.02661461","-0.053110003","-0.04670663","-0.029942917","-2.4973648E-8","-0.020247132","0.038852796","-0.06948021","-0.014071117","-0.036014475","-0.024785006","-0.016078377","0.05329854","-0.006101134","0.036626358","-0.021748722","0.0660234","-0.03720095","-0.05553355","0.024581574","-0.057473533","-0.034086168","0.027796563","-0.033281732","0.05666271","-0.04626115","0.03798143","0.02433763","-0.0854143","-0.0709869","-0.055827927","0.05874885","0.096721314","0.06588529","-0.008129769","-0.032769836","0.060172055","-0.0041023","-0.017562378","-0.11406062","-0.03286245","0.079540186","-0.053752143","0.020433716","0.018046789","0.008362613","-0.011955212","0.0066055246","-0.02336213","0.03290893","0.011312323","0.02209559","0.013402627","0.08051326","-0.108156435","-0.093761876","-0.03910345","0.04769811","-0.06119418","-0.05622887","0.0065420014","0.03893049","0.04851484","0.013915118","-0.002825662","0.041130915","-0.040248416","0.056286767","0.024394963"]</t>
+  </si>
+  <si>
+    <t>NK-28X5jMopMz2jCXsUDUJczU</t>
+  </si>
+  <si>
+    <t>Fajr Aviation Composite Industries</t>
+  </si>
+  <si>
+    <t>| Filiale de l’Organisation des industries de l’aviation de l’Iran (IAIO) au sein du MODAFL, tous deux désignés par l’Union; elle produit principalement des matériaux composites pour l’industrie aéronautique. Fajr Aviation Composite Industries produit également des drones qui seraient utilisés à des fins de déstabilisation régionale. A subsidiary of the IAIO within MODAFL both designated by the EU which primarily produces composite materials for the aircraft industry. Fajr Aviation Composite Industries also produces drones, which are allegedly being used for regional destabilisation. The Director Disqualification Sanction was imposed on 09/04/2025. A subsidiary of the IAIO within MODAFL which primarily produces composite materials for the aircraft industry and also produces drones</t>
+  </si>
+  <si>
+    <t>["-0.031470846","-0.010060694","0.003067984","-0.04205042","0.078371674","-0.06861513","0.031160826","0.028668802","-0.0147487335","0.03740632","0.041389298","-0.025466383","0.034106188","0.04283105","-0.05632346","-0.013188814","-0.009877341","-0.07516223","-0.03732414","0.03584642","0.058517277","-0.02124237","-1.5560951E-4","0.003840404","0.034711633","0.02415796","-0.05694275","0.065429494","0.006313117","-0.11371122","-0.019283872","0.10023114","0.013838056","0.020539293","0.058626074","0.042383276","-0.024933841","-0.053723764","0.030364191","-0.058852065","0.001374661","-0.05067999","-0.027023232","-0.080207415","-0.05276329","0.013801937","0.10671867","-0.035501294","0.01759709","0.053434692","-0.055377968","0.024078527","0.025838818","-0.023570634","-0.002485594","-0.02577534","-0.028973812","0.016223315","-0.038489144","-0.015420267","0.0038494978","-0.008835017","-0.041268848","-0.021052161","0.018545669","-0.042852473","-0.010578514","-0.05932999","-0.04041884","0.0014868651","0.059526373","-0.08904055","0.03180152","0.05719252","-0.048553765","0.091836475","0.061690863","-0.0012370865","0.026366973","-0.051009983","0.053713188","0.023345409","0.025341488","-0.06531828","-0.0428379","0.023734406","0.04544217","-0.050738394","0.0025171742","0.025218882","0.010025318","0.014455214","0.04342108","-0.0019474673","-0.0021090007","-0.03759417","0.029879907","0.01251287","0.04481595","0.03884291","0.03072843","-0.017714234","-0.00557419","0.0011691796","-0.12083924","-0.064612016","-0.007475623","0.012548131","-0.0052708783","0.0076729045","-0.060105436","0.08675596","-0.02857246","-0.053194683","-0.095535256","0.05710898","0.012970597","-0.011029866","0.0637139","-0.03784272","-0.031431165","-0.02106832","0.076722585","0.08045726","0.07476696","-0.057391025","-0.061341926","5.5549223E-33","-0.053794686","3.9667464E-4","-0.013684144","-0.024573347","-0.025552459","0.016186174","-0.031459354","0.07013236","0.020131303","-0.024268435","-0.059657577","0.051254656","8.598976E-4","0.03783719","0.12901911","-0.105069935","0.06959032","-0.09520882","-0.0056718746","-0.05062024","-0.017080093","-0.07969938","-0.01418848","0.10874332","0.06770148","0.025615538","0.01278093","-0.013390657","-0.039466627","0.09565161","0.060456447","0.091549106","0.012216203","0.059352282","-0.08950282","0.07301571","-0.07929608","0.012208175","-0.07394874","0.036571458","0.059707403","0.015942892","0.0075031146","0.014567646","0.0061276825","-0.06492839","-0.03325213","0.028762104","-0.015839646","0.0055938624","-0.011695746","0.0626283","0.07148648","-0.11120588","0.06183623","0.004017941","-0.041028913","-0.049594585","0.019316133","-0.021263218","-0.021877779","0.049334895","-0.084792316","0.08276389","-0.036593452","0.09395404","0.03520784","-0.009438024","0.04992941","0.04393878","-0.027004763","0.056789335","0.06785641","0.08548282","-0.06088621","0.017779477","-0.108742215","-0.018044684","0.05698566","0.012551945","-0.059112165","0.094455525","0.021726659","-0.08696881","0.016299987","-0.001194155","0.06046316","0.045520168","0.06881786","0.032439064","-0.047865458","-0.07460266","-0.0118572265","-0.0067468807","-0.004929502","-6.6648546E-33","0.037385557","-0.013015643","-0.062803805","0.0074912426","-0.021172151","-0.040262226","0.013560212","0.0059624473","0.00608404","0.00287394","0.0022047157","-0.028997654","0.08091796","-0.006809174","-0.031221563","0.008652437","-0.08189635","-0.07786055","0.016963191","-0.04956907","0.045127586","-0.033766072","0.11356966","0.008050416","-0.03221859","-0.038268015","-0.08153043","-0.02343731","-9.671489E-4","-0.03181325","-0.04210596","-0.04209689","0.011609724","0.0845701","-0.019008964","-0.08129936","-0.03389561","0.044061042","-0.044116113","-0.08408865","0.0019967072","0.011978992","-0.00524136","0.016328737","-0.037399974","-0.09622728","-0.01613986","-0.13739705","0.10134024","-0.16506405","0.03734277","-7.266402E-4","0.018256975","-0.038061008","-0.0037459584","0.071707696","0.07485927","0.012712672","-0.045585666","0.031230362","0.088601284","0.0035719038","0.027270235","0.0058133923","0.084070615","-0.019040832","0.017346924","0.055374373","-0.015565147","0.0145047195","0.13266577","-0.03546593","-0.005513989","0.028708596","-0.0044600316","-0.028167197","-0.01899333","0.069748834","-0.048798632","-0.019040883","0.06617697","-0.062272985","-0.05981807","0.10228304","-0.010678103","0.05529656","0.042737924","-0.06850114","-0.0014473646","0.0036029483","-0.004777253","-0.0036174415","0.042514984","0.060388297","0.0068053445","-4.5831385E-8","0.012645118","-0.029731875","-0.051258415","0.06672229","-0.0038387792","0.008840166","-0.0033899583","-0.048305977","0.010558566","-0.06030726","-0.007950827","-0.059817575","-0.010432447","0.02796947","-0.0014304809","-0.011932935","-0.03738676","0.11437727","0.0015835762","-0.05467866","-0.052448433","0.003354308","-0.0037678152","0.03394119","-0.06046269","0.028748253","-0.025970144","-0.082226925","0.021951163","0.07623042","-0.16560636","0.042037237","0.032632057","-0.027064968","-0.12370887","0.011906881","0.03734395","-0.0881087","-0.12247354","0.03528215","0.07132664","0.008400202","-0.020896394","-0.0026675756","0.084575966","-0.03395013","0.0024038237","-0.11984176","-0.0055333846","-0.009654596","0.05712859","0.013047633","0.0060020383","0.09577551","-0.0056519792","0.030592563","-0.011393628","-0.07795263","0.004036398","-0.0012934837","0.022783767","-0.006946677","0.04894193","-0.0038350374"]</t>
+  </si>
+  <si>
+    <t>NK-2AAxDhQ2A2F3MDjycvmntu</t>
+  </si>
+  <si>
+    <t>AIRRICA ANNETTE DOUGLAS</t>
+  </si>
+  <si>
+    <t>Entity Name: AIRRICA ANNETTE DOUGLAS | Type: Person | Jurisdiction: us | Risk Context: 1128a1</t>
+  </si>
+  <si>
+    <t>["-0.021492174","-0.04521674","-0.09484471","-0.028482473","0.033068612","-0.008959115","0.060825508","-0.032205604","0.021052137","0.0027674893","0.078560196","-0.060554393","-0.07690111","-0.062123172","-0.10050006","0.075155176","0.023511983","-0.011207953","-0.017535703","1.7110146E-4","-0.02174302","0.045238968","0.007756992","-0.013716147","0.0028069264","-0.054406807","-0.0016767078","0.021329474","-0.04408951","-0.0073373783","0.09518343","0.04431429","0.03862356","0.115757816","0.07403693","0.041090854","-0.06432751","0.03407503","0.0011702328","-0.017461693","-0.037011903","-0.08004916","0.072762266","0.08280711","-0.09804873","0.0016996718","-0.048163354","0.032957908","0.06338933","0.06743328","-0.03476436","-0.009718301","-0.057542093","0.015350953","-0.0064225276","0.028516702","-0.051887132","0.032590874","-0.07279799","-0.019360384","-0.022126064","0.04184677","0.05221342","0.056213263","-0.006147693","0.011119666","-0.046107467","-0.030733319","-0.06272771","-0.06536058","0.03770236","-0.0038841153","-0.020924598","0.06607557","0.005706393","0.06255431","0.006229471","0.041078307","0.10106066","-0.023110565","0.04770141","-0.0067955167","-0.014022867","-0.005996434","-0.052480437","0.041156854","-0.017098987","-0.066119894","0.0024827765","0.026182648","-0.018292198","-0.0050457646","0.17354223","-0.004415846","-0.008056261","-0.03594482","0.031179372","-0.0012055075","-0.09216535","0.050506752","-0.02944425","0.028405664","-0.007092462","0.02929901","-0.10978798","-0.05802699","-0.010620156","-0.027868927","0.018013995","0.06673135","-0.04579879","0.08131585","-0.03786886","-0.06058547","0.06538922","-0.043758314","-0.06636288","-0.032249305","0.05737434","-0.15575548","-0.044240717","0.010199884","-0.049869057","-0.0325788","-0.0983305","0.0076191635","0.04489701","-1.3004603E-33","0.043746624","0.067879215","0.06800489","0.059318803","-0.04947859","-0.028920716","0.006580395","-0.04439226","-0.02828146","0.07312398","-0.06396192","-0.005089713","-0.015531054","-0.06692736","0.0411907","0.04387592","-0.061975066","0.028459474","-0.00973786","0.036677085","-0.0032020647","-0.03806546","-0.060161147","0.013567185","0.020522749","-0.066759825","-0.020054793","-0.071054034","-0.006980733","0.044057906","-0.01018483","0.08012944","-0.014303931","-0.045496292","0.041105296","-0.011819994","0.00884861","-0.06680209","-0.055544212","-0.017979369","-0.027962232","0.039952558","0.061539106","0.04796077","-4.608977E-4","8.878003E-4","0.06054135","0.05119765","0.07620667","0.028393598","-0.07061479","0.006916769","0.0180954","-0.012839131","0.0312263","0.01397985","0.0029646473","0.056685437","-0.038504936","-0.06683288","-0.01157959","0.06410944","-0.014010587","0.008241686","-0.07530322","-0.045773532","0.04032565","-0.06409267","0.027402623","-0.03850784","0.04253836","0.015882628","0.03374161","-0.01378073","-0.057832804","0.033656444","0.0447108","0.0026314077","-0.0654767","0.030108519","-0.07384952","-0.002295537","0.046166267","0.0705929","0.06290093","-0.012778225","0.006742078","-0.052125826","-0.039436523","0.088403076","-0.005272693","-0.0062632575","0.017762361","0.003658536","-0.0073041595","-1.430893E-33","-0.06655348","-0.11561069","-0.05260433","-0.072081946","0.052638292","-0.09020127","-0.010681531","0.058789045","0.005639477","-0.071546346","-0.05094965","-0.009583387","0.044402417","-0.018217668","0.08223574","0.0035962826","-0.059882812","0.016245581","-0.009590399","0.020137385","0.047837254","-0.0568602","0.018270165","0.005253123","-0.007975798","-0.0018664578","0.07279762","0.05756935","-0.004678685","-0.1001961","0.028496822","0.09774381","-0.058881473","0.13749798","-0.103633076","-0.08630531","0.05132609","-0.07424238","-0.05290623","-0.070521586","-0.019125974","0.026823806","-0.050072003","0.016650425","-0.043961342","-0.020122698","0.042971294","-0.054214403","0.0368243","-0.08382302","-0.007172722","-0.0065249894","-0.0364018","0.06790279","0.058593888","0.08370435","0.08574829","-0.04295516","0.052182637","4.2301224E-4","-0.014785474","0.09899437","-7.2428E-4","0.11196828","0.041981824","-0.078758344","-0.08637795","-0.0024536336","-0.055008717","-0.027321385","0.028719006","-0.0760876","-0.060000043","0.05597803","0.010139041","-0.028054817","0.042799264","0.002875231","-0.024112307","0.043323394","-0.0041135447","0.028107127","0.027277969","0.07300805","0.040219523","0.09050863","0.03670261","-0.047094043","-0.015693134","0.07293823","-0.012581015","-2.9998607E-4","-0.06980236","-0.050568078","-0.124319","-2.4600629E-8","-0.024237461","0.049634792","0.08555003","-0.04327306","-0.010616785","0.04409555","0.04198209","0.019797519","-0.05005261","-0.020467538","-0.05867578","0.056719188","0.050735563","0.027526155","0.040789027","-0.10624889","-0.0434645","0.08292053","-0.016076434","0.046845764","-0.03351687","0.037166093","-0.019902159","-0.07925011","-0.027783068","0.036519222","0.03483397","-0.019791376","0.06058356","0.04227798","-0.082167245","0.085021876","0.0033252323","-0.030673265","-0.044373993","0.039661594","0.0550643","-0.07238232","-0.095607236","-0.044196587","-0.002102385","0.0839238","-0.012073266","0.032469563","0.122334436","0.02841384","0.0050365846","-0.0145205045","0.041808225","-0.012711648","-0.039132375","-0.029973216","-0.006242764","0.037892845","-0.040846817","-0.08899679","-0.021764016","0.029994106","0.050381597","-0.006525659","0.0047930684","-0.027836766","-0.024953559","0.040822748"]</t>
+  </si>
+  <si>
+    <t>NK-2Caw7MqHeocLTSmpxV4Rhp</t>
+  </si>
+  <si>
+    <t>ADELINA HERRERO</t>
+  </si>
+  <si>
+    <t>Entity Name: ADELINA HERRERO | Type: Person | Jurisdiction: us | Risk Context: 1128a1</t>
+  </si>
+  <si>
+    <t>["-0.057840895","0.027017672","-0.08629062","-0.015308712","-0.035247844","-0.008049298","0.047767717","-0.01964036","-0.008137247","-0.007821956","0.050405625","-0.10752843","-0.05213819","-0.06884968","-0.07737762","0.10696944","0.017444123","0.05314938","-0.038117368","0.025772735","0.049037106","0.065360986","0.021231113","-0.058983374","0.0065484745","-0.06920551","-0.026734944","0.105445","-0.0033754406","-0.046759024","0.067315735","0.06396454","0.07194455","0.05108936","0.06856225","0.06111394","-0.028042369","0.030925943","0.052523736","-0.017120166","0.04421104","-0.044099648","0.014569096","0.037152708","-0.08482784","-0.044846885","-0.06661225","-0.01439723","0.03040228","0.022953713","-0.10041062","-0.054137476","0.032414183","0.06198462","-0.060507834","0.021603944","7.374808E-4","0.045329526","-0.08145176","0.014123381","0.019429442","0.018922005","-0.013041969","0.0043042526","-0.0022382548","0.016038518","-0.00356209","-0.039539397","-0.018638296","-0.05955645","0.101796485","-0.020029023","-0.1261656","0.078075655","-1.8652382E-4","0.038832452","-0.015259103","0.023274016","0.09025785","-0.07355056","-0.043234266","0.0047609545","0.03349373","4.2444954E-4","-0.0062669343","0.026288353","-0.047748633","-0.03419609","0.01716988","0.010283926","-0.043150645","-0.020389125","0.131269","-0.006788169","0.06494449","-0.032876305","0.054214735","0.010880557","-0.03688803","0.06670017","-0.06446915","0.060139585","-0.07419151","0.068205364","-0.048596684","-0.042667925","-0.021025509","-4.108905E-4","-0.0077976095","0.04595445","-0.024531579","0.030371908","-0.03787711","-0.057109103","0.00588214","-0.04383277","-0.10521484","-0.011441128","0.048798386","-0.14895153","-0.011047954","0.021345451","-0.10486057","-0.06656355","-0.033546187","-0.03326049","0.008039095","-1.0202737E-33","0.09722076","0.065031774","0.026716433","0.062423788","0.003837344","0.03539765","-0.036682654","-0.024603168","-0.03094409","0.024389954","-0.05371199","-0.018067818","-0.0103351455","-0.083166175","-0.057426378","0.027723556","0.04749121","0.06990479","-0.017000452","0.118371874","0.059250887","-0.04572694","-0.056517087","0.008736891","-0.020502761","-0.049401086","0.023214407","-0.050496776","0.017345916","0.046610177","-0.033733673","-0.01395336","0.0072660195","-0.08273026","0.06342676","0.038858008","-0.05740454","-0.07117131","-0.040733222","-0.041263532","0.02118075","0.041677557","0.0652867","0.12142797","-0.014445843","0.012088891","0.047973227","0.010920398","0.0784152","0.0052491203","-0.020173788","-0.031901777","-0.04409987","0.0033807487","-0.00239263","0.036520407","-5.6633644E-4","0.094194606","-5.94341E-4","-0.020040292","0.017194385","0.019329391","-0.066242136","0.022343323","-0.017462142","-0.12798959","0.049700785","-0.040316157","-0.0014083303","-0.073363505","0.041773442","0.046997808","0.028596882","0.067581214","-0.08701894","0.062366802","0.059951648","-0.041450035","-0.043499183","0.014879202","-0.1061386","0.011602562","-0.0013561381","0.09645202","0.010677868","0.017887143","-0.013965892","-0.051822368","-0.10631691","0.020948866","0.027573615","0.01105719","-0.028735058","0.02102027","-0.039067496","-1.9045808E-33","-0.061481554","-0.08482643","0.003894556","-0.11125754","0.028264","-0.06859748","0.016612187","0.10698363","0.043081567","-0.036037095","0.010781657","-0.073071375","0.05295581","-0.028263371","0.030064944","0.073199235","-0.030134322","0.037349932","-0.02372104","0.026855847","-0.017247787","0.039603315","-0.012371025","0.041236993","-7.252026E-4","-0.046554394","0.040989965","0.029350104","-0.048282947","-0.057841122","0.06106038","0.018993825","-0.09296203","0.08928913","-0.06798024","-0.037620183","0.065192364","-0.10122128","-0.004053079","-0.0115601085","-0.03612353","0.049800616","-0.029771592","0.049640622","-0.0019206232","0.0061131874","-0.0017427403","-0.027729202","0.033664644","-0.004417829","0.048200425","0.017633185","-0.016233858","-0.02020309","0.02380116","-0.001890522","0.05788269","-0.06381095","0.040490787","0.0052487347","0.047783803","0.13792248","-0.026342435","0.18382251","-0.03088741","-0.016659964","-0.14408867","-0.0070041846","-0.05296957","-0.02374707","0.041996595","-0.050565086","-0.088513866","0.018535174","0.011649239","-0.04147275","-0.012068944","-0.017691523","0.016455915","0.009196037","0.015037006","0.042494893","-0.022708757","0.037384078","0.036086828","0.019159714","0.07445882","0.0156905","-0.006483687","0.046322335","-0.016103541","-0.03263242","-0.09617571","-0.0077331965","-0.0886633","-2.6921871E-8","0.032341424","0.04810582","0.049269512","-0.054859918","0.019718235","-0.017694386","-0.02743638","0.020399287","0.009867436","-0.014212704","-0.05301635","0.061809726","-0.034604274","-0.061157893","0.012667683","-0.073426254","0.013126585","0.07204686","0.00934601","0.034575343","0.011402539","0.017277898","-0.020055179","-0.10657011","0.0019313323","-0.04326222","0.044860605","0.0038526803","0.03561557","-0.03802855","0.016497249","0.103994966","-0.011076819","0.011769818","-0.028979318","0.05722232","0.024077026","-0.06358339","-0.051365443","-0.033194534","0.03976147","0.0082873115","0.01047615","0.03501552","0.07443044","0.024865119","0.020969527","-0.01822716","0.1098009","-0.043557994","-0.06281704","-0.05090619","0.06072238","0.039082207","-0.0784153","-0.051111914","0.0066803484","0.044286106","0.012961985","-0.011813021","0.063784115","-0.040424146","0.042169362","0.013673187"]</t>
+  </si>
+  <si>
+    <t>NK-2H98RCC5QJBzUBwtHk8TMs</t>
+  </si>
+  <si>
+    <t>JRS CARINA</t>
+  </si>
+  <si>
+    <t>Entity Name: JRS CARINA | Type: Vessel | Jurisdiction: Unknown | Risk Context: 07105 - FIRE SAFETY - Fire doors/openings in fire-resisting divisions (no responsibility of RO)</t>
+  </si>
+  <si>
+    <t>["-0.005588742","0.026512844","-0.08644748","0.03547328","0.04366728","0.027822629","-0.009542695","0.0145561285","-0.066265516","-0.030394942","0.031237636","-0.050611623","-0.04445717","0.06899775","-0.039737385","-0.003717367","-0.018870614","0.026585901","-0.06585831","0.06400793","-0.036121964","0.058283124","0.017230043","0.042050216","-0.04209026","-0.0267306","-0.050466042","0.06747314","-0.003112429","-0.058730695","0.012932649","0.041501902","0.042907737","0.028097264","0.04093199","-0.025786106","-0.004269894","0.027647521","-0.011836862","0.055484544","-0.030561455","-0.06009392","-0.017488506","0.037370235","-0.015356521","-0.051984884","-0.025594864","-0.052908543","0.06556321","-0.030390184","-0.10439496","-0.06970256","-0.021702128","0.058986716","-0.019874342","-0.036321625","-0.03206937","-0.008185475","0.01239423","-0.038657505","0.054757405","0.044814125","-0.03858508","0.040373694","-0.057358306","-0.03381118","-0.033838883","0.025003163","0.010936034","-0.04165054","0.09630039","0.008043788","0.016289784","0.051733926","-0.06955974","0.013023265","0.04240793","0.059785023","0.09498686","-0.03476503","0.04481635","-0.05226692","-0.06415406","-0.0058491016","-0.039412018","0.045503583","-0.012841007","-0.05506845","0.042338315","0.06847044","-0.08662246","-0.06362809","0.17455085","0.0048032086","-0.06850194","-0.0230556","0.061011266","0.013626398","-0.024204964","0.01570142","0.045175843","0.03568849","-0.021132272","0.022620967","-0.07052995","0.0228446","-0.10891044","0.07106026","-0.057023246","-0.046650637","0.0046316334","0.054253027","-0.056579795","-0.10032293","-0.032021265","-0.010954503","-0.07942211","-0.0019305455","0.035486408","-0.024412885","0.024842698","0.02219421","-0.02649342","-0.043542117","0.03135759","-0.010520901","-0.051043544","-9.945038E-34","0.0012178903","0.05382578","-0.034374457","0.07979368","0.054158174","-0.022362351","-0.07883649","0.00212698","-0.07816989","0.07551783","-0.07388988","0.047307506","-0.072261065","-0.14112982","0.038217403","0.09414255","-0.06844797","-0.050671753","-0.052853886","0.01353247","0.025066158","-0.0016716395","-0.033505525","0.01817803","0.020586781","0.006354487","0.029726822","-0.080106825","-0.009677419","0.06964048","0.033065245","0.009519919","-0.017436339","0.014853359","0.07764232","-0.0016030299","-0.018158188","-0.10415632","-0.10633426","-0.05610295","-0.039348796","-0.016447643","-0.0026771289","0.12417735","0.010635673","-0.024017809","0.072518334","0.060884688","0.042678323","0.053163815","-0.058222335","0.0012852312","0.0339663","0.024327941","0.0019499733","0.04028948","-0.0061151297","0.08048716","-0.049934354","0.004239496","-0.017396959","0.04804899","-0.051800378","0.050428774","-6.327578E-4","-0.039333202","-0.011336334","-0.10102447","0.15045917","-0.060873296","0.008916856","0.031218221","0.059200943","0.052779358","-0.01002549","-0.006546916","0.03582354","-0.018670857","-0.05019904","0.011568989","-0.16177776","-0.009983255","0.0053303423","0.12850887","0.061666496","-0.04581286","0.011060523","-0.047757212","-0.0738956","0.08124014","-0.026548717","-0.0063562253","0.033560466","0.045232423","0.0055274325","1.5937439E-34","0.043478977","-0.051819","0.018467419","0.0024399364","0.066593125","-0.017936738","-0.043987554","-0.0022163498","0.04413697","0.0017947457","-0.050360233","0.02200101","0.053099904","0.010962556","0.046105035","-0.06394197","0.02357333","-0.018610613","-0.08132367","0.03455999","0.018870026","0.051338036","-0.054224543","0.090182915","0.023761446","0.021565093","0.05395207","-0.021919856","-0.07966146","-0.030494792","0.03967179","-0.0119972825","-0.050966147","0.023539303","-0.09581505","-0.039113488","0.0834902","-0.05386272","-0.06992068","-0.036357503","0.054319438","0.058852464","-0.08325648","0.032194607","-0.070153534","-0.031534992","0.0033546542","0.011403964","0.1314998","0.0106460275","-0.0257419","-0.019764658","-0.07773145","0.044250056","0.052167792","-0.02541648","0.026351243","-0.030485934","-0.006894324","0.12076973","0.11899188","0.02824215","-0.052447554","0.11234809","0.025953278","-0.063398525","-0.066897914","-0.006001538","0.039925177","-0.04748638","0.05727705","0.0020960963","-0.01024476","0.034445167","-0.03813983","-0.016158605","-0.06212355","-0.05729167","0.009023591","0.020182634","0.07773835","-0.11722003","-0.032539554","0.12560922","0.07089734","-0.011495363","0.04409869","0.0280191","0.06888738","0.008284411","0.033338286","0.010872616","-0.058378197","-0.0033005946","-0.08301442","-2.9446813E-8","0.035187308","0.03800955","-0.04940558","0.0018937477","0.014598812","0.0037843832","-0.027351238","-0.033857357","-0.058186855","0.022358762","0.008894937","0.075494535","0.030792208","-0.0051415595","0.013573061","-0.07632784","0.014641378","0.121796004","-0.043644816","0.04166775","0.043654665","-0.031390734","-0.03892416","0.029228607","-0.035332218","-0.10330265","-0.016490944","0.054364886","0.11476922","6.2797434E-4","-0.008945385","0.06523531","0.014641373","0.023513963","-0.028816279","0.019972853","0.01608547","0.006586497","-0.06601389","-0.016260685","0.050368704","-0.02786438","0.005062017","0.044625994","-0.038863096","0.07082857","-0.00921302","0.0055810004","0.022582835","-0.044833813","0.012896077","-0.039508685","-0.010802034","0.07663942","-0.010913258","0.032329656","0.06125864","0.019781843","0.024649639","-0.033644084","0.006533304","0.011038162","-0.005295438","0.024848288"]</t>
+  </si>
+  <si>
+    <t>NK-2Km3wYsCDFZ2sdaaLL3RX2</t>
+  </si>
+  <si>
+    <t>AL-IHSAN CHARITABLE SOCIETY</t>
+  </si>
+  <si>
+    <t>BIRR, ELEHSSAN SOCIETY WA BIRR, BIRR AND ELEHSSAN SOCIETY, BIR WA ELEHSSAN SOCIETY, IHSAN CHARITY, JAMI'A AL-AHSAN AL-KHAYRIYYAH, AL-AHSAN CHARITABLE ORGANIZATION, AL-IHSAN CHARITABLE SOCIETY, AL-BIR AND AL-IHSAN ORGANIZATION, AL-BAR AND AL-IHSAN SOCIETIES, AL-BAR AND AL-IHSAN SOCIETY, AL-BIRR WA AL-IHSAN WA AL-NAQA, THE BENEVOLENT CHARITABLE ORGANIZATION) (also ELEHSSAN, ELEHSSAN SOCIETY, ELEHSSAN SOCIETY AND BIRR, ELEHSSAN SOCIETY WA BIRR, BIRR AND ELEHSSAN SOCIETY, BIR WA ELEHSSAN SOCIETY, IHSAN CHARITY, AL-AHSAN CHARITABLE ORGANIZATION, AL-IHSAN CHARITABLE SOCIETY, AL-BIR AND AL-IHSAN ORGANIZATION, AL-BAR AND AL-IHSAN SOCIETIES, AL-BAR AND AL-IHSAN SOCIETY, AL-BIRR WA AL-IHSAN WA AL-NAQA, AL-BIRR WA AL-IHSAN CHARITY ASSOCIATION, THE BENEVOLENT CHARITABLE ORGANIZATION) (also ELEHSSAN,</t>
+  </si>
+  <si>
+    <t>["-0.006697207","-0.006245612","-0.041540094","-0.0781829","-0.093449436","-0.039207187","-0.013275698","-0.08175215","0.020994222","0.03135091","0.10765796","-0.0620266","0.11741044","-0.0048075733","0.020249438","0.07350729","-0.047621567","0.030370183","-0.058559842","-0.01832255","-0.0010509267","-0.020143282","-0.013140423","0.06941606","-0.018992914","-0.009124055","-0.08606526","6.991092E-4","0.0011091551","-0.075701885","-0.019789316","0.02220578","0.12422037","-0.030921184","0.017781928","0.059382968","0.0011895297","0.09432253","0.018236393","0.10851556","-0.03028027","-0.03129076","0.052410226","-0.114383616","-0.012719617","-0.026617499","-0.07137975","0.006525301","-0.023933979","0.047879923","0.054255683","-0.039162558","0.02598328","0.08927476","-0.008208478","-0.088238694","-0.023805188","0.008820506","-0.04291421","-0.061569966","0.044567302","0.04701119","-0.030202463","0.05157261","0.030984888","-0.014513552","-0.026040962","-0.0038665207","-0.08945872","0.021193113","0.052902676","-0.097106755","6.773552E-4","0.08206407","0.015023294","0.0038609926","0.089041814","-0.0020830722","-0.057988636","-0.060266778","-0.034231015","0.07839474","0.04384066","-0.04764959","-0.07991536","0.065459564","-0.050066892","-0.011504939","8.481486E-5","-0.0022128557","-0.05300557","-0.0074205925","0.044043645","-0.07751042","0.02585953","-0.0813129","0.031601913","0.03039632","-0.03411535","0.059436932","0.026998073","-0.0011343425","-0.0474597","-0.07177336","-0.05840257","-0.0015163509","-0.043066572","-0.015546675","0.02167371","-0.014430767","-0.03987341","0.051619377","0.013703389","-0.08628556","-0.06016968","0.038689338","-0.045126837","0.035146922","0.04954268","-0.0036098321","0.023901135","0.0026266843","0.032654352","0.013115524","0.03708054","0.07306071","-0.05333288","4.552697E-33","-0.012478622","0.039800305","0.034909774","-0.06382443","0.031567365","-0.08111199","-0.059638508","0.017975572","-0.07102239","-0.11189439","0.035283506","0.0842024","0.06834886","-0.024638344","0.037171725","0.021494","0.017306816","-0.10640585","-0.008807742","-0.0018018961","0.0024471136","-5.268321E-4","-0.044194344","0.06590227","0.024339067","-0.029724538","0.054001596","7.83638E-4","-0.04823656","0.047067154","0.08271565","-9.898929E-4","-0.029977689","-0.103189684","-0.020320566","-0.030301793","-0.0037454562","0.006724741","0.02344809","-0.10224504","-0.041862544","-0.0032645068","0.059699763","0.10243434","0.09106638","-0.014839536","-0.003478513","-0.006612245","0.053329825","0.056794077","0.012717244","-0.024404738","-0.008196727","-0.042622138","-0.03817412","-0.05782947","-0.03173411","0.061141066","-0.021598445","0.026700798","0.020828338","0.033701994","-0.0115532605","0.014777425","-0.0054034363","-0.010943983","0.07112892","-0.017281042","0.07525394","-0.08438893","-0.028125405","0.012630435","0.019079115","0.11052623","-0.025477832","0.025840698","0.0017096482","-0.033805564","0.05300365","-0.034367096","-0.08738204","0.069319546","-0.012133265","-0.0019175466","-0.026061865","-0.027055373","0.00907491","-0.055947315","-0.017917188","-0.061498802","-0.06558841","0.042667236","0.038141638","-0.004084128","-0.040121604","-7.3285115E-33","0.08084998","-0.035214916","0.041545603","-0.018929563","0.010650928","-0.0064459345","0.047069132","-0.078035936","0.066623986","0.051248547","0.036863495","-0.013791164","-0.029925946","-0.022802385","0.041474983","-0.022817506","0.002017024","0.06262112","-0.039553978","-0.053158607","0.02822513","0.05729174","0.030883938","-0.0014923011","-1.08262735E-4","-0.018065672","-0.0068961014","-0.033703946","0.105216585","-0.01103622","2.3033435E-4","-0.036947373","-0.09726267","-0.013319059","-0.041652378","0.02599609","0.019296605","-0.02820108","-0.107998066","-0.04987631","0.040335476","0.080071844","-0.0076490478","-0.022037309","-0.023408111","0.006347573","-0.098909624","-0.039440736","-0.034918845","-0.045561448","-0.009942201","-0.028475042","0.0712731","0.015740283","0.065440945","0.11798843","-0.02891454","-0.01761318","-0.10462804","-0.03425664","-0.02886406","0.05904795","-0.020288719","0.08203134","-0.0076883226","-0.052484866","-0.0018789277","0.055523124","-3.9917893E-5","-0.04446408","0.036932524","-0.034467597","-0.13226818","-0.10986772","-0.02146972","0.014624541","-0.014031601","-0.021542063","-0.06370518","-0.09157071","0.05374133","-0.034582242","0.043882128","0.050306913","0.020805385","0.020243783","0.043605387","0.035546444","0.01787809","0.0977187","0.009549654","-0.047046665","0.084016606","0.0012542241","0.041304436","-4.8147044E-8","0.080299884","0.032131158","0.01144259","0.018683773","0.022843145","-0.079467386","0.0072106733","-0.0031274438","-0.06892062","0.05813506","0.009903778","0.08069591","-0.10717354","-0.026592026","0.07504011","-0.083790004","0.041466873","0.04256556","0.01901818","-0.010136086","0.018909425","-0.006167774","-0.071091644","-0.04894163","-0.045432333","0.02485493","0.0033248","-0.059369728","-0.0039323918","-0.02440731","0.04317578","0.033829603","-0.052751064","-0.1152888","0.001689322","0.029945089","-0.09403848","0.006333167","0.027364995","0.051900487","0.029943973","-0.052387923","0.009923196","0.035898756","0.018498503","-0.01037061","-5.0260755E-4","0.04731368","0.024145138","-0.13171205","-0.05906673","-0.07907622","0.015794024","-0.093813755","0.029871415","0.01948942","0.03741479","-0.044876598","0.070913404","-0.034464546","0.16535805","0.026462559","0.090358846","2.8227483E-5"]</t>
+  </si>
+  <si>
+    <t>NK-2Myxbs6wX9xFKGoQn3sLaY</t>
+  </si>
+  <si>
+    <t>Victor Vladimirovich Soyko</t>
+  </si>
+  <si>
+    <t>. Belarus is participating in the Russian military aggression against Ukraine by allowing Russia to fire ballistic missiles from Belarus into Ukraine, enabling transportation of Russian military personnel and heavy weapons, tanks, and military transporters in Belarus (road and railway transportation) to Ukraine, allowing Russian military aircraft to fly over Belarusian airspace into Ukraine, providing refuelling points in Belarus for Russian military aircraft engaged in activities against Ukraine, and storing Russian weapons and military equipment in Belarus. Being a high-ranking member of the Belarusian armed forces, Victor Soyko is participating in the actions of Belarus supporting the Russian aggression against Ukraine. The Director Disqualification Sanction was imposed on 09/04/2025</t>
+  </si>
+  <si>
+    <t>["-0.013218761","-0.0051673646","0.03035161","0.012272937","0.053948954","0.06905232","0.10834588","0.007314524","-0.004149927","0.04678788","0.0054242616","0.15110487","0.02277721","0.10270757","-0.01631832","0.040009353","-0.007800957","-0.00974486","-0.0768618","-0.017723758","0.028369255","-0.066111624","0.019440673","0.07893227","3.1567388E-4","-0.08087789","-0.011475289","0.03819278","-0.023840588","-0.013122198","-0.010481212","-0.015026248","-0.05544726","0.016328696","-8.426262E-4","0.02638064","0.058063477","-0.078223325","-0.14145137","-0.025287353","-0.023876587","-0.067709506","-0.043395605","0.04357655","0.023492385","0.029001327","0.003832928","-0.029282074","0.03652287","-0.040064342","-0.07482855","0.01496608","0.0031347019","0.036600936","0.0030782868","-0.041086007","0.050340332","0.044275742","0.06315998","-0.044251494","-0.022758573","-0.039174806","-0.05638946","-0.042192668","-0.07582727","-0.019919312","-0.028452318","-0.021453904","-0.023020575","0.075652465","0.07850191","-0.014361546","-0.06045433","6.3058964E-5","0.0033219743","7.0318836E-4","0.0097495","0.041634325","0.08746698","-0.015059672","0.08173232","-0.03816254","-0.051307607","-0.04193019","-0.018511275","-0.012477631","-0.048166092","-0.02377455","0.06788579","0.053987153","-0.005795692","-0.029412715","0.20722163","0.015064429","-0.05221195","-0.0017662289","0.038599744","-0.010525559","0.04721528","0.017516756","0.027886959","-0.02050178","-0.08251453","-0.003397462","-0.012160038","0.07617048","-0.016591297","-0.02716885","-0.06021519","-0.032137886","-0.0024644833","0.038503215","-0.018320484","-0.029363811","-0.029170325","0.087364376","0.0031805623","0.03627988","0.01787519","-0.034493122","0.013964217","0.058990482","0.032239385","0.04096659","0.024835102","-0.014621375","-0.11499989","7.97664E-34","0.092953704","-0.026202757","-0.050358143","-0.019209355","-0.099322334","0.022290543","-0.006943208","0.061363216","-0.02569519","0.06379835","-0.088807754","-0.003027914","0.02919784","-0.003857669","0.080362104","0.028496785","0.034393203","0.06991859","0.016925287","0.07536815","0.029342057","-0.04824739","-0.082822695","0.03379942","-0.012154014","0.0049534603","-0.114193335","-0.039833006","-0.05026765","0.01230662","-0.06859709","0.0332999","-0.0060740355","0.07128995","-0.01854552","-0.0150292935","-0.06203976","0.026491394","0.0011859568","0.06656123","0.03180156","-0.03208706","-0.065609686","0.03845642","0.06813695","-0.03613996","0.052643135","-0.0193661","-0.040168207","-0.017589796","-0.028491436","0.043040544","0.004454309","0.045338828","-0.0041654035","-0.0158302","0.047462743","0.024616007","0.016938869","0.01799561","0.060512055","0.021463526","-0.03415719","0.004040708","-0.0021174187","-0.100169316","0.030597402","0.079036385","-0.037851144","-0.013125483","-0.022836782","-0.035540134","0.0033973223","0.046802536","-0.037610523","-0.11602818","0.0067664674","-0.033102736","0.06802647","0.0055839056","-0.024336582","-0.08360271","0.09310769","0.054750334","-0.14246695","0.054922305","0.026493136","-0.076259464","-0.046973057","-0.0034661829","-0.086966835","-0.067711644","0.023197383","0.06470939","0.028914753","-4.3963647E-33","0.078507595","0.028129438","-0.016033122","-0.015639039","-0.03443605","-0.003687339","0.020005401","-0.01269955","-0.04774478","0.01879839","-0.0020991375","-0.15622212","0.057514332","0.022255016","-0.009732327","-0.019635245","-0.0179275","0.022371305","-0.10602086","-0.04794367","-0.079343975","0.0108293295","0.05028968","0.021743638","-0.0120501835","-0.022272019","0.108857416","-0.005545572","-0.015281003","0.08085612","-0.0354832","-0.07723664","-0.04546949","0.0124007","0.11511956","-0.032425486","0.01765455","-0.014358294","6.058345E-4","-0.012252157","0.057719007","0.075131975","0.016863532","0.065222874","-0.05237606","-0.023400443","0.014703223","0.014730903","0.08247662","-0.08382867","0.018124256","0.009894778","-0.032176133","0.11702774","-0.053701453","0.028098254","0.018137611","-6.164297E-4","0.08239169","0.05681001","0.06507815","-0.061284717","0.006905251","-0.024701772","-0.02500891","0.02962872","-0.010093998","0.0141333705","0.05406886","0.045750793","-0.04485912","-0.06409575","0.104051635","0.12486453","-0.029935785","-0.03614639","-0.0016700606","-0.0025297804","-0.001222345","0.008100041","0.062244672","0.014058878","-0.057124853","0.013477458","0.004281405","0.056216925","-0.011532752","-0.010686789","0.031515043","-0.055320043","-0.034471687","-0.04982824","-0.072709","0.097769134","0.031139147","-4.7306663E-8","0.05781903","0.008116924","-0.036755834","0.02055036","-0.07272309","0.04591314","-0.04255492","-0.11393224","-0.030119836","-0.00927801","-0.007341935","0.026483359","-0.09454832","-0.012954793","-0.017742455","0.027555162","0.008913811","0.01941622","-0.023564074","0.014336591","-0.04432444","-0.07249112","-0.068027966","-0.008429668","-0.052354775","0.012245607","-0.027752103","0.05966548","0.11629042","0.03671467","-0.060180623","-0.023390358","-0.08360856","8.953906E-5","0.0068115136","0.08702437","-0.05878354","-0.054228388","-0.06575613","-0.04386313","-0.050124448","0.006589096","0.0024944432","0.037610233","-0.0084623555","-0.08771018","-0.01753398","-0.06457442","-0.01216772","0.024174312","0.031459264","-0.003980405","-0.029315133","0.09041452","0.03531177","0.042428493","-0.015781762","-0.120699875","-0.06426449","-0.02148646","-0.075782806","-0.046501093","1.2535606E-4","-0.08681347"]</t>
+  </si>
+  <si>
+    <t>NK-2QKsrPrdNxDk42fgQZMnke</t>
+  </si>
+  <si>
+    <t>PUBLIC EXPRESS, INC.</t>
+  </si>
+  <si>
+    <t>Entity Name: PUBLIC EXPRESS, INC. | Type: Company | Jurisdiction: us | Risk Context: (also GEORGE TOMPKINS, PUBLIC EXPRESS, INC., PUBLIC EXPRESS, INC., ROLLINGSTAR) (also GEORGE TOMPKINS, MARENE TOMPKINS, PUBLIC EXPRESS, INC., PUBLIC EXPRESS, INC., PUBLIC EXPRESS, INC., ROLLINGSTAR) (also GEORGE TOMPKINS, MARENE TOMPKINS, PUBLIC EXPRESS, INC., PUBLIC EXPRESS, INC., ROLLINGSTAR)</t>
+  </si>
+  <si>
+    <t>["-0.015242291","-0.043591477","-0.0010435384","-0.017645631","-0.0033544311","0.029339045","0.070626736","-0.017921865","0.037920807","-0.03818363","0.0049821706","-0.024102082","0.022013545","-0.05794982","0.012773593","0.005582941","-0.032365277","0.03135748","-3.8096984E-4","0.02274522","0.0063182544","0.021658935","-0.070759885","0.044228103","0.026616247","-0.02715265","-0.03418021","0.0525007","-0.014086692","-0.04561824","0.004780035","-0.022449132","0.038637258","9.6388883E-4","0.07195827","0.0531952","-0.031454865","-0.044877827","3.0131667E-4","-0.019042294","0.048359968","0.017144032","0.052613","0.024347836","-0.021779593","0.007666332","0.036113728","-0.035491616","-0.0054682745","0.12413614","0.06530543","-0.06992994","-0.007216308","-0.03935644","-0.0394383","-0.04089253","-0.03449584","0.020774616","-0.05523197","0.0011128095","0.02269173","0.00503759","-0.010264304","0.057526883","-0.015379613","-0.0027911547","-0.013842445","-0.0101002045","-0.03630289","-0.16633704","0.017552158","-0.03843588","-0.066285","0.04152959","-0.0488058","0.021616971","0.046493728","0.025328811","0.052026335","0.017433967","-0.00805429","-0.015467938","0.025263613","-0.017808115","-0.028049836","0.046678968","0.025650384","-0.0143162785","0.045608666","-0.030273922","-0.022202663","-0.059821233","0.090992145","0.059420895","-0.019821351","-0.01430294","-0.045057744","-0.023699898","-0.04325461","0.046181276","-0.056777477","0.08765349","0.018251464","0.053679585","-0.036391497","-0.053995445","-0.06447109","0.02984275","-0.027803658","0.047564626","-0.032834694","0.04077955","0.02145959","-0.023343917","-0.013223835","0.017077448","-0.16362816","-0.055283487","0.11088747","-0.16236396","-0.014831718","0.06845318","-0.023263555","-0.023296675","-0.13624711","0.04968836","-0.004354284","-3.152289E-33","-0.037617013","0.06088908","0.10862133","0.04827786","-0.025298236","-0.01798594","-0.060249366","0.052324466","-0.029806303","0.065122984","-0.025604133","0.061850883","0.09265454","-0.026678093","-0.053466048","-0.035890687","0.014046248","0.0293605","0.029052362","-0.017174399","-0.055532638","0.011977433","-0.013103806","0.031606473","-0.023384836","-0.040884793","-0.027683463","-0.008962988","0.046945307","0.015821971","0.06622068","-0.0558988","-0.010109637","0.040092148","0.10938389","0.012145034","-0.04970344","-0.059235904","-0.05508022","-0.021440854","0.023056088","-0.021574961","-0.059424162","0.128478","-0.028988138","0.050741293","-0.0073771453","-0.029866379","0.07867931","-0.021851243","-0.048080407","0.08870546","-0.11072314","0.015852427","0.002136542","-0.05933203","0.051796153","0.053211637","-0.039336193","-0.037791897","-0.054347705","0.026468871","-0.07107653","-0.0015585686","-0.039859943","0.010407702","0.050080493","-0.05336438","0.052040815","-0.020722065","0.08378177","0.020628873","0.07480104","0.017319784","0.015146033","-0.029780392","-0.008175826","0.09756611","-0.057309013","0.017194772","-0.07642672","-0.07488057","8.209225E-4","0.02830714","-0.012857082","-0.011788446","0.047939334","-0.011330193","-0.053395703","0.08166757","-0.07349689","0.07303922","2.9861997E-4","0.13181746","-0.05002663","1.567053E-35","-0.09227766","-0.06224747","-0.019345226","-0.11192491","-0.011425672","-0.0256034","0.047964558","-0.03781304","0.07459047","0.03409877","-0.033128057","-0.046742983","0.021945268","0.026386077","0.040610533","0.016688481","-0.026777064","-0.009971075","-0.039614458","0.03517142","-5.660131E-4","0.010294448","-0.048762403","0.038992513","0.03467608","0.009376598","-8.7178865E-4","-0.038439386","-0.046752233","-0.0046813423","-0.03490842","0.0073409653","-0.03903255","0.12758695","-0.07032716","-0.020704558","0.06720035","-0.020702349","-0.018722566","-0.033378907","-0.024691567","0.048961002","0.0016418078","0.06753706","0.017508738","0.005018325","-0.051875632","-0.048961952","-0.0060955603","0.045472935","-0.098888345","0.042156674","-0.023131654","-0.061675735","-0.047995653","0.083954126","-0.002869877","-0.04922738","0.012164639","0.020654362","0.060158048","0.08171897","-0.019903513","0.11989989","0.032873567","-0.09560953","-0.05545949","-0.07259962","-0.009703552","-0.040899456","-0.056777727","-0.007957237","-0.016026955","-0.060602445","-0.031010667","-0.017910676","0.023980094","-0.041569766","-0.049043354","-0.025572143","0.074514724","0.06784659","0.07852852","0.018345794","0.034044273","-0.003399337","0.052059058","-0.051059484","-0.011817924","0.015155705","3.865218E-4","-0.0100949565","-0.08237908","0.0035707096","-0.063803405","-4.848622E-8","-0.0017720638","-0.018176436","-0.026384275","2.7059036E-4","0.08186655","0.0042758435","0.042501647","0.005598308","-0.05438923","-0.0035663482","0.016673256","0.019368926","-0.1016211","-0.007764572","-0.0113235535","-0.120293066","-0.12498515","0.067740515","0.0069272392","0.112810194","-0.026949711","0.04986792","0.043213863","-0.08135088","-0.015298379","-0.007768561","0.10858762","0.02540165","0.012246984","0.022188138","-0.007029843","0.08182423","-0.03146373","-0.020249348","-0.054446768","0.023037072","0.10143677","0.051319648","-0.003267996","0.13586381","-0.018893898","0.04793422","-0.033732247","0.025046425","0.06893337","0.04318428","0.012779258","-0.013815351","0.14050697","-0.024186479","-0.018775381","-0.011172383","0.036547802","0.021828746","-0.058447115","-0.041769445","-0.09152316","0.040472224","-0.030401966","-0.02148026","0.0040281177","-0.07746106","0.14745452","0.011164003"]</t>
+  </si>
+  <si>
+    <t>NK-2RgKvhQa6p7oUeeCT27wAP</t>
+  </si>
+  <si>
+    <t>Joint Stock Company State Research Institute of Instrument Engineering</t>
+  </si>
+  <si>
+    <t>. Therefore, JSC GosNIIP is supporting materially and benefitting from the Government of the Russian Federation, which is responsible for the annexation of Crimea and the destabilisation of Ukraine. (also AKTSIONERNOE OBSHCHESTVO GOSUDARSTVENNYI NAUCHNO ISSLEDOVATELSKII INSTITUT PRIBOROSTROENIIA, AO GOSNIIP) Tax Identification Number: 7717693545 Registration number: 1117746132811 (Date of UN designation: 2024-02-23)</t>
+  </si>
+  <si>
+    <t>["-0.10916766","0.023219718","-0.03106696","-0.08847794","-0.043615073","0.04587612","0.13001437","0.042385932","-0.0056621516","-0.05056522","-0.046540394","0.056059465","-0.07273322","0.034609746","-0.111778915","-0.11205657","-0.059810046","-0.008215155","0.022836102","-0.009256636","0.027843455","0.002451304","0.017568652","-0.040516056","0.060103774","0.037431628","0.017098647","-0.05332539","0.04136652","0.013890239","0.030578712","-0.026292019","0.0033354196","-0.043018848","0.049077574","0.023337027","0.03908401","-0.030230403","-0.016153011","0.039878927","-0.016980236","-0.04527478","-0.018385861","0.05330644","0.01100473","0.040899906","-0.05942719","-0.0143339615","-0.03438763","0.09033364","-0.010683606","0.016201042","0.024250569","0.012295553","0.055723432","-0.044105995","0.010187712","0.0014213085","-0.03561185","-0.031286824","0.042852264","-0.033128362","0.010149307","-0.057400838","0.022944195","0.03917702","0.017121209","-0.05371956","-0.040284183","-0.061330378","-0.0069519337","0.044730354","-0.022069272","0.010222818","-0.04580677","0.02437272","-0.04414807","0.17301388","-0.007911738","-0.054259866","0.09011245","-0.0035545928","-0.06952203","0.06342342","-0.052294277","-0.023160525","-0.0828169","0.021392053","0.10722387","0.11112305","0.07548318","0.06659813","0.07204276","-0.024138134","-0.065014526","-0.018224813","-0.025204936","-0.011109047","-0.015396388","0.03878428","-0.017034374","0.006254247","0.008008831","0.041912153","-0.033569816","0.0214058","-0.04888218","-0.0013819253","0.045873296","-0.02165967","0.0016370739","0.00881128","-0.005368841","-0.050042283","-0.03846601","0.019708758","0.013443131","-0.029888181","0.010444123","-0.13868892","0.02917724","-0.026541783","-0.0938172","0.035817724","-0.0438448","-0.013586084","-0.06841809","5.7700683E-33","0.01338356","0.017502258","0.048014935","0.018223362","-0.11608071","0.018465942","-0.024331579","-0.04251367","-0.10607264","-0.009062358","-0.031091288","-0.012461072","0.01621435","0.0042581935","-0.011834084","0.037407327","0.02477409","0.08594397","0.061920162","0.06281348","0.13621472","-3.7315715E-4","0.06557527","0.01662353","0.120907284","0.08405883","-0.0903423","-0.042929694","0.02327037","0.029552214","0.007930039","-0.063137695","0.0021634656","-0.07803818","0.016830456","-0.024962744","-0.01594966","-0.07207748","-0.018106624","-0.03815091","0.031072482","-0.030074121","0.017093686","0.093847476","0.061622642","-0.037758358","0.06486083","0.014147627","0.083940804","0.00850348","-0.068868585","-0.010569908","-0.09268553","-0.006636395","-0.039848834","-2.4809886E-4","-0.03450674","0.08675735","0.0037063807","-0.024406204","0.03173163","0.08222609","-0.04943807","-0.021874513","0.09734351","-0.0058737583","0.013048425","-0.011414652","0.0013531904","0.0066612554","-0.016781805","0.032194734","0.044979297","0.09521423","-0.1208686","-0.03743021","-0.050449423","0.027809061","-0.034239408","0.06562954","-0.007169538","-0.04144067","-0.017411048","-0.044253044","-0.00507894","0.08821451","0.09209405","-0.05842465","-0.03492914","-0.01818527","-0.019118965","0.030676357","-0.057286687","0.00787843","-0.048997495","-7.505452E-33","0.023187824","-0.10369674","-0.022804882","-0.01042557","-0.061319694","0.005671852","-0.012634481","-0.021001648","-0.05059474","0.062141865","0.0049241707","-0.036745466","0.084902465","-0.0059734765","0.02606681","-0.0041012415","0.008979629","0.08998515","0.018624188","-0.07101583","-0.024929522","0.08383824","0.068871155","0.07596989","-0.05054845","-0.020569842","0.05801535","-0.0018579667","-0.08178954","0.06628098","0.042346466","-0.06546692","-0.14552793","-0.04706589","0.016742375","-0.040334567","0.011990676","0.05802183","0.027179167","-0.027181465","-0.027119407","-0.029664248","0.020921638","0.041508265","-0.048100427","-0.013378431","-0.07124922","0.15013716","0.036221266","-0.07203453","0.03397544","0.07604505","-0.008588941","0.08817119","0.06868076","0.05338406","-0.0034982457","0.038145352","-0.003471453","0.013301808","0.037426386","-9.7240537E-4","-0.039744947","0.005742374","0.10576737","-0.056907237","-0.015219125","-0.012200951","0.092189565","-0.025068585","0.012392844","-0.119779065","-0.03317209","0.0348516","-0.014778148","0.03798955","0.008608704","0.0577094","0.0101489555","-0.004621462","0.057024013","-7.686545E-4","0.02604275","-0.014332531","0.067242295","-0.05307813","0.084986985","0.02107493","0.040046126","-0.038944215","-0.08423018","-0.02493537","-0.046070717","0.0027838196","0.009022829","-4.4719144E-8","3.471225E-4","-0.0036729604","-0.06674679","0.018526085","-0.050599333","-0.04263203","-0.06350852","-0.05385297","-0.104544856","-0.02295776","0.022149475","-0.07623747","-0.07113419","0.0061846185","0.016921269","-0.031126471","0.012794987","0.086474724","-0.039995596","0.05477606","-0.01722402","-0.07723703","9.687779E-4","-0.08325118","-0.04675052","-0.007582096","0.09111353","0.028722167","0.07810305","-0.04722058","1.022335E-4","-0.02034345","-0.041216943","0.021184148","-6.3927966E-4","0.053934567","-0.06793086","0.008854787","0.02899645","0.020717243","-0.053900283","0.032970585","-0.03516327","0.056052208","-0.10740675","0.0063769626","-0.077702634","-0.06858674","-0.043037783","0.03023884","-0.026048131","-0.011140498","0.03896389","0.06302697","0.016152477","-0.043874633","0.02777054","0.016908746","0.026243333","0.048539683","0.03145216","-0.05204349","-0.023059795","-0.0030894966"]</t>
+  </si>
+  <si>
+    <t>NK-2Uu3cZZ3dLekrLJfJJczzT</t>
+  </si>
+  <si>
+    <t>David James Coulter Cunningham</t>
+  </si>
+  <si>
+    <t>Entity Name: David James Coulter Cunningham | Type: Person | Jurisdiction: im | Risk Context: Section 2 Company Officers (Disqualification) Act 2009 | Disqualified</t>
+  </si>
+  <si>
+    <t>["0.025045931","-0.016394798","-0.049703244","-0.010093955","0.024948798","0.100755915","0.104428336","-0.08378564","0.003991115","-0.011101051","-0.037617262","-0.060446884","-0.0065077934","-0.003204379","-0.09148881","0.08877566","0.009985324","0.022487855","0.018651351","-0.056191523","0.052050497","0.090670474","0.021697687","0.006239078","0.005947611","-0.087257825","-0.05251609","0.01985867","-0.06563949","-0.058997948","-0.02852337","0.040456276","0.021596212","0.062091224","0.05940431","-0.037075046","0.017220523","0.05242472","0.050744887","-0.00848532","-0.021194989","-0.11029577","-0.013089071","-0.050976977","-0.11798176","-0.00511043","-0.007456347","0.011159362","0.036632452","-0.03396655","-0.05363026","-0.051554207","0.06950926","0.09264067","0.0029834495","0.019545112","-0.014604164","0.09058373","-0.08913986","3.5010322E-4","0.028284572","-0.018735541","-0.043560836","0.07175428","-0.013443962","0.028849501","-0.04330066","-0.057392627","-0.0025122112","0.0051570693","0.010436932","-0.0014243177","-0.075667284","-0.020843666","-0.01075184","-0.010041911","0.06331103","0.05435746","0.1031685","0.02553819","-0.10241573","0.008555415","0.035753474","-0.050051678","-0.06377354","-0.0027731364","-0.011049291","-0.005252554","-0.0071315067","-0.0066756825","-0.033376984","-0.065158375","0.12475429","-0.024669902","0.009086051","-0.035979405","-0.0042712525","-0.01661492","-0.012314082","0.08379068","-0.051461294","0.019684957","-0.08784937","-0.04158182","-0.048339296","-0.092214756","-0.0073333783","-0.032620408","-0.035832018","-0.024266053","0.024076989","0.09796624","-0.017082158","-0.026135253","0.01957731","0.026113924","-0.011447602","0.010164953","-0.025105136","-0.07987618","-0.016865222","0.0674495","-0.089502454","0.07150644","-0.06788974","0.044807374","-0.05191874","-1.1936636E-33","0.095043026","0.05501364","0.0625957","-0.012264268","-0.013910988","0.04576664","0.01645639","0.01954003","0.02006574","0.029762723","-0.059701838","-0.016933145","0.06034079","-0.10291129","0.018123403","0.035492696","0.038260352","0.07995945","0.03409846","3.1515223E-4","0.07459801","0.051373705","-0.070798054","0.0400419","0.005199334","-0.035055775","0.027175477","-0.032486837","4.2020858E-4","0.066063955","-0.022883533","0.035489205","0.027130043","0.004931605","0.083541065","-0.014017354","-0.05490463","-0.052395195","0.011008578","-0.02952634","-0.01280417","0.07251126","0.09409957","0.052403413","-0.089150496","0.03515071","0.056036778","-0.021198591","0.0917756","0.058940705","-0.009188902","0.026040258","0.053843517","-0.02885482","0.011113042","-0.018209742","0.022885036","0.032219127","-0.0015640495","-0.016997937","-0.020547293","0.01763139","-0.08705057","-0.02138409","-0.02205623","-0.09718924","0.0027842028","-0.06565215","-0.038668722","0.017091267","0.06805594","0.00940206","0.05220639","-0.015660534","-0.054806694","2.1086125E-4","0.006773266","-0.007883582","0.013243041","0.01874179","-0.010508794","6.865974E-4","-0.031544555","-0.09273462","-0.013752919","-0.040802363","0.053849313","-0.041778993","0.0068407017","0.031847622","-0.021562157","0.014935855","-0.02260192","0.024367409","-0.04429067","-1.6774402E-33","-0.07215582","-0.0807474","-0.058553133","-0.06904375","0.047732726","-0.007261003","0.0013090869","0.026826143","0.0020608453","-0.051377162","0.024513118","-0.0268099","0.029011691","0.03547928","-0.059962273","-0.011232078","-0.020844914","-0.022778654","-0.049812432","0.07150316","0.07432576","0.07665496","0.0013703544","-0.011586777","-0.016689679","-0.03932624","0.13906795","0.036865283","-0.006815258","-0.028044559","-0.011899791","0.036465686","-0.13404503","0.08238107","-0.07093991","-0.06769002","-0.008505098","-0.08160835","-0.017607503","-0.04859947","0.050987445","0.100140415","-0.008819598","0.0015175102","0.012043695","-0.068999685","-0.04063203","-0.06259124","0.08852345","-0.062388852","-0.14045085","-0.05288791","0.025983628","0.05373445","-0.007251463","-0.008750212","-0.04334637","-0.079986334","0.037313703","0.0034027032","-0.04399811","0.11540672","-0.013399696","0.15496272","0.026166996","-0.07338588","-0.115791865","-0.037430994","0.005757935","-0.075699136","0.004433815","-0.104035385","0.0284053","0.015226796","-0.03513454","-0.018802458","-0.026764823","0.0019189223","-0.06649637","0.03454411","0.0907475","0.0075618858","0.007984226","0.047775604","0.088053174","0.10088765","0.039734606","0.009070147","0.023992589","-0.0045829406","0.025910575","-0.068801425","-0.07976593","0.038262054","-0.041606963","-2.8595073E-8","0.027570432","-0.047919564","-0.016091192","-0.01285265","0.03683797","-0.033496406","-0.0077130343","-0.06190855","-0.033274163","0.016045729","-0.002164177","0.026891408","-0.0054313163","-0.021940213","0.06719643","-0.034726292","0.005546653","0.048639566","0.002741275","0.029879913","-0.0038133722","0.004345262","0.003739061","0.020862633","0.04479188","0.054757588","0.047608096","-0.005689993","0.033100925","0.08128225","-0.030538224","0.11747085","-0.08567953","0.056888882","-0.026420569","0.07622721","-0.018623462","0.07340122","-0.031397045","0.09817288","-0.03954796","0.0052617","-0.0013597277","0.076402634","0.060779493","-0.009443691","-0.059543937","-0.016998637","0.07489293","-0.0506708","0.06292218","-0.04852468","0.074440576","0.057574306","-0.049610987","-0.033448204","-0.0050546327","-0.035888646","-0.06504634","-0.0156180225","0.07577092","-0.076095514","0.06386175","0.00111431"]</t>
+  </si>
+  <si>
+    <t>NK-2XAfkJ9t2UuWnoRG5EBoYu</t>
+  </si>
+  <si>
+    <t>ABDULHAI SALEK</t>
+  </si>
+  <si>
+    <t>Entity Name: ABDULHAI SALEK | Type: Person | Jurisdiction: af | Risk Context: Serait mort en Afghanistan septentrional en 1999 - était membre de la tribu Wardak</t>
+  </si>
+  <si>
+    <t>["-0.054645177","0.05869887","-0.042462412","-0.031549115","-0.07703403","-0.013183831","0.017328255","0.04494263","-0.024464862","0.031261764","0.060962483","-0.054180205","0.07454547","-0.020768056","-0.01871417","0.03962818","0.008841597","0.117194496","-0.012728302","-0.059944082","0.013450819","0.04235794","0.08656397","-0.059812058","0.026603216","-0.051274102","0.0024332504","0.0336738","-0.05952626","0.0390415","0.022198873","0.008893525","-0.036116846","0.043171283","0.09078918","0.10183316","-0.09497017","0.06256859","0.05735224","-0.05270268","0.10845247","-0.105388254","0.024898402","0.022721875","0.027368676","-0.05398356","-0.07492499","0.0028276227","0.010669132","0.022026703","-0.039402198","-0.031235363","-0.032646824","0.049806375","0.08528616","-0.04397828","-0.05706188","0.0327784","-0.03122125","-0.052997995","0.011489671","0.08009849","-0.030157262","-0.030882888","-0.03762969","-0.043922108","0.0032191726","-0.010736624","0.03564995","-0.03894706","0.093339555","-8.514743E-4","0.02499442","0.008413475","-0.10881457","-0.13979928","-0.010354882","0.062364973","-0.04522305","-0.08063591","0.08037428","-0.008831777","0.06871791","0.013502877","-0.04323223","0.014108015","-0.011689164","-0.007950104","-0.026011806","0.015184827","0.056672856","0.016496146","0.10483479","0.010571032","0.035859227","-0.066298306","0.039729342","0.047962826","-0.08448852","0.07957124","-0.024341408","-0.064382486","0.0021475782","0.06398523","-0.085303254","-0.06116485","-0.074461944","-0.04483875","-0.043273292","-0.04672323","-0.08093498","0.026823107","-0.0712923","-0.039583076","0.06223615","0.019941473","-0.08976393","-0.04511383","-0.023508","-0.06504388","0.019840391","0.038277388","-0.07577865","0.0041207513","0.011719181","-0.025028009","0.04343474","3.0388309E-33","0.009058835","-0.010187462","0.03575177","0.036318008","-0.12574512","-0.07111984","-0.029218568","-0.07003542","-0.04842513","0.063529424","0.02445428","-0.062234566","-0.04402833","-0.061463676","-0.0070075616","0.033288732","-0.036092542","0.03145832","0.0058966135","0.056985173","-0.02319847","-0.040990613","-0.019968003","0.040380344","0.006031582","-0.050773855","0.028849808","-0.10718937","0.03433767","0.040952735","0.027397655","0.03618103","0.012541835","-0.06347394","-0.043403342","-0.018202653","-0.08508941","-0.07370681","-0.016580189","-0.012288441","-0.03888923","-0.031540766","0.0027323058","0.05372564","0.017865198","0.07356929","0.03233635","0.024297124","0.085262015","-0.010462964","0.05263326","0.0023754893","-0.06545346","-0.009937494","-0.049053583","0.012536831","0.011295002","0.062232647","-0.018008873","-0.007829806","0.0385269","-0.070902996","-0.042819105","0.032775767","-0.024912504","-0.058439203","0.011338882","-0.06244609","0.040032458","-0.027787002","-0.031692144","0.013282805","0.0023967496","0.06021011","-0.07926761","0.040295377","0.020291911","0.06034629","-0.08195292","0.08292831","-0.0724519","0.06588694","0.034735087","0.041046422","0.0155187","0.058032468","0.012830116","-0.093928345","-0.031718723","0.06439915","-0.035255253","0.07637228","-0.067959815","0.014006247","0.054782737","-5.1297677E-33","0.023949882","-0.021776088","-0.09997268","-0.018775653","0.004372557","-0.037070576","0.0049532154","0.06679954","0.074074596","0.044355944","-0.002652649","0.01506435","0.06700175","-0.0019591271","-0.011498684","0.083965376","-0.052852754","0.043475036","-0.018311584","0.030742098","0.049917083","0.031238543","0.0025113109","-0.002233345","-0.058619805","0.019286707","-0.010110629","0.030997394","-0.038195003","-0.044563815","0.034157753","-0.0313098","-0.04147614","0.07241835","-0.049249206","-0.030817006","0.048229925","-0.10184349","-0.05382055","0.04769693","0.013387687","0.10839767","0.019724399","-0.0023567628","0.004863226","-0.065918624","0.018399056","0.0107535515","0.077492446","-0.15521693","0.030995492","0.08968415","-0.013534882","-0.027192721","0.062700815","0.09237997","-0.030874413","-0.063526995","0.041547347","-0.022921644","-0.042449195","0.08812242","0.02723661","0.09100178","-0.011391816","-0.059431724","-0.033314317","-0.06233864","0.030887626","-0.02277286","0.054077297","-0.11026767","-0.0829863","-0.010337001","0.057612296","0.039172556","-0.074276954","0.08421412","-0.061966494","-0.0026231706","-0.0016292733","0.042500433","-0.044616282","0.025925517","-0.018695466","0.038045194","0.0760327","3.8070697E-4","0.026986154","-0.073352404","-0.013135169","-0.061752535","-0.012475236","-0.007701689","-0.0821753","-3.3722845E-8","-0.028321978","0.057237938","-0.007997773","0.023290098","-0.0019330693","0.004199103","0.03136373","0.033598565","-0.004123384","0.023875346","-0.034802787","0.019482935","-0.055288307","-0.007942883","-0.029620873","-0.08075658","-0.020703439","0.05250579","0.004936784","-0.03967189","0.06005582","-0.041401524","-0.0045671943","-0.070871286","-0.039997235","0.040752098","0.02692854","0.0058405995","0.0508684","0.04933634","0.011806997","0.07654283","-0.037246242","-0.0726067","0.052835062","0.12913194","0.038351376","-0.022485623","0.005763268","-0.0031330166","0.005327761","-0.040491085","0.118929066","0.047237583","0.010799551","0.0034693542","0.046529505","-0.060100354","0.0951422","-0.07351907","0.012105085","-0.024851963","0.011164051","0.00489652","-0.003913893","-0.013183316","0.03864171","0.017646424","-0.005826569","-0.07332323","0.07157861","-0.0998918","-0.058779527","0.021793501"]</t>
+  </si>
+  <si>
+    <t>NK-2a2MjT3Et4UPJXZvD3rtDv</t>
+  </si>
+  <si>
+    <t>DAVID K OCLINARIA</t>
+  </si>
+  <si>
+    <t>Entity Name: DAVID K OCLINARIA | Type: Person | Jurisdiction: us | Risk Context: 1128a2</t>
+  </si>
+  <si>
+    <t>["0.03965088","0.08776012","-0.095057614","-0.008031123","-0.037332844","-0.025032762","0.04985625","-0.052010667","0.053616665","-0.0153613435","0.01994228","-0.09101315","0.03766013","-0.038069047","-0.056313504","0.13787334","-0.009082544","0.040012952","-0.028748643","0.05626645","0.06509866","0.05165648","0.06255399","-0.04269971","0.0033974592","-0.01957281","-0.043192536","0.08837437","0.039079525","-0.07270149","0.065597124","0.09152319","0.08758441","0.026241947","0.0791063","0.015447175","-0.03875972","0.031131046","-0.030696716","0.025450176","0.042030506","-0.036091052","0.067308046","0.04463622","-0.08841331","0.002291293","-0.003978076","-0.050696325","0.0121712955","0.025829155","-0.08804778","-0.070087984","0.009151544","0.070051454","-0.012608906","0.008611135","-0.072323024","-0.012920905","-0.06608716","-0.027803544","0.061834004","0.056296602","-8.290833E-4","0.039906282","-0.010913395","0.018198902","0.0019402805","-0.058003426","-0.010618575","-0.08988335","0.0936776","-0.023875566","-0.05648542","0.04877348","0.0014269185","0.005241533","0.022471616","0.03380536","-0.0033237373","-0.045434922","-0.0040573003","-0.029578667","-0.0019881765","-0.05473122","-0.052305907","0.057394948","0.013851439","-0.014824893","-0.010625848","0.0059670033","-0.029084282","-0.0767041","0.17156838","-0.034432877","0.006031034","-0.04451768","0.102417335","-0.027173076","-0.075144194","0.06801054","-0.03649166","-0.014769265","-0.045068543","0.06396544","-0.09691148","-0.047853827","-0.033885125","-0.0022461375","-0.001652402","2.3221814E-4","0.016006464","0.03978135","-0.051305894","-0.02427678","0.02638484","-0.004616504","-0.06635075","0.012260168","0.02936479","-0.09854374","-0.027490154","-0.0076379185","-0.10878232","0.013786182","-0.076006","0.011197417","-0.009419351","4.150565E-34","0.10236884","0.08051372","0.0559237","-0.015288895","-0.0038467168","-0.0189851","0.015727518","0.0029450543","-0.039914265","-0.050908726","-0.019706652","-0.03555956","0.065153584","-0.05714977","-0.054113444","0.04732679","-0.03848808","0.015134305","0.01761302","0.07157887","0.05598349","-0.018777566","-0.043529697","0.09035216","0.0018626002","-0.0082833925","0.02320574","-0.06566436","0.044328727","0.05022128","0.022147587","0.027084906","0.004703514","0.0012226851","0.06814463","0.07059917","-0.07875938","-0.05443954","-0.048811153","-0.057749882","-0.02076166","0.0529263","0.025957065","0.12418097","-0.049815033","0.0025838949","0.054652408","0.026789732","0.053354472","0.01358608","-0.02569034","0.03514558","-0.103487484","-0.028584449","-0.060369298","0.0019717615","-0.024668194","0.119933635","-0.045549106","-0.043149702","0.050802894","0.01958769","-0.046263095","0.04888006","-0.05972062","-0.101630375","0.010741154","-0.07578038","0.037005752","-0.07014409","0.0123041505","0.05947991","0.015356147","0.03103936","-0.035006586","0.028365783","-0.008687479","-0.058185432","-0.013431713","0.058165964","-0.050155453","-0.011804861","-7.578447E-5","0.021524096","-0.036340542","-0.017889693","0.018756319","-0.02584866","-0.06404367","0.085091785","0.022547726","-0.017113866","0.03914317","0.0063853804","-0.019198231","-1.9409102E-33","-0.053844195","-0.1288188","0.047487315","-0.06836892","0.069938205","-0.0879161","-0.030266052","0.08354863","0.010964509","-0.05618114","-0.029490357","-0.04970143","0.07339323","0.015062225","0.051136173","0.014162203","-0.04471624","0.051590674","0.019839155","0.04279853","-0.016134914","0.0016356106","-0.0439098","-0.0072197486","0.014667389","0.021458907","0.04392962","-0.049952626","-0.048099905","-0.09837559","-0.04572022","0.059979133","-0.120996945","0.058126625","-0.13937631","-0.008378525","0.013724415","-0.12479231","-0.02494422","-0.021406004","-0.02766593","0.08604239","-0.01559882","-0.0058600837","-0.037808992","-0.025366666","-0.016849048","0.00824126","0.1076598","-0.04742396","0.023105735","0.07457677","-0.037794452","-0.034572545","0.09788296","0.017110128","0.030706747","-0.054646283","0.043858018","-0.03744198","-0.026265224","0.05856128","-0.013466971","0.16141962","0.013911509","0.023380691","-0.05732244","-0.008630484","-0.042696327","-0.045641486","0.009059024","-0.07738678","-0.061686426","-0.01800447","0.022610627","-0.03179532","-0.052041482","-0.009795152","-0.040731188","0.0052883523","0.013358705","-0.016522508","0.0027708523","0.069066994","0.055979077","0.02388953","0.110604495","0.035733588","0.044797603","0.06449145","0.0025533636","-0.008763677","-0.09906567","-0.003566215","-0.0036589773","-2.6811502E-8","0.013341122","-0.056896888","-0.03956412","-0.024210742","0.06643436","0.029983409","0.032922197","0.03457554","-0.012822055","0.0155756995","0.005067909","0.08553936","0.011724935","-0.05402702","0.054463606","-0.09230358","0.023120135","0.037436794","0.020198854","0.043598004","-0.040146265","-0.013396153","-0.0050568683","-0.0033481787","9.308447E-4","-0.011226574","0.025592359","-0.0011081721","0.05314","-0.05954355","-0.038853977","0.07448827","-0.030650754","-0.0010937348","-0.01920196","0.0127216345","0.029232575","-0.002004647","0.0039685857","0.019306166","0.07910005","0.07594634","-0.004737218","0.06955653","0.08517901","0.010668121","-0.023493964","-0.03250648","0.0372726","-0.1165299","-0.07178214","-0.106839865","0.023543118","0.047620848","-0.044048443","-0.0630611","-0.009272896","0.025987424","0.002281577","-0.023805398","0.052325696","-0.03540984","0.04020154","7.412117E-4"]</t>
+  </si>
+  <si>
+    <t>NK-2dJbv43DvHBMJMwqFfdxRc</t>
+  </si>
+  <si>
+    <t>Sergei Yevgenevich Zubkov</t>
+  </si>
+  <si>
+    <t>Entity Name: Sergei Yevgenevich Zubkov | Type: Person | Jurisdiction: by | Risk Context: act: sanctions anti money laundering act 2018 | section: 3A | description_identifier: disqualification under sanctions regulation</t>
+  </si>
+  <si>
+    <t>["-0.07724203","0.05753604","-0.030679902","-0.016353117","-0.016399398","0.020739175","0.13131535","-0.011295547","0.019478671","-0.029644586","-0.028535878","-0.0045727426","-0.021254176","0.06842734","-0.037130263","0.032733537","0.013287964","0.044888332","-0.06364336","-0.069725975","0.06045755","-0.025552858","0.08909656","-0.037652496","-0.025888445","-0.06495786","-0.05911904","0.049131077","0.025564944","-0.0028177437","0.021933934","-7.4331707E-4","-0.0069513456","0.07366302","0.08983785","-0.016984943","-0.03320133","-0.009597127","-0.015638264","0.031636324","0.048396863","-0.018473262","-0.019832198","0.10895579","-0.039809134","-0.03552814","-0.06058293","-0.026905783","-0.039154064","0.037278716","-0.1039814","-0.041579627","-0.0029519626","0.07245661","3.842863E-4","-0.06328304","0.003735348","-9.964285E-4","-0.021674031","-0.03155564","0.033309277","0.023152327","-0.03036014","0.005351355","-0.04695843","-0.0024035599","-0.04175682","0.033117186","-0.0081936205","0.025796764","0.048278637","-0.060199834","-0.10488437","0.01101668","-0.031779595","-0.10696272","0.050194595","0.08329969","0.07518743","-0.013578921","0.0041895024","-0.046763223","0.039427087","-0.03496822","-0.05265451","-0.060807504","-0.03523454","-0.031047434","0.06791286","0.035166427","-0.010070079","-0.021386258","0.21928681","-0.045798123","0.03672479","0.0041818107","0.03189847","0.0025276837","0.028025687","0.05689843","-0.0022022945","-0.042965673","-6.137208E-4","0.055129874","-0.056777075","0.026721524","-0.018120963","0.05599192","-0.0960214","-0.016344909","-0.022611892","0.041933645","0.02942757","-0.02905227","0.025854442","0.042274483","-0.012136173","0.103747316","-0.04810691","-0.095059365","0.046821404","0.03273139","-0.03748457","-0.034296446","-0.08435307","0.070693016","-0.07208342","2.0302979E-33","0.019681579","-0.034822516","-0.08624377","-0.028731488","-0.055176627","0.0403447","0.024344618","0.021851677","-0.11060475","0.12413578","-0.03259704","-0.038905855","-0.021963928","0.0033266498","0.0042524803","0.05635619","0.016515436","0.070791416","0.01629877","0.09881322","0.14672711","0.019908324","-7.7006995E-4","0.025950056","0.018585363","0.00649096","-0.098525144","-0.087343596","0.019634647","0.027608192","0.005184476","0.040159687","0.040173568","-0.0110459","0.06346622","-0.027017666","-0.10851109","-0.008849758","-0.015315446","-0.027244821","0.038388055","0.020919336","-0.035260666","0.042593956","0.035355393","0.03917168","0.0662897","0.0068711187","0.12446728","-0.02218884","-0.046414092","0.035945103","-0.09042597","-0.012304674","-0.0139500955","0.0133882025","0.0088476455","0.13548689","0.0026095759","-0.06280263","0.010974494","0.02698152","-0.04371178","0.07246532","0.01127567","-0.116763085","0.012481125","0.032273587","-0.08154964","0.015941828","-0.01196643","0.04993472","0.00514484","0.032321133","0.014937753","-0.10627339","0.011165596","-0.043771043","-0.07213113","-0.020251436","-0.13521807","0.00879303","0.057479355","0.0057971156","-0.06570008","0.03586144","0.012271433","-0.03619452","-0.014786804","0.034127947","-0.07589412","-0.02801881","-0.02253692","0.043377407","-0.081270635","-3.887191E-33","0.0011303866","-0.026760457","-0.006950949","-0.054432742","1.037098E-4","-0.011207053","0.04588661","0.024136243","-0.023131609","0.032898504","0.04598153","-0.035199285","0.03135378","0.0365781","0.024311515","-0.0073594865","-0.005438412","0.044870548","-0.14752436","0.0019592831","0.012322055","0.03279633","8.135466E-4","0.033566326","-0.061165042","-0.0022012244","0.17956759","0.0061128875","-0.040597938","0.05384654","-0.037085112","0.048576538","-0.09397108","0.014689897","-0.03138067","-0.034639206","0.020882571","-0.061853334","-0.09079932","-0.035423905","0.0075996243","0.050505646","-0.06847302","0.071019","-0.04303088","-0.013570377","-0.03413358","0.031023761","0.06884256","-0.08130578","-0.0455717","0.015058822","-0.010825374","0.038798463","0.025467211","0.023410585","-3.4666533E-4","-0.09268807","0.041626714","-0.0070950817","-0.025322953","0.055326607","0.027886659","0.08858153","0.080142826","0.007234531","-0.0784386","0.038986724","0.08642759","-0.046040703","0.05751229","-0.05798147","-0.021710366","0.031500172","0.017482286","0.06733632","-0.056517337","0.015508197","-0.010198726","0.03500477","0.069629245","0.0048460863","0.0056948722","0.035762217","0.08458017","-0.007938321","0.013284141","-0.031424776","0.054521874","0.020976884","-0.007728577","-0.11172155","-0.028929133","0.020696683","-0.006875335","-3.3114397E-8","-0.0228649","-0.013478376","-0.03084385","0.02952134","-0.04552452","0.011243227","-0.084422156","-0.062234882","-0.07267829","0.052537683","0.0015475962","0.05778452","-0.035229206","-0.003571441","0.022536956","-0.06145109","-0.029943248","0.05886086","-0.011474823","-0.012320356","-0.00513907","-0.02686625","-0.019895192","-0.0049043023","-0.0147314295","-0.03856235","-0.011631132","0.043693908","0.09346108","0.004969325","-0.017789487","0.044446737","-0.03396181","0.03823742","0.01210155","0.051097192","0.026764836","-0.055863187","-0.0037636904","0.020478647","-2.4714685E-4","0.012157087","0.0076111075","0.06663824","-0.01455736","-0.0019086087","-0.094397224","-0.063181885","0.08710924","-0.014209343","0.014133873","-0.051040687","-0.013287361","0.080963165","3.803041E-4","0.024951506","-0.008409333","-2.6265316E-4","-0.07167673","-0.021675669","0.048410863","-0.088210054","0.052755896","-0.111115515"]</t>
+  </si>
+  <si>
+    <t>NK-2iReTSQXATxNKYRsztewNm</t>
+  </si>
+  <si>
+    <t>Rachel Bertrand</t>
+  </si>
+  <si>
+    <t>Entity Name: Rachel Bertrand | Type: Person | Jurisdiction: us | Risk Context: Cruelty to the Infirmed</t>
+  </si>
+  <si>
+    <t>["0.006538496","0.050727762","-0.007202267","0.026921678","0.025952782","0.025309464","0.06762276","-0.0362245","-0.011425975","0.032178894","0.028686978","-0.050349597","0.017965352","-0.0038198894","-0.07387685","0.07595687","0.06783774","-0.012900908","-0.040109847","0.0788856","-0.047508184","-0.0012942102","0.06654924","0.031559736","-0.012163464","-0.06937887","-0.012880504","-0.04182143","-0.0046857945","-0.03171593","-0.012418311","0.10787412","-0.0031494354","0.032637797","0.02904194","0.02028778","-0.012260312","0.017259175","0.027893845","-0.0083901975","0.059580293","-0.07924201","-0.015490783","0.064334475","-0.10398769","-0.067333594","-0.0023493837","0.005364027","-0.008406467","-0.05994832","-0.07777719","-0.06510018","-0.032597743","-0.030617688","-0.008105606","-0.023839511","0.012998704","0.009691384","-0.075247936","-0.01192368","2.447666E-4","0.01225793","0.0054209316","0.026518103","6.123695E-4","0.04624029","-0.004685677","0.019738458","-0.020847242","-0.037920095","0.096727885","-0.028553378","0.018403227","0.006299277","0.008030886","-0.0313442","0.08212883","0.0034937751","0.069303244","-0.01777935","-0.015556858","-0.093706876","0.01570899","-0.045538995","-0.021142196","0.006189039","0.063901305","-0.039216038","0.05477616","0.020069629","-0.07244269","-0.042118732","0.16518146","0.025213517","-0.06277548","-0.016130706","0.004294999","-0.0445883","-0.039990775","0.078953385","-0.0206261","0.0044177356","-0.035007678","0.066891655","-0.013584291","-0.067317836","-0.12544255","-0.065289","0.0148379775","0.046191502","-0.0687858","0.035684403","0.018105961","-0.0068504307","0.019628268","-0.0072097755","-0.07027824","-0.009779465","0.075118124","-0.11845672","0.045300025","0.05727135","-0.08749706","-0.07689396","-0.05515909","-0.0076536653","-0.0060302704","-3.9272954E-33","0.006716326","0.012361963","0.04833018","0.080784515","-0.0873694","0.02241552","-0.01588561","0.039677154","-0.07659135","-0.037121173","5.7045225E-4","-0.01773959","0.059889928","-0.030707732","-0.13837178","-0.013328151","0.022884589","0.070612505","-0.0031346495","0.035389274","0.018903622","0.0069902763","-0.049579673","0.05622141","-0.0384478","-0.090839624","0.049514204","0.008440675","0.05505974","0.05309728","0.005701393","0.043317415","0.06256669","0.0025591033","0.06630197","0.088242695","-0.049306996","-0.042544864","-0.012239369","-0.009883682","-0.027253227","0.030045867","0.019812318","0.0695002","-0.07513715","-0.01540353","0.01245957","-0.07970699","-0.005859705","0.004215769","-0.03149284","0.04423069","-0.05056281","0.022928974","-0.041970626","0.04911808","-0.011862118","0.037020523","-0.07505326","-0.1182274","0.054883175","-0.017553838","-0.052363142","-0.008337528","-0.014031086","-0.07152392","0.027641464","-0.071438156","0.013455926","-0.003522755","0.013085738","0.114229344","0.09035233","0.0074146506","-0.0154187","0.009969233","0.005346154","-0.030127017","-0.04702441","-0.0070926137","-0.041550864","0.0019662299","-0.0057371305","0.11182407","-0.019123282","-0.024951106","0.040191572","-0.058256958","-0.030203791","0.02920433","-0.06649976","-0.040397994","0.02628064","-0.04041127","-0.032274988","5.8540165E-34","-0.06750583","-0.09714339","-0.0075021423","0.011807786","0.08796843","-0.10701481","0.023464914","0.070255555","0.021446586","-0.012288632","-0.08865541","-0.112695776","0.07232284","0.012160105","0.037180834","0.05522924","-0.00952926","-0.04870514","-0.0075619845","-0.010280191","-0.021183033","-0.05695489","-0.11955596","0.03896497","-0.03135968","0.040672008","0.06279681","-0.07759602","-0.020615738","-0.087255105","-0.07333543","0.08225618","-0.090486534","0.06003068","-0.090870745","0.04360227","0.05435812","-0.09268652","-0.0437534","-0.054799523","-0.02173177","0.07030717","-0.032496985","-0.006909448","0.0121322395","0.013638361","0.058141533","-0.02977433","0.07773015","0.013208205","0.03198111","0.094843365","-0.03901549","0.039846983","0.04470964","-0.04040148","0.014094472","-0.09687263","0.05824259","0.050957892","0.0140494825","0.07687332","-0.036232624","0.14223258","-0.048462406","-0.06326164","-0.097132936","-0.048224144","-0.008149016","-0.06287098","0.071085654","0.012843093","-0.061555654","-0.028159278","0.029509697","0.019282611","-0.029950052","-0.05494203","-0.06517936","0.061490443","0.08622819","-0.04243645","0.021767367","0.09982201","0.05579761","0.06285736","0.01915376","0.015998343","0.043576866","-0.007682904","-0.03997084","-0.029248357","-0.08521915","-0.032833543","-0.061554637","-2.760004E-8","0.02687442","-0.013623533","-0.007522831","0.0018123185","0.039428852","0.080848984","-0.012733794","0.0014693135","-3.1463415E-4","0.042441852","-0.045952924","0.024488613","-0.016901385","-8.085168E-4","0.056125943","-0.031485185","0.009108465","-0.0055158143","-0.0128198","0.046484016","-0.049566176","0.074238606","-0.03627999","-0.11903731","0.006365095","-0.018856015","0.002436774","0.008593947","-0.013144841","0.019065669","-0.045697447","0.07061157","-0.05710901","-0.03575317","-0.022118429","0.04699691","0.08314085","0.01567623","0.015723974","0.120434165","0.07199588","0.055119313","-0.0045805397","0.06783439","0.10990334","0.022695042","-0.024611043","-0.022164993","0.060630262","-0.040990453","-0.047969796","-0.05290249","0.013855684","0.022644693","0.0126102315","-0.01881556","0.008459907","0.018470518","-0.013056598","0.029337492","0.049159013","-0.07049007","0.07536451","0.012284426"]</t>
+  </si>
+  <si>
+    <t>NK-2oH5jfdfjrYmaW2nx8HpPP</t>
+  </si>
+  <si>
+    <t>Hwa Song Pak</t>
+  </si>
+  <si>
+    <t>Entity Name: Hwa Song Pak | Type: Person | Jurisdiction: kp | Risk Context: Executive Order 13810 (North Korea)</t>
+  </si>
+  <si>
+    <t>["-0.039113052","0.14465909","0.024731398","-0.056596477","0.01510078","0.049609974","0.05390948","-0.052503232","-0.057851974","0.028857652","0.05488702","-0.04531403","0.07515394","-0.07620179","0.0137589555","0.022002975","0.037587967","-0.032441776","-0.056369483","-0.06476137","0.02076092","0.052061465","0.012682713","0.009633852","-0.038781695","-0.002091725","0.016222889","0.038370334","0.01518205","-0.03173419","-0.024234835","0.015790585","0.05220517","0.0749614","0.05228776","0.04324062","-0.05592148","-0.012464761","-0.010698932","-0.036055963","0.06547512","-0.045784596","0.087398","-0.019528084","0.01036364","3.8770755E-4","-0.08280096","-0.10357554","-0.077666864","0.07554695","0.014193034","-0.008727885","-0.007391166","0.06785337","0.058073305","-0.021087404","-0.024708401","0.04950691","0.049115174","0.01704653","-0.02766086","-0.017717311","-0.034689654","-0.042474665","0.039250463","-0.018741079","0.07568621","-0.0052561914","0.010123723","-0.026264913","0.07493864","0.017726792","0.009348753","0.04575928","-0.10255162","-0.07432467","0.04606057","0.011066939","-0.0021491952","-0.093391076","0.041962747","0.037766296","0.034398936","-0.06286493","-0.06553184","-0.01625118","-0.08702895","-0.047911394","-0.046609122","0.035319455","-0.017748512","-0.0638975","0.12755038","-0.032708295","0.0040887655","0.014683057","-0.0010248763","0.0026652545","-0.03069215","0.054876655","0.02388486","0.04488515","-0.036155954","0.0111878505","-0.027361006","-0.08266493","-0.042078964","0.012662105","0.022737062","0.009581415","-0.08765227","0.034953557","-0.06463526","-0.047556195","0.021085054","-0.029920483","-0.043064766","0.0015069096","0.030591728","-0.053318612","0.03548772","-0.08207788","-0.056041613","-0.074298225","-0.030889371","-0.028962597","0.002776314","-7.915205E-34","0.09463532","-0.0029090894","0.012377458","-0.021505056","-0.033362933","-0.07579291","-0.031091712","-0.047110923","-0.04622619","0.03974399","0.023466265","-0.027700504","-0.03305132","-0.06495203","-0.09113285","-0.0560828","-0.08201936","0.0723487","-0.014670871","0.1336526","0.038964197","0.062868476","-0.015846908","-0.022982696","0.016602555","-0.021170346","-0.06296227","-0.02430196","0.06080013","0.056202102","0.030124914","-0.035883587","0.07217278","-0.0071824235","-0.047070093","-0.021167856","-0.036531642","-0.082632385","0.005478438","-0.13127327","0.021164678","0.05263679","-0.06453633","0.11947403","0.023429679","-0.0055441842","-0.018515693","-0.008757726","0.06364439","0.0147765195","-0.037578322","0.022275947","-0.021015374","-0.06794154","0.007119144","-0.05796358","0.038286917","0.046422344","0.042012505","-0.024346549","0.027479053","0.04088981","-0.053963743","0.05714534","0.07889377","-0.064161524","-0.019504812","-0.06912614","0.06754384","-0.10364668","0.082017936","-3.6220698E-4","0.04606854","0.022067856","-0.058586106","-0.005434551","0.012380707","-0.026123872","0.027248552","0.031145606","-0.09030168","0.003735087","0.03932422","0.06027437","0.027415559","0.0369071","-0.012270396","-0.08121788","-0.026627546","-0.0072019007","-0.031516995","0.05218499","0.054101743","-0.014355048","-0.018007142","-7.533619E-34","-0.0026293837","0.00929572","-0.028684359","-0.011721091","0.0942673","0.026465101","0.06966043","0.023714822","0.021132048","0.022526836","0.033731762","-0.07789626","0.042937864","0.009918853","0.09736118","-0.025035782","0.0053103506","0.097323075","0.00870826","0.07427382","0.006764648","-0.054569863","-0.013866172","0.11112275","-0.0065552425","2.3783756E-4","0.039061736","-0.014929501","-0.029054092","-0.012112729","-0.008967328","-0.059774127","-0.08301208","0.09158481","-0.036842782","-0.1469289","0.025852218","-0.04112736","-0.041117948","-0.05437622","-0.0408582","0.06320628","0.013936532","0.0145757245","-0.11078808","0.0145447","0.022543753","0.08946754","0.0055761538","-0.07640584","0.019559743","0.032108508","-0.034694962","-0.02818386","-0.039334297","0.041054007","-0.0126500605","-0.028477525","0.084949724","-0.00164731","-0.011213504","0.051595915","-0.023450593","0.12362202","-0.01928295","0.04133447","0.033860076","-0.060607508","0.07229718","-0.048036724","-0.04143368","-0.08507158","-0.008995114","-0.0021004877","0.03991763","-0.013215117","-0.031272206","0.0063072233","-0.016410243","-0.052480765","0.054674514","0.042587988","-0.11594235","0.047117956","0.05711951","-0.0033494616","0.05423825","0.0062774257","0.05005949","0.036998745","-0.016001847","-0.038504247","-0.07185643","0.042012397","-0.039618786","-2.5950479E-8","-0.00700023","-0.049670245","0.044601623","0.0371256","0.04918895","0.059777014","0.01493089","-0.13918944","0.048450116","0.0069748294","0.064235136","0.030184908","-0.02004914","-0.11320521","-0.047070637","-0.120087564","0.03903564","0.07485603","-0.024742741","0.045157187","-0.07861723","0.008332592","0.05329061","-0.07551296","0.021664938","0.06920492","0.0153293265","0.06298211","0.07817164","-0.017005032","-0.015517278","0.06452412","-0.10992352","0.053390883","-0.016554877","0.032270696","0.037536368","-0.034409255","-0.007818692","-0.010931553","0.0052773487","0.060841545","0.046783052","0.06894452","0.006809223","-0.009239484","-0.013612145","-0.016733507","-0.0070675756","-0.039650027","-0.0759243","-0.066838","-0.034276545","-0.01641001","-8.764055E-4","0.045211226","0.097178966","0.031358823","-0.0077236593","-0.0107429","0.12542902","-0.012753058","0.008359714","0.018103197"]</t>
+  </si>
+  <si>
+    <t>NK-2qY6qiMngLENHkcYsD8KMc</t>
+  </si>
+  <si>
+    <t>Beijing Guoke Tianxun Technology Co., Ltd.</t>
+  </si>
+  <si>
+    <t>Entity Name: Beijing Guoke Tianxun Technology Co., Ltd. | Type: LegalEntity | Jurisdiction: cn | Risk Context: For all items subject to the EAR. (See § 744.11 of the EAR)</t>
+  </si>
+  <si>
+    <t>["-0.073833205","0.035096068","0.010237395","-0.06274344","0.0014668897","-0.028152341","0.15857522","3.836033E-4","-0.020038947","-0.025537565","0.09970641","-0.06933004","0.03155882","0.0026517208","-0.02434416","-0.014694122","0.031520743","0.010992334","-0.04010743","-0.039606947","0.027925933","0.0268002","0.059294406","-0.0054475605","-0.071760334","-0.046091553","-0.014257762","-0.00449199","0.07990171","-0.01844505","0.011773962","0.11778796","0.038010333","0.03473344","0.0535257","0.07146368","-0.04507794","-0.068523765","0.008290808","0.017826838","0.08036426","0.015045114","0.073060304","-0.029708685","0.045680918","0.09351723","0.027069265","-0.10771882","-0.030903472","-0.021002736","0.029939149","-0.05699043","0.013264167","0.070071675","-0.048847","0.09163082","6.5493915E-4","-0.009069232","-0.035864152","0.0054851645","0.020944543","0.01672543","0.039398212","0.014264973","0.039765425","0.066524774","-0.011137615","0.008655538","-0.027718466","-0.07178893","0.03833765","-0.0347752","-0.08991401","0.05066807","-0.061874263","0.0050414638","0.06271769","-0.020951083","0.034810405","-0.07978142","-0.021651015","0.010108673","0.089064196","-0.07348518","-0.011851207","0.0336536","-0.034395676","0.05060723","0.030168185","-0.0476965","-0.0056485794","0.032470617","0.031987067","0.096573114","0.020760225","-0.008557632","0.022315793","-0.010134524","-0.021799257","0.025831725","0.04848952","0.058135383","-0.030807007","0.01634905","-0.026622808","-0.06518964","-0.101005815","-0.042955834","0.008851653","0.013197185","-0.050258335","0.020163925","-0.027947206","-0.0278788","0.0062047597","-0.0036695888","-0.093153834","0.09514925","0.04636435","-0.119539216","0.0028627184","0.019777415","-0.095691875","-0.104155","-0.07568477","-0.024673494","-0.06799912","-2.891081E-33","-0.028242929","0.074705616","0.0036320738","-0.029929148","-0.005601008","-0.0018531331","0.01134978","-0.007368248","-0.054464795","0.057099022","-0.022341058","0.014782212","-0.0780354","-0.04330486","0.058294278","0.015754424","-0.097000726","0.055378977","0.028754808","-0.030244913","0.05099988","-0.05547798","-0.059216786","0.020952629","0.03978002","-0.021925127","-0.022870798","-0.07062244","0.02955859","0.025858732","-0.0072486345","0.038523093","0.06551557","-0.027472418","0.009020767","0.10041921","-0.0150753325","0.021673696","-0.03325821","0.03877711","0.032257326","-0.005064922","0.030588342","-0.009395235","0.009895298","0.026429683","-0.051293813","-0.061399914","0.089057624","-0.06519236","-0.05104221","-0.040291764","0.01787214","-0.0058482597","0.051108994","-0.054927558","-0.056252357","0.019466585","-0.06245753","-0.022503098","0.02440133","0.027494032","-0.0982022","0.089414395","0.026171966","0.030716315","0.060513943","-0.04067276","-0.026011381","-0.1063243","-0.04022485","0.02786549","0.04330645","0.01834014","0.0036446052","-0.062039286","-0.12971663","-0.032707438","0.015615745","-0.025353089","-0.1586531","0.020142123","0.045455996","0.080023184","0.025698755","-0.03131167","0.03888434","-0.001595188","-0.034748368","0.009968742","-0.06802958","-0.008811438","-0.020404875","0.06701815","-0.059349112","9.698506E-34","-0.0876681","-0.002074277","-0.055541746","0.038402136","0.015334759","-0.015324722","0.07964649","0.030175516","0.014872008","-0.016464928","-0.032216735","-0.031598367","0.018846674","0.02099574","0.052395083","-0.0023656602","-0.02608364","0.031684097","-0.06626217","0.050419766","0.051788017","-0.103281334","-0.041363157","0.045564253","-0.032286752","0.063879356","0.05967843","-0.10112887","0.04523294","-0.021219462","-0.072237276","0.022934834","-0.06760265","0.117382474","-0.04017392","-0.104358405","0.06043281","-0.06592759","-0.02916642","-0.056267515","-0.01816951","0.029335383","-0.0057014083","0.031188408","-0.0421583","-0.024272295","-0.029283755","-0.05565805","0.050037816","0.012281613","0.014270078","0.017401965","0.04176364","-0.009115013","-0.06575248","0.044040464","-0.024399675","-0.022689885","0.006516878","-0.0544354","0.09296655","0.08197702","-0.052669827","0.11787634","-0.003491905","0.07410238","-0.012684639","0.04636259","0.063182496","-0.058384795","0.0981473","0.032932926","-0.03877688","-0.062070757","-0.009524117","0.0034757822","-0.03132718","-0.050580375","0.017045692","-0.022086153","0.11106896","0.05627002","0.003135162","0.04901466","0.03416196","-0.045125313","6.509154E-4","-0.017570697","-0.006317556","-0.023707863","-0.044929054","-0.032850467","-0.071014464","0.054668643","-0.06849098","-3.2536047E-8","-0.027734902","-0.023998832","-0.010212659","-0.06438229","-0.04042288","0.0057367035","0.044397525","-0.0021339448","0.04251615","0.011325689","0.017918404","-0.03834254","-0.04020782","0.08499711","-0.062962435","-6.9684547E-4","-0.043090645","0.060694303","0.027699986","-0.02800804","-0.058049254","0.04905959","0.046077978","-0.13732144","-0.010680454","0.0034933276","0.0047256444","0.08686385","0.026374348","0.033531796","-0.04281065","0.009080067","0.0056429966","0.04187397","-0.031151803","0.01929413","0.03476093","-0.049363155","0.09110655","0.008009422","-0.0262774","-0.05237603","0.049095456","0.04494365","0.12356772","-0.06515351","0.03806938","-0.027537812","0.11520509","0.05366764","-0.047969643","-0.024687069","0.055972397","-0.047058042","-0.035469968","0.101231374","0.03503003","0.045774937","-0.0528919","-0.0063769454","0.019303719","-0.05599211","0.06868549","0.06951755"]</t>
+  </si>
+  <si>
+    <t>NK-2sJaJRaPJcWUfMbHjTtWcL</t>
+  </si>
+  <si>
+    <t>JANAN AGHA</t>
+  </si>
+  <si>
+    <t>. Review pursuant to Security Council Resolution 1822 (2008) was concluded on 23 Jul. 2010. 9.3.2017 L 63/22 Official Journal of the European Union EN</t>
+  </si>
+  <si>
+    <t>["-0.04797508","0.03350601","-0.039649565","0.056232784","0.013272522","0.06611054","-0.021771772","-0.017007094","-0.035503652","0.0055008456","-0.007808578","0.01614724","0.029418254","0.026497388","-0.08894571","0.014521174","0.026979806","-0.06998625","0.0128446575","0.027189968","0.0069915857","-0.027149718","0.09450681","3.3903925E-4","-0.033670943","-0.07343728","-0.049438387","-0.09138958","-0.07912824","-0.007974115","0.0075333146","0.042425487","-0.069054335","0.0031628574","0.053307068","-0.05490245","0.055882107","-0.04055195","0.027289772","-0.0063806223","0.0074054115","-0.10778486","0.0012208746","-0.0018673065","0.0312504","0.05743483","0.0058409837","-0.062330164","-0.15457964","0.06836182","0.066238075","-0.031318374","0.07214985","-0.031915396","-0.020915808","-0.01113372","-0.07182283","-0.0045573222","0.02888245","0.009538976","0.035637647","0.03131349","-0.12019447","0.0254537","0.07817435","0.005663879","0.017662186","-0.11461209","-0.027762549","0.02935851","0.023689337","-0.06811028","-0.016613172","-0.003864186","0.046772167","0.07516496","-0.014198586","0.04375783","0.060939044","-0.105682425","0.042581312","-0.011127891","-0.059664194","-0.009235248","0.05899438","-0.08699184","0.077566735","-0.06517274","0.008040857","0.04622632","0.05521577","0.05120516","0.06498142","0.025199285","-0.008110963","-0.055543568","0.021858456","0.056826685","-0.03623497","0.060629386","0.010986232","0.036765356","-0.12380617","-0.03923133","-0.10151529","0.016956823","0.008931138","-0.004653225","0.026764201","-0.01786379","-0.03975288","-0.04180106","-0.014233339","-0.10388717","0.019548792","0.02200267","0.028009621","-0.043726463","0.114561066","0.014234147","0.04518189","-0.013694787","-0.056514382","-0.025759004","0.023040002","-0.018663801","-0.008306737","-5.516353E-34","-0.056985144","-0.051790394","-0.020310652","0.03941534","-0.03419364","0.032613814","-0.034831427","-0.06963605","-0.05332605","-9.6951745E-4","-0.07148943","0.062130928","0.066066526","-0.074493945","0.0075408155","-0.0036140347","0.018916326","0.11620516","-0.015215411","0.011195498","0.1259474","-0.06134522","0.11504575","0.041108947","0.11663369","-0.026141811","-0.072999604","-0.012182375","0.04270961","0.03221441","-0.027401607","0.03928347","0.013118791","-0.029123537","-0.031499144","0.06726886","0.007231861","0.007847347","-0.054345503","-0.09017652","0.028327776","0.028286709","-0.0054454734","-0.0074115205","0.10672076","-0.046682097","-0.019304276","-0.03624778","0.04246105","-0.03084492","0.01712801","-0.024771046","-0.07882031","-0.010341092","0.017983273","0.07133607","-0.027649112","0.070701174","0.021315286","-0.02230847","0.06527292","0.0958078","-0.0759286","-0.055013582","0.02016225","0.066475995","-0.03681388","0.09127315","0.006289459","-0.12793873","-0.0029874952","0.012415235","0.0718345","0.0011031525","-0.02879445","-0.0106628435","-0.023256306","0.06587717","0.02372539","0.017029835","-0.05014625","0.012457724","0.031180648","-0.0015525245","0.043201298","-0.04189661","0.056117512","0.004831458","0.004325774","0.0046125487","-0.07464082","-0.005048693","0.103252605","0.06868275","-0.00231916","-1.2367047E-33","-0.03578972","-0.029979331","-0.071965024","-0.030318832","-0.06846206","0.03373452","-0.059655778","-0.008424301","-0.0060633766","0.013486311","0.0385792","-0.10824754","0.08860613","0.003908845","0.004631014","-0.02417257","0.0042819236","-0.05123375","0.0026230672","0.02179456","0.092908435","0.038302366","0.037708588","0.057224695","0.024762455","-0.013514873","0.08106814","-0.009730308","0.024421336","-0.06582906","-0.030221757","-0.037048828","-0.06425601","0.104255915","0.03634852","-0.07827505","0.10349636","-0.02226642","-0.0044830227","0.04115613","-0.015548423","-0.0014011222","-0.04644669","0.050037496","-0.012665371","-0.0044952827","0.035806045","0.03415338","-0.041146517","-0.07060236","0.035448946","-0.027882902","-0.046125833","-0.0033258894","-0.019701691","0.07732404","-0.014298301","-0.02398099","0.07803578","0.057902757","0.050689075","0.1236131","-0.027557379","-0.015290971","0.035889108","0.00698924","-0.087555476","0.07300896","0.058959212","0.0129008265","0.039871477","-0.08655227","-0.09667916","0.033598274","0.062140886","-0.043428585","0.06820648","-0.017055692","-0.012947395","0.040593386","-0.020312004","-0.023623968","-0.06696807","0.010458394","0.11592558","-0.08953343","0.06638529","-0.08966922","0.06970004","0.009232978","-0.036162797","-0.097908944","0.018490942","-0.02862951","0.049997997","-4.0009787E-8","0.036536083","0.02896296","-0.039825562","0.04576438","0.06661659","-0.045342088","-0.016023736","-0.01796345","-0.10388985","-0.03053521","0.058921557","0.0109839775","-0.052003045","-0.08199495","-0.030396348","-0.0662169","0.023156323","0.06068244","-0.019345049","0.04001335","0.020773903","-0.010750186","-0.013849993","-0.0660109","-0.045875236","0.04892961","-0.020272862","-0.04185281","-0.084551916","0.02290558","-0.015133153","0.060777996","0.0031694213","-0.028336542","-0.020683233","0.04725215","0.039064445","0.07191242","0.005151654","-0.022703802","0.0036785353","-0.0022771035","0.044300336","0.029567672","-0.026984405","0.01653483","-0.05188413","-0.07582893","0.022108985","-0.020931467","-0.01943127","-0.061914686","0.060346067","0.048769824","0.0037096427","0.0027084486","0.03133043","-0.06309006","-0.0070065367","0.03832438","0.07689407","-0.07836539","0.013729641","0.03114099"]</t>
+  </si>
+  <si>
+    <t>NK-2u3XwBr2zPupG7QsfRbpbz</t>
+  </si>
+  <si>
+    <t>Green Wave Telecommunication</t>
+  </si>
+  <si>
+    <t>Entity Name: Green Wave Telecommunication | Type: Company | Jurisdiction: my | Risk Context: (also GREEN WAVE TELECOMMUNICATION SDN BHD, GREEN WAVE TECHNOLOGIES, GREENWAVE TELECOM) (also GREEN WAVE TELECOMMUNICATION)</t>
+  </si>
+  <si>
+    <t>["-0.009890768","0.010888997","0.004082808","-0.08503004","0.002072153","-0.008134837","0.107662335","0.05408232","0.0025083353","-0.05657484","0.04807536","-0.08342721","0.0470003","-0.0429945","0.055147246","0.055990234","0.003654196","-0.07457183","-0.06272011","-0.051411714","-0.014642524","0.019608364","-0.009382764","-0.058497146","-0.0395399","-0.051296905","0.023894291","0.099305786","0.020152146","-0.066996604","0.007099954","0.1424948","0.069491364","0.061932478","0.017873595","0.017188821","-0.07780548","-0.05000066","-0.0070223855","0.023354948","-0.010789015","-0.020567842","0.015744641","0.038848054","-0.019261507","-0.030511279","-0.006576031","-0.011376284","-0.05320775","-0.021121088","0.010399664","-0.056482673","-0.015332509","0.10292088","0.026495285","0.032816593","-0.045361035","0.044457294","0.0047201947","-4.2466415E-4","0.05586102","0.018067388","-0.021335052","0.021074468","-0.009826173","0.07013203","-0.008152294","0.06517077","0.0017874944","-0.08577667","0.037899055","-0.044708245","-0.013135398","0.07816291","-0.0053127636","0.013960009","0.06690512","0.07217619","0.02006275","-0.07748298","0.007957833","0.04488778","-0.0011643888","-0.07869443","-0.042084813","0.061753605","-0.0121892225","-0.016374545","-0.014806792","-0.0055571767","-0.04962075","-0.01990477","0.0875778","0.032091677","-0.017678889","0.00461702","-0.023473512","-0.12708278","-0.00874512","0.027287735","-0.012464769","0.015822604","-0.034172866","0.023064978","-0.15824156","-0.047939833","-0.0830263","0.07811851","0.049492657","-0.049050216","-0.023608929","0.10097302","-0.06815677","-0.04472192","-0.023588317","0.010924389","-0.062186457","0.056716997","0.09661374","-0.080445655","-0.057058338","0.005696109","-0.10396158","-0.051373072","-0.13378036","-0.04518622","-0.019889819","-6.4742537E-34","0.04619632","0.082302846","-0.010841799","-0.012293848","0.026341842","0.034307268","-0.011408489","0.04339694","-0.05297632","-0.038897008","-0.023456123","0.03830313","-0.02715232","-0.09454103","0.03087276","-0.034951746","-0.059978258","0.030833941","0.014609912","-0.014697497","-0.025220377","-0.022803083","-0.05107006","-0.004632474","0.042662688","-0.03857288","0.07880145","-0.08054183","0.091471575","0.036905978","0.04174632","0.039396588","0.04366321","0.008111458","0.10647765","0.06614909","-0.06110903","-0.043426935","-0.05551483","0.029042022","0.007559774","-0.024537288","-0.04032521","0.04330221","0.005130474","-0.019978799","0.016633851","-0.0565458","0.0147","0.002504218","-0.065025955","-0.0041925698","-0.007939272","0.034288034","0.07217082","0.023651674","0.033846863","0.025811836","-0.080277674","-0.028332345","-0.031294692","0.0016168191","-0.08080832","-0.008373666","0.026895395","0.0038248135","0.012986374","-0.058430243","0.06900434","-0.06683989","-0.023255495","-0.032254133","0.0072470563","0.02622822","0.02290659","-0.010298479","-0.09564255","0.0698973","-0.059199087","0.098037444","-0.10247519","0.04111965","-0.027625078","0.009743499","0.021382289","0.03680995","0.039280217","-0.1194941","-0.053307038","0.06680928","-0.06832796","0.030542225","0.07368966","0.115132846","-0.058095254","-1.3458825E-33","-0.08428345","-0.013919672","-0.028804164","-0.04766771","0.08762837","-0.054815255","0.08033606","0.03241377","-0.021798294","0.0266649","-0.017795995","-0.03662896","-0.033696838","0.017525863","0.010863489","-0.020739317","-0.014373026","-0.008395183","-0.065660425","0.08917036","-0.02888843","-0.09789773","0.0034095827","0.075386316","-0.0048421505","0.0666557","-0.008054699","-0.009185425","0.022139633","-0.023267563","-0.070457794","0.022852886","-0.07446354","0.06823277","-0.026927188","-0.017307442","0.06529053","-0.10662164","-0.020154059","-0.054851193","0.0065374104","0.047143098","0.030301247","-0.016756535","-0.11408864","-0.0053154402","0.020292843","-0.022232248","-0.071925975","-0.032819353","0.020074083","0.09071646","0.012382573","0.0074549504","0.026906349","0.023379587","0.05631965","-0.025639093","0.0013603804","0.024880428","0.08490845","0.012274931","-0.01191823","0.13902158","0.041941885","-0.0297225","0.0037062035","0.00627768","0.050121058","-0.11358624","0.013795253","-0.025895817","-0.040513072","-0.017393751","-0.015181981","-0.14067253","-0.014425992","-0.05222733","-0.09067672","0.033000182","0.09120463","0.10055467","-0.01290312","-0.0037387894","0.061908003","0.0034208507","0.100936495","-0.039907277","0.0037545918","-0.0070618815","-0.028131511","0.046929687","-0.05893225","0.08889594","0.0010246885","-2.8128582E-8","0.0055831694","-0.021675633","0.03052376","-0.009313001","0.038980674","-0.062025443","0.003990686","-0.025928864","-0.010537526","-0.010269513","-0.07224454","-0.014545481","-0.06253736","0.015463839","0.033529703","-0.07878344","-0.06649788","0.010237748","0.025005024","0.025279792","0.03738306","0.022299407","0.008502525","0.011414727","0.028680056","0.053881034","0.030691944","-0.014189006","0.077211015","0.056880314","-0.020366399","0.074383125","0.012795046","0.052845795","-0.10916441","0.021012535","0.08113148","0.003136172","0.008012477","0.05852142","0.0093054995","0.041221093","0.036392614","0.08918546","0.056010302","-0.047317263","-0.004986094","0.02980447","0.09498875","0.027925987","-0.06485359","0.0012601062","-0.008992612","0.0070003513","-0.056364264","-0.051297743","-0.015136038","-0.01061557","-0.058611628","0.017999098","6.002526E-4","-0.024895554","0.038951144","0.06041681"]</t>
+  </si>
+  <si>
+    <t>NK-2we8EXArQ4RFWdk4YUC4su</t>
+  </si>
+  <si>
+    <t>LOUISA LUNEAT DUPREE</t>
+  </si>
+  <si>
+    <t>Entity Name: LOUISA LUNEAT DUPREE | Type: Person | Jurisdiction: us | Risk Context: 1128a2</t>
+  </si>
+  <si>
+    <t>["-0.030867783","-0.040938783","-6.54629E-4","0.001319747","0.028400436","0.044028204","0.010632388","0.068086445","0.029786011","-0.016889881","0.069681905","-0.10909152","0.0047322134","-0.10371525","-0.053437613","0.10047146","0.04907213","0.07278231","-0.04406477","0.006862719","0.04529547","0.021652607","-0.019947967","-0.03880575","0.010408445","-0.025201544","-0.0034601972","0.025476681","-0.009296878","-0.052066658","0.05105821","0.016003598","-0.003672729","0.07277701","0.04534661","0.0077907764","-0.06970616","0.001290764","0.07443844","0.003369719","0.0017702676","-0.07451955","0.061443675","0.0047953934","-0.08911038","-0.021273267","-0.05772969","0.012166846","-0.024309278","-0.0012789005","-0.038635466","-0.042316563","-0.0032190324","0.036820486","-0.013414546","0.01934884","-0.028171651","0.08895604","-0.029037109","-0.019279182","-0.0049575735","0.07509571","-0.01714349","0.006285883","-0.030454872","0.0014656439","0.013349898","-0.0024355156","-0.014279833","-0.0742903","0.02429866","0.0030322224","-0.12998343","0.07220882","0.057254072","0.030316833","0.004506188","0.10177457","-0.013083136","-0.057729207","-0.014128266","-0.0071390956","0.051884465","-0.051910292","-0.03989367","0.0038064183","-0.026945107","-0.0042790812","0.044763137","-0.06386383","-0.05886431","-0.07211238","0.07522373","0.021933781","-0.02149356","0.04497333","-0.04907189","-0.008569396","-0.08272645","0.054613296","-0.0757949","0.041487083","-0.0060361805","0.04883188","-0.06833077","-0.12872532","0.013760717","-0.0043069315","0.00275856","-0.024225794","0.08451979","0.04687301","-0.0063909856","0.005052062","0.04437772","-0.06598366","-0.07128592","-0.008298935","0.054289646","-0.115610704","0.040082302","-0.003291571","-0.088832565","-0.069790654","-0.08221891","-0.03343184","0.022065703","3.1498907E-34","0.09629363","0.019134972","0.07633845","0.111631","-0.03478727","0.030644061","0.028630877","0.0052898023","-0.11217787","-0.02702897","-0.022620741","-0.012785564","-0.034481794","-0.10148009","-0.07682598","0.09195234","-2.9137268E-4","0.015902951","-0.030936489","0.032589965","0.051560108","-0.006232277","0.002988071","0.03687434","-4.9737026E-4","-0.0524914","0.03590207","-0.08775042","0.026988193","0.062163264","-0.062762305","0.021882795","0.059196483","0.0025732133","0.061279524","0.060099106","-0.031082246","-0.057879936","-0.015743297","-0.044671167","0.0051977555","0.0256971","0.06940782","0.08090866","-0.014076142","0.010038183","0.06372589","-0.023334686","0.083789065","0.028785463","-0.014694915","-0.05317568","-0.07431001","0.025778744","-0.020009665","0.030167298","-0.03538609","0.056702662","-0.009308368","-0.011652949","0.013402287","0.07723763","-0.048450172","0.03136412","-0.0049203755","-0.0888198","0.04391188","-0.068634294","0.05821064","-0.09540718","0.025605638","0.013962889","0.02675978","0.039550357","-0.044784375","0.010848625","0.09847076","-0.012222777","0.029682487","0.0027678497","-0.04083328","-0.03859459","-0.006575426","0.031355638","-0.011253728","-0.028127976","-0.06413097","-0.09106903","-0.06082232","-0.008071738","0.016228437","0.03059721","0.005012388","0.017575542","-0.03901383","-2.0938348E-33","-0.03474246","-0.08444214","0.013716838","0.020226102","0.06390651","-0.08548848","-0.0055289473","0.036670692","0.001365474","-0.009986933","-0.01464243","-0.09733521","0.06688514","0.024874853","0.035634283","0.07603813","-0.0017674358","-0.078196324","-0.00408232","0.04799792","-0.0133147035","0.004999588","0.013866254","0.037796266","0.014917064","-0.0028003876","0.022230014","0.008932395","-0.06274523","-0.08896103","0.004597143","0.042298395","-0.057837244","0.039638076","-0.13124946","-0.07599905","0.10887182","-0.051184073","-0.034766212","-0.035259806","-0.044302408","0.003859256","-0.039030723","-0.014842756","0.026010089","-0.03357968","0.034213703","-0.059343487","0.082396515","0.009169222","0.0380473","-0.0074665584","-0.04548072","0.0482802","0.013230842","-0.039707348","0.04605462","0.015015264","0.03228748","-0.011074358","-0.0021493689","0.11176308","-0.058811177","0.12920074","0.08732507","-0.0023884599","-0.12601641","-0.014863081","-0.050125703","-0.04577245","0.052185934","-0.09056236","-0.06369698","-0.023760078","0.0019652853","-0.025881207","-0.020865595","-0.03608148","-0.03193041","0.05224084","0.025466379","-0.027906805","0.0014314674","-0.012892163","0.04485284","0.01777486","0.058278732","-0.007653278","0.012955993","0.013669534","-0.056408025","-0.02115068","-0.028350806","0.0018828084","-0.037054602","-2.8126282E-8","0.01393893","0.08639027","-0.045016218","-0.001897515","-4.7631483E-4","-0.095541686","0.06285359","0.05837398","-0.03491354","0.042154633","-0.11145346","-0.013148232","0.02780752","-0.0075687715","0.109213635","-0.028577179","-0.009582173","0.040968187","-0.015307651","0.10847179","0.08744959","-0.019680135","0.017392974","-0.07423063","0.019013684","-0.041276928","-0.030443227","-0.020816086","0.034870096","-0.028112663","0.008111275","0.1034597","0.016133148","0.020091465","-0.06447183","0.014230702","0.07792599","-0.05839194","-0.036924765","0.05329143","0.035009403","0.08973473","0.049915045","0.03955562","0.09761604","0.060995612","0.050594926","-0.006707672","0.098245196","-0.041762058","-0.08720486","-0.06685376","0.040578764","0.04427024","-0.055043098","-0.07057313","0.060177885","0.1115734","0.055000845","-0.0601451","0.02691458","-0.055009574","0.04522258","0.050771847"]</t>
+  </si>
+  <si>
+    <t>NK-2yL7TM7nRMQZuMN5CHPWWa</t>
+  </si>
+  <si>
+    <t>Voice of Europe</t>
+  </si>
+  <si>
+    <t>. R (UE) 2024/2642 : “Voice of Europe” (Voix de l'Europe) est un média en ligne se livrant à une campagne internationale systématique de manipulation des médias et de dénaturation des faits par l'intermédiaire de son site internet et de ses comptes Facebook, YouTube, Telegram et X. “Voice of Europe” a diffusé une désinformation concertée concernant l'Ukraine, l'Union et ses États membres dans le but de soutenir les intérêts de la Fédération de Russie en matière de politique étrangère</t>
+  </si>
+  <si>
+    <t>["-0.04062485","-0.011671191","-0.065834284","-0.1588713","-0.016607553","0.05823716","-4.006224E-4","-0.004945887","0.034172572","-0.028435672","-0.10704166","-0.00710205","0.03229622","0.025488688","-0.03546219","-0.10375077","-0.024102466","-0.044473547","-0.040548198","-0.019165825","-0.008375206","-0.016021295","2.8702326E-4","0.05857905","0.06319104","-0.01660104","-0.0053680083","-0.08496301","0.01061999","0.0033148215","0.0323692","-0.018435277","0.06355202","-0.055512544","-0.0042496044","3.9926168E-4","0.020292051","-0.054661978","-0.048175666","-0.00434163","0.029952198","0.018302122","-0.04505226","0.01698257","-0.04891843","0.016557222","-0.082363345","0.07629953","-0.10641432","0.07273299","-0.046250872","-0.025178634","0.08078309","-0.017937524","-0.018979825","-0.056681745","0.04080146","0.10020827","0.012453257","0.012288735","-0.022785665","-0.10394114","0.013260191","0.06709132","-0.02706662","0.06804043","0.0013513861","0.01770276","-0.06323832","0.016587345","0.027899431","-0.016840374","-0.02630269","-0.0509819","0.09608559","-0.11530267","-0.05296527","-0.07236537","-0.014671605","0.0030876142","0.14850329","0.013852905","-0.047742583","-0.05649231","-0.010543783","-0.07550884","0.017942635","-0.107693695","-0.0261103","0.030567506","-0.10147292","0.033854786","0.10172","0.071061306","0.019468507","0.024953913","0.008122943","-0.041392747","0.052415345","0.03924556","-0.03690768","-0.022761706","-0.027461959","-0.049714815","-0.0949773","-0.057461753","-0.08106648","0.043309864","-0.06034477","0.04700935","-0.078608066","-0.006435215","-0.014403557","-0.045212246","0.03364901","-0.051790226","0.04227601","-0.07992305","0.019145062","-0.016121868","0.017404692","-0.0058745905","-0.034389902","0.03832447","0.07512871","-0.029031448","0.006388584","2.483272E-33","-0.016524415","-0.052702542","-0.0020984923","0.08551141","-0.077385396","0.0780595","-0.0621038","-0.01741674","-0.014889121","-0.061815068","-0.044195455","0.04825601","-0.020799601","-0.006786876","-1.9354533E-5","0.032483034","0.035987765","0.08306694","0.0028503195","-0.0065166675","0.06642654","0.04997828","0.07057757","0.04520608","0.14390656","0.019157218","-0.05888205","-0.10735403","0.030146407","0.0078907395","-0.045520075","0.001014397","-0.036233354","-0.0049139927","0.020693047","0.016026067","0.026512913","-0.01870398","0.009033149","-0.008163428","0.01890568","9.958234E-4","-0.056502923","-0.030299304","0.052043017","-0.06290959","-0.041726794","-0.020505542","-0.0068919645","0.026170911","-0.021125989","-0.0042521865","0.022125209","0.022722233","0.104751654","0.062192682","-0.07448291","-0.01141859","-0.0041308897","-0.08199924","0.045795023","0.011874778","0.031692892","-0.0412448","0.053668447","-0.008254286","-0.048056554","0.026143787","0.0061202617","-0.017497977","-0.01044377","-0.04772323","0.06949195","0.064001285","-0.07638274","0.09646112","-0.044619087","0.025447449","-0.06331299","0.11037411","-0.07397633","-5.028978E-5","0.038813993","0.016136184","0.035568543","0.0014815225","0.059586372","-0.040756103","0.07784867","0.077972926","-0.12604754","0.033348422","-0.027025828","0.053585008","-0.059627","-7.2868116E-33","-0.01765275","0.059657604","0.012726292","0.053682555","-0.04368622","0.027255213","0.011738764","0.032599755","0.0075311847","0.08475882","-0.018382574","-0.14119554","0.04695151","-0.020193001","-0.03468507","-0.041120183","0.095455274","-0.04633743","-0.034959838","0.027309792","-0.036697183","-0.068030395","0.008429979","0.024343504","0.0054033017","-0.14184892","0.016828725","-0.04892305","0.02452307","0.009408173","-0.040695507","0.04081005","0.031171035","0.07324501","0.06632814","0.08342536","0.058513284","0.035865147","-0.00602918","-0.061698407","-0.08752689","0.04087552","-0.042035554","-0.003386317","0.012005972","-0.026502151","-0.02720621","0.0048837326","-0.1100224","-0.10286708","0.06463912","-0.025596472","0.06728557","0.02012708","-0.01556215","-0.024497433","-0.03309269","0.013337271","0.06932596","0.012709612","0.025913278","-0.007897064","-0.08704038","-0.057842858","0.032512683","-0.06977103","-0.043514434","0.059731033","0.03347755","0.01543792","0.08394069","-0.021402953","-0.03896606","0.050588183","0.0036487407","-0.020821739","-0.035953045","0.016181942","0.007052793","-0.00785336","-0.011720348","0.034082234","-0.0077661276","-0.011586472","0.09893011","0.019541847","0.010949608","-0.06710141","0.0071825883","-0.030849928","-0.041007336","0.036407545","-0.07158624","0.058009338","0.058699336","-5.6056557E-8","-0.05905549","-0.031588662","0.005551802","0.0048667365","-0.050193977","-0.075274065","0.04966176","-0.08458867","-0.025619779","0.0026396678","-0.058879603","-0.082132705","-0.0057570226","-0.015745219","-0.042901102","0.010590799","-0.10530106","0.011308139","0.050378006","0.07352598","0.052160233","-0.020813752","0.0042276434","-0.10429217","-0.038869623","-0.055929553","0.034076255","-0.06709004","-0.029734157","-0.041110795","-0.019485537","0.03497914","-0.022507705","0.008518752","-0.07941422","0.03958758","-0.012433267","0.106646195","-0.0814557","0.022524351","0.047236092","0.06900115","0.026527341","-0.06536008","-0.0037264694","0.008095444","0.027910281","-0.017331805","0.047949627","0.012651708","-0.022749566","0.04117321","0.0259421","0.013375685","0.04118237","-0.005379291","0.06933349","-0.034223236","0.074692056","0.04640383","-0.024891729","0.044823013","0.016835788","-0.040126417"]</t>
+  </si>
+  <si>
+    <t>NK-3257FP6kjdhRwBZFPX5u7R</t>
+  </si>
+  <si>
+    <t>GUSTAVO ADOLFO URQUIJO JR.</t>
+  </si>
+  <si>
+    <t>Entity Name: GUSTAVO ADOLFO URQUIJO JR. | Type: Person | Jurisdiction: us | Risk Context: 1128Aa</t>
+  </si>
+  <si>
+    <t>["-0.039830025","0.07138804","-0.016090808","-0.009813806","-0.07694684","0.04200429","0.041908268","0.051574327","0.010035936","-0.022304066","0.039069783","-0.086162426","-0.007274722","-0.03643922","-0.043033734","0.0776921","0.028053746","0.068335876","-0.008363339","-0.07308041","0.06420505","-0.009155642","5.0220868E-5","-0.086826645","0.013649886","-0.0375412","-0.0019841513","0.04836834","0.05460204","-0.07684128","0.023697902","0.027404496","0.015196255","0.025435673","0.050914314","0.03047127","-0.034489095","-0.013497594","0.008431749","0.0076839332","0.034718238","-0.05337062","0.051391963","0.012521273","-0.055818215","-0.06697837","-0.011217491","0.019592077","0.02232392","0.023948893","-0.095198676","-0.051742718","0.048217416","0.05768311","0.03569398","-0.030190006","-0.008583724","0.021814406","-0.01919586","0.01852724","0.026198339","0.013564388","-0.011105827","0.01576336","-0.061447866","-0.05254046","0.022567922","0.045417745","0.02380638","-0.07591178","0.08877579","-0.048086125","-0.053514965","0.030493734","-9.849175E-4","-0.041779045","-0.0082934955","0.102512404","0.034958664","-0.083860226","0.025092715","-0.015948014","0.033011265","-0.06870317","-0.02796041","0.036499713","0.010108682","-0.032353625","0.030868018","0.03801369","-0.06575867","-0.03689687","0.14179733","-0.015203421","-0.018169258","0.023952896","0.029246876","0.009413255","-0.062458728","0.052529436","0.026304714","0.01936335","-0.0069283103","0.043568954","-0.025942096","0.011201861","-0.040962845","0.06618432","-0.0065964595","0.034313608","-0.058022123","0.043290015","-0.06468284","-0.0041188286","-0.0062869205","-0.062698655","-0.052437805","0.009752205","-0.024689205","-0.08970236","0.038236283","-0.037509076","-0.13017417","-0.02760245","-0.07210412","0.0034699356","0.05079465","-2.1985585E-34","0.10890761","0.026378328","0.0027427527","0.05694599","-0.07165807","0.062499933","0.0017234974","0.04178086","-0.10419901","0.013572177","-0.09042358","0.029971404","-0.04366261","-0.0012946523","-0.040371735","0.03590334","-0.0190531","0.082513615","0.035015315","-0.023843441","0.05313087","-0.04499595","-0.09114672","0.018107835","0.0302265","0.06892553","0.039082605","-0.13024996","-0.029083762","0.05849643","-0.0030824202","0.0487054","0.018098107","-0.010525376","0.08752516","0.016344773","-6.0150126E-4","-0.03682896","-0.08810226","-0.03440703","0.041437447","0.057706706","-0.014915233","0.0619604","0.022395404","-0.042333543","0.08338196","-0.044538394","0.12884347","0.047991738","-0.08949298","0.006829901","-0.013305748","0.0017821463","0.007599856","0.0035408477","-0.020255629","0.12537764","-0.034530267","-0.078456715","-0.059629805","0.08925679","-0.0860866","0.036558814","-6.429641E-4","-0.1250767","0.025311302","-0.02648974","0.032252032","-0.05219931","0.024546994","0.023158018","-0.011194005","-0.010390749","-0.036587074","-0.05162574","-0.034281213","0.019778952","-0.02170499","0.041098583","-0.077585205","-0.012980628","0.01855555","0.049477197","-0.007610624","0.08179257","0.049641665","-0.010304481","-0.102592975","0.03883874","0.008585507","0.06811447","-0.006122367","0.05636343","-0.024637403","-2.2752751E-33","-0.009198391","-0.09557976","0.06286882","-0.047993727","0.09559089","-0.08063749","0.021968495","0.10765751","-0.043400474","-0.040770926","-0.01700049","-0.047200434","0.082066394","-0.018840164","0.00627006","0.047982305","-0.051620964","-0.05136774","-0.08574995","0.046663508","-0.023297131","-0.019345911","0.0073588206","0.059909202","-0.051577196","-0.045172554","0.10075496","-0.04149627","-0.06272454","-0.027958298","-0.00593164","0.00986436","-0.11663636","0.05069999","-0.06749145","-0.067154475","0.011699383","0.004983053","-0.030643484","-0.0044366745","0.013225653","0.114375524","-0.025856951","0.0023596182","0.013356079","-0.017768439","-0.016979432","-0.07642222","0.009559613","-0.014014669","0.016809724","0.034485668","-0.007159164","0.013811389","0.046025276","-0.036901746","-0.0029025816","-0.04761698","-0.028381677","0.06688675","-0.02086834","0.11612474","5.245805E-4","0.1581356","0.054462466","0.0015616894","-0.07433083","1.3094788E-4","-0.046923835","-0.08035201","0.1161658","-0.08765181","-0.020789564","-0.02735534","0.053025197","-0.061581664","-0.014861587","0.008873","-0.0154987825","-0.011750694","0.08502743","0.035777744","-0.034695055","0.028843388","0.015777016","0.002527442","0.03903511","-0.008867445","0.060398933","0.052914947","-0.0026266386","-0.030893182","-0.10579059","-0.04448388","-0.010940024","-2.8077709E-8","-0.019511072","0.024960125","-1.8848843E-4","0.030686298","0.037377458","0.013328297","-0.06318343","0.015771406","-0.016523024","0.044802684","0.02241103","0.048419688","-0.06499435","0.022303108","0.07039272","-0.12888147","-0.00903074","0.08200785","0.0092450995","0.07225149","-0.01008399","0.008485554","0.009170799","-0.06058233","0.067984074","0.005736978","-0.020624675","-0.07235617","0.0554875","-0.030282307","-0.031834234","0.10726892","-0.04546873","0.01907288","-0.03466007","0.06222728","0.04923949","-0.03688155","-0.042352423","-0.037877165","0.06837315","0.03026107","0.023173857","0.016950324","0.039017655","0.017490137","0.029247498","-0.05130795","0.07242137","-0.036101926","-0.066489376","-0.11786517","0.033806622","4.9208733E-4","-0.07043455","-0.04755162","0.0090951035","0.0097698625","0.011999861","-0.048325375","0.087727115","-0.064752944","-0.033164605","0.033045538"]</t>
+  </si>
+  <si>
+    <t>NK-355Sbv9ZUXJLakBMDPJHk7</t>
+  </si>
+  <si>
+    <t>Mr Murtaza Ali Lakhani</t>
+  </si>
+  <si>
+    <t>Entity Name: Mr Murtaza Ali Lakhani | Type: Person | Jurisdiction: gb</t>
+  </si>
+  <si>
+    <t>["-0.031992234","0.058147777","-0.050878517","-0.032989442","-0.07568704","-0.01889442","0.065759026","-0.06918861","0.010816909","-0.019923918","0.062254023","-0.10898995","-0.004021179","-0.019316848","-0.034792773","0.13734989","0.054895744","0.06352203","-0.03308831","-0.05953108","0.04110708","-0.0074876817","0.042408258","0.026181417","-0.09451053","-0.07272542","-0.021731803","0.02206638","0.025284419","-0.030546604","0.04592525","0.07897983","0.050016724","0.0434172","0.05600993","0.02562626","-0.06323924","0.016427","0.017567884","-0.027200809","0.077990495","-0.03813561","0.07944807","-0.02039508","0.010053389","-0.044882886","0.018315393","0.0056333207","-0.030645866","0.04445137","-0.087951995","-0.027004352","-0.0053569577","0.02976292","0.0044929325","-0.056892786","-0.024939733","0.03903899","-0.06588611","-0.018357033","-0.03609351","0.092450984","-0.0196824","2.7086522E-4","-0.007529644","-0.04347929","0.021482518","-0.050264575","0.03223437","-0.0707241","0.10566665","-0.045740273","-0.06792129","-0.015183287","-0.090154886","-0.04325408","0.039264064","0.07771796","-0.040323988","0.0052221618","-0.018405357","-0.011372265","0.060036026","-0.06019264","-0.046185013","-0.024642467","-0.033570014","0.007019399","-0.038980894","-0.020694252","0.04163885","-0.007193817","0.118691325","0.009628549","0.022207903","0.004385798","0.03767851","-0.023682991","-0.045393854","0.07424334","-0.029636927","0.019091856","-0.0074071204","0.048935484","-0.045615394","-0.020152636","-0.040440045","0.023945639","-0.035620365","-0.025258936","-0.022107352","0.06751262","-0.072930634","0.03517371","0.03881375","-0.006064472","-0.079480246","0.0647948","0.057101466","-0.12200285","-0.006216281","0.009900702","-0.1467833","-0.06507084","-0.07216328","-0.014161659","-0.026974967","-1.2819249E-34","0.0893141","-0.006768343","0.044833977","0.062002003","-0.09887689","0.010144439","-0.012173752","0.01943705","-0.065404624","0.028844902","0.009280965","0.0017347304","0.041146286","-0.087435886","-0.020960305","0.029427936","-0.009281478","0.010361569","0.0037259203","0.04537911","0.010407168","0.019237814","-0.03669507","-0.02219641","0.010311898","0.05478325","0.058113337","-0.09313334","0.03708506","0.06347334","0.0072139883","0.023834217","-0.008776688","0.0148888845","0.038343772","0.047817826","-0.047482956","-0.041437443","-0.02954196","-0.019105045","-0.014563897","0.00846365","-0.041502476","0.03168588","-0.043872483","0.0045080646","0.034224648","-0.03667842","0.11554372","0.038619317","-0.010219132","-0.013821601","-0.071292594","0.0019242902","-0.02656181","-0.022795621","-0.00888621","0.09318261","0.012976656","-0.03139337","0.03491306","-0.08029066","-0.06513606","0.06716473","-0.0068565756","-0.13766353","-0.0027204168","-0.04234971","0.03861632","-0.07887105","0.05763059","0.047288284","0.044236254","0.0462598","-0.023257945","-0.025613807","-0.0035693944","-4.3980536E-4","-0.114859045","0.15396576","-0.06653457","0.0778172","-0.017619472","0.017652158","-0.012969763","0.044733416","0.025737822","-0.012433575","-0.004941749","0.037400223","-0.14386667","-0.016510498","-0.0053451895","0.05895505","0.009494362","-2.2120737E-33","-0.0077530155","-0.115586676","0.011993729","-0.022490237","0.03125665","-0.08192267","0.035163224","0.0630966","-0.0158929","0.023628457","-0.048406582","-0.021798331","0.029908236","5.0777046E-4","0.043610442","0.08116843","0.0033358308","-0.017422903","-0.08867182","0.0731708","-1.7422426E-4","0.0030795191","5.618265E-4","0.007440811","-0.001822491","0.013408367","0.034657624","-0.06988523","-0.03626095","-0.040957052","-0.085466355","-0.03570459","-0.15610534","0.07090892","-0.10897302","-0.09358515","0.039900906","0.0033939527","-0.003959862","0.06421908","-0.05043971","0.12993853","0.030246519","0.06965964","0.03307985","-0.0069799563","-0.021293147","-0.03228755","0.04174161","-0.05594633","0.008565363","0.039590817","-0.0013203499","-0.07336333","0.08547319","0.006101484","-0.02616984","-0.0681381","0.015569875","-0.028147846","-0.008923533","0.08107195","-0.059612762","0.08874472","-0.019649584","0.07306246","0.03873581","-0.018850986","0.02089383","-0.06882978","0.049534813","-0.14750648","-0.10075353","-0.02827223","0.011861617","0.023580085","-0.06245528","0.023137728","-0.0015254619","-0.008757673","0.13077371","0.011770431","-0.007868521","0.01820213","0.045899577","8.5275364E-4","0.030260079","0.011531129","0.109050766","-0.007059517","-0.012186526","0.0054395595","-0.03225661","-0.036156606","-0.02267713","-2.5292076E-8","-0.050758064","-0.03035661","-0.055388495","0.054451663","-0.023120755","0.038352657","-0.022387393","0.032513022","0.013976591","0.04544646","-0.040153507","-0.021693204","-0.036869626","-4.6664976E-5","0.020685636","-0.09832534","0.022944285","-0.009081167","0.056538314","0.041796356","0.01803038","0.012754854","0.02770764","-0.022239402","-0.03029965","0.026474696","-0.043758716","-0.053529993","0.041920856","0.024282604","0.024794575","0.115120955","2.9333262E-4","0.022404732","0.0021393604","0.012709319","0.11247113","8.912888E-4","-0.012854026","-0.026723806","0.041894127","0.007526052","0.05052952","0.0072376938","0.068153895","0.016874896","0.012650661","-0.043144643","0.058495373","-0.04889531","-0.023864422","-0.092799746","0.040532164","0.08090663","-0.050833426","-0.022220545","0.06658434","0.00603272","-0.008882817","-0.076329194","0.0836087","-0.021887455","-0.025067253","-0.023742389"]</t>
+  </si>
+  <si>
+    <t>NK-379HDReSyxwLoqHZrJYVNK</t>
+  </si>
+  <si>
+    <t>Reconnaissance General Bureau</t>
+  </si>
+  <si>
+    <t>. Il s'occupe du commerce d'armes conventionnelles et contrôle la Green Pine Associated Corporation, la société de fabrication d'armes conventionnelles du pays The Reconnaissance General Bureau is the DPRK's premiere intelligence organization, created in early 2009 by the merger of existing intelligence organizations from the Korean Workers' Party, the Operations Department and Office 35, and the Reconnaissance Bureau of the Korean People's Army.</t>
+  </si>
+  <si>
+    <t>["-0.16946751","-0.0041081705","-0.076908395","-0.02751654","-0.021181142","-0.09477799","0.05815689","0.048350606","0.051622193","0.052393798","0.0016227424","0.035373226","0.0416701","-0.011501488","-0.063052714","-0.007983656","-0.009750603","0.010693435","0.013594142","-0.03544461","-0.047601175","-0.015770454","0.047057487","-0.011696916","-0.0069080796","-0.023972463","0.013817995","-0.009030645","0.029357059","-0.06662493","0.041934744","0.026491906","0.08898518","0.046701454","0.09750321","0.0786384","0.045746807","-0.016115313","0.030660601","0.051023852","-0.026984638","-0.0042130607","0.052119713","-0.018571747","-0.024847139","0.11051364","-0.006395518","0.059818834","-0.044439003","0.055725414","0.061950803","-0.08830784","-0.03554072","0.046959616","0.034215927","0.032072835","-0.031669457","-0.088331945","-0.007310349","-0.03283506","0.0025387593","0.026370136","0.036907688","0.003310608","0.026494227","0.059035737","0.023676613","-4.514623E-5","0.015314551","-0.17125271","0.02088075","-0.03961958","-0.017078655","0.08201021","-0.012478797","0.0343197","0.008202653","0.047023978","0.05220821","-0.19064878","0.068904236","0.07711472","-0.018037556","0.09004623","-0.06730397","0.014142949","-0.047526844","0.0011155988","0.099893056","-0.047017217","0.027872149","-0.026760405","-0.056512207","-0.04263383","-0.06899576","0.017501002","-0.008954231","0.015812501","-0.03549749","0.10615381","0.06851104","-0.014755628","-0.015416487","-0.044684805","-0.12042026","-0.050812706","0.08271847","-0.02951508","0.0077933297","0.0050187856","-0.0020536226","0.031116592","-0.022009216","-0.012827166","-0.005265749","-0.0100834025","-0.095114","0.015677597","0.051189747","-0.08415016","0.0075221364","0.019535976","-0.055664446","0.002212225","0.034491487","0.06918987","-0.015274939","5.6778457E-34","0.00662171","0.08518236","0.018652705","-0.016204985","-0.11053404","-0.04391814","0.005054948","-0.008332575","-0.062793314","0.030196888","-0.090172455","0.03652672","-0.010080873","-0.026781613","-0.01657056","0.024242824","0.0012644093","0.05778226","0.0071349405","0.042322066","-0.009040849","0.0050936956","-0.0044455417","0.027571552","0.13715726","0.118518","-0.10356523","0.03864661","0.056148916","0.024685923","0.005133841","-0.016153602","0.023448594","0.115920655","-0.0076258397","-0.059682764","-0.103525355","-0.025736978","0.04288722","0.058803197","0.050299406","0.012191645","-0.082143486","0.043010816","0.05257054","0.06121904","-0.014557649","-3.9497658E-4","0.034532543","-0.06364428","-0.00896525","-0.026020834","-0.042495705","-0.05519116","0.017273178","-0.0055432376","-0.081802174","-0.047041517","0.051136196","-0.015515075","-0.008352141","0.08038293","-0.09385489","0.12894663","0.05256534","-0.018534347","-0.046390094","0.035554413","0.04978878","-0.009096045","0.0040169824","-0.03187837","0.024089232","0.034370795","-0.06373521","-0.01941608","0.036896516","0.05834551","-0.021091787","0.029704774","-0.091648385","0.02531603","0.004639851","-0.007537138","-7.6763955E-4","0.024205152","0.036420953","-0.044339467","-0.033042207","0.0043773414","-0.14619498","-0.024836203","-0.03539317","0.033288658","0.02117269","-2.4749273E-33","-0.02027747","0.035040084","-0.051769327","-0.046176217","-0.03451901","-0.001760762","0.004296882","-0.051652692","-0.028608816","0.052370448","0.036805075","-0.0039547924","-0.07340456","-0.0074371635","0.031191101","-0.012792965","0.040148918","8.936557E-4","1.502816E-4","0.019872328","0.04260857","0.006004095","0.06451067","-0.056776248","0.045442257","0.021710835","0.08195215","0.025061375","-0.008692854","0.07987514","0.076081865","-0.037689246","-0.022725442","0.065629765","-0.009207476","-0.04887893","-0.053012684","-0.04254979","-0.054451738","-0.061620116","-0.022640726","0.005505388","-0.033042207","0.025367485","-0.039313637","-0.0358736","-0.040069856","-0.02447288","-0.005477564","-0.1301298","-0.02604984","4.838219E-4","0.019746792","-0.086297564","-0.049723577","0.07261285","0.028093195","0.0690712","0.040165212","-0.012777187","0.020199656","0.027905162","-7.197579E-4","0.02194662","-0.023665242","-0.009563892","0.09753679","0.058569953","0.025304182","0.0010726519","0.10785481","-0.016830426","-0.052417427","-0.045958877","-0.06538721","0.045032516","-0.03439335","0.043942533","-0.038128916","0.008408768","-0.05067304","-0.03466816","-0.005928484","0.052870646","-0.051166177","0.055952","-0.02151542","0.061011817","-0.0077659246","0.0066126296","-0.042203028","-0.058672763","0.008612929","0.11208542","-0.020809932","-4.5925788E-8","-0.0029725845","0.07701434","-0.033832353","0.03156069","0.040668294","-0.12343024","-0.084873974","0.011134751","-0.0074108355","-0.010641711","0.059022266","-0.050110716","-0.020233432","-0.03763677","0.019294478","-0.04805491","7.025179E-4","4.693796E-5","-0.06501056","-0.003983959","0.08052456","-0.05894416","-0.01327648","-0.09332506","-0.06529818","-0.013473747","0.009236255","-0.062163204","-8.220949E-4","0.051068626","0.031372115","0.06511734","-0.021158345","0.029113576","0.1342868","0.010272616","-0.027435763","-0.031232107","0.04890907","-0.0048653693","-0.041850198","0.100722015","0.025162004","0.030361414","-0.036113434","-0.008425381","-0.006181756","-0.07648095","0.04920819","-0.010779457","-0.010967129","-0.0020844867","-0.023318604","0.052634735","0.009699572","-7.8258617E-4","0.039404","-0.0375787","-0.14715098","-0.026238235","-0.009395194","-0.048520386","0.0053270995","-0.0067852493"]</t>
+  </si>
+  <si>
+    <t>NK-399YAWJ7K6kHhH97eDpyZQ</t>
+  </si>
+  <si>
+    <t>SHENG LU</t>
+  </si>
+  <si>
+    <t>Entity Name: SHENG LU | Type: Vessel | Jurisdiction: pa | Risk Context: Jumped detention</t>
+  </si>
+  <si>
+    <t>["-0.028407864","0.051119518","0.012672521","0.013960984","0.041086514","0.0043548937","0.05134203","0.0021237826","0.015192862","-0.0074805785","0.14675517","-0.06594053","-0.019892894","-0.0077457805","-0.060195","-0.014414693","0.017988661","0.010385728","-0.03659757","0.01521047","0.019972628","-0.020651758","-0.034301125","-0.03726847","-0.04842976","0.005287127","-0.014483902","0.0061816284","0.0895466","-0.07290846","-0.015948616","0.1248718","-0.08193944","0.03678609","0.061928723","0.05058525","-0.010156632","-0.027883671","0.033203162","-0.015312758","0.076272085","-0.038452033","0.07733678","9.892109E-4","0.03391216","0.04549263","-0.05040953","-0.011346516","-0.074992426","-0.007674189","-0.026251128","-0.040339787","0.024728216","0.11136763","-0.032458466","0.023402749","-0.004217696","0.026949441","-0.0105992565","-0.062840946","-0.021022184","0.10384487","0.015563293","0.030547528","-0.05695296","0.015307059","-0.034689166","0.0061130384","0.016045157","0.021884186","0.021489225","-4.503447E-4","-0.06374935","0.023244713","-0.013984436","0.009674739","-0.02269084","0.028065784","0.026855435","-0.078503005","0.06114119","-0.00399018","-0.016964488","-0.049333576","-0.027024906","0.046297546","0.025139","-0.01664663","0.010538038","-0.027607622","0.02095312","-0.027256759","0.13485567","-0.012489502","0.0024957312","0.014855956","0.02022063","0.021351954","-0.041712884","0.02215826","0.048137557","0.059987057","0.027876105","0.025629576","-0.058618","-0.080344096","0.02782258","-0.07733729","0.021664463","-0.009669911","-0.057979718","0.119622946","0.0016356657","-0.1093096","-0.035918314","0.022934226","-0.13305481","-0.06036566","0.061076704","-0.09516662","0.02302779","-0.031144273","-0.035137586","-0.029139245","-0.08164995","-0.008338125","-0.008625031","-3.224966E-33","0.04626019","-0.042909246","-0.047762156","0.039795514","0.01719453","-0.043784153","-0.030598365","-0.07466377","-0.060869884","0.035368","-0.07606935","-0.04353694","-0.012188119","-0.07621778","0.0026587644","0.031599008","0.0026978243","0.037133638","-0.021062812","0.011577261","0.07486354","-0.025223749","-0.03742148","0.008694876","0.029782707","0.022622366","-0.054470334","-0.10045629","0.022393938","0.061782487","-0.01754518","0.053693067","0.092322685","0.018871186","0.008056619","0.07503791","0.033060193","-0.06951154","-0.017185992","-0.021749027","-0.030237574","-0.008913757","0.052841455","0.09912656","-0.0025974012","-0.060002945","-0.032547064","-0.09234996","0.0065586497","0.022842033","-0.004079909","-0.0364995","-0.012315512","-0.027312154","0.0071661538","0.0466958","-0.02108021","0.10598044","-0.03834348","0.054163672","0.03872549","0.029362515","-0.06855778","0.043243226","0.044755362","-0.06655172","-0.0062266383","-0.00732292","4.6452877E-4","-0.07588945","-0.03718439","0.020632561","0.014634203","0.034921758","-0.008552723","-0.013472081","-0.0015873504","-0.017116483","-0.0722414","-0.0010472107","-0.10618106","-0.08280477","-0.017545868","0.08392878","-0.001765588","-0.023635112","0.032974396","-0.06672287","-0.031642154","-0.012856731","-0.039576","-0.009153073","0.033046592","0.026739568","0.0059356694","1.2228114E-33","0.010060882","-6.908428E-4","-0.073909536","-0.021119691","0.04712507","-0.048088606","0.08303579","0.0323812","-1.1184754E-4","-0.056265473","-0.18065715","-0.008560906","0.040577363","0.088070124","0.07514356","0.0548415","0.02842043","0.03802144","-0.03443402","0.1390833","0.022519656","-0.0634779","-0.0571301","0.098628394","0.0032557365","0.102826424","0.06976141","-0.033533163","-0.08029843","-0.068668075","-0.049167354","-0.035050195","-0.007215819","0.121901356","-0.13977166","-0.096779555","0.069772355","-0.07127945","-0.054221552","-0.06291479","-0.022413526","0.05215213","-0.030323705","0.038768936","-0.016042762","0.017148832","0.014422913","0.024061993","0.046619132","-0.016257081","-0.074671574","0.028613817","-0.027397307","0.042369556","0.031161401","-0.022432541","0.028457772","-0.054644555","-0.036950447","-0.0036772843","0.01988871","0.09022263","-0.076901495","0.11226875","0.060973752","0.013899509","-0.08544828","-0.08159851","-0.08725442","-0.07557581","0.023947163","-0.010138842","-0.0813224","-0.0097554065","0.021880371","-0.03269166","-0.011130713","0.006413508","-0.007505273","-0.020644058","0.053840693","-0.05939114","-0.022567317","0.022518575","-0.020543259","0.03553618","0.037390783","-0.032158926","0.05517218","-0.08802829","-0.037746117","-0.03578793","-0.0912145","0.0056516146","-0.0067912997","-2.290617E-8","-0.028840033","0.07631311","-0.02303586","0.060194645","0.017155064","-0.02223014","0.015774185","0.014082097","0.0014725766","-0.013465276","-0.040449996","0.018657895","-0.020756662","-0.041894782","0.038552374","-0.050986975","-0.05629996","0.04454956","-0.010597957","0.043391548","-0.03304655","0.04551084","0.052363317","-0.04424401","-0.043904763","0.0010428271","0.07241055","0.0085212","0.110775426","-0.042652134","-0.017743563","0.05448934","7.764764E-4","0.06675959","-0.017764999","0.106123514","0.019846326","0.0092555685","0.05713267","0.011082205","0.019105611","0.046043586","0.03500207","-3.145989E-4","0.08286968","0.067212574","-0.008770087","0.025543358","0.1533523","-0.0821425","-0.07931091","-0.074856296","-5.3812494E-4","0.089201406","0.010562894","0.012304483","0.03318262","0.07276993","-0.001799678","-0.04820018","0.04650736","-0.008486729","0.004659658","0.05736635"]</t>
+  </si>
+  <si>
+    <t>NK-3EjBtKgVicLeUg4fMZYC9S</t>
+  </si>
+  <si>
+    <t>Ajay Gupta</t>
+  </si>
+  <si>
+    <t>Entity Name: Ajay Gupta | Type: Person | Jurisdiction: ae | Risk Context: (also AJAY KUMAR GUPTA, AJAY KUMAR GUPTA) (also AJAY GUPTA) Associated with: Atul Gupta (brother/business partner); Rajesh Kumar Gupta (brother/business partner); Salim Essa (business partner). Associated with: Atul Gupta (brother/business partner); Rajesh Kumar Gupta (brother/business partner); Salim Essa (business partner). The Director Disqualification Sanction was imposed on 09/04/2025. Disqualified</t>
+  </si>
+  <si>
+    <t>["-0.054475386","0.010151836","-0.07164446","-0.0053540547","0.01585011","0.017514417","0.070691675","-0.070771106","0.047285944","-0.055409197","0.069498464","-3.2957987E-4","0.10766587","0.029507132","-0.028213054","-0.011067763","-0.0043385667","0.07666801","-0.04402348","-0.14184892","0.022585653","0.03025103","-0.031021597","-0.063420765","-0.009697728","-0.0698632","-0.039056797","-0.09779715","-0.0041893446","-0.03670886","0.0155875385","0.01580243","-0.028324962","0.015321874","-0.0108980145","0.011664623","-0.11024286","0.008869119","-0.021345397","-0.10424411","0.025529373","-3.505643E-4","0.02442532","-0.062719285","0.0049495045","-0.06816265","-0.0027192018","-0.0575386","-0.046339564","0.020776797","-0.0763815","-0.010756376","-0.0040142415","-0.0075615216","-0.023610005","-0.06676396","-0.032827087","-0.005784167","0.012884517","0.06390099","0.053921565","0.029947989","-0.028679436","0.03551212","-0.03190267","-0.03377816","-0.024927244","-0.08670734","-0.0151060065","0.053309955","0.0755079","-0.07042924","-0.033218674","0.036946986","-0.026529903","0.04980885","0.034170646","0.09760392","0.060255982","-0.059992604","-0.038770948","-0.020771148","-0.0095022265","0.0017933614","-0.07698411","-0.022073256","-0.020292059","-0.03714517","0.044819027","0.049194846","0.048512794","-0.0011352132","0.18345894","0.052263774","0.0018117797","-0.038467165","-0.027508734","0.0049894224","-0.029789345","0.04480469","-0.103716984","0.04161171","-0.084391646","0.041737325","-0.07493311","-0.008494662","0.03518932","0.006482937","-0.05603056","-0.011446316","-0.0036118743","0.09273867","-2.3297098E-4","-0.07995511","0.034259498","0.010913474","-0.0024366458","0.06852234","0.0103328265","-0.030635195","-0.04787235","0.09791894","-0.022720167","-0.075601034","-0.06718849","-0.029019594","-0.059415296","1.5755985E-33","0.061022155","0.010844989","0.068261266","-0.025542557","-0.014266758","0.012990797","-0.008791012","0.019393036","-0.015734076","0.054074552","-0.012475253","-0.056064148","0.035556648","-0.068557106","-0.0093855485","0.030017333","0.13498457","0.0059338855","0.025635887","-0.06599249","0.05871194","0.06692369","5.1728636E-4","0.028825056","-0.015135248","0.017724242","0.019477656","-0.03963093","0.020089103","0.07191644","0.023399478","0.015568049","-0.00529284","0.06455019","0.05163006","0.008191998","-0.028608868","-0.030322898","0.008944264","0.0012517333","-0.023953341","0.05119264","-0.0036209452","5.0054706E-4","-0.06729228","0.054470103","0.07153295","-9.359753E-4","-0.0024469164","0.08384591","0.00173062","-0.003770325","0.05298148","0.03475068","-0.030409956","0.04402476","0.008068789","0.013450517","-0.018309336","0.04291601","0.021695605","0.0044538556","-0.13523842","0.035536475","-0.08284185","-0.046343558","0.05391695","-0.06180538","-0.05327881","-0.081547216","-0.025094163","0.060614463","-0.028694503","0.04201308","-0.07758201","-0.030385943","0.0038895805","0.02877057","-0.028548924","0.029271206","-0.07171861","0.09361271","0.08186957","-0.09246611","-0.034349997","0.059547953","-0.049855303","0.0057955617","0.019414824","0.07732664","0.045323793","0.03770222","0.0485656","0.09688985","0.052122016","-4.409416E-33","-0.06475848","-0.04130243","-0.011630804","-0.108496465","0.05703239","-0.059930522","0.040071372","-0.0014569183","-0.045262713","-0.0045314566","-0.009741479","-0.007651326","0.065993704","-0.015617725","-0.052305833","0.0019119384","0.018501999","0.034165632","-0.1004514","0.032619808","0.051293146","0.09862161","0.038158126","-0.03222715","-0.032877926","0.0103046885","0.03275637","0.03882233","0.0058111423","0.035497077","-0.026834765","-0.03764754","-0.083808735","0.034333624","0.008320344","-0.12298541","-0.034313153","-0.057549298","-0.033632137","-0.019427886","0.009045542","0.122374415","-0.009292104","0.017327039","0.1077781","-0.02254501","0.077612415","-0.032850612","0.0714058","-0.105060756","-0.04542287","-0.033078633","0.028801031","0.05534241","0.070078425","-0.0062478036","0.07904363","-0.02169193","0.07674212","0.04670854","0.054382168","0.010481501","0.08681755","0.0749976","0.034932557","0.028187538","-0.014611911","0.025066664","0.040128335","-0.10412898","0.04371063","-0.093789145","-0.07900791","-0.0030500325","-0.009560778","0.01708873","-0.090251975","0.0017755165","-0.06474129","0.009351253","0.08172721","0.03317425","0.010001849","0.034091964","0.07730393","0.02602446","0.04920162","-0.031631086","0.13252488","-0.016858567","-0.04760597","-0.07757163","0.03827502","0.07689162","0.009014238","-4.8140507E-8","-0.083395995","0.01840735","-0.03430637","-0.027595114","0.0072949748","-0.013245977","-0.06008703","-0.03346577","0.024924533","-0.0037592174","-0.0067986897","-0.0013909925","-0.07121717","0.02306664","-0.025182495","-0.0513484","-0.015846746","0.02956136","0.048991423","-7.8159757E-4","-0.04223598","-0.044595703","-4.3167736E-4","0.038331993","0.013355271","-0.10109089","-0.024334647","0.0066900114","0.048891824","-0.0053643193","-0.0913448","0.017602589","-0.0047960123","-0.0353938","-0.06329758","0.03753384","0.0021170215","-0.004238092","-0.0022235757","0.10568143","-0.01708685","0.021712909","0.07346792","0.050634157","0.036008295","0.047723845","-0.014202002","-0.036137454","-0.05023763","-0.09279271","-0.08522318","-0.030182786","-0.053146176","0.021453006","0.031508725","-0.09352208","-0.011968734","0.010866951","-0.060314093","-0.023602663","0.069367446","-0.0855631","-0.009521946","-0.03619543"]</t>
+  </si>
+  <si>
+    <t>NK-3KRoVfPHitLoVonaD9y6bE</t>
+  </si>
+  <si>
+    <t>ASHRAF SEED AHMED HUSSEIN</t>
+  </si>
+  <si>
+    <t>Entity Name: ASHRAF SEED AHMED HUSSEIN | Type: Person | Jurisdiction: gb | Risk Context: The Director Disqualification Sanction was imposed on 09/04/2025. Disqualified (also ASHRAF SEED AHMED AL-CARDINAL) (also ASHIRAF SEEDAHMED, ASHRAF SAID AHMED HUSSEIN, ASHARAF SEED AHMED, ASHRAFF SEED AHMED, ASHRAF SEED AHMED HUSSEIN, ASHRAF SEEDAHMED HUSSEIN ALI, ASHIRAF SEEDAHMED, ASHRAF SAID AHMED HUSSEIN, ASHARAF SEED AHMED, ASHRAFF SEED AHMED, ASHRAF SEED AHMED HUSSEIN, ASHRAF SEEDAHMED HUSSEIN ALI)</t>
+  </si>
+  <si>
+    <t>["-0.021485006","0.10796916","-0.065923065","0.021494437","0.016725024","0.06491687","0.041253835","-0.09008317","0.035896804","-0.019745057","0.018266484","-0.011794867","0.05624844","-0.039898045","-0.06903848","0.032183636","-0.016385242","0.058837093","-0.042251732","-0.07031981","0.022349808","0.016581971","0.030068133","-0.03190569","-0.021173138","-0.057914164","-0.09857739","0.024641888","0.024856836","-0.07476837","0.011495384","0.06544174","0.037292425","-0.011472181","-0.030798199","0.0055806246","-0.11662218","0.01720273","-0.011083305","-0.036039166","0.1618422","-0.024757518","-0.014536151","0.027780877","-0.034972318","-0.05850731","-0.025174635","-0.026987221","-0.030181764","0.09522657","-0.09241906","-0.07638675","0.007992884","-0.026439583","0.02238337","-0.083226174","-0.009907423","0.0048907273","0.021902079","-0.031054726","0.08579557","0.01563404","-0.080905095","-0.024194423","0.02199886","-0.0645997","0.04318377","-0.05264379","0.065755285","-0.025537323","0.1127092","2.823051E-4","-0.0065887053","0.046127684","-0.047710024","0.11612337","0.010307987","0.12560873","0.07523882","-0.08777272","-0.03679891","-0.10147046","0.0109330155","-0.08168967","-0.025606949","0.046478733","-0.013442592","-0.011588658","0.019273186","0.0039947964","-0.022200098","-0.01925112","0.21675856","0.049853668","-0.005997768","-0.033624623","0.03461206","0.013943014","-0.14367095","0.07124138","-0.011511552","0.05574356","-0.087238036","-0.024328215","-0.03210103","-0.075877756","-0.058200933","-0.086917825","-0.059704266","0.0031591842","0.017711988","0.045135282","0.03607854","0.0040706005","0.018057462","0.050002214","-0.039193","-0.0019120638","-0.05387995","-0.016263628","-0.040654603","-0.0033269243","0.0012950435","-0.026094394","-0.018802665","-0.03135281","-0.055722598","8.861433E-33","0.07650483","0.005981426","0.031958684","0.012555573","0.0051139626","0.022661332","-0.027208446","0.01671594","-0.089142114","0.025277112","-0.03223768","-0.002569651","0.026428727","0.0065175495","0.0044504837","0.011608084","0.024296759","0.012666361","-0.0062978035","0.0034169569","0.020934774","0.066257544","-0.06655406","0.012537065","0.017352642","0.028288653","-0.030585818","-0.11270103","0.046106126","0.07498445","0.016327647","0.019949429","0.0018468791","-0.012524737","0.08825632","-0.050056867","-0.0563909","-0.033236723","-0.06075822","0.024111416","0.046457995","-0.01375143","0.029075684","0.032630593","-0.055229373","0.018465392","0.07116235","-0.032516588","0.006838818","0.039545905","0.008412866","0.04184006","0.0680039","-0.05212602","-0.025918225","-0.04963525","0.003396049","0.0550993","-0.056829385","-0.0015115491","0.017188476","0.019334067","-0.050220385","0.08624917","-0.10114177","-0.08057347","0.0079530245","-0.027273504","0.029153733","0.024368394","0.09363749","0.018171994","-0.05637205","0.024780331","-0.059881784","-0.042374097","0.030919075","0.031170847","-0.09043596","0.02458438","-0.018273417","0.029768959","0.026938621","-0.12973784","-0.10674246","0.047324635","0.025868686","0.030497465","-5.0364825E-4","0.012955217","0.04167163","0.12419545","0.058581028","0.004118745","0.008396662","-9.744606E-33","-0.015691618","-0.040226813","0.013683937","-0.121782325","0.06298715","-0.01288424","0.07424483","0.033211056","-0.016716946","-0.019062983","0.054078847","-0.027705343","0.13700862","-0.003731063","-0.014431916","0.042641815","-0.02269672","-0.03869679","-0.060682867","0.013191742","0.007258487","0.029563956","-0.027239649","0.05420781","-0.033879675","-0.014033211","0.10848623","-0.0011875756","0.009108122","-0.030935932","-0.005039913","-0.037902918","-0.15786088","0.06437114","-0.047908433","-0.013496174","0.031634167","0.014090916","-0.07364221","0.035530042","-0.06543469","0.054131445","-0.08741902","0.0062565855","0.039784234","-0.049323328","0.081367046","0.034143604","0.041811787","-0.07668017","0.012366922","0.010298367","0.0059345504","0.08352246","0.08156576","-0.01932301","-0.042893246","-0.010709323","0.046739537","0.027791953","-0.02773099","5.400513E-4","0.04964915","-0.016412996","-0.013085437","-0.00929864","-0.024865301","0.0068395115","-0.028247787","-0.049956586","0.089086294","-0.048603375","-0.056939173","0.028277049","-0.020529358","0.07949137","-0.0018815327","0.05611721","-0.062276237","-0.0058576604","-0.013370266","0.014461404","0.011409279","0.09084549","0.037285116","0.02265633","0.08619998","-0.036366787","0.073046856","0.009918599","0.0021224555","-0.07932844","-6.217347E-4","0.0032553722","0.0109750815","-5.594136E-8","-0.01927844","0.025182161","-0.061537832","0.012338371","0.03358407","-0.010775264","-0.059478905","-0.03463077","0.0034773801","0.029442228","0.020586597","0.020750716","-0.03183382","0.013393397","0.056286752","-0.050409436","-0.041493893","0.09243239","0.023190185","-0.0035905098","-0.070252135","-0.027803862","0.039030124","0.004295698","-0.031324934","-0.022402741","-0.021491477","-0.13043591","0.058985155","0.06785767","-0.051021777","-1.6243914E-4","0.006089719","-0.09012081","-0.06820691","0.08344935","0.03877441","-0.023172308","0.016645312","0.047121212","0.034377746","0.0016654287","0.0013260666","0.024784816","-0.019770926","-0.031890977","0.020185003","-0.054173864","0.009543616","-0.116589755","-0.005337798","-0.05229949","0.027215682","0.027882447","0.051426638","-0.039237633","-0.056860816","-0.0039858688","-0.006513226","0.034992073","0.07650993","-0.059416085","-0.0017745112","-0.010296331"]</t>
+  </si>
+  <si>
+    <t>NK-3NdnQExkqYiji3bJG4FiLp</t>
+  </si>
+  <si>
+    <t>JINAO CORPORATE FZE</t>
+  </si>
+  <si>
+    <t>Entity Name: JINAO CORPORATE FZE | Type: Organization | Jurisdiction: ae | Risk Context: act: sanctions anti money laundering act 2018 | section: 3A | description_identifier: disqualification under sanctions regulation</t>
+  </si>
+  <si>
+    <t>["-0.042948656","0.06544886","-0.03795277","-3.9418705E-4","0.004578639","0.06165754","0.07495749","-0.04008826","0.028306937","-0.0014837971","0.06553637","-0.09617905","-0.03535554","0.026998797","0.016370855","-0.0147089865","0.013662135","0.03175466","-0.06513087","-0.09578334","0.106319316","-0.03283606","0.030066853","-0.044857413","-0.1293147","-0.032178145","-0.042646207","0.08415952","9.016031E-4","-0.094221406","-0.048201706","0.062396143","0.026716435","0.054615572","0.035930187","0.005088161","-0.053111","-0.036185116","0.015268858","-0.055694055","0.06780462","-0.04293809","0.005964093","-0.076274544","0.010362041","-0.061022606","-0.003733235","-0.028482351","-0.031720895","0.006899785","-0.050632764","-0.034876015","0.024509171","0.06472621","0.02267403","-0.032419804","-0.024949279","-3.3765033E-4","-0.012454102","-0.0215677","0.050915923","0.034382004","-0.0456591","0.0117713725","0.022285605","-0.035007693","-0.011709938","0.04812739","-0.014134755","-0.026510313","0.021442795","-0.07192251","-0.044627856","0.002578393","-0.05894339","-0.0021908744","0.043904886","0.070430264","0.07283952","-0.05129276","-0.01147993","-0.031379364","0.05576776","-0.07283321","-0.044066686","0.003497215","0.01376034","-0.011726067","0.08720644","0.06877979","-0.0071485215","0.0031716374","0.12944251","0.028495345","0.019954596","0.03965084","-0.004979607","-0.0013631609","-0.01026021","0.07178771","0.0427882","0.035509143","-0.0069036186","0.010322728","-0.053594943","0.023923386","0.021289025","0.044147912","-0.04814717","0.039814986","-0.0802814","0.09487214","-0.04661929","-0.0965809","-0.01868832","0.026922097","-0.052231472","0.057111762","2.2469088E-4","-0.069961324","0.055045824","0.0584459","-0.03434636","-0.04414907","-0.026184225","0.028295401","-0.11666322","1.247559E-33","0.011286315","0.028394759","-0.057593904","-0.0034795934","-0.045923073","0.031124542","-0.028276827","0.04361808","-0.11992462","0.104185924","-0.036277898","0.006030995","-0.016631996","-0.053492945","0.04733683","-2.921393E-5","0.052391518","0.034684293","0.087414876","-0.04398895","0.09632618","0.0068002394","-0.028302561","-0.028567115","0.023969883","0.045653693","-0.029726658","-0.06245959","-0.041437622","0.07412013","0.053452116","-0.0125233885","0.06293687","-0.004205525","0.04407001","-0.003141322","-0.08440365","-0.024655702","-0.082480915","-0.06112457","0.049741596","-0.008057054","-0.051039208","0.07691025","-0.015862713","0.045696687","0.015917053","-0.036428653","0.15795296","0.006411833","-0.026167464","-0.0136445435","-0.037221532","-0.041023772","-0.005406738","-0.02036355","-0.02448741","0.04630407","-0.031153625","-0.061712135","-0.01749836","0.0033329804","-0.118548036","0.07573441","-0.03060874","-0.060895156","0.013024963","0.042050596","-0.016427085","-0.0405761","2.2868677E-4","0.04387248","0.08146111","0.09484745","-0.025382707","-0.061635144","0.037271764","-0.0064230603","-0.035875246","0.03382383","-0.07712321","0.012297525","0.020640602","0.011566022","-0.039514426","0.08135011","0.03171415","-0.037566844","0.019529374","-0.012218517","-0.008882402","0.0028416093","-0.00865621","0.05223976","-0.012409202","-3.220588E-33","-0.022877077","0.020787826","-0.034010626","-0.09749232","0.057188544","-0.027803794","0.11215363","0.038996663","-0.027371181","-0.026527647","-0.044527587","-0.07436043","0.02924037","-0.0438635","0.030295437","-0.006612968","0.0063099656","-0.04072039","-0.080280155","0.061609585","0.001213572","0.018279139","0.01592559","0.057764743","-0.05855316","0.033043817","0.08973657","-0.012275312","-0.03154317","0.06616929","0.012626904","0.04934633","-0.079657465","0.1128114","-0.08475127","-0.1307167","-0.018372476","-0.03430781","-0.03537077","-0.034147505","0.0055609597","0.08195544","-0.081107944","0.04536103","-0.01339515","0.01160722","0.048234794","-0.057336625","0.056691345","-0.08452539","-0.030734053","0.006715277","-0.07542781","0.0059856223","0.034895573","0.06223783","-0.01307449","-0.07385412","0.0058959886","0.02953467","0.020641884","0.043485373","0.046591837","0.12711856","0.11094898","0.014653846","-0.014287564","0.030435694","0.05894108","-0.032032106","0.09385921","-0.036090404","-0.07243177","0.021067303","0.035422657","0.035232123","-0.052851487","0.013824195","-0.08340736","0.048479255","0.10083401","0.011141577","-0.046556134","0.048581436","0.039694753","-0.020091437","0.024180258","-0.023736192","0.070007406","-0.008849014","-0.0031002944","-0.10620688","-0.029564701","0.042912297","-0.024166772","-3.0960752E-8","-0.05813013","-0.024642715","-0.035071716","0.04068743","-0.010060941","0.021203026","-0.06814246","-0.043877494","-0.011187563","0.013723586","0.0049249334","0.024139008","-0.07700758","0.059256267","-0.040589385","-0.08154155","-0.068543166","0.122528784","0.0037227252","-0.04582925","-0.0636081","0.01108925","-0.0065339124","-0.05796253","-0.009375799","-0.039056942","-0.08012839","0.046679992","0.08280043","0.011339262","6.520182E-4","0.052514393","0.008560553","0.018493202","-0.0700017","0.06283064","0.07250173","-0.031977393","-0.066723086","0.05479389","0.0358678","-0.012117807","0.06569677","0.0506119","0.018280884","0.010733698","-0.057545956","-0.012457841","0.094332315","-0.07454628","0.004821135","-0.035698242","-0.0018459427","0.053599045","-0.03038506","-0.0064310646","-0.011545988","0.020386796","-0.07057303","-0.021523794","0.104864225","-0.1130164","0.027762003","-0.048420623"]</t>
+  </si>
+  <si>
+    <t>NK-3Svkui27JYrsp5ZEfTqioU</t>
+  </si>
+  <si>
+    <t>Sergey Nikolaevich MENSHIKOV</t>
+  </si>
+  <si>
+    <t>Entity Name: Sergey Nikolaevich MENSHIKOV | Type: Person | Jurisdiction: ru | Risk Context: Sergey Nikolaevich Menshikov is an “involved person” under the Russia (Sanctions) (EU Exit) Regulations 2019 because he has been, and is, involved in obtaining a benefit from or supporting the Government of Russia by working as a manager or equivalent of a person (other than an individual) which is carrying on business in a sector of strategic significance to the Government of Russia, namely Gazprom which is carrying on business in the energy sector. | The Director Disqualification Sanction was imposed on 09/04/2025. Member of the collegial executive body of PJSC Gazprom Member of the Board of Directors of PJSC Gazprom Neft</t>
+  </si>
+  <si>
+    <t>["-0.0685252","-0.0072033633","-0.0059886626","0.0062565673","0.0045526437","0.041956972","0.1471061","0.023874719","-0.013911934","-0.04627495","-0.007826646","0.07374807","-0.038425542","0.11804618","-0.027422588","-0.013941655","0.009152217","-0.024767138","-0.013715325","-0.05362237","0.008225064","-0.0695123","0.03621897","-0.044638235","-0.036697786","-0.02861866","4.0634675E-4","0.030975912","0.034247696","-0.0027885574","0.05948831","-0.05896432","-0.034334708","-0.0012341511","0.060367137","0.057742573","-0.057165857","-0.0622726","-0.022322576","0.049902707","0.015789587","-0.021650018","-0.12043524","0.05003097","0.0039827446","0.054580282","-0.057288136","-0.11344347","-0.06916057","9.276513E-4","-0.068932466","-0.027036868","0.0048938855","0.02560668","0.08018435","-0.058233496","0.030119281","-0.022332415","-0.030787323","-0.017332733","0.049828254","-0.054024324","-0.1107697","-0.009315322","-0.0092774555","0.024282513","0.021079306","-0.01894157","-0.051444408","0.08727256","0.05004023","-0.06881899","-0.08251416","-0.002955789","-0.055248026","-0.076825924","0.004401549","0.059801042","0.06908238","-0.029436836","0.072986044","-0.029367646","-0.038115982","0.022218864","-0.10710682","-0.021685917","-0.0068476833","-0.02177265","0.067737564","0.0943359","0.030956239","0.012336206","0.201151","-0.04177083","-0.03313561","0.0042256713","-0.03738429","0.018037388","-8.406072E-4","-0.019406784","-0.004427874","-6.5677287E-4","-0.006214789","0.01162444","-0.038912125","0.052155994","-0.03983086","0.037776504","-0.0053577474","0.053861357","-0.066956304","0.022374112","-0.014349146","-0.06758671","-0.0032209174","0.036247306","-0.03524995","0.03715602","-0.022048349","-0.003231788","0.031243963","0.034246646","0.028801478","0.011659418","0.009892776","0.0492323","-0.11104326","-1.1155849E-33","-0.011610326","-9.792784E-4","-0.07461468","0.02741935","-0.088002354","0.09184218","0.001324132","-0.025195872","-0.055707417","0.040087774","0.011304805","0.029624602","-0.020776872","-0.0127986055","-0.012022034","0.057812266","0.042168718","0.032175247","-0.0059800725","0.1340592","0.14360014","0.023910638","0.048491143","-0.049583375","0.03280845","-0.004143045","-0.10060402","-0.01971662","-0.010799056","0.0051542646","-0.042898197","0.074229576","0.009963339","0.05957286","0.023762645","-0.048959434","-0.07427966","-0.006632246","0.04762515","-0.020663824","0.022508336","-0.046731737","-0.0152945","0.0055633895","5.4772454E-4","-0.0015747817","0.07376987","-0.004071064","0.04310861","-0.031975105","-0.022461653","-0.013221432","-0.018919613","0.03837449","0.008608752","-0.02694193","-0.0059122513","0.023708753","0.049839363","-0.07958747","0.03369712","0.09985084","-0.012783919","0.08969708","0.04192102","-0.13082561","0.017369311","0.06276977","-0.099190995","0.053195722","-0.009206767","-0.04008181","0.009978849","0.06134529","-0.060053505","-0.10831678","-0.06720794","0.023201484","-0.055239934","0.058187757","-0.03985345","0.0038685205","0.071662985","-0.033408187","-0.027538598","0.022328632","0.04088969","0.007565318","-0.012658509","0.042077456","-0.048155796","-0.10552396","0.048873674","0.09150771","-0.050546728","-3.141892E-33","0.014034107","0.0078142","-0.017166814","-0.021311007","0.015681371","0.0069695977","0.09898018","-0.025436789","-0.028479548","0.06473328","0.023714637","-0.022192298","0.03849886","0.027438626","-0.008193115","-0.04033407","8.7522273E-4","0.0013460183","-0.101110585","-0.10407008","0.006368246","0.03864726","-0.02273979","0.07971013","-0.07679397","0.011892173","0.14041404","-0.04038928","-0.0702881","0.04977754","-0.08307741","-0.022861514","-0.10668018","0.047217317","0.015498918","-0.03700819","-0.014356854","0.047252424","-0.049798887","-0.04728276","0.017885273","0.05886922","0.012318395","0.03991701","0.009908829","0.0044524735","-0.0039163125","-0.03977601","0.022547657","-0.094878994","-0.05489436","7.711031E-4","-0.022890775","0.0344086","-0.016840678","0.044776466","0.016914722","-0.06740412","0.071867906","0.032328796","0.023612214","0.005972124","0.08872179","0.007722734","-0.03096922","0.041468333","0.0029103803","0.017276486","0.09373634","-0.04718619","0.0044492446","-0.06056789","-0.0329791","0.031312305","-0.014945182","0.07497096","-0.067931145","0.0147017175","0.032602057","-0.041954044","0.076900326","-0.023565203","-0.049024176","0.0458684","0.060758214","-0.07245799","-0.03487785","-0.061127882","0.09076045","-0.08324293","-0.016959997","-0.04242209","-0.030252289","0.06898393","0.01158173","-4.730605E-8","-4.7959786E-4","-0.03202395","0.011682161","-0.02522681","0.029233577","-0.113828614","-0.055229284","-0.08385317","0.024259746","0.06965211","0.041469898","-0.004379234","-0.04383836","0.043975163","7.3758094E-4","-0.014519672","0.0134521695","0.109569944","0.0020851302","0.0041836086","-0.036462255","-0.041928712","-0.040652554","0.0048570265","-0.019687762","-0.044211466","0.031437483","0.058354244","0.03375739","0.023277974","-0.0682789","-0.022953171","-0.041783232","0.060744848","0.06344884","0.03487954","0.0012064236","-0.0109458","0.009693971","0.007884345","-0.028901052","-7.16791E-5","0.037769504","0.09095634","-0.06769823","-0.013783998","-0.090189286","-0.09923797","0.07023642","0.070030116","0.041936945","0.045668554","-0.015973866","0.018408595","0.0028931976","0.008733682","-0.004747038","-0.04165991","-0.1192219","-0.056975346","-0.021313308","-0.089248426","0.0070212865","-0.034460984"]</t>
+  </si>
+  <si>
+    <t>NK-3VDe4Uhs7cm8grJoAFYX89</t>
+  </si>
+  <si>
+    <t>Abdallah Asad Tahini</t>
+  </si>
+  <si>
+    <t>Entity Name: Abdallah Asad Tahini | Type: Person | Jurisdiction: Unknown | Risk Context: (also ABDALLAH THAHINI, ABDALLA AS'AD THINI) (also ABDALLAH ASAD TAHINI)</t>
+  </si>
+  <si>
+    <t>["-0.012213557","0.030012444","-0.0103408145","0.042252686","-0.07718796","-0.03704172","0.08453875","-0.04738142","0.0010697768","-0.047658972","0.100679964","-0.16461979","0.06813686","-0.064536855","0.07334543","0.04668486","0.03406106","0.01727876","-0.030347874","-0.049884904","0.052051313","0.06879849","0.020914368","-0.009882515","-0.018842962","-0.04566307","0.0014434336","0.013638958","1.2801708E-4","-0.03586231","-0.030423345","0.015433394","-0.020952033","0.018808331","0.040117513","0.03683102","-0.061323132","0.0850353","0.0652836","-0.009822249","0.061223492","-0.11347038","0.006667495","-0.012679625","-0.04480965","-0.04978244","-0.020569671","0.051858738","0.030598741","0.016433004","-0.08262133","-0.03911653","4.3895503E-4","0.051068418","0.0050560865","-0.04563217","-0.004670573","0.02590916","-0.10851084","-0.025644787","-0.03554716","0.045966893","0.010268825","0.0019165496","0.03666749","0.018539587","0.018727364","-0.041356873","-0.02004576","-0.02121222","0.09311699","-0.007450077","-0.02862604","0.102749884","-0.06259071","-0.082571454","0.04911681","0.04829364","0.012111368","0.009885342","-0.019156182","0.03666856","0.029071106","-0.05882012","-0.024783893","0.013826947","0.01667895","-0.026053866","0.0037319902","0.011693004","-0.010631556","-0.053648356","0.11811525","-0.029731715","0.06418499","-0.06369991","0.012132266","-0.005741726","-0.13049537","0.031508792","-0.06879359","0.03100914","-0.059909694","0.08378301","-0.034990303","0.036049","-0.074316606","-0.07441863","0.02712408","-0.031129073","-0.03602628","0.02282485","-0.06015576","-0.048727136","0.0014346243","0.017815584","-0.08205142","-0.046908524","-0.032888513","-0.09125102","-0.046613764","-0.014764429","-0.02368957","0.016810939","0.025505958","0.001599623","-0.026177935","2.6993457E-33","0.04088759","0.041673377","-0.01024138","0.030031066","-0.030631943","-0.030579394","-0.063964576","-0.0050685806","-0.0711565","0.022941856","0.017538551","-0.09535621","-0.032763734","-0.042572435","-0.0162766","0.04269663","-0.0072109345","0.020626456","0.0075230543","0.017500918","-0.011731892","0.10549413","0.0060571074","0.03306986","-0.041968953","-0.0024278876","0.073606536","-0.03816565","0.005822909","0.0446173","0.05165516","-0.040403966","-0.016925294","-0.01604738","0.039645217","0.02197911","-0.038213234","-0.023215214","-0.08539726","0.035976972","-0.005342897","0.021603148","0.08925527","0.03839713","-0.07095805","0.0013909702","0.03880995","-0.07299635","0.10282632","0.033676025","-0.010506275","0.03191902","-0.024705471","-0.055453483","-0.01184814","-0.05702727","-0.006747215","0.053204276","-0.009899704","0.0035655457","-0.029992562","-0.10657273","-0.048998725","0.06968432","-0.11750362","-0.0054754633","0.006051953","-0.0669229","0.10940589","-0.023061994","0.002371639","0.023591239","0.028483495","0.10493137","-0.032096673","0.029087616","0.06377359","-0.090115525","0.02026093","0.033802927","-0.082283445","0.03592565","0.0463223","0.07857856","-0.0469461","0.024856512","-0.0034538035","-0.06007481","-0.018713498","0.041844603","-0.042359874","0.07045718","-0.02184074","0.0256579","0.01203943","-4.947944E-33","0.009615914","-0.09259802","-0.015411737","-0.082352996","0.041534945","-0.07524252","0.058934897","0.15381159","0.007548101","-0.007993384","-0.05326072","-0.0707396","9.6675954E-5","0.015141794","0.09202315","0.09794033","0.016225003","0.010307475","0.0011928126","0.11126658","-0.003290651","-0.029089535","-0.049827892","0.02347203","0.00770584","0.025443384","0.04600214","-0.028943338","-0.009313839","-0.0803462","-0.038914915","-0.025610695","-0.08190043","0.0449907","-0.08923154","-0.032780293","0.048571404","-0.075741984","-0.09607916","-0.0156051675","-0.035029735","0.115119964","-0.027945798","-0.0041346196","-0.0036090552","-0.017282289","-0.042700432","-0.039282385","-0.004865044","-0.08135736","0.05137571","-0.015866965","0.01761018","-0.004764197","0.041569978","-0.04778141","-0.010209997","-0.028927784","0.082653806","0.026763787","0.018910062","0.03022727","0.0051890262","0.032579537","-0.0105133355","-0.022427244","-0.061949182","-0.034035385","-0.030461678","-0.04430335","0.08110128","-0.11832589","-0.11726522","-4.1513E-4","0.031986594","-0.018281579","-0.05348074","-0.009663826","-0.023690032","-0.010270191","0.05261122","-0.05075265","-0.046649385","0.04124562","0.0512891","0.08619626","0.09978276","0.04057095","0.031363748","0.015018439","-0.02060744","-0.020390652","-0.0118171405","0.071572565","-0.078145355","-3.9512063E-8","-0.014133317","-0.022788463","0.051780704","0.009987013","0.03225842","0.014115663","-0.0012952728","-0.04531987","0.014460826","-0.021414092","-0.031505264","0.032585405","-9.7200356E-4","-0.020296078","0.06895681","-0.065471984","-0.07182322","0.10839603","0.009048291","0.04683723","-0.006259575","0.02247168","-0.03232058","-0.08272635","0.005075003","0.012460883","-0.006044047","0.02223002","0.043056957","-0.022007274","-0.06914412","0.08911505","0.0010558253","-0.0073886253","-0.007403597","0.092110075","0.108110964","-0.07002184","0.0024707627","0.0659501","0.027675623","0.037857313","0.05275738","0.044803802","0.14819436","0.0066994973","0.02548615","-0.050139654","0.05684256","-0.099933565","-0.032791723","-0.03952087","0.021262355","0.07175755","-0.036168687","-0.027930476","-0.009162319","0.031189544","-0.015627436","0.002683526","0.14871983","-0.037232965","0.008964933","-0.0020405834"]</t>
+  </si>
+  <si>
+    <t>NK-3YeafgdDP5Tb7mAtFrh54a</t>
+  </si>
+  <si>
+    <t>Drs. Coffey Internal Medicine and Family Care</t>
+  </si>
+  <si>
+    <t>Entity Name: Drs. Coffey Internal Medicine and Family Care | Type: Company | Jurisdiction: us | Risk Context: Violation of KMAP Policy</t>
+  </si>
+  <si>
+    <t>["-0.02470594","0.086144686","-0.019610737","-0.067194864","0.00203159","-0.013137423","6.308021E-4","0.0027737794","-0.013219455","-0.0612088","0.024523959","-0.10918058","0.04061398","-0.054251328","-0.017949682","-0.026822755","-4.8081056E-4","-0.07929029","-0.01207401","-0.0014582518","0.001875998","0.09481241","-0.012912033","-0.0014721386","-0.057069115","0.0015056533","0.008259846","-0.05484053","0.020312846","-0.008791044","-0.020098565","-0.017063575","-0.023700833","0.03614198","0.057613187","0.06754572","-0.12431149","0.046719797","-0.009201932","0.06682091","-0.02670277","-0.011084115","0.027829487","0.0014638763","0.014869728","0.039882135","-0.065717354","-0.075605616","0.035435952","0.08535211","-0.05025216","-0.056061298","0.038966615","0.07652417","0.047699984","0.017835388","-0.073560536","0.031948134","-0.056150705","-9.371748E-4","0.043805525","0.010808044","0.025288466","0.035141923","-0.020204721","0.013110044","0.03930125","-0.031206954","0.06570864","-0.09548784","0.055216953","-0.05495125","-0.052138492","0.09173709","0.012830108","0.027018802","-0.01903912","0.025087617","0.043237187","-0.10617768","0.04766918","0.034780733","6.004744E-5","-0.020067913","-0.09320873","0.047172997","-0.01223516","-0.065275","-0.021434218","-0.043326672","0.057917167","-0.09692608","0.10225748","-0.042975575","0.0054024616","-0.018996688","-0.013629676","-0.012298231","-0.09417943","0.02494439","-0.014314269","0.05708537","-0.08492375","0.056259856","-0.024569241","-0.09111929","0.021918913","-0.011925423","-0.030487685","0.108247004","-0.020448687","0.06534462","-0.014511882","-0.12101749","-0.010808576","0.008809368","0.015907766","0.024603453","0.09018589","-0.006448479","0.018342562","-0.014261237","-0.121273674","-0.07425019","-0.046986606","0.019903215","0.04179183","-2.1043035E-33","0.031502526","0.055132817","0.07396708","-0.020420296","-0.026125045","-0.044634055","0.0037496556","-0.03127572","0.020132413","-0.10450475","0.008034295","0.07736994","0.023259804","-0.11839171","-0.10333629","0.07276867","-0.0772036","0.07134199","0.008453611","0.091591775","-0.016691929","-0.018354073","-0.028387932","0.06157241","-0.06007175","-0.02268114","0.003459057","-0.006739801","0.0700965","0.03327238","-0.022696598","-0.004235707","0.038607314","-0.05274264","0.019357828","0.07807643","-0.06401391","-0.018368127","-0.016449405","-0.030506585","-0.046180356","-0.005118589","-0.0051048766","0.09775176","-0.033332888","0.011372096","0.008976016","-0.018576348","-0.019467315","-0.06284596","-0.026038855","-0.0476014","-0.021326918","0.024709977","0.0405055","0.027148109","0.044503707","-0.0022505186","0.019670125","0.04204031","0.06049862","0.017215932","0.013252313","0.07873581","0.0015916373","-0.076917954","-0.034073554","-0.0031651447","0.033601932","-0.09518805","0.0061589763","0.023665823","0.0750867","0.06646579","-0.06873833","0.0074351346","0.003073688","0.038443543","-0.057962514","0.018131204","-0.031821303","-0.0072768703","0.06682961","0.061796486","0.053926047","-0.045452684","-0.026223829","0.020399857","-0.100285724","0.027933765","-0.06780903","0.0706154","0.057094395","0.1029654","-0.0401265","-1.1006903E-33","-0.020839488","-0.026345031","5.6140666E-4","-0.097422935","0.043581396","-0.014410621","0.07560246","-0.004149714","0.060649883","0.04003122","0.0038158447","-0.028852342","-0.01698857","0.0045225043","0.01770343","0.029395107","-0.020854283","0.04355952","-0.047862805","0.04214568","0.04271892","-0.009779369","-0.06267256","0.09832948","0.016762909","0.06416779","-0.021593127","0.030661583","-0.043011572","-0.06669113","-0.017368557","-0.03997653","-0.014280112","0.12244219","-0.0341121","-0.07215002","0.012349478","-0.053414803","-0.028462756","-0.080193944","0.016418971","0.010071484","-0.04059554","0.05726126","0.027236976","-0.054032415","0.016450772","-0.014696491","0.08046828","-0.055338286","-0.017753374","-0.0057720593","-0.014428353","0.0028207945","-0.02692536","0.058050808","0.015096851","-0.027086522","0.0460709","-0.040121518","0.0448446","-0.017575888","-0.085570894","0.13234545","-0.0059673185","-0.01525579","0.012948228","-0.08962926","0.022138733","-0.04434321","-0.047157392","-0.05883176","0.024827266","-0.12718245","0.02171198","0.0049320376","0.04426675","-0.0023051875","-0.043822277","0.011160613","-0.0019868664","-0.06893935","0.004123858","0.10898922","-0.006390289","-0.016638147","0.09129459","-0.08173799","-0.032939047","0.016851839","-0.05008139","-0.009943741","-0.07504755","0.023253044","-0.032858223","-2.5234776E-8","0.0838071","-0.030402774","0.023108402","0.021247232","0.02854162","-0.0268738","-0.0323382","-0.008848755","-0.028096402","0.03588868","-0.06785534","0.07277069","-0.03605127","-0.020740116","-0.013439507","-0.09687815","-0.053780586","0.13953412","0.0024675652","0.058175717","-0.05674643","-0.017724779","0.015199032","-0.05098697","-0.04003632","0.08995275","0.05818002","0.03150357","0.03154317","-0.019995656","-0.0032035604","0.070283","-0.04566245","0.057445586","-0.084231056","-0.08254899","0.060452007","0.03565882","-0.06235963","0.032779444","-0.0029526292","0.06710487","-0.0048370366","0.044238802","0.006790526","0.009572131","0.0024718852","0.09530683","0.06169518","0.0196797","-0.025647927","-0.07855858","0.01612274","-0.024174476","-0.031511","0.02842537","0.016064702","-0.00612482","-0.13141675","0.0624113","-0.0027989002","-0.03717041","0.115118116","0.09749734"]</t>
+  </si>
+  <si>
+    <t>NK-3cab8SqMtaaeWcAnMzJVFz</t>
+  </si>
+  <si>
+    <t>Karasani Dis Ticaret Limited Sirketi</t>
+  </si>
+  <si>
+    <t>Entity Name: Karasani Dis Ticaret Limited Sirketi | Type: Organization | Jurisdiction: tr | Risk Context: Website: http://karasani.com.tr/ Місцезнаходження: Турецька Республіка, м. Стамбул, район Бюкчекмедже, вул. Чеввал 1/3, міжкімнатні двері № 180 (Türkiye Cumhuriyeti, İstanbul ili, Büyükçekmece ilçesi, Çevval Sokak 1/3, iç kapı no: 180); Турецька Республіка, м. Стамбул, район Башакшехір, вул. Шелале 13E, Будинки магнолій B1:48 (Türkiye Cumhuriyeti, İstanbul ili, Başakşehir ilçesi, Şelale Sokak 13E, Manolya Evleri B1: 48) Telephone: 532 062 57 24 Telephone: +90 533 136 83 78 Registration number: 0079-0681-5280-0001 (Central Registration System No.) Email: info@karasani.com.tr</t>
+  </si>
+  <si>
+    <t>["-0.0154311815","0.03649409","-0.055660315","-0.018402178","-0.064703","-0.012781905","0.027425831","0.05452646","0.00826107","0.030557888","0.07459458","-0.060602374","0.020357884","0.011161391","0.002596328","-0.08975078","0.025436342","0.0057953745","-0.13010143","-0.040958215","-0.007935851","-0.09062493","0.046176773","-0.028113604","0.0029928747","-0.033327658","-0.06883919","0.0065467344","-8.7453023E-4","0.02102654","-0.025931392","-0.0074953167","0.0056419326","-0.046778228","0.023317302","0.090713926","-0.042432327","-0.0468011","0.03385517","0.057106","0.022014339","-0.08761188","-0.07857275","-0.01216975","-0.016435923","0.054882675","-0.05483331","0.0040367125","-0.0403397","0.0013061957","-0.035885688","0.014389718","0.030098699","0.021682033","-0.02515895","-0.17712173","-0.07501939","-0.0074343015","-0.04929368","0.005791309","-0.04125577","0.034650568","0.03726913","-0.041499227","-0.050035104","0.0068920567","-0.025477558","-0.06917497","-0.0039058283","0.05081901","0.07494918","-0.04986479","-0.18808343","0.06733264","-0.08491135","-0.011288371","0.032499522","0.045110032","-0.008977705","-0.10922682","0.07506552","0.06899825","0.17201507","-0.06446557","-0.07104719","-0.033957906","0.04897057","-0.028245237","0.030342499","0.018267773","0.13407917","0.01959996","0.021202942","-0.051323738","0.1605275","-0.07407058","0.004005008","0.01671117","0.033915784","0.0019467334","-0.01587889","-0.08658921","-0.08269035","0.022465942","-0.079415806","-0.013974973","-0.03987762","-0.06591352","0.01885729","-0.0016939495","-0.07417396","0.012729286","0.0074933465","-0.0571725","-0.04146657","0.065802105","-0.09226165","0.0056827622","0.04370441","0.009813435","0.051024046","-0.004082696","-0.0067424164","0.038641088","-0.01811925","0.038133286","-0.006474372","8.122252E-33","0.00859291","-0.083178334","0.017685598","-0.0393794","-0.003913474","-0.00998018","-0.030133098","-0.018742599","0.0045838985","0.0110006835","-0.05216882","-0.059258353","0.024543656","-0.08820813","0.05174548","0.06309838","0.034365688","-0.009834213","-0.052023094","0.030332929","0.0313193","0.025401952","0.044898193","9.3007606E-5","-0.018428667","0.049955193","-0.025936369","-0.01870491","0.055564884","0.0035432356","-0.015698427","-0.043558147","-0.042721182","-0.041528467","-0.05751516","0.027111622","-0.03786468","-0.049184926","-0.0887991","-0.018198013","0.0069581997","-0.01340218","-0.014792058","0.036506493","0.022811063","-0.034087252","0.00398069","-0.056332506","0.0271338","-0.059025884","-0.07639538","0.10324631","0.010331772","-0.008822101","0.014858145","0.030294996","0.009841416","0.054328866","-0.07681429","0.011858784","0.011090364","-0.056731533","0.01401004","0.054766603","0.020273758","0.012591357","-0.036246885","0.04298119","0.054399583","-0.017005932","0.010019132","0.07214931","0.010046042","0.03767073","-0.05437276","0.019423442","0.014880117","0.049704086","-0.016974073","-0.0015341932","-0.10825501","0.038337957","0.047738694","0.018162638","-0.047038645","0.02772257","0.015118435","-0.07321375","-0.02194787","0.033582393","-0.0826826","0.03321562","-0.086581685","0.048906267","-0.038050365","-1.2331748E-32","0.0014232404","0.05677939","-0.07755203","0.02453971","-0.0029714566","0.05219913","-0.022621866","0.031864405","0.03212398","0.0934909","0.04167144","-0.05915654","0.010995133","-0.02823291","-0.0035632728","0.029268287","-0.02922997","0.111310534","-0.06495405","-0.0060086716","0.007330016","0.071473345","-0.011504817","0.014923748","-0.008833147","0.025582848","-0.017711276","-0.06177055","-0.054408308","0.006774742","0.022762898","0.0352239","-0.09278657","0.06717574","0.04524863","-0.029004388","0.045483023","-0.0472262","-0.04338913","0.089968495","0.0595545","0.02499767","0.055133138","0.044887453","0.00785583","-0.019161794","0.023724943","-5.1866885E-4","0.093264125","-0.12835936","0.025542527","0.031141592","-0.023195717","0.020717772","0.03987106","-0.0068727015","-0.0231316","-0.010692809","-0.022147149","-0.032715943","0.028318252","0.07638665","-0.018721208","-1.8484631E-4","0.008843583","0.016657539","-0.043808043","-0.045005713","0.13685514","-0.079351","-0.020554366","-0.09757121","-0.009152166","0.008221827","0.016424417","0.037317235","-0.019705523","0.06811926","0.01103204","0.0038301682","-0.010906885","-0.057642505","-0.029290544","-0.01175549","0.042529453","0.044424884","0.058440167","-0.021474462","-0.0074034147","0.028083028","-0.02473843","-0.008537212","0.0029745174","0.11887283","0.031156724","-6.6619315E-8","0.09426174","0.025457859","-0.012790122","0.059210513","-0.012650542","-0.0743677","-0.020185154","0.014124602","-0.10973517","0.0844048","-0.09831979","0.041236218","-0.034635223","-0.058739115","-0.096523196","-0.046814617","-0.02505776","0.02706247","0.029702425","0.0034076464","0.03526936","-0.06596725","-0.015975801","-0.12830824","-0.093803026","-0.07296939","0.058342528","0.03978216","0.004004081","-0.0260368","0.012360071","0.018416297","-0.009759048","-0.06668029","0.04432246","0.040365774","-0.026386034","0.047115404","0.010900289","0.040388048","-0.037680596","-0.059479117","0.07143691","0.051385563","0.056097567","0.06235524","-0.111720935","0.010155683","0.053374905","-0.09888967","-0.04260599","0.012298768","0.0383787","0.06653096","-0.011649337","0.053828157","0.006579069","0.034903407","0.006205143","0.008714889","0.0042179804","-0.09802143","-0.042988144","-0.037536774"]</t>
+  </si>
+  <si>
+    <t>NK-3f65Cf3cFJAdn88hdRMv5k</t>
+  </si>
+  <si>
+    <t>AFFORDABLE TOWING SERVICE, LLC</t>
+  </si>
+  <si>
+    <t>Entity Name: AFFORDABLE TOWING SERVICE, LLC | Type: Person | Jurisdiction: us | Risk Context: (also AFFORDABLE TOWING SERVICE, LLC, AFFORDABLE TOWING SERVICE, LLC, DENNIS CLEVELAND, AFFORDABLE TOWING OF SPRINGFIELD, LLC) (also DENNIS CLEVELAND, AFFORDABLE TOWING OF JOPLIN, LLC, AFFORDABLE TOWING OF BOLIVAR, LLC, AFFORDABLE TOWING SERVING SOUTHWEST MISSOURI, LLC) (also DENNIS CLEVELAND)</t>
+  </si>
+  <si>
+    <t>["-0.054053936","0.03688146","0.011201658","0.05574936","0.021453125","-0.017871998","0.029994737","0.068555385","-0.015148208","-0.021840136","0.046895158","0.03458404","0.06912007","-0.011404603","-0.021784497","0.021357818","0.10517798","0.060531504","0.035207495","0.015539695","-0.029999383","0.056772154","0.008528518","-0.048148178","-0.0050971615","0.0042442367","-0.045407996","0.046144444","-0.02025086","-0.02521458","-0.035425786","-0.019479958","-0.07545941","-0.04375129","0.09913241","0.03932554","-0.030981569","0.055019464","-0.056143958","-0.023225","0.07693674","-0.039527707","-0.04538363","-0.022369897","-0.08917096","-0.038460456","-9.003541E-4","-0.03785041","-0.009267702","0.08995919","-0.035205156","-0.01881082","0.036741458","0.01040398","-0.020441169","0.052632492","-0.008093604","0.037646875","-0.05986782","0.03723131","-0.05009918","0.011933372","-0.07772799","-0.013602831","0.073770806","0.015927913","-0.0151640875","0.06773253","-0.02300962","-0.066433914","0.06577888","-0.046262313","0.0029048102","0.061291825","0.036313687","-0.06734284","0.09426016","0.09367411","0.012740597","0.012421439","-0.035488315","0.001109625","-0.0032542828","-0.09785409","-0.053118553","0.099107414","-0.06157927","-0.047428876","0.05466469","0.0063591087","-0.04430871","-0.085178986","0.012804929","0.010708008","-0.04162826","-0.04016438","-0.022659704","-0.030724352","-0.09531033","0.04623509","0.043837693","-0.012557552","0.014494183","-0.0012469776","-0.09184231","-0.02923293","-0.04721955","0.016605262","-0.020043025","0.014288123","0.06705165","0.039029013","-0.066884466","-0.009676256","-0.02902714","-0.10347026","-0.11518853","-0.0152677195","0.050689474","-0.07665626","-7.686084E-4","0.0019805613","0.050256066","0.013757751","0.022283472","0.02296995","0.036831167","-3.4321875E-33","0.05122887","0.09480809","0.041130964","-0.005841688","-0.052371826","0.024219038","-0.014430542","0.019814843","-0.05896262","0.04539669","-0.05826603","0.11403288","0.035303563","-0.064397395","-0.033139303","0.026296383","7.6106266E-4","0.021179052","0.06996989","0.01138654","-0.025310192","0.05959931","0.009696354","-0.004886333","-0.06897254","-0.123442486","0.0027836827","-0.021146243","0.06618139","0.053335045","-0.0014912044","0.038607996","0.047626235","-0.039149024","0.105618484","0.03926957","-0.09000812","-0.04288693","-0.08474301","-0.069400966","0.0028957785","-0.050825275","-0.018622233","0.077523746","-0.012612493","-0.004719035","0.041708544","-0.049063094","0.0029532406","-0.07519659","-0.06463432","-0.052703083","-0.013106205","0.053871166","-0.077038996","0.013241821","-0.025254035","0.053652316","-0.006478841","-0.02278272","-0.027571486","-0.03366876","-0.02460898","-0.019934636","-0.0086983405","-0.073723264","0.050753865","0.009233378","0.057589117","0.024706539","0.065015264","0.0067796228","0.16169924","0.14709102","0.046484962","0.023409905","0.010438735","0.103383586","0.024791846","0.081829436","-0.05404912","0.028219216","0.03253732","0.0057533304","0.122922204","0.0017290838","-0.026793096","-0.120849706","-0.06666614","0.040415443","-0.058246523","0.07512948","-0.064909235","0.04696576","0.020307824","9.0404877E-35","-0.00210855","-0.004305199","0.0680812","-0.013356554","-0.008237025","-0.08837203","-8.3032483E-4","-0.0074896305","-0.013696408","-0.025416825","-0.08980062","-0.03206076","-0.047569964","-0.0013788948","0.107979536","-0.024528159","-0.08942068","-0.05483975","0.073193364","0.036315914","-0.018380627","-0.015283653","-0.004423778","0.07936143","-0.039935697","-0.06784046","-0.035750024","0.05377275","0.0032767053","-0.031833448","-0.01355126","-0.013231637","0.013927921","0.028982732","-0.0693476","0.019857112","0.021999147","0.019329073","0.0042350525","-0.045834552","0.030641122","0.018013151","-0.017557606","-0.063420795","0.038050756","-0.0152366115","-0.039775368","-0.09917354","-0.014423919","0.002285275","-0.010385777","0.001718112","-0.060108293","0.022983357","-0.021619672","-0.029511226","0.039825555","0.029481625","-0.035286184","0.085585654","0.061217323","0.068320595","-0.038775112","0.12630814","0.08105814","-0.038900837","-0.01861434","-0.1692704","-0.0820026","-0.013607111","-0.022783164","-0.016948648","-0.027762078","0.01371853","0.024691239","-5.708497E-4","-0.018248888","-0.0040438944","-0.024904866","-0.060246233","0.0946527","-0.059556164","-0.020678785","0.069824226","-7.681845E-4","-0.008959483","0.026241908","-0.035037395","0.010228532","0.03829502","0.0129098585","-0.062003896","-0.079996064","0.0668549","-0.12565404","-3.500732E-8","0.06563726","0.0474819","-0.01538413","-0.002137981","0.022172151","0.0020798524","0.044612974","0.01977336","0.013439054","0.055034492","-0.009482428","-0.040611934","-0.024811987","-0.0018093557","-0.01378339","-0.027117487","-0.01671128","0.04391089","-0.03367376","0.07217165","0.022496713","0.048442416","0.013767568","0.046915095","-0.0010503691","-0.05010763","-0.04372223","0.05027785","0.073491946","-0.10864456","-0.03788873","0.048811637","0.019907746","-8.6594763E-4","-0.05071085","0.017169727","0.058029257","-0.006776079","0.053444553","0.0700964","0.030609444","0.09901834","0.01249165","0.03304442","0.109296754","0.029480623","-0.012976092","-0.0038070416","0.041605704","0.0013774752","-0.08698815","0.0020006185","0.016027706","0.004758831","-0.015140733","-0.1401514","0.020118427","-0.024098441","0.0047137924","-0.01082521","0.064587645","-0.073009424","0.06566343","-0.028508462"]</t>
+  </si>
+  <si>
+    <t>NK-3jhj93akjs5wzAiWiSjBXR</t>
+  </si>
+  <si>
+    <t>Joint Stock Company Lomo</t>
+  </si>
+  <si>
+    <t>| Fax: (812) 542-1839 JSC Lomo is a Russian military industry company. It provides various military components of the weapons used by the Armed Forces of the Russian Federation, including the semi-active homing heads for Krasnopol missiles, the Mowgli-2 and Mowgli-2M night-vision sights for the Igla-S portable anti-aircraft missile systems, and homing heads used in the Kitlov-2 ammunition. The Krasnopol missiles, Igla-S portable anti-aircraft missile systems and the Kitlov-2 ammunition are used by the Armed Forces of the Russian Federation during Russia’s war of aggression against Ukraine. Therefore, JSC Lomo is supporting materially actions which undermine and threaten the territorial integrity, sovereignty and independence of Ukraine</t>
+  </si>
+  <si>
+    <t>["-0.08558557","0.032190587","-0.019672211","-0.05516603","0.057075374","-0.044839423","0.085385084","0.06609898","-0.015390982","-0.047261618","-0.02925631","0.10769673","0.00802","0.040852338","-0.0250679","-0.016442489","9.5561706E-4","0.013123793","0.012135357","0.026404515","0.049435418","-0.056116067","0.10226876","0.033048723","0.008783604","0.11105535","0.045641635","0.05792059","-0.038517457","-0.05538856","-0.020308036","-0.016556721","-0.022349132","-0.028471671","-0.034543253","-0.015630832","0.0838075","0.0012082873","0.0068169185","0.037130818","-0.02772044","0.007909996","0.0059158527","0.053880043","-0.0062951427","0.020179955","-0.019867258","-0.03499774","-0.079847515","0.07042988","-0.048535276","-0.046587955","-0.0106694745","0.023343861","0.0051029273","-0.093232885","-0.080691345","0.029046375","0.008802549","0.07223973","-0.0088266","-0.024020597","-0.025085555","0.018278787","0.032563515","-0.04436428","0.018042222","-0.024289371","-0.0022886572","0.04854884","0.06469693","0.04903548","-0.041962735","0.006305143","0.013865227","-0.041113485","0.028918047","0.054494258","0.10743064","-0.038875517","0.05734576","0.023464713","-0.032927096","0.014988135","-0.027718132","0.005941283","-0.06600864","0.051917717","0.038280644","0.011768069","0.054271817","0.012317645","0.062390707","0.0046958895","0.006030115","-0.016658029","0.06693517","0.08380476","-0.05950953","0.02292958","0.0579656","-0.058340877","0.023192775","0.035990324","-0.0929642","-0.020771248","-0.092364796","0.012624526","-0.046854567","-0.010618962","0.018371264","0.022342406","-0.055978853","-0.039071675","-0.089922346","-0.03637332","-0.043942373","0.02255444","0.040115938","-0.08216847","0.017396962","-0.052486796","-0.03636959","-0.029628763","-0.01631383","-0.0148437545","-0.14043403","6.6329317E-34","0.015125977","0.02250888","-0.04805607","0.0045409985","-0.14338739","-0.057060663","0.008859997","-0.018504117","-0.08867708","0.092276275","-0.06153911","0.1487405","-0.0793602","0.029346019","0.0821047","-2.5120165E-4","0.029868968","8.665859E-4","0.029218681","0.08950299","0.10735073","0.026875844","-0.0229238","0.06891427","0.0788048","0.08308637","0.019886121","0.056180604","-0.0724276","0.07139318","0.029111331","0.0063256086","-0.012848115","0.0025793866","-0.0023696558","-0.093687385","-0.122978345","-0.018847916","-0.038783308","-0.036796898","0.051379506","0.030767197","-0.05039662","0.023616523","0.055800278","-0.04837284","-0.007498198","0.015101307","0.017679298","-0.03752527","-0.016592847","0.011020627","-0.015728151","0.06796112","0.026025299","0.018332122","-0.028208863","0.012649211","0.04307131","-0.016079593","-0.02086238","0.05687526","0.06512497","0.08517604","0.0093665905","-0.0629608","-0.053649817","0.009379147","-0.03189394","0.10145899","0.04884489","0.027298955","0.045462515","0.0068454896","-0.030227771","-0.11002572","0.009913785","0.003521404","-0.00512105","0.0411221","0.06605296","-0.013538725","0.095766455","0.041541953","-0.042090118","0.017283797","0.05835305","-0.05742079","-0.10275546","0.07483573","-0.11007636","-0.06962347","-0.033634923","-0.001985591","-0.03315611","-1.2879286E-33","0.10500432","-0.0036185056","0.050567456","0.039523598","-0.115176335","0.050614227","0.06538117","-0.022362122","0.00127526","0.0832534","0.030379107","-0.010481056","0.046640303","0.016701346","0.089358434","-0.04821512","0.023665277","-0.009121639","-0.034730714","-0.12233461","-0.0018142911","0.023298673","0.037939344","0.0075183497","-0.042454198","-0.03951451","0.035568897","-0.016025491","-0.097552344","0.0565873","0.019908724","-0.060636908","-0.010688338","0.022279888","0.01252521","-0.087342456","0.091338105","0.024317795","-0.052979596","-0.09824895","-0.031510238","0.03076804","0.027331268","0.09895571","-0.06887891","-0.049564667","-0.025835846","0.018658984","0.062108237","-0.052073695","-0.017458364","-0.06310046","-0.08063677","-0.045890465","-0.017785896","-0.013009594","-0.046538137","0.017407674","-0.02360309","0.028469158","0.09366815","-0.07259337","-0.027324162","-0.03622039","0.023334408","0.026776396","-0.016084613","0.034048107","0.085644096","0.0387772","0.0721651","0.002779079","0.028751934","0.008029165","0.043396663","0.03912362","-0.06509945","0.02403888","-0.0061558797","0.015547633","0.05538075","-0.09304433","-0.08495832","0.06666067","0.039254103","-0.0023101266","0.02239027","0.086613454","-0.004808534","-0.017688986","-0.015920326","-0.021689987","-0.0173886","0.09265825","-0.030423002","-4.495385E-8","0.011363071","-0.058371726","-0.028881561","0.0073634596","-0.15764762","-0.004588939","-0.021711495","-0.052790817","0.0052564004","-0.03731827","0.046051994","0.025546735","-0.01404428","0.01359105","-0.023177184","9.064235E-4","-0.007826726","0.032844156","-0.06229263","0.040934663","0.028919032","-0.0037499547","0.031006625","0.042704213","-0.04132141","0.03493288","-0.016258122","0.0022162215","0.08916997","0.0723951","-0.077074684","-0.078919135","0.012083842","0.014195854","-0.0259","0.0048187254","-0.027797148","-8.81215E-4","0.01657151","-0.025487766","0.05932732","-0.03151646","-0.033186555","0.097992495","-0.0725237","0.013248187","-0.08082793","-0.057968725","-0.065824375","-0.03889823","0.0073608705","0.036838625","-0.077710085","0.065060966","-0.054724265","0.04318636","0.045603547","-0.06622439","0.028715665","-0.043775972","0.012683889","-0.05808242","0.0129822595","0.007626039"]</t>
+  </si>
+  <si>
+    <t>NK-3nFfbgJBVn8pupYgimf3Fv</t>
+  </si>
+  <si>
+    <t>Ismail Abdallah Sbaitan Shalabi</t>
+  </si>
+  <si>
+    <t>Entity Name: Ismail Abdallah Sbaitan Shalabi | Type: Person | Jurisdiction: de | Risk Context: Unknown | Passport of the Hashemite Kingdom of Jordan, no.: E778675, issued in Rusaifah on 23 June 1996, validuntil 23 June 2001; Passport of the Hashemite Kingdom of Jordan no.: H401056, JOR 9731050433, issued on 11 April 2001, valid until 10 April 2006. National identification no.: Address: Currently in detention awaiting trial. Name of father: Abdullah Shalabi; Name of mother: Ammnih Shalabi. nationality possibly Palestinian;arrested 23 Apr 2002; Понастоящем е задържан и очаква съдебен процес. Име на бащата: Абдуллах Шалаби; Име на майката: Аммних Шалаби</t>
+  </si>
+  <si>
+    <t>["-0.0159685","0.04121977","-0.089379","-0.02559166","-0.005304555","0.011701674","0.025183462","-0.012977509","0.009260734","0.0026492365","0.09512158","-0.006254252","0.06388046","-0.066637985","-0.02853574","-0.047609325","0.009401498","0.014017294","-0.044358432","-0.014491503","-0.03548887","-9.927246E-4","0.11415522","-0.05516114","-0.0564237","0.043326903","-0.033191502","0.037996594","-0.009528065","-0.031384364","0.028885948","0.03079133","0.0019913374","-0.025978403","0.064383514","0.08007245","0.021806909","0.055871505","-0.014382154","-0.06775385","0.092275545","-0.06299501","-0.058564432","-0.017968183","-0.019369854","0.006032009","-0.046812963","-0.0027129655","0.04186229","0.05183984","-0.10342043","-0.027361495","0.078850426","0.010113372","0.006596759","-0.08082925","-0.02610103","-0.024129067","-0.026567971","-0.013904021","-0.040170345","0.07528602","-0.011125114","-0.05119454","0.0075761983","-0.02716135","0.09749931","-0.1564945","0.08113364","-0.039024197","0.10199273","0.014551919","-0.1043095","0.025813645","-0.11324736","-0.013199839","-0.028263912","0.035144757","0.0065363785","0.01584171","-0.007612083","-0.052588463","0.066317864","-0.033233974","-0.032940295","-0.05681763","-0.004717394","-0.025098449","0.01957873","-0.01566468","0.077296965","0.009800695","0.080758564","-0.10176707","0.09208765","-0.056699682","0.034780532","0.08807617","-0.013394449","0.04724091","-0.021560838","-0.050789494","-0.070640415","0.04726991","-0.024984794","0.010883352","-0.027296731","-0.009309059","-0.046258222","0.012830593","0.035157178","-0.08548061","0.0010176105","0.049792316","0.076461546","0.07891611","0.0305811","0.0026928768","-0.030614227","-0.02899824","-0.015673496","0.04856263","0.038903557","0.027747145","-0.05412914","0.015695345","-0.06815224","4.4999096E-33","0.033242427","0.014156234","-0.031223062","0.015952446","-0.027411489","0.0028257365","-0.06252525","0.06924791","0.019078158","-0.005485761","-0.016464464","-0.08929953","0.06993084","-0.09557434","-0.037764724","0.06983674","0.05117707","-0.020744376","-0.0011729291","0.075359516","0.07190512","0.017102169","0.06683593","0.02840926","0.0047555347","0.026049338","-0.021831376","-0.11781399","0.072345376","-0.0118707055","-0.022941088","-0.017605072","0.037543897","-0.0807362","0.052993104","0.038322337","-0.026647476","-0.012644861","-0.04805534","-0.038123105","-0.0057183933","6.691739E-4","0.042093664","-0.010480096","-0.02672658","0.010764882","-0.03625484","-0.06376653","0.047386937","0.0012905734","-0.03484788","0.035850126","-0.04057018","-0.06530151","-0.11747464","0.017020904","-0.048839904","0.05637386","-0.0042874636","0.07311888","0.06046307","-0.010367702","-0.052061312","0.058112696","-0.010073191","-0.12193892","-0.012978644","0.060827278","0.0015344146","-0.0017387993","-0.0040320903","0.063815854","0.02660791","0.05786644","-0.018680664","-0.003754105","0.019087698","-0.015127563","-0.107090786","0.01293759","-0.012836012","0.0244468","0.052246023","0.05392531","-0.08898728","0.019125039","0.060174167","-0.031334396","-0.093890026","-0.028082587","0.004023537","0.043265965","-0.045356568","-0.014962724","-0.0071824268","-8.235847E-33","0.09334822","-0.056656092","-0.0022485044","-0.027180862","0.058267474","0.016054168","0.08644853","0.08954723","-0.024007425","-0.048307758","0.07557283","-0.05926715","0.07249109","0.03838621","0.03287783","0.06486661","-0.110423684","0.0688774","-0.022732114","0.056782346","-0.066623285","0.07028905","0.040053733","-0.0058342144","-0.01298237","-0.0019938208","0.060234815","0.0164545","-0.08327375","0.041451078","-0.012079327","0.008357527","-0.07581796","0.01872885","-0.030654566","-0.012397704","0.055144142","-0.053611092","-0.009177344","0.093075745","-0.0071964585","0.06393396","0.013402426","-0.019235486","-0.035482656","0.041153166","0.009539277","0.1017258","0.045070067","-0.1203962","0.014317127","0.020372385","-0.049982917","0.044140667","0.0792098","-0.0056898957","-0.02860091","0.017714305","-0.0343423","0.022157572","-0.073242016","0.022833118","0.016382989","-0.06619024","-0.006592023","0.01486349","-0.044845585","-0.11168984","0.033535697","-0.021180814","0.0073742066","-0.16731168","0.017525043","0.018160677","0.066852406","0.04916256","-0.052004218","0.11095106","0.017932642","-0.039229963","0.039213236","-0.050981827","-0.08318058","0.026923694","0.07478207","-0.032982655","0.11881949","-0.04810396","0.0013474635","-0.12728158","-0.0022500765","-0.076207094","0.00954259","-0.0013293214","-0.02916727","-4.898553E-8","0.036544856","0.011892132","-0.014345611","0.020013276","-0.0010264778","0.010902898","-0.020287687","-0.04396166","-0.08517404","0.0157347","-0.03502339","0.0099968705","-0.06446279","-0.0659025","-0.07280854","-0.010758822","-0.07648245","-0.0024584774","0.01872645","-0.03771063","-0.0730052","-0.05621995","-0.04466341","-0.04429972","-0.03990469","-0.01861098","0.01174017","-0.08191963","0.014770394","-0.07318654","-0.036165837","0.03552967","0.04624418","-0.06390042","0.040468212","-0.0058190087","0.018933324","-0.0034978366","-0.009893356","0.0014466303","0.0493782","-0.002735548","-0.047237348","-0.02533235","0.025822287","0.002942123","-8.3507283E-4","-0.0039610043","-0.03766012","0.03485655","0.009368418","0.06773652","0.081416905","0.06451565","0.03531551","-0.042212233","-0.0073231105","-0.064300865","-0.0018889358","0.066217035","0.10937126","-0.0857239","-0.0074677365","-0.06258825"]</t>
+  </si>
+  <si>
+    <t>NK-3pC6fq8wB56bdrHBKWvdZV</t>
+  </si>
+  <si>
+    <t>Ivan Josephovich Boguslavsky</t>
+  </si>
+  <si>
+    <t>. Militaire de haut rang des forces armées biélorusses, Ivan Boguslavsky participait aux actions de la Biélorussie visant à soutenir la guerre d’agression menée par la Russie contre l’Ukraine.</t>
+  </si>
+  <si>
+    <t>["-0.0046924306","0.08119944","-0.040063575","-0.018639823","-0.11274562","0.04846545","0.057541434","0.070716575","-0.0042967526","0.003353556","-0.09481693","-0.0049202517","0.020627063","-0.034799527","-0.063797146","0.011833872","-0.041832086","0.044720884","-0.0058460524","0.06384942","-0.019772088","-0.045904502","0.069444984","0.074169576","-0.027784307","-0.01398272","-0.022704372","0.0055410652","-0.039146412","-0.03940929","0.018339798","0.07095784","0.08259306","-0.023558686","-0.013507596","0.042796392","0.021711178","-0.03109798","-0.03940361","0.05892256","-0.03473485","-0.015130411","-0.07989223","0.0032951557","0.00784828","0.015615528","-0.055521324","0.037441347","-0.009363346","0.097225115","-0.05513753","0.005390318","0.007756024","0.0014233754","0.026991563","-0.16513771","0.05602724","0.0072287717","0.052452743","-0.05793392","0.019445315","6.334147E-4","0.008192239","0.0046351524","-0.054712325","-0.07907875","0.014892371","0.018238762","-0.024235532","0.018641537","0.13535264","-0.03917316","-0.12620838","-0.05976281","-0.021224918","0.0052495277","0.036515858","0.008619921","0.027828332","-0.09645347","0.0445856","-0.018944146","-0.03598699","1.323778E-4","-0.0036762892","-0.03393731","0.017374348","0.026820505","0.056792337","0.039262913","-0.013632361","0.022939388","0.073487274","-0.055560615","0.009381658","0.01224764","0.009592592","-0.031490706","0.02744413","0.03140148","0.04982874","-0.066214435","-0.027975904","0.02444571","-0.04319797","0.026390554","-0.01788889","-0.057805195","-0.036767215","-0.049728528","0.014096934","-0.07811062","0.025969902","-0.07723585","-0.02964484","0.053739976","0.023800073","-0.048968982","-0.054695826","2.3385258E-4","0.058130335","-0.021239676","0.0016090858","-0.0030061982","0.043243203","0.040202603","-0.002250946","6.515396E-33","0.0433177","-0.10594602","-0.025207622","0.057119083","-0.1036366","-0.07718837","-0.055302538","0.015661666","-0.033400558","-0.0046058036","-0.03563113","0.06360888","0.07676075","-0.02117416","0.053264152","0.044025928","0.038569618","0.0113275945","0.06789234","0.025145432","-0.014377941","0.0010297843","-0.038270246","0.043153223","0.08850059","0.017833536","0.021163208","-0.015889216","-0.0203941","0.0043254704","0.013944885","-0.034202278","-0.05401083","-0.030921478","-0.0019043463","-0.039310705","-0.06788223","0.028393729","-0.058367517","-0.01638493","0.0366368","-0.0855245","-0.07581173","-0.009724224","0.10600549","-0.056304887","-0.009022513","0.029975537","0.028347123","0.039922383","-0.017265119","0.038769048","-0.03722621","0.033304375","-0.02536107","0.027495835","-0.019559078","0.066044524","-0.01105029","0.042417772","0.074845865","-0.031442493","0.029099183","0.015869897","0.03215413","-0.0892003","-0.0068490333","0.12497513","-0.038997553","-0.09362052","-0.05343398","-0.050176837","0.019209249","0.022387963","-0.031028865","0.0039013098","0.06684819","-0.031082697","-0.09557197","-0.016347962","-0.115457505","-0.0023270645","0.09531001","-0.012635227","-0.02681646","0.005084887","0.033590417","-0.08484922","-0.07702363","-0.008775533","-0.13242312","-0.015236774","-0.02295163","0.060116045","0.020453392","-9.7624446E-33","-0.009226033","-0.03320402","-0.019837076","-0.0072299372","0.007924156","0.04036745","-0.017097142","-0.033215877","-0.10687588","0.085823365","-0.030210227","-0.041282408","0.019386915","0.012549366","0.03527735","0.007868237","0.11574962","0.012181843","-0.07132328","-0.014344015","-0.09207073","-0.007063791","0.08556878","-0.0010986368","-0.060380466","0.018491551","0.09153675","-0.078372866","-0.055868126","0.13452753","0.05595986","-0.059954472","-0.0452885","0.091915615","0.08935959","0.061581526","0.09841305","0.0034286364","-0.01743476","0.038338915","-0.07696866","0.061155073","0.028430259","0.034119327","0.06261724","-0.078313194","-0.014676517","6.764083E-4","-0.07119598","-0.064098224","0.094191395","0.056208674","-0.033157386","0.02732395","8.237455E-5","0.003138078","-0.023585076","-0.0021530243","0.04677361","0.014825462","0.032814164","-0.030903665","0.0013292445","-0.067604385","-0.030120092","-0.016240172","-0.05575129","0.08233009","0.0025772317","-0.037135143","0.037081085","0.006602013","-0.005871339","0.11908688","0.010921073","0.056658242","0.021925928","-0.025699317","0.02406116","0.007407383","-0.016526397","0.007210023","-0.02343797","0.04162547","-0.044244952","-0.026233446","-0.02119297","-0.02597749","-0.03707107","-0.07746136","-0.03994768","-0.013832851","0.07069297","-0.0021276232","-0.046816636","-4.375413E-8","0.0693246","0.0600313","-0.021638239","0.08749629","-0.053416982","-0.08360369","-0.09692876","-0.096090585","-0.066367306","0.042912275","-0.03425464","-0.024531722","-0.03219178","-0.038460538","-0.009367329","-0.01682903","-0.0039066984","-0.027068665","-0.047128726","0.015278452","0.0468837","-0.061889708","-0.11428019","-0.026346007","-0.061856274","-0.013453678","-0.03328113","-0.14292292","0.09743148","0.013838594","0.06564613","0.094290726","-0.046429943","-0.026756916","0.03642134","0.04178976","0.01365864","0.035636827","-0.0045758695","0.006773253","-0.030584447","0.026889775","0.029323258","-0.060453106","-0.015611023","-0.011685418","-0.04142788","-0.06872857","-0.008381139","-0.008992753","0.02941913","0.020765318","0.05548382","0.14644691","0.04478209","0.042428378","0.04873568","-0.1075953","0.061683252","0.008331536","-0.030175265","0.003040439","0.035407703","-0.008990922"]</t>
+  </si>
+  <si>
+    <t>NK-3shCmPwvC4NYqkDGx6ag3f</t>
+  </si>
+  <si>
+    <t>Denis Aleksandrovich DIDENKO</t>
+  </si>
+  <si>
+    <t>Entity Name: Denis Aleksandrovich DIDENKO | Type: Person | Jurisdiction: ua</t>
+  </si>
+  <si>
+    <t>["-0.04705951","0.012330344","-0.036043834","-0.045058165","-0.06275855","-0.041989762","0.04540707","0.050486825","0.016566282","0.0062992848","0.02221672","0.0014927165","0.014458415","0.032910544","-0.050465446","0.041097827","0.030653164","0.057799898","-0.006513311","-0.0028782084","0.024731986","0.005243377","0.07251571","-0.036981344","0.04550961","-0.08069472","-0.0337501","-0.035337165","0.014943601","0.035040863","0.04925989","-0.004106079","0.020078087","0.04842601","0.12301716","0.033793136","-0.029687766","0.04697655","-0.00871853","0.04657345","0.03339254","-0.053923193","0.036448307","0.09192933","-0.013085976","0.027740983","-0.015465207","-0.01571786","-9.220542E-4","0.054250423","-0.1044414","0.027691577","0.03395065","0.013476701","0.0074073044","-0.026385285","0.030367436","0.07436672","-0.053269297","-0.033952866","-0.009484058","0.004133166","-0.05322794","0.0070823296","-0.0798396","0.01951424","-0.001967122","-0.014434131","0.043102626","-0.0720324","0.098417714","-0.04794952","-0.03756483","-0.011529434","-0.024027282","-0.123118415","-0.007819565","0.07982662","0.017467655","-0.01112321","0.03140823","-0.021737548","-0.07107","-0.028465562","-0.021594364","0.05300542","0.031385995","-0.022642162","0.056183055","0.0012510918","-0.006829264","-0.012379904","0.14022389","-0.0880572","0.0017530792","-0.017229449","0.031511363","-8.7159005E-4","-0.036027357","0.10220882","-0.06519633","-0.055514243","0.007951093","0.11250086","-0.058934994","0.00306392","-0.037687626","-0.0056415205","-0.053592615","-0.0019429802","-0.010308266","0.022344343","-0.01734771","0.03099102","0.096511975","-0.035018522","-0.008532591","0.018383758","0.03523479","-0.12430628","0.009298924","-0.034608997","-0.06356781","-0.009359812","-0.04673784","0.035758898","0.017416542","-1.7070375E-33","0.078454256","0.046198223","0.005063287","0.03162967","-0.13618284","0.02971831","-0.017373791","-0.0013930826","-0.04177258","0.053200778","-0.019099528","0.003417971","0.012332807","-0.027997946","-0.04796604","0.027986212","0.022387605","0.13422972","0.045646075","0.08909676","0.06087223","0.09096858","-0.0029397367","0.010820467","0.030661795","-0.01796784","-0.039263036","-0.12949525","0.039954145","0.030728338","-0.04138551","-0.029581545","0.019441945","0.01942688","-0.0046636676","0.029604945","-0.102301165","-0.05263381","0.029205026","0.0069516054","0.03359466","-0.002741232","-0.011932794","0.035329532","-0.008672662","0.02979805","0.082521796","-0.013973614","0.05879933","-0.025946094","-0.018862538","-0.0061361217","-0.05565372","0.013647486","-0.049344093","-0.025017148","-0.053850606","0.097631164","0.03560963","-0.05384693","0.043125685","-0.05070714","-0.06799269","0.016032662","0.033665195","-0.18056715","-0.00526288","0.09244178","0.081770755","-0.093392886","0.020146769","-0.017508471","-5.1602715E-4","0.069295935","-0.012389168","0.011839134","-0.057004634","-0.0057388544","-0.08893684","0.077051125","-0.1274876","0.027675333","-0.059556417","0.041309204","-0.015355141","0.13355377","0.0759069","-0.071157806","-0.03316951","0.00435578","-0.11178566","-0.082606085","0.019802134","0.081755295","-0.003109307","-6.9373296E-34","0.014077802","-0.14033253","-0.011546334","-0.008554988","0.06649955","-0.047326848","-0.02370341","0.07424104","-0.054536078","-0.01170872","0.03194719","-0.10523576","-0.013850114","-0.015789907","0.008077539","0.08676839","0.009713586","0.009474048","-0.06976188","0.07655041","-0.04788712","-0.05136756","-0.023212627","0.0774473","-0.021102505","0.0421823","0.11188471","-0.068546504","-0.06210491","0.02775407","-0.056375206","0.032291424","-0.12311214","0.09360325","-0.007047935","0.06183752","0.0062763984","-0.01615822","-0.041131485","0.0504122","0.014524098","0.06312602","0.026252888","0.058349315","-0.019981757","-0.01116095","-0.027538912","0.018555308","0.043717306","-0.1103905","0.008966881","0.012623748","-0.041426532","-0.06992647","0.024764951","0.03838877","0.059446868","0.012502282","0.012336913","-0.014676104","-0.059447005","0.01863701","-0.04181892","0.118754864","-0.06466402","0.008508075","-0.039634492","0.026472352","-0.05355123","-0.07526901","0.039449107","-0.1521057","-0.009857894","0.014252465","-0.0010345874","-0.030958258","-0.029532317","-0.0021600982","0.044406373","0.014280332","0.032239884","-0.0027163082","-0.05815433","0.041913338","0.0010066439","-3.1254665E-4","0.016697152","-0.068082735","0.04734793","-0.038516767","-0.026516443","0.024607856","-0.01962641","-0.004329579","-4.4914873E-4","-2.3383361E-8","0.06537479","-0.0021327946","0.004820276","0.05746547","-0.03956294","-0.044472177","-0.039529946","0.03594325","-0.049629867","0.025051495","-0.023076488","-0.01516293","-0.05497774","-0.062754944","0.04914141","-0.045488313","-0.032095324","0.058464687","0.013724112","-0.02231595","-0.020256596","-0.025201535","0.008373666","-0.11747197","-0.050578024","0.026789958","-0.003230549","-0.04514674","0.08153974","-0.024033032","0.057706207","0.039370805","-0.07795853","0.0036890577","0.08342794","0.040713537","0.064133175","-0.08294261","0.020464832","-0.027797846","-0.010556354","0.039400563","0.016663516","0.057037134","0.047658477","0.059743818","-0.004738011","-0.039142676","0.053882748","0.009375707","-0.017946448","-0.01342866","0.017534256","0.060278628","-0.034348555","-0.016260438","0.032520983","0.01070139","-0.06111195","-0.036327932","-0.004836589","-0.014632771","0.01570779","-0.069426626"]</t>
+  </si>
+  <si>
+    <t>NK-3wTqAJRDsxpTUgktNmzJFg</t>
+  </si>
+  <si>
+    <t>DONG HUA 9</t>
+  </si>
+  <si>
+    <t>Entity Name: DONG HUA 9 | Type: Vessel | Jurisdiction: Unknown | Risk Context: 07110 - FIRE SAFETY - Fire fighting equipment and appliances (no responsibility of RO)14811 - POLLUTION PREVENTION - BALLAST WATER - Ballast Water Management System (no responsibility of RO) | 07109 - FIRE SAFETY - Fixed fire extinguishing installation (no responsibility of RO) | 03104 - WATER/WEATHERTIGHT CONDITIONS - Cargo &amp; other hatchways (no responsibility of RO) | 14104 - POLLUTION PREVENTION - MARPOL ANNEX I - Oil filtering equipment (no responsibility of RO)</t>
+  </si>
+  <si>
+    <t>["-0.032288555","0.049088202","-0.015631165","0.025968747","0.1295939","0.0016227366","0.026478186","0.044100568","-0.104948364","-0.051543508","0.107622914","-0.011009245","-0.0010053712","0.012730291","-0.037678372","0.023576066","-0.018673053","-0.062208757","-0.05104101","-0.047531623","0.057882242","0.0060055987","0.0048862994","-0.0017117033","-0.08729421","-0.016046233","-0.016384723","0.055079315","0.013566664","-0.06095581","-0.014107606","0.08688004","-0.02274959","-0.011273918","0.045727074","-0.025954844","0.0010858017","0.0107082445","-0.056383006","0.0016694887","0.027399039","-0.10638502","0.07850927","-0.026809284","-0.02570106","-0.03335455","-0.005331843","-0.060345046","-0.022210473","0.022118857","0.00258719","0.0045765154","-0.042997666","0.084021166","-0.008469069","-0.086588115","-0.018880095","0.01735991","0.0032543237","-0.011570462","-0.021573024","0.091503404","-0.1043099","0.029232306","-0.038728304","-0.02586961","-0.04331972","-0.020296492","0.017786294","0.017090257","0.059476655","0.013865423","0.05327193","0.029701464","-0.009218493","0.002409181","0.0012777335","0.03670632","0.040299963","-0.055468813","-0.011888888","0.014399456","-0.009178359","-0.026669962","-0.005772923","0.0675577","-0.017632408","0.016511394","-0.001442013","-4.928852E-4","-0.09046507","-0.0042387974","0.10509142","0.08398751","-0.036911756","0.021272665","0.055848546","0.030542716","-0.12015179","0.032877874","0.049254846","0.055076476","-0.07866004","-0.022949547","-0.053014454","-0.031199124","-0.07085113","0.017431563","-0.027782328","-0.064601086","-0.0017249639","-7.358088E-4","-0.075088434","-0.07722206","-0.0338219","-0.025593128","-0.11472587","-0.025989471","-0.010421517","-0.111751825","0.003305041","-0.02125862","-0.029600097","-0.07704472","0.027674045","-0.024814075","0.039098326","3.553919E-33","0.023185775","0.037548453","-0.07672132","0.02605599","0.048218742","-0.0019388889","-0.022582902","0.022143105","-0.057365697","0.11406808","-0.03731715","0.053167805","-0.09684273","-0.07390116","0.07771345","-0.03338954","0.013173373","0.03441511","-0.01082346","-0.04244505","0.010057359","-0.028848797","-0.04541855","-0.057472914","0.043623526","0.05949614","-0.0147957085","-0.044850163","0.036614314","0.08428968","5.950602E-4","0.032487314","0.020133961","-0.024541808","-0.0011358964","-6.3185894E-4","-0.10284762","-0.10687577","-0.13302217","-0.042642474","0.020021606","0.006072486","-0.03145283","0.032195702","-0.001730334","-0.02636868","0.042340767","-0.0025002712","0.09590912","-0.014402065","-0.042830758","-0.005557766","-0.014031569","0.009292519","0.049206752","-0.04225738","0.015114494","0.040216584","-0.017114779","-0.026824398","0.006713467","-0.022251232","-0.051842272","0.048942674","0.06844812","-0.05675405","0.10846941","-0.06878014","0.10845451","-0.11009486","-0.017532546","-0.0117040705","-0.0010798001","0.048673324","0.014374273","0.011883826","0.0072295787","0.03408455","-0.068592675","0.07255874","-0.12660661","0.033589978","-0.014059706","0.07153414","0.014416288","-0.0101825455","0.05548567","0.042040568","-0.0671424","0.054970205","-0.054486815","0.003394147","0.027487732","0.027200308","-0.025783287","-3.8199783E-33","-0.059546288","-0.005525821","0.011045425","-0.05110692","0.040859926","-0.021732144","0.08303259","-0.025717286","0.088099785","0.01680296","-0.047581792","-0.013912257","0.07837574","-0.038213126","0.07163352","-0.007257627","-0.042099487","-0.0055393334","0.00423141","0.0664288","-0.01229563","0.07291662","-0.03335856","0.11328606","-0.07842582","0.071332306","0.04787131","-0.05366584","-0.07466576","9.1659086E-4","-0.018637951","-0.022112207","-0.062433325","0.10185541","-0.1118192","-0.08866514","0.102058664","0.038861252","-0.06432363","-0.029703353","0.07506653","0.03358843","-0.039575957","-0.0062789097","-0.089185044","-0.10691067","0.0073993327","-0.09823122","0.02466147","0.03471795","0.009468805","0.012878447","-0.0688848","0.011633031","0.04804923","0.013340525","0.005047147","-0.032016546","0.042209797","-0.031036498","0.099607006","0.080584764","-0.055263497","0.17634033","-0.0032398365","0.050201397","4.6640544E-4","-0.013216524","0.032400105","-0.060172126","0.06842324","0.006863589","-0.026149508","0.036226925","-2.0033949E-4","-0.09793145","-0.061690744","0.048231505","-0.036213133","0.06424904","0.070237614","-0.049350694","-0.04630454","0.06829702","0.001076762","-0.069800004","0.039899357","0.03392616","0.1279473","0.010056211","-0.012275787","0.028932733","-0.14180657","0.042206366","-0.03598769","-4.4278853E-8","-0.0035543027","-0.0062260167","0.0025205202","0.05360939","-0.06392549","-0.07004851","0.010977284","0.023345696","-0.040484384","0.037401013","0.04943656","-0.012094921","-0.004182719","-0.017616037","0.00301198","-0.079167806","0.039449804","0.10071419","-0.04968318","-0.043212917","0.018489197","-0.004932217","0.023333685","-0.013491347","0.0018462066","0.044322595","-0.02839671","0.029162595","0.08298468","0.02364713","0.030884748","0.012443612","-0.024700614","-0.0011070217","0.0054773428","0.041949768","0.080425456","-0.025063578","0.0119376425","0.02163338","0.036738645","0.0129510015","0.033602394","0.06019546","0.049336724","0.03308258","-0.04769183","-0.04316659","0.022031693","-0.010534879","-0.01650123","-0.077064216","0.055096444","0.036005143","0.002527747","-0.04049509","0.02638236","0.024533745","-0.03338611","0.0071000527","0.040354334","0.050109748","0.04679096","0.025319602"]</t>
+  </si>
+  <si>
+    <t>NK-3zGaGguoqRoQXkg4UaeWjR</t>
+  </si>
+  <si>
+    <t>Mikhail Ulyanov</t>
+  </si>
+  <si>
+    <t>Entity Name: Mikhail Ulyanov | Type: Vessel | Jurisdiction: ru | Risk Context: 1.1 | Shipping sanctions: a specified ship is prohibited from being provided with access to or having its master or pilot cause it to enter a port in the UK, may have its registration on the UK Ship Register terminated, and a master or pilot of a specified ship may be given a port barring direction, a detention direction, and a port entry direction or a movement direction. IMO number: 9333670 Transport crude oil or petroleum products or mineral products that originate in Russia or are exported from Russia and practice irregular and high-risk shipping practices as set out in the International Maritime Organisation General Assembly resolution A.1192(33).</t>
+  </si>
+  <si>
+    <t>["-0.05929426","-0.028914073","-0.06764023","0.017012095","0.058149707","0.021780137","0.0712325","0.022303268","-0.061466917","-0.045944296","-0.00493052","0.076911174","-0.056362852","0.086872935","-0.083974645","-0.003093368","0.041636333","-0.07560037","-0.0195134","0.031881377","0.027267225","0.044642955","0.0022776444","7.499515E-4","-0.064246394","-0.008399623","0.04372383","0.038324594","0.068391204","0.0042989342","-0.04145277","0.014436095","-0.019519053","0.08060418","0.06345394","0.03707974","-0.07495677","-0.07830331","-0.02662786","-0.01899229","0.07154323","-0.08911763","0.00934954","0.088742085","0.013710574","0.0055253417","-0.050131936","-0.06225259","-0.045813244","-0.013659327","-5.092893E-4","0.05516933","-0.023020811","-0.003140848","-0.022087775","-0.1348345","-0.032907337","-0.05407493","-0.056733813","0.08406953","0.05566726","0.037141375","-0.050514832","-0.04962444","-0.037650514","-0.031110326","-0.015877241","-0.019450942","-0.03188766","0.10834394","0.030297652","-0.08156786","-0.09816863","0.03504887","0.0070121004","-0.060804207","0.010022752","-0.004412656","-0.0017109049","-0.02470266","-0.037553627","-0.02266173","0.024718724","-0.07284213","-0.07198111","-0.022876495","0.016140584","0.01717978","0.07758192","0.045883007","0.00926622","-0.048723765","0.13765708","0.059714735","-0.01368466","-0.0023829876","0.064891815","0.041852444","-0.024466107","4.098319E-4","0.005246929","0.051432937","-0.100095436","0.036560133","-0.12200096","-0.05001715","0.015599746","-0.041845847","-0.04239198","-0.04071425","-0.042010117","0.02564363","0.0038415457","-0.048088986","-0.056792185","0.0050170925","-0.065628685","-0.01983827","0.025870396","-0.02423487","-0.009826871","0.05265547","0.09774031","0.03121509","-0.053448115","0.03955374","-0.0036202983","-8.728838E-34","-0.031741414","-0.024044342","-0.09248133","0.0068299165","-0.040893577","0.07820486","-0.067962885","-0.01564667","-0.010317736","0.10595123","-0.062062796","0.028397003","-0.011306677","-0.015749725","0.018422106","0.0570274","0.05570211","0.05695576","0.035450507","0.039720036","0.074748285","-0.08328091","-0.029271327","-0.05429881","-0.014013617","0.061340623","-0.06382014","-0.03716014","0.055951744","0.02933727","-0.02860909","-0.0025001206","0.011277439","0.024761973","-0.042031687","0.023843637","-0.08876246","-0.021249326","-0.0316252","-0.0020526992","-0.020212254","-0.02354073","-0.070989415","0.04866932","0.022377176","0.03795221","0.04243699","0.016834287","0.030852787","-0.014914381","-0.05508187","3.531866E-4","-0.0037526886","-0.01812103","-0.008923594","-0.048839595","0.036799222","0.07603182","-0.009531827","-0.097465366","0.007078667","0.019847112","-0.0070718583","0.036545664","0.11310991","-0.05390869","0.016693631","0.017528778","-0.028632924","0.002380588","-0.03484323","-0.0025399227","0.023399401","0.028498353","0.0018604187","-0.04575766","-0.042622615","0.051907156","0.01304906","0.04894775","-0.14243135","0.06697437","0.033539996","0.028949676","-0.049682427","0.037700996","-0.04688615","0.02147188","0.01244462","0.01396744","-0.048865363","-0.037498813","0.02890537","0.016765416","-0.00590306","-2.402589E-33","-0.025079206","-0.025924617","-0.0797278","-0.0053341193","0.05074184","0.01579885","0.13908364","0.008066504","0.014320054","0.04755587","-0.0025216416","-0.027508767","0.059584048","-0.0119337225","0.02317831","-0.043903418","-0.012637144","0.13862865","-0.04156733","-0.023857044","0.05008096","-0.0038796868","0.030606784","0.062949084","-0.086002395","-0.017553438","0.11991397","-0.09708922","-0.116859004","0.026150484","0.035695825","0.0835434","-0.051591672","0.077334546","-0.10035803","-0.035954222","0.018671865","0.08784206","-0.09574421","-0.033317856","-0.012965775","0.037673008","-0.020455606","0.09557163","-0.063256286","-0.02630041","0.051362272","0.0010658051","0.10715399","-0.04930751","-0.014703011","0.018624116","0.041911174","-0.036338683","-0.002913323","0.04821433","-0.021464134","-0.05766182","0.06662056","0.06236294","0.09371942","0.02730034","0.0105246175","-0.0013113733","-0.0018853823","0.056232594","-0.06064417","0.024760623","0.07027717","-0.025935879","0.05451833","-0.10483333","-0.03857886","0.059697505","0.020318888","-0.03469775","0.0032719057","0.015010339","-0.030612394","-0.011528727","0.06340609","-0.01979506","-0.04311516","0.08097907","0.05375629","-0.08899334","0.044470377","-0.03758753","0.044898074","-0.06421002","-0.04056691","0.021700075","-0.10306476","-0.035830297","-0.069703214","-4.2868592E-8","-0.011840477","-0.075242214","0.032225143","0.04967433","-0.07214533","0.02973309","-0.054413732","-0.030762684","-0.03472272","0.03677304","-0.003484667","-0.028503744","-0.07613944","0.0038063372","1.040731E-4","-6.021692E-4","0.026571838","0.06599149","-0.031538963","0.0023297733","-0.03781564","-0.023238538","0.030386016","-0.033576094","-0.0757949","-0.01184355","-0.0024824878","0.052336134","0.13197853","-0.012978451","0.051446464","0.038108878","0.011267455","0.13507499","0.011942921","0.020262811","-0.017740432","-0.02393629","-0.018226285","0.018020032","-0.06368118","0.038788665","0.03154578","0.06100276","-0.027956521","0.045932457","-0.12619306","-0.058182746","0.010485846","0.015647894","0.048657622","-0.06420813","0.069118105","0.088880844","0.07393685","0.032341715","-0.011038024","-0.061006643","-0.021539746","0.033522412","-0.00414021","0.008766318","0.042673055","-0.0013599482"]</t>
+  </si>
+  <si>
+    <t>NK-43tNXzjCgvhSKuSaG69pV5</t>
+  </si>
+  <si>
+    <t>SAMUEL L FORD</t>
+  </si>
+  <si>
+    <t>Entity Name: SAMUEL L FORD | Type: Person | Jurisdiction: us | Risk Context: 1128a1</t>
+  </si>
+  <si>
+    <t>["-0.0029747705","-0.069127895","-0.054210093","0.03064107","0.03769038","0.076290324","0.04902249","-0.010352998","-0.04444693","-0.013181064","0.022468714","-0.023790548","0.040554225","-0.008078922","-0.033347312","0.08238432","-0.004630172","0.021811","-0.049241733","-0.0028549028","-0.0010662065","0.08367131","-0.022401763","-0.01697746","0.009401394","-0.054928306","-0.016441587","0.006150688","-0.0016769129","0.002136351","0.024908636","0.0243774","0.027963968","0.048940293","0.10485566","-0.047239013","-0.065542184","0.047775723","0.019373741","-0.09198666","0.032313284","-0.066746905","0.06667684","0.009685639","-0.054202814","-0.01310039","-0.025979396","-0.03448776","0.035765216","0.07602723","-0.07167109","0.03565003","0.006110582","-0.034279756","-0.020499295","-0.03073616","-0.056883074","0.05742778","-0.08215896","0.011145618","0.03311815","0.017584208","9.6736714E-4","-0.008561617","-0.014413479","0.008331152","-0.0033415076","-0.0045294347","0.038306322","-0.07194493","0.089567624","-0.0049604024","-0.12186986","0.018487241","0.003976604","-0.017903063","0.05912839","0.061047673","0.032463063","-0.026337499","0.0011808982","-0.020532968","0.015682962","-0.017541217","-0.093899995","0.0029283438","0.02763136","-0.038759008","0.029398551","0.021426046","-0.015708463","-0.11795774","0.11127589","-0.0057474817","0.015559425","-0.029568102","0.010236064","-0.06379497","-0.04834207","0.07713077","-0.055023048","-0.0470639","-0.029748887","0.07328403","-0.09709549","-0.042789314","-0.08093653","0.010405191","-0.025641378","-0.017710483","0.06908313","0.09323966","-0.022362908","0.039131273","0.044961914","-0.080666795","-0.076722875","0.015928784","0.058360904","-0.04557089","0.018209836","0.014300102","-0.07229854","-0.016595224","-0.10051365","-0.023427702","0.04377158","-2.0487827E-33","0.06148592","0.035122886","0.055228747","0.04294733","-0.0403488","0.021147707","-0.016809711","0.0045116516","-0.010417239","0.019600049","-0.010609832","0.01950605","0.0778176","-0.05180452","-0.111455776","0.017668318","-0.03501794","0.048634857","0.0059546656","0.006718796","-0.017447334","0.028382372","-0.0056717107","0.03308278","0.03166645","-0.02387963","-0.026287397","-0.040403474","0.018090343","0.06575173","0.0018632261","0.04849604","0.036761694","0.06436203","0.1259455","0.04368705","-0.091817714","-0.09178791","-0.06208595","-0.04641982","0.049453285","0.09878439","-0.021038344","0.09751963","-0.09171418","-0.021608463","0.039583232","0.0038843234","0.004261247","0.04579887","-0.06301207","0.045830615","-0.05102232","-0.0844824","-0.05960679","-0.019978737","0.019252565","0.10294616","0.014391919","-0.10299544","0.0321556","0.026390612","-0.05645494","0.022554724","0.016965095","-0.09711423","0.0025397856","-0.058804654","0.058876734","-0.05027428","0.06672485","0.062799826","0.029113192","0.010274914","-0.0038769084","0.031006832","0.0013014354","0.017212532","-0.020127354","0.034967087","-0.15836926","-0.0017306587","0.009655756","0.019153021","0.008295894","-0.017827917","-0.031153064","-0.05139956","0.02209027","0.0064471066","-0.021947494","0.009173246","0.018698063","0.041003082","-0.023028847","-1.642784E-33","-0.10642704","-0.096565805","0.019628119","-0.030582523","0.061948225","-0.11265651","-0.021337697","0.008620547","0.041364204","0.023429094","-0.013664881","-0.04676382","0.023395065","0.03554805","0.095408276","0.0013396563","0.030298976","-0.035443462","-0.038863152","0.1016865","-0.011635585","0.008945985","-0.056256987","0.017607551","0.0014152764","-0.029637953","-0.018507656","-0.058335222","-0.031267274","-0.07205018","-0.03595176","0.05817912","-0.046130173","0.08952681","-0.0814125","-0.047411393","0.090800345","-0.07511818","-0.026654145","-0.001983228","-0.015790628","0.08859041","0.007294654","0.049131546","-0.0017780501","-0.07085717","0.040635724","-0.065605","0.063477814","-1.7137152E-4","-0.014183779","0.033856433","0.0023604245","0.0045095356","0.026522664","0.007232188","0.09539971","-0.05645334","0.0144173335","0.077754386","-0.021575008","0.054512892","-0.008094197","0.114134215","0.0039195623","-0.031830963","-0.114932284","-0.028263263","-0.001664847","-0.15191486","0.041440014","-0.12029902","0.0034157191","8.0677413E-4","-0.06868846","-0.06891945","0.021447077","-0.0347131","-0.011710745","-0.030593934","0.058729127","-0.058105953","0.014968902","0.0446607","0.058496293","0.047964506","0.027491331","0.029364826","0.06540275","0.042414226","0.00231216","-0.06828756","-0.05739803","-0.010996549","-0.08936472","-2.6602146E-8","-0.025511283","0.02354461","-0.024649872","0.047930066","0.025983851","0.05170856","-0.005145047","0.044068016","-0.04034423","0.03202994","0.0022148532","0.05437118","-0.027175656","-0.076272406","0.026069492","-0.060745236","-0.043859612","0.043994077","-0.002803693","0.10163673","0.014937682","0.0014340006","-0.017456673","-0.06077281","0.015127937","-0.038093206","-0.00434611","-0.0031748032","0.028291035","-0.07441729","-0.07939031","0.12555234","-0.04697194","0.008932518","-0.030096218","0.001231788","0.112862356","0.014924663","-0.015875382","0.02252136","0.067628466","0.11582222","-0.029521829","0.040316757","0.09800733","0.06401152","-0.04008708","-0.048058257","0.0020655263","-0.06367249","-0.05883483","-0.06357598","0.033855032","0.10182966","0.0143432645","-0.0652033","0.013805675","0.020860305","-0.015739674","-0.06142729","0.007113576","0.019363344","0.034151077","-0.037589528"]</t>
+  </si>
+  <si>
+    <t>NK-48vpWnBDsvRetrA6Z3yVJz</t>
+  </si>
+  <si>
+    <t>JOINT STOCK COMPANY 'STATUSBANK'</t>
+  </si>
+  <si>
+    <t>Entity Name: JOINT STOCK COMPANY 'STATUSBANK' | Type: Organization | Jurisdiction: by | Risk Context: 1, Part 2</t>
+  </si>
+  <si>
+    <t>["0.03839426","-0.003973116","-0.082741454","0.014086065","-0.033044476","0.019409612","0.038974762","-0.011128068","-0.0092484895","-0.046361726","0.057705786","-0.016168833","-0.0064831506","-0.03656771","-0.03696049","0.037543967","0.035400983","0.04351047","-0.041158777","-0.030312542","0.015561921","-3.957379E-4","-0.010990016","0.01455048","0.0053234743","-0.035103828","-0.04224642","0.060325142","0.019231083","-0.058280498","-0.022251062","0.06625182","0.052233133","0.05160153","0.06694416","0.015093808","-0.03134045","-0.045331683","0.076661915","-0.03416704","0.009767394","-0.043844588","0.058889024","-0.010239579","-0.01986885","0.01970095","7.5045056E-5","0.013382678","0.028276984","0.05243094","-0.049266126","-0.08976865","0.047180492","0.052315727","-0.008726576","0.039252903","-0.07382036","-0.017858775","-0.07932843","-0.0026424117","0.031323414","0.04162485","0.04428712","0.04261003","0.04505233","0.0040688566","0.048427578","0.08516488","-0.07122851","-0.0760637","0.047498737","-0.06339108","-0.13728137","0.016677056","-0.12407867","0.01020921","0.025652511","0.07283402","0.08088318","-0.07483831","-0.029530864","0.06549724","0.036023166","-0.048537336","-0.034395967","0.026827838","0.051071502","0.021328734","0.030902037","0.018961666","-0.052559815","-0.054299656","0.1738839","0.003696372","-0.017567463","0.010414479","0.030796248","-0.01533101","0.027644526","0.029110556","0.038623564","0.01876781","-0.032108586","0.030976668","-0.0572646","-0.0102953045","-0.057815813","-0.012996667","0.056964755","0.029102506","-0.051962256","0.10308842","-0.08344349","-0.07403068","-0.05002705","-0.031131487","-0.065011874","0.018638385","0.06523084","-0.14203668","-0.021717764","0.04203486","-0.06066967","-0.08607551","-0.07904401","0.02851589","-0.05696485","-3.327176E-33","0.002395999","-0.01001348","0.047873247","0.027523465","-0.038208295","0.028472548","-0.01996674","-0.029111275","-0.14899588","0.04537967","-0.0059619904","-0.008987071","0.0057870047","-0.10562166","-0.054578863","-0.044489548","0.012217966","0.062798604","0.064821854","0.024030805","-0.015342704","0.02323718","-0.0519067","0.061425004","0.061593812","-0.033580933","-0.022844337","-0.050490797","-0.02912913","0.04268303","0.0838746","-0.013240827","0.0059265844","-0.03332675","0.058969315","-0.020822471","-0.05538624","-0.015710618","1.9501458E-5","-0.02513111","9.971266E-4","-0.01639575","-0.019927112","0.02242933","0.012645844","0.04757324","-0.050734352","0.023680197","0.056772944","8.86746E-4","-0.07342256","-0.025638819","-0.008130604","-0.0712139","0.03052141","0.050134294","-0.02332765","0.06344262","-0.050324135","-0.05632452","-0.0622061","0.017409587","-0.088850245","-0.013381401","0.014376921","0.088249326","0.0044768224","-0.009310525","0.026527673","-0.0038694034","0.039989367","0.02707567","0.06381864","0.094441764","-3.064331E-4","-0.026920939","-0.02827818","0.03957268","-0.0325373","0.044612844","-0.06666986","-0.008414408","-0.05692177","0.09187247","0.027970718","0.043568507","0.022851152","-0.08861384","-0.08845835","0.016070522","-0.07220245","0.025445756","-0.0016343604","0.080023825","0.05141241","3.211916E-34","0.019266164","-0.052841563","-0.032031324","-0.1015153","-0.016809918","-0.06624306","0.024525613","-0.00934744","-0.05372812","0.056610446","-0.0053482405","-0.07518373","-0.07182397","0.015632136","-0.022328468","0.038478065","0.012738843","-0.021655822","-0.025437178","0.11663201","0.029482832","-0.043744706","-0.0054249717","0.1275533","0.024145031","0.04099112","0.0017021409","-0.06432616","0.01910355","-0.042843387","-0.017333752","-0.03709743","-0.05798129","0.089521736","-0.10090601","-0.12145994","-0.0047583976","-0.13009472","0.023050703","-0.06474262","-0.01671681","0.107127704","-0.04037387","0.027319549","-0.013267348","0.025931971","0.009085276","0.01149797","0.017404202","-0.07051252","-0.057967927","0.036025584","-0.040427368","0.06211027","5.97593E-4","0.037276443","0.06000531","-0.011969671","-0.006121766","-0.030231552","0.021920951","0.10721183","-0.0067839925","0.13812654","0.011751368","-0.04400738","-0.08240208","-0.010049569","-0.0074402303","-0.08141697","0.037930965","-0.049596317","0.0036410717","-0.024615763","0.034651473","0.037741136","0.019690681","-0.09265163","-0.051769663","0.039318424","0.041774772","0.05166989","0.018316189","0.07756309","0.04322364","0.0241007","0.04883208","-3.495282E-4","0.060993828","-0.0035497355","-0.012812911","-0.012021155","-0.02816731","0.022140566","-0.060256407","-2.613957E-8","-0.021658313","-0.0336273","-0.022030428","-0.06575113","0.023131631","-0.042839956","0.0015270223","-0.02544673","-0.03333138","0.06369087","-0.0109554995","0.01733183","-0.15635924","-0.0098712435","-0.02500875","-0.034489304","-0.07000103","0.07726509","0.030367931","0.04246836","-9.3109446E-4","-0.03628731","0.03244919","-0.0356598","0.01673664","-0.021293668","0.076899566","-0.018560736","0.111909375","-7.6018606E-4","0.013302055","0.10319392","0.02833697","0.0051487302","-0.029346278","0.020750731","0.11157958","0.03242865","0.0011101514","0.022235457","-0.027922917","0.047309577","-0.008342231","0.045855653","0.11260529","-0.0042638173","-0.009086555","0.008304961","0.06874311","-0.12044191","-0.03612349","-0.023522496","0.03394302","0.08190361","-0.06677852","0.002434127","-2.3436914E-4","0.034201667","-0.011926521","-0.06510647","0.050058767","-0.048150208","0.05058422","0.03801864"]</t>
+  </si>
+  <si>
+    <t>NK-4EJDdfpAJBeJK4XxhuhZHM</t>
+  </si>
+  <si>
+    <t>Tureya OOO</t>
+  </si>
+  <si>
+    <t>Entity Name: Tureya OOO | Type: Company | Jurisdiction: ru | Risk Context: Executive Order 14024 (Russia)</t>
+  </si>
+  <si>
+    <t>["-0.030574853","-0.02122929","-0.05536537","-0.0025240022","-0.015884569","0.027570512","0.07009325","-0.024907151","0.0049652387","0.01318836","0.020809216","-0.02353663","-0.021811863","-0.021752615","-0.04294875","0.031332243","0.09041913","-0.019989677","-0.034647316","-0.04058509","0.033542246","0.009240535","0.017172769","-0.0054797013","0.008097755","-0.02540899","-0.048280198","-2.002827E-4","0.0023267518","-0.08535875","0.067763925","-0.008589445","0.06296444","0.036845487","0.07647008","0.059100445","-0.02968477","-0.10854868","0.04505543","0.028464844","0.047410943","-0.03428955","-0.0077015916","0.06959369","-0.025913723","-0.022962162","-0.04271403","-0.010511962","0.00540511","0.0045721508","-0.047917537","-0.048541293","-0.052515145","0.0806918","0.011331025","-0.013518418","0.024970045","-0.0589767","-0.058811005","-0.012348976","0.048120115","-0.015355021","0.0053569796","0.022786217","-0.0260433","-0.009066965","0.059916902","-0.03640992","-0.06575785","-0.028767753","0.080650695","-0.0053327484","-0.08702406","0.0576945","-0.12541175","-0.013049285","0.043308012","0.06904015","-0.001714263","-0.058040984","-0.055706285","0.036246497","0.04347497","-0.03842824","-0.028953899","0.0095111","0.04396524","-0.05974869","0.06419114","0.06687113","0.019699777","-0.047844812","0.18044016","-0.026225321","0.008267066","-0.06776919","0.054983493","-0.024365347","-0.050347295","0.009615364","-0.05413789","0.027102295","-0.047641296","0.05207163","-0.14543767","-0.03024888","-0.09084832","-0.068180986","-0.036313917","0.037931018","-0.06124891","-0.0023087435","0.01920396","-0.03473034","-0.0059657875","0.01678488","-0.11516908","0.00666577","0.034573413","-0.13411868","0.028449476","-0.0062405593","-0.079714246","-0.030393004","-0.07644466","0.043294024","-0.013117169","-8.13703E-34","0.105246775","0.029523972","0.00914342","0.004902144","-0.0037758755","0.049072817","-0.05208948","-3.463429E-4","-0.076261505","0.057732902","-0.04449147","0.01968932","-8.1260875E-4","-0.10677821","-0.034625705","0.046652324","0.024246268","0.07809289","0.017695382","0.108156405","0.05163179","0.029076641","-0.06296118","0.057347268","-0.017335031","-0.007788579","-0.02147916","-0.08589071","0.007281805","0.05066946","0.023221722","-0.0416715","0.015302869","0.02558537","-0.045522045","-0.03486377","-0.061481513","-0.060639948","-0.0078963665","0.0045436053","0.06707462","8.1016624E-4","0.030347144","0.08573328","0.010424861","-0.014464927","0.039908253","0.0148503","0.13919689","0.022127112","-0.052624926","-0.008562939","0.005500342","0.020755844","0.01599759","-0.022000805","1.8287988E-4","0.072369896","0.030159246","-0.06415232","0.040556952","0.014353028","0.0055955895","0.0026405083","0.012536148","-0.07577193","0.033996508","-0.020944174","0.023247376","-0.03865887","0.044326656","0.045833014","0.05189797","0.05312835","-0.024895132","-0.06233406","-0.01440523","-0.0054849363","-0.0049360814","-0.011024456","-0.11519727","0.04325519","0.075020686","0.08903419","0.022749983","0.018669069","0.06718981","0.031183295","-0.049707018","0.042192478","-0.0888686","-0.019487604","0.033754706","0.040326916","0.047242202","1.2746284E-34","0.013307164","-0.11019997","-0.016347919","-0.035456467","0.027253717","-0.014573213","-0.004633309","0.05955693","0.011460733","0.048231497","0.048220046","-0.07097205","0.051417142","0.0044527138","0.06414676","-0.05150876","0.046178512","0.017565748","-0.102515616","-0.033719257","-0.008536432","-0.03606155","0.034329988","0.08323373","0.020814335","0.035463214","0.062993586","-0.09476839","-0.073385574","-0.013652426","-0.020073427","0.011655603","-0.09305214","0.1912049","-0.0695985","-0.045794673","0.0602532","-0.08922901","-0.07096075","0.017878465","-0.012458887","0.057079233","0.06730983","0.054405566","-0.11044078","-0.06357481","-0.02811901","0.0306909","0.021515312","-0.05825217","0.029908726","0.06359856","-0.04238061","-0.024175497","-0.02671532","0.020064935","0.018289521","-0.04010698","0.033062078","0.029963065","0.06278693","0.0972785","0.0050820997","0.0819759","-0.027450422","6.4403145E-4","-0.051453467","0.03450877","0.062073357","-0.0796995","-0.027378073","-0.1111941","-0.0515266","0.041426983","0.084645465","-0.02665238","-0.01629888","-0.020091938","0.019613052","0.0024614395","0.067422025","-0.0012871056","-0.022287192","0.079524286","0.021339811","0.008912287","0.03381226","-0.03405551","0.090319864","0.036848694","-0.051416755","-0.022665527","-0.047792517","0.072502606","0.00804813","-2.3787862E-8","0.013637475","-0.03763719","0.075716116","0.035657827","0.034939695","-0.08059754","0.0433174","-0.029097706","-0.061279763","-0.017076362","-0.016184121","0.016163768","-0.018264074","-0.045147885","0.015523786","-0.022403168","-0.0131450035","0.078732505","0.0113115655","0.054082267","-1.3969405E-4","-0.003334264","0.03186664","-0.1008488","-0.060661282","0.010178015","0.05868616","0.022444606","0.089959554","0.018219164","0.025881236","0.021686781","-0.033331946","0.06981941","-0.07959008","0.015423906","0.070985205","-0.024667121","-0.009957262","0.011065941","-0.020507973","0.014468872","0.02442743","0.04938595","-0.0021632104","0.06215954","-0.07579762","-0.07109697","0.03072558","-0.05467473","-0.08544671","-0.016938858","0.046449985","0.090138674","-0.106454276","-0.023983082","0.03534178","-0.012601829","-0.0078798765","-0.017084224","0.05030174","-0.07440327","0.046770003","0.024111902"]</t>
+  </si>
+  <si>
+    <t>NK-4JEDvUBY6SUqtKY6HKYwBx</t>
+  </si>
+  <si>
+    <t>LCU 2015</t>
+  </si>
+  <si>
+    <t>| 01138 - CERTIFICATE AND DOCUMENTATION - SHIP CERTIFICATES - International Energy Efficiency Certificate (no responsibility of RO) | 07106 - FIRE SAFETY - Fire detection and alarm system (no responsibility of RO)14104 - POLLUTION PREVENTION - MARPOL ANNEX I - Oil filtering equipment (no responsibility of RO) | 08107 - ALARMS - Machinery controls alarm (no responsibility of RO) | 01199 - CERTIFICATE AND DOCUMENTATION - SHIP CERTIFICATES - Other (certificates) (no responsibility of RO)</t>
+  </si>
+  <si>
+    <t>["-0.04690736","0.038267497","-0.05293682","0.029593144","0.11847802","0.04575032","-0.013215108","0.016394146","-0.026469624","-0.1177286","0.02440914","-0.026175963","-0.0031768803","-0.0054956474","-0.09972363","-0.04521933","-0.04689703","-0.0363664","-0.014374143","-7.3797285E-4","0.02782397","0.037210323","0.04532052","0.04454495","-0.06287848","0.036959037","0.003658401","-0.01593132","-0.014058219","-0.0560276","0.044141695","-0.0033677085","0.06284333","-0.035478134","0.08342763","-0.009925754","0.12309582","-0.020200226","0.0034819185","-0.01747721","0.015529419","-0.13117814","0.0023097054","0.009216163","-7.834562E-4","0.023084491","-0.013719795","-0.05319017","-0.071494155","0.045594428","-0.013247796","-0.021665825","-0.0421862","0.07141955","0.0011304176","-0.0674124","-0.10578596","-0.024295965","0.014477302","0.0061327927","0.03887674","0.027073147","-0.072745524","0.018491935","-0.012394209","0.012102033","-0.036267705","-0.004336395","0.012682915","0.0377318","-0.0037252444","0.03234257","0.031322904","0.03403338","-0.028639438","0.011842077","-0.011555723","0.0011059855","0.027088407","-0.118249536","-0.0138431145","-0.05084555","-0.04907343","-0.0131311575","-0.02000213","0.025165256","0.020426104","0.016476827","0.016905336","0.074678846","-0.0056986045","-0.06738548","0.12750894","0.016661234","-0.020768605","0.035069205","0.0074453023","-0.008501505","-0.010920584","0.013845158","0.07330975","0.044628408","-0.06293883","-0.035419818","-0.07797304","0.05467529","-0.10381854","0.0015073412","0.025651082","-0.04458613","-0.0042077317","-0.024528729","-0.060281083","-0.13674141","-0.031104784","0.028261337","-0.07496741","-0.033270165","0.09466851","-0.07896763","-0.02821295","-0.03000876","0.03020777","-0.029813241","0.011104901","-0.0046091904","-0.0059757647","1.2482622E-33","-0.0042179544","0.047088176","-0.07634757","-0.0014166598","-0.009806924","0.030472094","-0.02014763","-0.0011408963","-0.029334214","0.08871128","-0.011409591","0.090213194","-0.01708462","-0.0708473","0.01718078","6.7736657E-4","0.05165291","0.01503537","0.03777263","-0.029145868","0.018820988","-0.019210866","0.024518626","0.08910893","0.09997832","0.065003574","0.026937142","0.012202532","0.0072660935","0.05071586","0.100223914","-0.007196081","0.013089336","2.3861766E-4","0.04765921","0.062284913","-0.05207564","-0.08736343","-0.044727817","-0.09147484","-0.0079437215","-0.020496462","-0.008529941","0.08178511","0.06672863","-0.011326295","0.037971344","0.0656764","0.18698566","0.033130687","-0.04416376","0.009259223","-0.065142624","-0.063929744","0.058181003","-0.08459631","0.0049696774","0.0705083","-0.034879353","-0.036034547","-0.01883486","-0.02432915","-0.04935759","0.0039460924","0.04082754","0.024872676","0.033103853","-0.048116032","0.047310248","-0.083812274","-0.04577455","-0.0057455353","0.060225073","0.047546573","0.01839039","0.0060994644","-0.039784517","0.005479895","-0.02269331","0.080042385","-0.13898891","0.07087933","-0.014342141","0.036981363","0.038935013","-0.0054526757","-0.0020622802","0.059549555","-0.051400296","0.001463785","-0.006896554","0.0022633497","0.02321177","0.07633426","-0.03746676","-1.657121E-33","-0.022166967","0.025090542","-0.016813109","0.014471261","-0.06386797","0.01109982","0.035551663","0.0022201932","0.0554725","0.02123067","0.0011023834","-0.07154961","0.021291219","-0.053254522","0.007322808","-0.08066225","-0.029313412","0.03589992","-0.028515738","0.044592798","0.005796028","0.11008365","-0.051654175","0.12662059","-0.027831996","0.09796161","0.032626215","-0.02296286","0.03350523","-0.013851664","0.02297488","0.0075766225","-0.04114422","0.06833863","-0.12677446","-0.10012524","0.11253615","0.045479994","-0.021712815","-0.0130485995","0.066719465","0.042721346","-0.050322562","0.083507754","-0.10483885","-0.059286583","0.042106684","-0.04920129","0.010979537","-0.018980555","-0.024563575","-0.0362945","-0.06172688","-0.009453718","0.047430422","0.080840565","-0.032246724","0.053323194","0.044519804","0.013811617","0.100455366","0.062939554","0.024250962","0.11967629","-0.023493629","-0.027025193","-0.04717078","0.017184436","0.06641943","-0.023289487","0.07390975","-0.0059032724","-0.07407145","-0.04914018","-0.022966957","-0.067220286","-0.014529522","-0.0048147496","-0.09349096","0.027202038","0.016205657","-0.012541065","-0.04805774","0.101257816","-1.2795068E-4","-0.024444317","0.07235153","-0.062398326","0.07819008","0.04782197","-0.0524644","0.06798695","-0.043554105","0.052719668","-0.047504902","-3.018198E-8","0.025469055","0.0049477294","-0.044747427","-0.02351653","-0.0011361013","-0.030166456","-0.025951467","0.035623156","-0.13877292","0.020660384","0.03384932","-0.044677105","-0.06554786","-0.11997277","-0.010933905","-0.06076369","-0.018951736","0.071362175","-0.051821608","-0.009230356","0.07099506","-0.018350627","0.010183846","0.0060474975","-0.006033175","-0.012359008","-7.8532746E-4","0.08451754","0.07693586","0.014528957","0.027519105","-0.028019154","0.032916628","-0.03406234","-0.0036181053","0.025978737","6.261991E-4","-0.026781484","-0.015046979","0.038141564","-0.020172728","0.0010493909","-0.061166547","0.072686955","-0.06324697","-0.019786084","-0.119784474","-0.071995705","-0.0033332545","0.003708207","-0.021896482","-0.08440796","0.037229113","0.051481023","-0.01643414","0.05246969","0.03386336","-0.043850984","0.008751288","0.036661502","0.070275165","0.025553118","0.03289691","-0.01757811"]</t>
+  </si>
+  <si>
+    <t>NK-4NuBkHDmsSgYdX7t5L9nFG</t>
+  </si>
+  <si>
+    <t>GT HONOR</t>
+  </si>
+  <si>
+    <t>Entity Name: GT HONOR | Type: Vessel | Jurisdiction: Unknown | Risk Context: IMO number: 9258478 Are operated in such a way as to facilitate or engage in the violation or circumvention or otherwise significantly frustrate the provisions of this Regulation.</t>
+  </si>
+  <si>
+    <t>["-0.08250331","0.03844225","-0.03364017","-0.009513365","0.031735335","-0.025929552","0.093674004","0.030848794","0.048916023","-0.011219242","0.030729929","-0.0444876","-0.014524031","0.058128063","-0.053768713","0.06627389","0.045027077","-0.046506044","-0.07741625","0.037038468","0.04659757","0.05239074","-0.0785173","0.048627876","-0.11095952","-0.10830047","-0.016528547","0.049352612","0.03466221","-0.042476837","-0.04290266","0.06525772","0.08051921","0.02811821","0.02693184","0.04290258","-0.009126226","-0.03760935","-0.014814984","-0.05804616","0.0028365266","-0.09350137","0.040361013","0.045090638","0.044293106","0.022874016","0.018344056","-0.007796157","-0.0057116547","0.06557105","-0.035880856","-0.022962542","-0.037647624","0.052943286","-0.015655154","-0.03382231","-0.10623273","-0.031504422","-0.021806546","0.039727263","0.05080259","0.04360896","0.030631687","0.011947106","-0.03303483","0.025405735","0.0055119265","-0.009642182","-0.064127535","-0.02745825","0.110430084","-0.05791483","-0.02630521","0.0036254483","0.017529918","0.104306825","-0.027598264","0.029058851","0.070609435","-0.050010733","-0.006527951","-0.031008871","0.05498879","-0.06155907","-0.001447587","0.012553093","0.05644665","0.026755422","0.07595292","0.115356505","-0.023659589","0.0151220355","0.13847457","-0.0028604416","0.03638946","0.009591793","0.0071853055","0.012651689","-0.040237624","0.057692792","0.03762815","0.10016168","-0.09347376","0.0218657","-0.030255161","-0.0131369755","0.036491573","-0.035768364","-0.003990599","-0.05079759","-0.06689282","0.049290415","-0.010323972","-0.047087602","-0.022487866","0.028219352","-0.06818891","0.07121834","0.07701091","-0.063080035","0.008821099","-0.045643266","-0.046878923","-0.047827493","-0.06524759","0.032861594","3.8383536E-5","3.3873231E-34","-2.1968388E-4","0.02703231","0.037104093","0.006228966","0.013791207","-0.037926383","-0.059210964","0.02150833","-0.050181378","0.058662966","-0.090890974","0.030563142","0.03220347","-0.046751883","0.01325967","-0.031640463","-0.05440876","0.095093206","-0.008379907","0.005425838","0.043585904","-0.07012339","-0.09765383","-0.022776727","6.363701E-4","0.18857338","-0.038098384","-0.07793061","0.030650225","0.0510003","-0.014248883","-0.020082552","0.013453121","0.005039862","-0.025671061","0.018578129","-0.03039073","-0.0662664","-0.06267927","-0.020245198","-0.023543796","0.03616966","-0.086394355","0.018210612","-0.042538326","-0.007103538","0.07774177","-0.03761521","0.0674497","0.027953152","-0.08263543","0.0040514776","-0.062320825","-0.05510792","0.042437997","-0.07791774","-0.026054561","0.1281772","-0.020912567","-0.11571467","-0.013010441","0.033791","-0.040495556","0.018806241","0.017839376","-0.02430842","-0.038847595","-0.07762292","0.0526276","-0.05985614","0.03434438","0.03536504","-0.055208977","-0.028720979","-0.0049687717","-0.027209958","0.013758518","-0.009986523","0.0072405003","0.07574333","-0.118516475","0.046926066","-0.025964946","0.055835746","-0.003858509","0.06815809","0.05080064","-0.0036505144","-0.04657666","0.007194436","-0.022889093","-0.013040315","-0.031642023","0.06437766","-0.017089013","-1.8708503E-33","-0.018396612","-0.018316958","-0.013558475","-0.008860954","0.020630386","-0.035741057","0.039907537","0.0014219214","0.03695598","-0.021411676","-0.053548437","-0.015068383","0.01642271","0.019376485","0.04939347","-0.06982458","-0.0109235635","0.03498276","-0.078720234","0.03177752","0.07535034","-0.0062966365","0.01920384","0.08266184","0.014846567","0.05955898","0.047216438","-0.056216497","0.008615539","-0.040316023","-0.044260394","0.060586862","-0.04210934","0.06923463","-0.050977718","-0.076322526","0.1004187","0.041914605","-0.06080988","0.039254077","-0.03757408","0.054628637","-0.045532294","0.059541274","-0.12975109","-0.0034601467","0.09305967","-0.016108826","0.111590676","-0.023913156","-0.022116639","-0.0011177636","-0.017942447","0.06528575","0.02566426","0.03408475","-0.026870577","-0.018190458","-0.03030477","0.058996636","0.036067236","0.07838234","-0.008462783","0.03898761","0.033533458","0.052686907","-0.05874571","-0.028896462","-0.07537959","-0.016568694","0.07362736","-0.049419742","-0.054844335","-0.02366925","0.035552047","-0.11194716","0.0255172","-0.058823258","-0.04156752","-0.0010035178","0.09801933","-7.0024526E-4","0.0071472754","0.02257531","-0.049743336","-0.039497808","0.08397246","0.046956673","0.053444326","0.025860108","-0.038154446","0.04389533","-0.10613303","-0.05258614","-0.10976876","-3.8130082E-8","-0.012483212","-0.04938848","0.036918167","-0.0028482785","-0.058932945","0.010243454","-0.09082751","0.038247857","-0.0034294282","-0.011109852","0.044373844","-0.042086538","-0.01369251","-0.03544192","0.025118425","-0.087265","-0.019922974","-0.008515428","-0.00649129","0.0210378","-0.034449153","-0.032592427","0.026798591","-0.09977932","-0.014443833","-0.03188913","-0.013858076","0.010863176","0.03548886","0.027591974","0.043307204","0.09549472","0.04028943","0.048185837","-0.071409844","0.048637673","0.009183889","-0.0013340147","-0.067272596","-0.056934703","0.043197494","-0.0350953","-0.014342175","0.048938718","0.05201273","0.0595044","-0.05914377","-0.07251208","0.0064758807","-0.075769834","-0.018312598","-0.083949916","0.06867923","0.10136831","-0.0025378906","-0.03937741","0.10178335","0.0053964364","0.04849429","0.003843127","0.046543464","-0.015008327","0.044900477","-0.08339493"]</t>
+  </si>
+  <si>
+    <t>NK-4RSxEa6pqUwkFKcKqyoe7H</t>
+  </si>
+  <si>
+    <t>Tosse Silooha</t>
+  </si>
+  <si>
+    <t>| (Date of listing 01.12.2011) Date of listing 01.12.2011 The Director Disqualification Sanction was imposed on 09/04/2025. Tosse Silooha is a company involved in Iran’s proliferation-sensitive nuclear activities. It is involved in fabricating components for nuclear power plants such as cooling tower plants, and industrial chimneys. The company is also supporting the Government of Iran. Disqualified Tosse Silooha est une société qui participe aux activités nucléaires de l’Iran posant un risque de prolifération. Elle participe à la fabrication de composants de centrales nucléaires tels que les tours de refroidissement et les cheminées industrielles. Par ailleurs, l’entreprise soutient le gouvernement iranien.</t>
+  </si>
+  <si>
+    <t>["0.029323673","0.06552634","0.0013192698","-0.010741823","0.017474636","5.2665867E-4","0.07390198","0.03542925","-0.013701014","-0.027738692","0.012309003","-0.014376025","0.0022496737","0.017756222","-0.0670733","-0.048507247","-0.043632213","-0.023920193","-0.0022212963","-0.09284773","0.044685498","-0.060818393","0.06394529","0.052096225","-0.016992794","0.0023385994","-0.049269397","0.016389126","-0.040026035","-0.045347873","0.009307004","0.09916066","-0.021303644","-0.10155357","0.07726847","0.024112033","-0.05511902","-0.08185774","-0.004802455","-0.01278697","0.02264508","-0.05267235","-0.09024932","-0.051761147","-0.13776174","0.007307152","0.044043258","-0.037792295","-0.06982586","-0.041393608","0.06291844","-0.08098018","0.06735668","-0.020352071","0.028005786","-0.07937082","0.063520096","0.0021948684","0.018201096","0.08666643","0.10171356","-0.048184596","-0.038700886","0.020999502","0.06765105","-0.052390683","0.055008747","4.6331185E-4","-0.06712223","-0.020356372","0.05921021","-0.026101505","-0.009826756","0.060013864","-0.07436504","-0.0017671869","0.03450281","-0.025181022","0.073718116","-0.021493241","0.025840096","-0.0070447964","0.050705258","-0.10176822","0.0061735227","0.058611948","-0.06947876","0.019435983","0.052905746","-0.003203005","-0.028581044","0.09501291","0.03803571","-0.017841654","0.081401505","0.023411974","0.01307816","-0.0751314","-0.024469085","0.063431464","0.050293323","0.010059086","-0.06087724","-0.048451655","-0.091296434","0.04063801","-0.07860514","-0.07569742","-0.1051746","0.0628292","-0.018749177","-0.0049487073","0.00555619","-0.08344105","-0.07943847","0.022755452","0.009430296","-0.01458228","-0.029960508","-0.050454196","0.018617941","-0.033561055","-0.023040643","0.011007275","-0.005498805","-0.035637476","-0.06496155","8.0363876E-33","0.0340118","0.039247405","-0.072303206","-0.06204468","-0.030545147","-0.008514003","0.007120356","0.01722626","-0.043726087","0.044112045","-0.0041987025","-0.058660004","-0.0028109","-0.03347119","0.080158025","-0.059607852","0.09358243","0.08029267","-0.012228826","-0.060449563","-0.04366354","-0.020231588","-0.017690938","0.04031405","0.043686416","0.07068799","-0.09466898","-0.07465662","-0.007902749","0.024712114","0.07099415","0.031000873","-0.073720954","0.042028867","-0.013002783","-0.07954815","-0.14017956","-0.02184416","-0.023942767","0.0054218206","0.05138025","0.045028366","0.013361193","0.00964088","0.011728343","0.047099333","-0.031138893","0.010900637","0.092101246","-0.013080655","-0.004248306","0.006484565","-0.079570286","-0.002896467","0.06931023","0.005532235","0.0040947082","-0.022612283","0.05527949","0.02992963","0.019274106","0.027935602","-0.09797918","0.012181656","-0.02421863","0.024701739","-0.035846386","0.05282956","0.009110496","0.0273721","-0.037705608","-0.026349152","-0.0043326193","0.12161147","-0.018826623","-0.037427563","0.02476496","0.06185844","0.03260585","0.04293016","0.06886258","0.025128629","0.03298776","-0.10698961","-0.07799008","0.02715947","-0.001442607","0.05195844","-0.02913188","0.06644176","0.04614064","-0.06520218","0.06442256","0.01169174","-0.04307819","-1.0084377E-32","-0.02575344","0.06380941","-0.005853451","-0.12269385","0.059362948","0.049011152","-0.04985427","-0.09574869","-0.065496445","-0.011963695","-0.010556333","-0.0121775875","0.002136654","0.009356965","0.0024621654","0.025726529","0.058211718","-0.027003009","-0.05899982","-0.040935777","0.028478565","-0.00759843","0.021761317","0.005092441","-0.038090717","-0.10437364","0.011995953","-0.07088373","0.06425998","0.030159086","-0.017349536","-0.038157362","-0.11361506","0.11336635","0.0028110384","-0.080143936","-0.009162288","0.0010186541","-0.0049575074","0.040624242","0.0052689323","0.032470856","0.012401686","0.10915372","-0.10583458","-0.022182733","-0.064594","-0.06514158","0.046094414","-0.058611166","0.006218366","0.032679666","-0.016930684","-0.07720295","0.03436171","0.041102007","0.024280656","-0.058443718","-0.0033481417","-0.07048682","0.09437867","-0.003414037","0.051426005","0.042765815","-0.01517507","0.05367","-0.05330403","-0.018786158","0.008629268","0.053607278","0.023601333","7.5385894E-4","-0.034462336","-0.07567243","-0.086143635","-0.01746875","-0.0775437","0.05716232","-0.020599075","-0.0022759852","-0.03885738","0.049667165","-0.049233746","0.0137433745","0.126475","-0.011656797","0.00371381","-0.05501184","0.08000005","-0.025950069","0.030932989","-0.047027603","0.02624435","0.0881954","0.04107148","-5.9569512E-8","0.039438598","-0.13342386","-0.025127567","-0.028234893","0.049122166","-0.00330901","0.057919726","-0.016553463","-0.0058934162","3.7726946E-4","0.010509267","0.04579199","-0.00894389","0.04415148","0.0055087977","-0.010036696","0.0016160863","0.11176211","-0.010264019","-0.009847767","0.015078427","-0.0098202415","-0.051710054","0.009798323","-0.056128867","0.056332484","0.01839454","0.052792165","0.044552244","0.035579376","0.018222205","0.022293512","-0.04372912","-0.058671802","-0.04189172","0.048094373","0.034389548","-0.0040147593","-0.13944797","-0.016856065","0.019714093","0.05228607","0.047250256","0.10413318","0.02036352","-0.015542282","-0.057836402","-0.05519862","0.07334215","1.1812153E-4","0.009724306","0.031136025","-0.01962792","0.10755403","0.008048407","0.044915438","-0.01618753","-0.03556467","-0.036152672","0.022548677","0.04765229","-0.06655775","0.10524307","-0.011070722"]</t>
+  </si>
+  <si>
+    <t>NK-4UU6yAAFMmm9vPyo9mQLC3</t>
+  </si>
+  <si>
+    <t>Viktoria SERDYUKOVA</t>
+  </si>
+  <si>
+    <t>| In taking on and acting in this capacity, Viktoria Serdyukova is responsible for supporting and implementing actions and policies which undermine and threaten the territorial integrity, sovereignty and independence of Ukraine. Viktoria Serdyukova is the former so-called “Commissioner for Human Rights of the Luhansk People’s Republic”. In this role, she supported the war of aggression Russia launched against Ukraine on 24 February 2022. She supported the illegal annexation of the territory of Luhansk and the adoption of Russian legislation in that and other illegally annexed territories</t>
+  </si>
+  <si>
+    <t>["-0.04867471","0.07341153","-0.025192168","-0.011340715","-0.056758035","-0.026410494","0.032914966","0.021839999","-0.001075975","0.028442657","-0.06145282","0.07027064","-0.03808569","-0.0046285694","-0.03762946","0.07534198","0.005117656","0.032799397","-0.07866972","0.017980317","0.05368484","-0.13315333","0.06163494","0.013851626","-0.004690624","0.051435463","0.02344629","0.023035258","-0.028315712","0.064195104","0.076157585","-0.06227171","-0.07071351","0.015945857","-0.029760081","0.0487502","0.009014738","-0.017990714","-0.011688998","-0.031270284","0.0065892376","-0.0894772","-0.091490515","0.01055283","-0.04321353","-0.047204006","-0.04672744","-0.02038923","-0.087900974","-0.053579923","-0.043441635","-0.050355967","-0.049864527","-0.026152775","-0.033003904","-0.09651747","-0.035159245","0.043952517","0.068778686","-0.05312746","0.03138794","-0.011742667","-0.020020932","-0.024092302","-0.045937948","-0.066862896","0.021706289","-0.08422837","-0.04099541","0.04305822","0.029472528","0.04295411","-0.02773678","-0.037257608","0.052367087","-0.056351487","0.032101933","0.10876333","0.030059345","-0.06311297","0.096102","0.008680903","0.020118825","0.05527698","-3.0180445E-4","-0.0050633266","-0.009611526","0.045881145","0.08517974","0.011337551","0.06596319","-0.013083645","0.14211032","-0.01608807","-0.01603329","-0.059555817","0.0016476596","-0.0038130046","0.0060688276","0.041537747","-0.04733753","-0.0556732","-0.035852887","-0.03867591","-0.06484018","-0.045283128","-0.009596163","-0.06313845","-0.11423919","-0.0055189417","-0.032203306","-0.103839174","-0.064265005","0.0107805","0.03601608","0.060155064","-0.029544614","0.027855305","-0.0044386983","-0.093344","0.03381506","-0.016489923","-0.03376618","0.02702741","0.106074214","0.007002555","-0.115446694","-2.480385E-33","0.037439965","-0.06463832","0.013344377","0.06318285","-0.120340265","0.014139366","0.09862928","-0.027181506","-0.042305425","0.0063928463","-0.050906274","0.023267474","0.007252607","-0.014196498","0.036021776","0.095149785","0.012571977","0.0137018785","-0.017315239","0.14854391","0.15193813","-0.0053761606","0.014174421","0.056311425","0.015583801","-0.0098320935","-0.049517557","-0.027495176","9.896571E-4","0.05870552","-0.08953192","-0.079719245","-0.030591888","-0.016027","0.03337834","0.065088205","-0.12957972","-0.0036039862","0.026606767","-0.0065263864","-0.020591525","-0.013082185","0.043469694","-0.0020484403","0.046763927","0.008477058","0.0055275676","-0.06822522","0.037159476","0.001826563","-0.043114457","-0.0029758925","-0.008930148","0.035564978","-0.049054146","-0.003369625","0.008520479","0.0705948","0.028182318","-0.011722406","0.020240763","-0.026547669","-0.0091635985","0.045585062","0.027872212","-0.03368093","0.023706544","0.1040209","-0.0705189","0.00871014","-0.0069285044","0.02955432","0.069096155","0.107041515","-0.095195785","-0.022896469","0.060672123","-0.03995078","-0.07085705","0.026358213","0.04324143","-0.0051730378","0.04554557","0.013748794","-0.031938463","0.01951296","-0.03789862","-0.042727154","-0.036507208","0.049732827","-0.051185716","-0.0045154877","-0.013247531","0.07332512","-0.062472668","-1.7694325E-33","0.06262763","-0.011239255","0.016050339","0.016880328","0.0032967776","0.09751363","-0.03592723","-0.03060252","-0.0045264196","0.092272356","0.07466402","-0.1358348","0.0061360234","0.09605079","-0.047735456","0.015896311","0.02883329","-0.0032035916","0.022035968","-0.09267117","-0.12962954","0.07898765","0.05234607","0.03490488","0.023217898","-0.08550127","0.118990384","-0.0070213224","-0.06629986","0.05317708","-0.04682316","-0.08022382","-0.046493173","-0.049302462","0.08179385","0.009637512","0.050738417","-0.053344928","0.008061789","0.026682157","0.011789113","-0.040644597","0.09863912","0.111784674","0.009472612","-0.0033944766","5.069162E-4","0.01418593","0.015747463","-0.07190606","0.05824903","0.048557993","-0.012136456","0.03597735","0.049462646","0.060158506","0.032567814","0.032190483","0.053143483","-0.0036837668","0.01861975","-0.023408253","-0.022584548","0.021979565","0.011693397","0.026403366","0.014234467","-0.045775894","0.06185302","-0.002757973","0.06027272","-0.07122919","-0.102687106","0.06775837","0.009375016","-0.012269518","-0.07799336","0.038707495","-0.038164284","-7.2266406E-4","0.04984574","-0.06649038","0.027296675","-0.044070665","0.040397834","0.0045821313","0.021033384","-0.027024923","-0.036845513","-0.06303331","0.009026066","0.021441191","-0.041624065","0.08900165","-0.019020103","-4.0386556E-8","0.02718176","-0.033568285","-0.01910258","0.050492715","-0.087764665","-0.012293616","-0.053369287","-0.06046596","-0.060761828","0.050955493","-0.017720502","-0.008310057","0.02742192","0.010400734","0.009956208","-0.0043458315","0.06394539","0.04063275","-0.010682572","0.010351627","0.0417","-0.07676572","0.0195872","-0.071330845","0.026495185","-0.0408651","-0.03419436","0.025776332","0.041907795","-0.058332246","-0.015375928","-0.025874885","-0.061111562","-0.0025654307","-0.04088485","0.037518535","-0.024738492","-0.04147093","0.013111838","-0.029698996","3.3477257E-4","0.11497911","0.03907541","0.015664501","0.0069318064","0.023032501","-0.010917525","-0.1516456","0.02008701","-0.043513555","-0.03494762","0.048046388","0.030562978","0.09629419","0.022368543","0.043950267","0.023858562","-0.010035716","0.01779981","-0.046424415","-0.020692794","0.03682648","-0.017151754","-0.032418072"]</t>
+  </si>
+  <si>
+    <t>NK-4WhTLz52oVmat4W9oTFAVi</t>
+  </si>
+  <si>
+    <t>MICHAEL GALATIS</t>
+  </si>
+  <si>
+    <t>Entity Name: MICHAEL GALATIS | Type: Person | Jurisdiction: us | Risk Context: MEDICARE SUSPENSION</t>
+  </si>
+  <si>
+    <t>["-0.053270236","-0.0012812744","-0.060449608","-0.014549052","-0.030911125","0.069254085","0.07564561","0.022851765","-0.013966708","-0.026872104","0.021572266","-0.0050948462","0.0084106615","-0.041602846","-0.07141807","0.012843323","0.01384855","0.059387144","-0.048632026","0.07242766","0.08256718","0.05371038","0.023160921","0.036695592","0.031205835","-0.047050897","-0.004022106","0.020140836","-0.01599133","-0.002385036","0.063923955","0.012381268","0.027797388","0.063729465","0.015394028","0.0010730919","-0.04914986","0.059615567","0.011523035","-0.036277153","-0.0033416457","-0.04484305","0.06329406","0.017708432","0.0057311845","-0.056158382","-0.026783187","0.030586965","0.010941765","0.07962125","-0.087453716","-0.10656438","0.035651546","0.090270326","0.035740823","0.007988576","0.004251396","-0.058330685","-0.04803507","-0.04443109","-0.060040828","-0.008581698","0.027973723","0.07909007","-0.050515756","0.020381844","-0.012726682","-0.048678473","0.06393451","-0.053200983","0.040248264","-0.08483906","-0.07686895","0.04827102","-0.023807254","0.040410526","0.05270831","0.09100864","0.06699542","8.0451334E-4","0.04897718","-0.0015258569","0.0032369879","-0.0027301798","-0.06671249","0.025542753","-0.030265749","-0.0430389","-0.032947842","-0.061999332","8.884219E-4","-0.035390753","0.13368206","-0.086781554","-0.017223073","-0.052244127","-0.009949525","-0.08914224","-0.047996663","0.09731224","-0.040243354","-0.027200332","0.05642742","0.09485557","-0.0034476772","-0.051850643","0.017648997","0.06377643","-0.052992932","-0.01684308","0.011351822","0.03567579","-4.5698942E-4","-0.020102331","-0.011188233","0.061004024","5.5760687E-4","0.0052747396","0.09140129","-0.0748326","0.011161856","0.021192202","-0.056509938","-0.045921527","-0.050850365","0.089087896","-0.0057641286","-1.8301938E-33","0.1005368","0.007685775","0.053928304","0.014805019","0.03984677","-0.008902924","0.008135055","-0.031900242","0.056705594","-0.010904068","-0.05554308","0.050208494","0.056866717","-0.06570442","-0.059208784","0.049328648","-0.046688724","0.06328972","-0.033615064","0.081560776","-0.009833515","0.0047803246","0.018107256","-9.818132E-4","0.015313781","0.03679391","0.033248007","-0.055987522","0.06954202","0.02014193","-0.010243226","0.09281145","0.042430732","-0.07266733","0.06534316","0.06755573","-0.004132855","-0.038164336","-0.028027548","-0.03255658","0.014069157","0.033319533","0.06800795","0.03800447","-0.042122442","-0.052187018","-0.0014363483","-0.053913757","0.035414383","-0.035061363","0.021441795","0.02490582","-0.039859604","-0.02811391","0.0022172744","0.02588126","0.0092078615","0.12572563","0.037341323","-0.047180988","0.0335221","-0.024656488","-0.004680018","-0.0023110982","-0.0054722","-0.01783765","-0.008543001","-0.029160123","-0.027207026","-0.036164198","0.01337775","0.017647972","0.05952658","0.030561235","-0.0765214","0.047597133","-0.019849429","-0.007397263","-0.033828527","0.0052071777","-0.11685916","-0.0027937244","-0.018463172","0.09941299","0.007827656","0.015478998","-0.024129339","-0.025854278","-0.07090815","-0.04506641","-0.086869195","0.0088064745","-6.48426E-4","0.09816506","-0.057957888","-1.6245198E-33","-0.08693328","-0.08298739","-0.024850363","-0.045007505","0.0944437","-0.07170902","-0.037457652","0.041692704","0.014921717","-0.01526535","-0.018578574","0.005824131","-0.017943988","0.0038941985","0.012967372","0.050195307","0.004053107","-0.011678431","-0.08647505","0.076859","0.086550534","0.027005188","-0.055278763","0.045529597","-0.014223646","-0.01594952","0.07989286","0.031060113","-0.02730656","-0.099109106","-0.03187245","-0.035195477","-0.05117018","0.0071279607","-0.052981276","-0.042800035","-0.026662244","-0.042790648","-0.05455582","-0.0582374","0.023732938","-0.005083438","-0.035425853","0.08868448","0.111591","-0.05272981","-0.05335535","-0.029999504","0.07882088","0.026773512","-0.09023342","-0.060824383","0.020017961","0.05161365","-0.01934966","0.003786872","0.08389434","-0.078988336","0.008005512","0.022076447","-0.020519903","0.03361204","-0.0799825","0.050828993","0.045668002","-0.063674405","-0.06272246","-0.072280474","-0.07022477","-0.06019365","0.033902846","-0.14897369","-0.0024328292","0.002251222","0.07122648","1.6148812E-4","-0.03479678","-0.014386125","-0.043491278","0.012078369","0.091834694","-0.048753787","-0.0096494","0.090771064","0.0021758198","0.030187173","0.088340394","-0.0055441093","0.034912627","-0.025232047","0.0086774295","-0.03441872","-0.09968585","-0.0574773","-0.14371602","-2.3592788E-8","0.053510204","0.027594293","-0.015888058","0.012652236","-0.015763292","0.010569064","-0.068031445","-0.021912912","-0.034872115","-0.030963102","0.0077199107","0.11448491","-0.037252624","-0.080330655","0.0339311","-0.058746908","-0.08970055","0.112063214","-0.02312332","0.033596847","-0.07643591","-0.0032866583","-0.03321735","-0.031742338","-0.008074873","0.031474162","0.039192412","0.03472877","0.025239289","-0.031150408","-0.018618694","0.13031986","0.005186439","0.077815056","-0.09038154","0.038971737","0.081172794","-0.034058988","0.08058279","-0.01908144","0.05483538","0.004157022","0.047155086","0.006677147","0.011134662","0.057129815","-0.006296632","0.03890644","0.039429627","0.009102801","-0.057611547","-0.08097259","0.01807861","0.0018103549","-0.07988672","-0.05610223","0.05409751","0.009154727","-0.04773292","-0.06952667","0.097826794","-0.11306805","0.03469865","0.036219798"]</t>
+  </si>
+  <si>
+    <t>NK-4Z8QQfetY8tH3Z6ZdffwMt</t>
+  </si>
+  <si>
+    <t>SANABEL RELIEF AGENCY LIMITED</t>
+  </si>
+  <si>
+    <t>| Type: Company | Jurisdiction: gb | Risk Context: (also SANABEL RELIEF AGENCY LIMITED, SANABEL RELIEF AGENCY, SANABEL L'IL-IGATHA, SRA, SARA) (also SANABEL RELIEF AGENCY LIMITED, SANABEL RELIEF AGENCY, SANABEL L'IL-IGATHA, SARA, AL-RAHAMA RELIEF FOUNDATION LIMITED) (also SANABEL RELIEF AGENCY LIMITED, SANABEL RELIEF AGENCY, SRA, SARA, AL-RAHAMA RELIEF FOUNDATION LIMITED) (also SANABEL RELIEF AGENCY LIMITED, SANABEL L'IL-IGATHA, SRA, SARA, AL-RAHAMA RELIEF FOUNDATION LIMITED) http://www.sanabel.org.uk (website); info@sanabel.org.uk (email). (also SANABEL RELIEF AGENCY, SANABEL L'IL-IGATHA, SRA, SARA, AL-RAHAMA RELIEF FOUNDATION LIMITED) (also SANABEL RELIEF AGENCY LIMITED, SANABEL RELIEF AGENCY, SANABEL L'IL-IGATHA, SRA, AL-RAHAMA RELIEF FOUNDATION LIMITED)</t>
+  </si>
+  <si>
+    <t>["-0.040510423","-0.018701954","0.022155313","0.0077104582","0.06383343","0.016731145","-0.019656638","0.08648986","0.0010724763","-0.0482226","0.040059205","-0.02567793","0.011311215","0.02178055","-0.03140586","0.047889937","0.019133722","-0.01531561","-0.08495291","0.006055901","0.1008357","0.05601023","0.0036229044","0.042502537","-0.019309731","0.033353806","-0.05738653","0.071742","0.037222907","-0.04665192","0.053558562","0.0731712","0.027584236","-0.108564906","0.07321009","0.087612286","-0.07708732","-0.0070654587","-0.03731953","0.032602254","-0.019031433","-0.036016624","0.024037447","-0.03820076","0.02099537","-0.060020212","0.020922778","0.01948309","0.008481879","0.06959849","0.0032191519","-0.025935784","-0.002599074","0.046454728","-0.09144477","-0.07411581","-0.119043134","-0.061984826","-0.0078090546","0.015578099","0.027073957","0.00127932","-0.024625257","0.033228062","-0.030283675","0.024014032","0.009447404","0.0137997065","-0.010434117","-0.105261914","0.014346334","-0.1390555","0.046768833","0.09116597","0.013031845","0.04878235","0.12262757","-0.016573103","0.03440812","-0.027198287","0.015858453","0.037559822","0.10180725","-0.031151209","0.0017013691","-0.0038078625","0.07218622","-0.028016968","0.059400268","0.024516845","0.06719294","0.009554137","0.061747324","0.022239644","-0.05954625","-0.04989995","-0.029564453","-0.036536608","-0.0919843","0.050729223","-0.0614869","-0.038708694","-0.07231765","-0.057661958","-0.05277799","-0.06757162","-0.039708916","4.9468724E-4","0.041681375","-0.001354128","-0.03966032","0.07234301","-0.062104452","-0.049158234","-0.06753716","0.029951353","-0.07333557","-0.025912562","0.027388966","-0.11301387","0.005863088","0.028790092","0.0035606865","-0.1033159","0.0060931738","0.012721315","-0.017645996","6.642589E-33","-0.0105088735","0.069434874","0.034239616","-0.017686106","0.0013867012","-0.04059518","-0.024862997","0.057912167","-0.038600147","0.029906835","-0.027632415","0.047246255","0.021803278","-0.055286504","-0.10413489","0.047077097","0.06372102","-0.1025105","0.0143055245","-0.054306403","-0.015692787","-0.027327709","0.029199393","0.060792923","-0.0036071423","0.012073375","0.031494938","0.0019222223","0.0137009295","0.029039454","0.03151342","-0.009401857","0.027661184","-0.11526581","-0.01799632","0.06877617","-0.080573104","-0.09296642","-0.0064783096","0.0026623819","-0.035796523","0.07965856","0.049302027","0.07178074","0.050382335","0.0057959002","-0.010755251","-0.048897065","6.913019E-4","-0.0068267393","-0.064520776","0.05122514","-0.07206139","0.066514045","-0.00521462","-0.015983751","-0.039306816","0.010759843","0.04811507","0.027072452","-5.5239117E-4","-0.06412654","-0.08137963","0.0373196","-0.036546685","-0.03416004","-0.004875889","-0.055002093","0.0122479275","-0.0517452","-0.065058425","0.050293997","0.1252389","0.07380253","-0.09669439","-0.02430924","-0.041390184","0.1392184","0.06518456","0.0028171383","-0.06602856","0.021674832","0.029518433","0.07740897","0.027426561","0.0020987142","0.012452231","-0.1077596","-0.042552706","-0.051011037","-0.03853143","-0.0022846572","0.056943465","0.031158058","0.026104758","-9.060154E-33","0.042136088","-0.033891704","0.012748128","-0.054711144","0.045326125","0.047259834","0.05659787","-0.035926335","0.045989048","0.020819105","-0.045779467","0.038472988","0.0027589458","-0.029657912","0.009947148","0.025638564","0.019702466","0.015905859","-0.08760088","-0.02257582","0.0307707","0.110286295","0.055844244","0.006457286","0.013453259","-0.006814886","0.06601048","-0.06307576","-0.0067336676","0.020638388","-0.008728775","-7.1245496E-4","-0.09279535","0.05569528","-0.06852108","-0.016427428","-0.02238335","-0.096479475","-0.08691899","0.0071252836","0.0821783","0.03817019","-0.023409754","0.030905087","-0.015922973","-0.0013531743","-0.024008727","-0.055477116","0.08882834","-0.014775975","-0.0123616","0.0011138278","-0.0062152212","-0.024934102","0.029064637","-0.0025913934","-0.028181113","-0.084130704","-0.060902122","-0.022748353","0.0045572794","0.09845889","-0.027074458","-0.0057772878","0.07119918","7.202624E-4","0.02821108","-0.07522575","0.03859826","-0.06761875","0.042672567","-0.03649883","-0.049092676","-0.09030481","-0.034935232","-0.03785742","-0.04245771","-0.048563518","-0.068289034","-0.02490109","0.1253892","-0.03724701","0.04224478","0.061977036","0.046315853","0.08460923","0.048532788","-0.028381983","0.019908572","0.050348274","-0.07060102","0.056965385","0.002288925","0.04524717","0.07312001","-6.2306526E-8","0.035499237","-0.019712538","-0.026376804","0.007907583","0.0456522","-0.059104096","-0.054952856","0.04679054","-0.044191875","0.06647242","0.06757244","0.11156968","-0.07603775","-0.031286504","-0.096167564","-0.060191076","-0.06669553","0.060749803","0.0014623364","0.010120671","-0.0542211","0.005606437","0.042079113","-0.100955695","-0.013262622","-0.038647644","0.048850883","0.042129107","0.013021425","0.038569883","0.015661824","0.0023331146","0.041118205","-0.009611666","-0.022008058","-0.018648462","0.021942819","-0.0017069278","-0.02142472","0.034919485","0.0053201215","0.0026794337","0.057950836","0.08667675","-0.03537064","0.014856988","-0.05417057","0.0011286889","0.08296405","-0.08417903","-0.021355106","-0.10051075","0.00901488","0.07049277","-0.05091973","0.006205215","-0.033013534","-0.0108778635","0.016892396","0.038261432","0.04329457","-0.1541646","-0.027850533","0.013036316"]</t>
+  </si>
+  <si>
+    <t>NK-4dWAmMSseqKTGL9QPUa92r</t>
+  </si>
+  <si>
+    <t>UMANSKI ELEVATOR, OAO</t>
+  </si>
+  <si>
+    <t>Entity Name: UMANSKI ELEVATOR, OAO | Type: Company | Jurisdiction: ru | Risk Context: For more information on directives, please visit the following link: http://www.treasury.gov/resource-center/sanctions/Programs/Pages/ukraine.aspx#directives. (also UMANSKI ELEVATOR, OAO) (also OTKRYTOE AKTSIONERNOE OBSHCHESTVO 'UMANSKI ELEVATOR', OPEN JOINT STOCK COMPANY 'UMANSKIY ELEVATOR', OTKRYTOE AKTSIONERNOE OBSHCHESTVO OTKRYTOGO TIPA UMANSKI ELEVATOR)</t>
+  </si>
+  <si>
+    <t>["-0.044472344","0.031918366","-0.04412233","0.010565204","-0.0242338","-0.08732263","0.02193834","-0.01874167","0.039643254","-0.035249658","0.07266182","0.008990586","-0.031966727","0.0025882835","-0.05480251","0.08796182","0.050330777","0.06693579","-0.05585963","-0.0010744504","0.07693006","-0.023024952","0.08086583","-0.0049814363","-0.01254169","-0.044129483","0.0047198865","0.097533375","0.050243758","-0.08142816","-0.019683532","-0.05591365","0.06963382","0.0038382355","-0.0077972566","0.08311896","0.01362446","-0.0972103","-0.020242987","0.025867188","-0.010677267","-0.06939585","-0.025702426","0.04289344","-0.048646327","-0.021161105","0.0021371266","-0.07368311","-0.010194192","0.01704308","-0.044010326","-0.009921869","-0.029548973","0.04010954","-0.04626837","-0.079273775","-0.054231387","9.2709975E-5","-0.011111354","0.0040847724","0.08846741","-0.0061031696","-0.057055507","0.05762964","-0.026923334","0.06695464","0.029420441","3.8555186E-4","-0.06679406","-0.041577414","0.08025185","-0.09955195","-0.023250943","0.061109073","-0.03029352","-0.0035566348","0.039706405","0.07926273","-0.019986752","-0.036416937","0.015509125","-0.0026455699","-0.0010619782","-0.090504214","-0.1311583","0.06507424","0.012982723","-0.01580282","0.07470343","0.03666861","0.024259603","-0.058590878","0.12420999","-0.016186928","0.08289578","-0.06013056","0.005954824","-0.0055249278","-0.056769576","0.007953529","-0.01667798","0.05244061","-0.054633852","0.017232953","-0.07827227","-0.022339623","-0.0588511","-0.03817447","-0.02587693","0.020029942","-0.027187807","0.008540685","-0.017417423","-0.07460509","-0.07783653","-0.050201073","-0.068340264","-0.03243294","-0.0053549893","-0.032468144","0.021381406","-0.05288026","-0.04849079","-0.007466004","-0.021973355","0.003376258","-0.027838385","3.2169662E-33","0.04829989","0.04351806","-0.05095494","-0.082546175","-0.03615284","0.030689785","-0.053685226","-0.011759924","-0.04084072","0.061234392","-0.039726812","0.032261584","-0.027830647","-0.053990606","0.06097616","0.041130327","0.04579841","0.047665272","0.02005065","0.050847944","0.07874526","0.041051097","-0.05293307","0.055966448","-0.018004319","0.042794015","-0.01591112","-0.076155424","-0.04359468","0.042508148","0.01843166","-0.023096003","0.010729813","0.032872412","-0.08122895","0.003366246","-0.091232054","-0.028910665","-0.033046197","-0.028845988","0.03516564","-0.05506081","-0.04880735","0.08183519","0.070411615","-0.015081995","-0.007759784","0.011382553","0.09242815","0.02640219","-0.067593224","0.04592268","0.0022973404","0.010861325","-0.00799007","-0.061307665","-0.04540403","0.045194853","0.008144051","-0.0634359","-0.07274714","-0.042903077","0.037091408","0.055505764","-0.034721784","-0.022805667","-0.010914069","0.095046505","0.016345799","0.008090472","-0.003539755","-0.019991772","0.02593834","0.15752085","-0.11086847","-0.0028992118","-0.056540284","-0.034514464","0.078453474","0.013598952","-0.04853495","-6.7760394E-4","0.07049529","0.028234133","0.061377965","0.12515034","0.019176437","-0.030864013","-0.023379892","0.13905461","-0.047891688","0.051753085","-0.049637645","0.06115058","0.070187114","-5.3775366E-33","0.07101283","-0.031777702","-0.079910755","-0.06454167","-0.004414265","0.0034633758","-0.0077667097","0.05735635","-0.012466141","0.06480892","-0.016789742","-0.11816885","0.024189567","-0.0058159684","0.082616836","0.008328417","0.044635814","0.025513735","-0.04643289","0.04234035","-0.013731639","-0.012833865","-0.024362119","0.080076866","0.01984755","0.009768576","0.07406418","-0.07603149","-0.050188627","0.045355868","-0.04440466","0.008141963","-0.059143726","0.1166812","0.012567794","0.001023611","0.08275562","-0.038885828","-0.04919229","-0.01817611","0.03019838","0.07199067","-0.01601726","0.014335297","-0.07441219","-0.040151015","-0.049527384","-0.013228178","0.019291524","-0.18354152","0.026133947","0.066036515","-0.007263921","-0.028360195","0.03545619","0.050317712","-0.00773273","-0.045896623","0.008112594","0.010708846","0.0276295","-0.025066882","0.028656341","0.105475135","0.019089099","0.05863107","0.004826837","-0.03839574","-0.047228266","-0.036347106","0.038166046","-0.10146425","-0.022926766","-0.031185571","0.013443424","0.015461347","0.07085209","-0.013367218","-0.04564486","-0.038639303","0.04886732","-0.046279233","0.01889064","0.040804405","-0.0117583005","0.021678828","0.024088673","0.036068946","0.012813372","0.046675142","-0.048843246","0.038787767","-0.062255397","0.03344096","0.04160336","-4.632447E-8","0.033710454","-0.079838015","0.056940045","0.026829718","0.011631218","0.025927737","-0.004131247","0.022926938","-0.12601125","-0.0046751522","0.037145276","0.086959034","-0.078878686","0.03827089","-0.032743864","-0.03377344","-0.019840717","0.13999167","0.011379952","0.018198758","-0.034799024","-0.04554775","0.12881447","-0.05038592","-0.03326065","0.008123505","0.02832881","0.052640222","0.1547972","4.6803532E-4","0.008660345","-0.013425625","-0.04303881","-0.004106767","-0.06686208","0.06889167","0.062406015","0.004055116","-0.05054151","-0.018838655","-0.031437397","-0.04614889","0.019775141","0.06054258","0.037050225","0.04783443","-0.060187235","-0.032210927","0.04181495","-0.083630145","-0.024999136","-0.050123002","0.017298605","0.06925594","-0.015309068","-0.010230779","0.018433241","-1.2642443E-4","-0.049467675","-0.016615542","0.034474067","-0.025614727","0.028316088","-0.058025718"]</t>
+  </si>
+  <si>
+    <t>NK-4fa3SNWJz2XnjbgGNGKmM7</t>
+  </si>
+  <si>
+    <t>KHATIBA AL-TAWHID WAL-JIHAD</t>
+  </si>
+  <si>
+    <t>. The number of fighters of KTJ is about 500. KTJ also cooperates with such terrorist organizations as Khatiba Imam al-Bukhari (QDe.158) and the Islamic Jihad Group (QDe.119). Khatiba al-Tawhid wal-Jihad (formerly known as Jannat Oshiklari) is a terrorist organization operating under the umbrella of the international terrorist organization Al-Nusrah Front for the People of the Levant</t>
+  </si>
+  <si>
+    <t>["-0.01870228","0.02841217","-0.07257507","0.03799847","-0.045041118","0.06753207","4.0014472E-4","-0.048802577","0.05564918","0.023743557","0.009069448","-0.08116423","0.07605312","-0.001092888","0.013579363","0.07177922","-0.06481244","-0.018313974","9.673851E-4","-0.056139324","-0.056293383","0.022052065","0.10342866","-0.024081102","0.063912325","0.02751934","-0.017396633","-0.018192975","-0.012889199","-0.053534146","0.055502348","0.020044925","-0.0023465576","-0.004873603","-0.046519376","-0.0035851598","-0.015649708","0.052688137","0.015469096","0.026616286","0.040667173","0.00229025","-0.0069445507","-0.056998335","0.021520212","-0.0023609246","-0.07362284","0.041684024","-0.028712017","0.012704973","0.05638723","-0.14390528","0.04930101","0.04905873","0.058055207","-0.10676322","-0.051607195","0.0020673545","0.07921827","0.066813685","0.059711523","0.062110554","0.0054628123","0.0013388903","0.021704864","-0.09128915","0.020604089","0.009095551","-0.019803602","-0.066480756","0.08096476","-5.331422E-4","0.029389929","0.06008368","-0.06326107","-0.052422605","0.015252237","0.04680384","-0.057702146","0.06450787","0.048565492","0.070722185","-0.016866447","0.0048940885","0.008629684","-0.039426144","-0.027666824","0.09648706","0.0384901","0.029225385","-0.009389537","0.060370374","0.004154212","-0.0056659593","-0.009591614","-0.07742261","0.047147818","0.073303886","-0.069015145","0.052599788","-6.706151E-4","-0.026391048","-0.023731574","-0.038466007","-0.04104118","-0.02390963","0.03964296","-0.014854875","-0.0922122","-0.04743332","-0.044066843","-0.05242722","-0.08715295","-0.05561302","-0.0014504673","-0.044380225","0.026623743","0.035951287","-0.09529168","0.0055032047","0.008392991","-0.0016806342","0.0074088024","0.038499363","0.027770773","0.0500083","-0.08017107","1.5723137E-33","0.039946586","-9.893666E-4","-0.039256904","-0.042890515","-0.037343476","-0.06385289","-0.044473078","0.050586533","-0.051073194","-0.07239093","0.008412975","-0.0017968286","0.0045114425","0.015172426","0.044042703","-5.709326E-4","-0.010148117","-0.030384362","0.024600042","-0.043237083","0.041423608","0.023620272","-0.083110936","0.09286158","0.005104251","0.045152687","0.09272076","0.011306002","-0.055366367","0.045266952","0.044347927","0.03925617","-0.06978301","-0.02677592","-0.05369211","0.04534141","-0.07815705","-0.03880196","-0.08501176","-0.044431183","-0.05730554","-0.005940707","0.018514924","-0.0037487745","0.03933911","0.02042268","-0.0023493771","-0.048910636","0.04317354","0.026740916","-0.06823474","0.057302512","-0.044498596","0.0060537015","0.016100056","0.02681521","0.01629394","0.026680024","0.018265326","0.0753525","-0.072440214","-0.03463199","-0.13424718","0.043776337","-0.034220684","-0.0031740256","0.012396396","-0.025344515","0.0056664324","0.004621439","-0.010536425","0.060105465","0.087691724","0.036232695","-0.07698794","-0.05718826","0.051200774","0.018836606","-0.04128292","0.050329924","0.041335374","-0.04465333","0.07919716","-0.044714693","-0.054836936","-0.041165616","0.030676331","-0.007454791","-0.11005552","-0.018982401","-0.046788536","0.016361592","-0.008833019","0.04450534","-0.024141226","-2.5727762E-33","0.0775771","0.059125435","-0.026959771","-0.02152638","0.03442464","0.08395006","0.028894473","0.11059802","-0.06201579","0.05345158","0.026762819","-0.033948887","0.021059364","0.03592375","0.080092594","-0.059848364","0.054824483","0.025400719","-0.023180071","-0.08528237","-0.04772881","0.07241986","-0.020432161","-0.07614063","0.08170733","-0.00979027","0.04949548","0.03592219","-0.06134094","0.054340012","0.04274714","-0.06086747","-0.03287649","-0.007538498","0.030109817","0.012379926","0.007578804","0.050129987","-0.022847006","0.033193644","0.058664396","0.07382191","-0.04325387","-0.082982145","-0.028727273","0.03534663","0.020389415","-0.009718541","0.05644432","-0.14279017","0.03365373","0.05177153","0.040363036","-0.03183927","0.11379289","0.061006755","-0.114875406","-0.006354596","0.030243529","-0.05871552","-0.018737903","-0.070590556","0.104398735","0.05428259","-0.07592565","-0.010177322","-0.03332535","0.0475297","0.04812473","0.044961266","-0.0238203","-0.013693441","0.00372568","-0.007183934","-0.106650144","-0.072392076","-0.078818426","0.028960152","-0.022392586","0.022678526","0.111257374","-0.08937761","-0.041891348","0.027176835","0.08416143","-0.0071622203","0.08952829","0.04015533","0.040526118","0.02808795","-0.040405072","-0.03728638","-0.018454062","0.04119621","-0.016858498","-3.825052E-8","0.036900885","-0.07820064","-0.07234281","0.0070985043","0.065624565","0.034760706","-0.054025356","-0.06501174","-0.016418163","0.051369548","0.07479741","0.022961678","-0.101860076","0.043299776","-0.034834605","0.0041128746","-0.051708724","-0.01818532","0.050134793","0.022008922","0.008269228","-0.023449294","-0.031147562","0.03182295","0.004038941","0.073265254","-0.05042824","0.02759865","0.036044132","0.01944229","-0.049426373","0.025012538","-0.09123351","-0.010150037","-0.05893384","0.084817566","-0.07247283","-0.02642807","0.016169844","0.089680426","-0.03084414","0.0139360335","0.031233747","0.06482071","-0.043767963","0.016122892","-0.006029744","-0.08138537","-0.07129595","-0.12118401","0.02484327","-0.017640216","-0.021261051","0.06217715","-0.062573366","0.059388537","0.012217181","-0.08434344","-0.05625179","-0.0089881215","0.03858533","-0.11075696","0.09108616","0.048233278"]</t>
+  </si>
+  <si>
+    <t>NK-4gess3vLnSjfkERGLnmTQN</t>
+  </si>
+  <si>
+    <t>Burim KRASNIQI</t>
+  </si>
+  <si>
+    <t>| Disqualified</t>
+  </si>
+  <si>
+    <t>["-0.062669344","0.104368515","-0.0310136","0.026934782","-9.993383E-4","0.020689191","0.088641204","-0.006766113","0.008996043","0.014218149","0.032887544","-0.081190206","0.019674888","0.030222261","-0.16878176","0.063900866","0.017908314","-0.004244615","-0.01640014","-0.024077741","0.10015936","0.00875042","-0.0082370825","0.037511572","0.042780083","0.045065995","-0.055587664","0.07116804","0.0013811844","-0.05591306","-0.059575345","0.060773212","-0.0019290212","-0.02000748","-0.009725308","-0.079987876","-0.01408534","-0.03609814","-1.5257386E-5","-0.022934444","-0.0059982263","-0.044057924","0.010661933","0.0074763084","0.036448117","0.07229461","-0.06549478","-0.04779608","-0.11077866","0.025203254","-0.034838405","0.057823077","0.01677735","0.011348744","0.02133222","-0.013841291","-0.07975561","0.0093583","-0.020883027","-0.046486706","0.014383972","-0.051748864","-0.08042296","0.05007645","0.046911247","0.07093422","-0.030674206","0.07001904","-0.0443974","0.053770356","0.06842156","0.01578544","-0.043951258","0.027730996","0.074188106","0.03113284","0.0070734713","-0.045216147","0.09049169","0.011720114","-0.15034765","-0.069901966","-0.010350079","-0.022546673","0.0050854664","0.011539895","-0.029418519","-0.04141397","0.017750256","0.049857616","-0.0966034","-0.021602064","0.1139792","0.035400648","-0.054082308","-1.9631367E-4","-0.016390853","-0.056626927","-0.046784554","0.19938815","0.027219255","0.07425281","-0.098889776","0.02691571","-0.026886376","-0.016821127","0.011245705","0.003026188","-0.013580437","-0.110762134","0.02188313","0.014377061","0.11868735","0.0036361471","-0.0073279114","0.048917353","0.07497197","0.04098453","0.024088183","-0.057947684","-0.011782054","0.058281787","0.020769311","-0.041227084","-0.0078001223","-0.060090847","0.002947241","-5.2501284E-33","0.11083423","-0.024701802","0.016116038","0.045121316","0.0401392","0.027062338","-0.009968974","0.012864121","-0.04480173","0.093836464","0.016882377","0.062652744","-0.017307501","0.010340087","0.156505","0.0066910065","0.09277351","-0.11370657","-0.020709971","-0.018352225","0.0417467","-0.013817333","-0.00904042","0.034521155","-0.04395622","0.013937962","-0.059286617","-0.055910766","-0.00647907","0.037999813","0.030222086","-0.025297284","0.034910627","0.03723258","0.039786384","-0.04826599","-0.059219927","-0.038811058","0.0105797","-0.0021724657","-0.04445395","-0.016135933","-0.039219413","-0.025867872","-0.0044766827","0.04996284","0.09449165","-0.03325318","0.0418537","0.06700718","0.01478214","-0.019544238","-0.04480928","0.020368004","0.013731218","-0.047397807","-0.020441363","0.05284318","-0.029005175","0.049350318","-0.01237849","-0.0052318373","-0.02645775","-0.044274334","-0.08284703","-0.021904398","-0.021307172","-0.018951086","0.04376259","-0.056226626","-0.029968228","-0.002357586","0.03712714","-0.019728845","0.048253734","-0.025485571","-1.031284E-4","-0.0015687813","0.028888617","-0.04633943","-0.040552076","0.013311326","-0.05445806","-0.05448613","0.052654054","0.06017461","-0.02323631","-0.13486774","-0.008586436","0.008496908","0.05515034","0.008984948","0.07099899","-0.04171279","-0.039600283","2.604094E-33","-0.016421778","0.010240544","-0.094327286","-0.06457526","-0.0096518565","0.03107849","0.042426102","-0.0028840853","-0.0751574","-0.03385915","0.02716117","-0.0066422643","0.08073076","-0.010408663","0.024703037","0.089653775","-0.021262038","-0.0034518945","-0.102726094","0.046073485","-0.100403175","0.02171131","0.08494042","0.007640326","-0.04143914","0.05584611","0.14692011","0.061169904","-0.05029944","-0.027640212","0.0028740012","0.027408307","-0.09367776","-0.055988222","0.010349249","-0.0031016346","-0.009786354","0.011007493","0.0028826627","0.048275933","0.098068416","-0.0013986151","-0.04084396","0.049993265","-0.011779594","-0.025905682","0.062216554","-0.063250065","0.08583404","0.02784987","-0.03861998","0.013813463","-0.034401707","0.050669227","-0.009001143","-0.05409182","-0.05789465","-0.03857103","0.12394305","0.005489318","-0.019301198","0.057578687","-0.020122252","0.06726292","-0.002864979","-0.03832815","-0.029879022","0.120395325","0.0060935835","-0.017154086","0.012597183","0.022946538","-0.041383635","-0.011857835","0.01652191","0.098678015","0.043080367","0.06909687","-0.02099553","0.051138844","-0.1479947","-0.008052558","-0.032661784","-0.0061219605","0.005633534","0.032556206","0.03685318","-0.050230373","0.04395847","0.004276219","0.01317851","0.0014107964","0.0588977","0.0052706474","0.03135108","-1.3780289E-8","-0.009799691","0.06264988","-0.06651605","-0.015097526","-0.0033881362","0.06489102","-0.0331727","-0.07254439","-6.440228E-4","0.043214537","-0.0018666104","0.060235105","-0.038593214","-0.012335498","0.026761277","-0.031523474","-0.04965441","0.07763379","-0.009689141","-0.020397512","0.0115340995","-0.033567254","-0.05919294","0.030593673","-0.010060002","0.008768537","-0.012904538","-0.007911145","-0.01774178","0.0016006617","0.037158944","0.026132487","-0.043463036","-0.009130302","-0.10647169","-0.016717356","0.04092273","0.019271594","-0.044921316","0.075212725","-6.0137676E-4","-0.016246349","0.030057788","0.0058079255","-0.059952926","-0.009861496","0.106218785","-0.04095387","0.015567643","0.013622403","-0.05014713","-0.06073041","0.044954598","1.3233384E-4","0.06042929","-0.045789428","0.025349362","0.029660014","-0.062702775","0.033407655","0.16208756","-0.092090264","-0.035729207","-0.045794763"]</t>
+  </si>
+  <si>
+    <t>NK-4iSKCpWUXd5veMEXv9q89B</t>
+  </si>
+  <si>
+    <t>2Rivers DMCC</t>
+  </si>
+  <si>
+    <t>Entity Name: 2Rivers DMCC | Type: Company | Jurisdiction: ru | Risk Context: 2025/1476 (OJ L202501476)</t>
+  </si>
+  <si>
+    <t>["-0.07421148","-0.03566367","-0.060539152","-0.0031229437","0.025789643","-0.012477775","0.020298049","0.04645817","0.054846913","-0.04673443","0.026841033","-0.09591681","-0.004660437","-9.992616E-4","-0.026184468","0.02629902","0.032753367","0.05425628","-0.0139141055","0.013812981","0.056096066","0.013110031","0.02115577","-0.012765301","-0.03946208","9.7414834E-4","0.031874333","0.11618453","0.009134309","-0.089567736","0.057866875","0.03854701","0.034592465","-0.018837672","0.14883202","0.056745395","-0.0461891","-0.01067002","0.03046971","-0.04984303","0.04555535","-0.04375635","0.06821114","0.03878515","-0.013323864","-0.002657107","-0.059663005","-5.9429277E-4","0.015609669","0.013286706","-0.0420185","-0.06755727","-0.01431647","0.03443618","0.010068511","0.028457152","-0.07877225","0.026069485","-0.012682119","-0.036645155","0.08272482","0.0072146757","-0.020188306","0.052209273","-0.020823715","0.0044402285","0.024016565","0.04936732","0.0065311445","-0.072809055","0.059348814","-0.054646388","-0.09537955","0.026604086","-0.014563903","0.017102286","0.0105121825","0.029533163","0.037367485","-0.1316928","5.5443266E-5","0.0051798024","0.020280248","-0.029837696","-0.09017674","0.086796395","0.056964744","-0.035110116","0.07579778","0.020657217","0.040634718","-0.04655388","0.11919593","-0.030490583","-0.040650424","-0.028277954","0.04084013","0.0080355955","0.01749892","0.046083402","0.013162915","0.01303003","-0.096141905","0.046742033","-0.06655411","-0.059092578","-0.061886255","0.052815255","0.004791529","-0.0056288345","-0.049196053","0.10320848","-0.07592601","-0.041946273","-0.050442398","-0.04056722","-0.05396142","-0.0047476273","0.07717533","-0.08180408","-0.0353542","-0.026602346","-0.1114617","-0.05146917","-0.0901061","-0.025870213","-7.496074E-5","1.4615187E-33","0.06069839","-0.0011949922","0.02013198","0.072008625","-0.03584402","0.06509041","0.0063097826","-0.024250047","-0.08430163","-0.0064950287","-0.08793467","-0.019443356","-0.013223732","-0.113145694","-0.014751053","0.011850371","-0.022561982","0.03031629","0.023079762","0.01692623","0.00730009","0.004236786","-0.0584586","0.009170938","0.06833396","0.021194756","0.0046486207","-0.056453403","0.07334671","0.090667695","0.028637484","-0.033298347","0.028567793","0.03980978","0.06308338","0.09442702","-0.07755885","-0.051992312","-0.030687489","-0.015043851","0.017971283","-0.026839469","-0.074964024","0.03881465","-0.024138253","-0.025217963","0.027221786","0.01861427","0.04858895","0.031009706","-0.04344994","-0.0044714794","-0.015415942","-0.008180996","0.012229344","-0.030760387","-0.017923744","0.04517355","-0.018575424","0.023021093","-0.004144391","0.06352428","-0.07833247","-0.002847423","0.070732735","-0.04751969","0.005247998","-0.039259218","0.035228144","-0.08334839","0.0323929","-0.005550626","0.08506158","0.075909406","-0.04404033","-0.040545367","-0.04159838","0.009894152","0.0050820843","0.067437015","-0.110266574","0.016051149","-0.027393695","0.06839914","0.052009214","0.023626639","0.02452324","-0.075886376","-0.08970683","0.0567647","-0.060887955","-0.044143893","-0.009860688","0.0826935","0.042545896","-3.415121E-33","-0.046741188","-0.058358498","-0.038714312","0.0021152103","0.008922468","-0.07206864","0.026162608","0.044191632","0.046822347","0.036897946","0.031631764","-0.030399144","-0.027610565","0.021496715","-0.0013848995","0.0048484607","0.006414416","-0.026712937","-0.085001126","0.08504112","0.016849322","-0.015321543","-0.01649688","0.0865042","-0.027971953","0.04982111","0.04364621","-0.016539764","-0.058757123","-0.011850833","-0.027264614","0.026414918","-0.10107125","0.15768917","-0.10679711","-0.09959072","0.04507637","-0.062192008","-0.023330014","-0.05081853","-0.029369727","0.058132336","-0.029183589","0.047663447","-0.041043878","-0.064217664","0.089266844","-0.02284598","0.11963577","-0.059307676","-0.026410239","0.022453416","-0.016325848","0.0862207","-0.025523297","-0.00261077","0.07516071","0.022603588","0.018685663","0.021048203","0.041150156","0.1191669","-0.01847316","0.12887044","0.059961088","0.004761762","-0.04334303","0.009243227","-0.017619105","-0.14282481","0.052474637","-0.06879493","-0.059873227","-0.058691293","-0.016487947","-0.08071186","-0.015039556","-0.0039299186","-0.00925094","0.011868956","0.07513411","0.030910768","-0.018158095","0.076965995","0.0281914","-9.463094E-4","0.06675216","-0.0131097045","0.03232059","-0.006647648","-0.039497565","-0.019813951","-0.060405724","0.04389393","-0.018465208","-2.98991E-8","-0.02018222","-0.0042756046","7.545302E-4","0.023267342","0.06284153","-0.018130051","-0.048455704","0.053931996","-0.028455552","0.0578137","0.012295623","0.012496843","-0.11049552","-0.056878474","-0.009619011","-0.03372674","-0.05726176","0.09826093","-0.0059172465","-0.030658575","0.0026047842","-0.027693707","0.056905556","-0.10191219","-0.049759347","-0.0293355","0.054226276","0.025381241","0.105254054","-0.065338165","0.0020841432","0.03891391","-0.025037518","0.023198467","-0.037694268","-3.6258134E-4","0.05367925","0.018771984","-0.015174226","0.026523337","-0.017618079","0.046261996","0.0014691129","0.07855253","0.04382647","0.06428485","-0.06826293","0.006661872","0.03789528","-0.050706714","-0.08599458","-0.09178592","0.032510623","0.063187875","-0.117865145","-0.013184833","0.008095905","0.026691323","-0.07764735","0.008878363","0.020145658","-0.018925281","0.017003097","0.039677743"]</t>
+  </si>
+  <si>
+    <t>NK-4koTPtD62zPUTB4f4HScdz</t>
+  </si>
+  <si>
+    <t>Sergey Alekseevich RYABTSEV</t>
+  </si>
+  <si>
+    <t>| Risk Context: Sergey Alekseevich Ryabtsev est un juge russe qui travaille au tribunal de district de Lefortovo à Moscou. À ce titre, il a participé au sabotage de l'enquête sur l'empoisonnement d'Alexeï Navalny en refusant de traiter la plainte concernant l'inaction de la direction des enquêtes du service fédéral de sécurité de la Fédération de Russie (FSB). De plus, il ne cesse de rendre des jugements qui vont à l'encontre de la liberté d'expression en Russie. Par conséquent, Sergey Alekseevich Ryabtsev est responsable de graves violations des droits de l'homme en Russie, y compris d'actes de torture et d'autres peines ou traitements cruels, inhumains ou dégradants, de détentions arbitraires, ainsi que de la violation systématique de la liberté d'opinion et d'expression.</t>
+  </si>
+  <si>
+    <t>["-0.036144964","0.048605755","-0.07111484","-0.093400545","0.033177964","0.07500995","0.12532888","0.055585448","0.028839983","0.043448605","-0.018468617","0.029576592","0.04312213","0.057685822","-0.06274587","-0.053249978","-0.015965015","0.007963004","-0.044301838","0.085389756","-0.005879846","-0.06771617","0.066569395","0.012472842","-0.03570529","-0.022822391","0.008752426","0.013255909","-0.0017380217","0.037070125","0.0114082685","-0.045125064","-0.0496641","0.012172415","0.026737344","0.054473817","0.013507789","-0.031681538","-0.04283474","0.06904532","-0.006914429","-0.016458433","-0.11709434","0.10030679","-0.09453504","-0.040556636","-0.039599147","-0.0143647455","-0.04378842","0.0037570624","-0.055122785","-0.0154269","0.08097256","0.019074192","0.034060568","-0.089906506","0.02167048","-0.015409754","-0.021482885","-0.010919522","0.001974933","-0.042761173","0.0062365523","0.018543929","-0.05950111","-0.055648144","0.036680494","0.004159515","-0.015191255","0.071273305","0.036807783","-0.00652046","-0.10314987","0.055858277","-0.05749818","-0.009666823","-0.013550787","0.008231585","-0.00671482","-0.07631881","0.06924516","-0.05547688","0.0031677554","-0.008315671","-0.057663873","-0.04054463","4.6633475E-4","-0.06250502","0.12653477","0.0658242","0.033024956","0.0013217512","0.10794425","-0.09049785","0.095196076","-0.06549067","0.015159297","-9.69311E-4","-0.054255888","0.05781543","-0.002012538","-0.020932406","-0.08636708","0.038933642","-0.04548977","-0.0860227","-0.14150712","-0.124214426","-0.1265388","-0.04562486","-0.022991892","0.015558861","0.028692927","-0.0029811852","0.083422385","0.02527269","-0.010345231","-0.021420103","-0.035190113","-0.020008653","0.054866552","0.031301174","0.0257154","0.016135845","0.015471288","0.024075532","-0.021150297","8.438255E-33","0.068019554","-0.038499527","-0.07080889","-0.045125775","-0.05215773","0.005734315","-0.07380091","-0.025822228","0.035507612","0.05332532","-0.031392824","0.022756098","0.031152224","-0.04603676","0.038519394","0.10037712","-0.0060374364","0.062477577","-0.039251033","-0.0077966414","0.02142067","0.06543013","0.04455971","0.045532778","-0.051767264","0.0016060377","-0.016910132","-0.091583565","0.029679138","0.018462012","-0.067043416","0.034406777","-0.0038597058","0.045380417","0.0419032","-0.060163964","-0.054158174","0.0011089062","0.04180162","0.014931437","0.022319075","-0.042039502","0.025969133","0.010396212","0.05066608","0.008479779","0.04036363","-0.035170455","-0.015307584","-0.03723957","0.003709325","0.017145438","0.03962478","-0.025685605","-0.028507344","-0.008293734","-0.10014779","-0.006502523","-0.058514617","-0.015195649","0.01874755","-0.035918914","0.02245011","0.002221544","0.006912833","-0.10105445","-0.02518815","0.009411673","0.036362156","0.00997458","-0.028915627","-0.014528215","0.018509116","0.053114668","-0.010397013","-0.009344356","0.0175217","0.02172645","-0.06820519","-0.0052149626","-0.17266072","0.017448254","0.100046396","0.04639516","-0.04499698","0.017405448","0.028027872","-0.05101493","-7.262189E-4","0.06615329","-0.10035997","-0.027379936","-0.0058058365","0.01993589","-0.055578303","-1.3057531E-32","-0.095847435","-0.028326547","-0.15638629","0.031357393","0.002300196","0.027843736","-0.0016978113","0.011515827","0.04674987","-0.03865483","-0.086731754","-0.08355919","-0.0053271377","0.0035945217","0.012802547","0.017385522","-0.053456638","0.047445387","-0.07591196","0.0021157102","0.023916274","0.02636849","0.03611224","0.057666875","0.016766837","-0.03189172","0.092805564","-0.0804636","-0.041377634","0.05808771","0.049134508","0.05631487","-0.043013565","0.116786115","0.02626961","0.056444414","0.104945734","-0.03301833","-0.07188123","0.08903393","-1.7833179E-4","0.06497045","-0.0058626556","-0.021108853","-0.011975372","-0.037375685","-0.08746038","-0.06952953","0.036754943","-0.15230043","0.0032437062","0.04085945","-0.0023120535","0.062829226","-0.05618845","-0.049259197","-0.033259563","-0.058508","-0.0044415398","0.07079366","-0.010230978","0.053874712","-0.011109317","-0.015056885","-0.0075458353","-0.0015897065","-0.05373434","0.02717679","0.011174322","-0.045038305","0.10387013","-0.10105554","0.0015669941","0.055197958","0.043624938","0.005448839","-0.044938635","0.0402183","-0.039109435","0.03341577","0.0016070245","-0.006023233","-0.044923794","0.008196117","0.0018738279","0.014328918","0.006675035","-0.026504625","-0.0100935595","-0.032869514","-0.014249814","-0.051394347","-0.051635634","0.067241915","-0.013750153","-7.1149834E-8","0.08582061","-0.015986372","-0.061770115","0.05077321","-0.020121325","-0.034628812","-0.05333851","-0.0031579114","-0.10872451","0.043257486","0.027416209","0.018430134","-0.0071277083","-0.0030116714","-0.065821916","0.017509604","-0.042737644","0.006010167","-0.05506218","-0.0014082241","-0.007721083","-0.034088343","-0.07266614","-0.115041465","-0.05093618","0.03847507","-0.040968195","-0.06269972","0.037250802","0.08401028","-9.63924E-4","0.020170506","-0.053722754","-0.015694162","0.019174336","0.07272087","-0.016114965","0.001514796","0.064053334","0.07937304","-0.025306603","0.03623411","0.04055792","0.044150643","0.028765298","-0.05369645","-0.09766101","-0.040381208","0.056341633","0.06613225","0.04162946","0.05177495","-0.005247882","0.07676691","0.027078845","-0.007977321","-0.01729461","-0.07204417","-0.09720041","-0.01140548","0.03517727","9.968621E-4","0.08100302","-0.060901564"]</t>
+  </si>
+  <si>
+    <t>NK-4mtWBti7Fkrh4ZC6pun7wu</t>
+  </si>
+  <si>
+    <t>Basij Resistance Force</t>
+  </si>
+  <si>
+    <t>Entity Name: Basij Resistance Force | Type: Organization | Jurisdiction: ir</t>
+  </si>
+  <si>
+    <t>["-0.023030419","0.07224651","-0.045782298","-0.004989327","-0.01533398","0.020597761","-0.041951012","-0.024161447","0.022969346","0.031157477","0.055146545","-0.14212377","0.03959189","-0.013140973","0.035099033","0.0066659176","0.04539284","0.05720415","0.001160541","-0.0013235959","0.023110412","0.014270465","0.079214714","0.008598221","-0.042811707","0.0034888894","0.014400826","0.027974393","-0.02866383","-0.10689322","-0.027360309","0.016428936","-0.05143442","0.097485915","-0.020085374","0.036638986","-0.006790665","-0.0046560476","0.0075543","0.005952927","-0.015172089","-0.077931195","0.010685153","-0.08432001","0.02427477","0.048271544","-0.033967987","0.046958134","-0.0027138037","0.0076847114","0.010128234","-0.07662505","0.05230034","0.0687462","0.006016786","-0.07227955","-0.0031616332","0.031786937","0.034735236","-0.010833694","0.033747043","0.07588325","-0.006741114","0.012312823","0.019519446","-0.042473342","0.050786182","0.10118196","-0.04589766","-0.051781293","0.07859813","-0.05322746","-0.051494904","-0.025166193","-0.012690854","-0.013481822","0.011670669","0.09684493","0.03814213","-0.12728046","0.027641045","0.049586568","0.016961798","0.044531725","-0.010044154","0.048597075","0.10539919","0.004727302","0.0217675","0.0066354","-0.03642367","-0.008520312","0.13537551","0.0030595418","0.015336362","0.019288272","0.066232905","0.009162998","-0.023610244","0.018145705","0.04362313","0.017517485","-0.015495393","0.01144927","-0.04601367","-0.07820496","-0.016452994","-0.018585695","0.046476714","0.037817124","-0.05032028","0.041939195","-0.09346385","-0.105217725","0.008571384","-0.062508576","-0.035865355","0.011789957","0.02175033","-0.06068016","0.025380325","0.0034389612","-0.10861418","-0.0070059937","0.034875415","0.0485629","-0.10153257","-2.1704851E-33","0.0026540407","-0.0042269053","0.033983923","-0.018627552","-0.11057335","-0.053846613","-0.04372372","0.044758543","-0.119084015","0.017903375","-0.070020825","0.02909616","0.036173616","-0.036338173","0.03554654","-0.026390878","0.012954119","-0.02198193","0.019471766","0.010884636","-0.0407319","0.054271962","-0.074056886","0.051489573","0.01441222","-0.020773595","-0.03399106","-0.060067557","-0.06548912","0.0430523","0.07362333","-0.064454556","0.0016235352","-0.015779248","2.3900678E-4","-0.01119509","0.017492905","-0.040426567","-0.074719205","-0.068182945","-0.01567329","-0.003663225","-0.0021269391","0.054321762","0.091620296","-0.011961294","0.0324115","-0.11884848","0.06334055","0.03291102","-0.045953576","0.031979386","0.02614654","-0.022949597","0.038232867","-0.0038248769","-0.06232093","0.10478588","-0.0052051754","-0.0014250656","-0.009841984","0.002875431","-0.087443285","0.08644504","-0.04654616","-0.065404154","-0.06526762","0.024058493","0.056666348","-0.062056642","-0.029186118","0.046107333","0.026871411","0.083256386","-0.00652848","-0.034882657","0.042630177","-0.011504038","0.005516122","0.051875934","-0.15121163","-0.017169511","-0.030625684","0.043741502","0.0024872667","0.009544403","0.05347193","-0.102275126","-0.020991182","-0.06390511","-0.006482898","-0.022809178","-0.054050714","0.053192724","-0.0015333986","-1.4440778E-34","0.061104875","-0.03741802","-0.035742756","-0.032250058","0.05787757","0.01758954","-0.0307663","0.05209827","-0.034649514","0.04141083","0.014040498","-0.094418705","-0.0017180353","0.022442367","0.058780607","0.00159416","0.0046408297","-0.036377374","-0.042207826","0.07656081","-0.017920136","0.047377404","0.048713345","-6.925082E-4","0.03537449","0.004117767","0.075977825","-0.010385961","-0.04378929","-0.046547502","0.013148004","-0.07267167","-0.11470188","0.116095915","-0.036358297","-0.09534617","0.03493051","0.009324131","-0.06562405","-0.023643121","-0.04492802","0.062042158","-0.10411859","0.041290842","-0.061370112","0.00859529","0.026691139","-0.0070221717","0.04051436","-0.08000765","-1.0611044E-4","0.020220997","0.029506482","-0.03897518","0.08057257","-0.016366256","-0.03277048","0.0054845596","0.0016851197","0.057627615","0.019423943","0.05251745","0.0059849587","0.12271764","0.033045862","0.026805248","-0.0689038","0.08861863","0.017262721","-0.07487452","0.07090714","0.011001549","-0.026699282","-0.0021951569","0.04928485","-0.075633764","0.025242798","-0.036458306","-0.0997164","-0.007849829","0.10510535","-0.04097719","-0.08956648","0.045479238","-0.010224214","0.09302461","0.051877156","-7.075129E-4","0.015638642","0.0045275707","0.011209646","-0.027035875","-0.019265696","0.08864145","0.01137415","-1.9753726E-8","0.010639782","0.013053219","0.023732748","0.029836956","0.031585325","-0.033912376","-0.013505913","-0.08368033","-0.08240746","0.06471625","-0.0046598874","0.049004998","-0.0031640183","0.025637109","0.014503106","-0.075153396","0.028854618","0.04061569","-0.0015485944","-0.0070943204","-0.042809397","-0.017472493","-0.01710303","-0.068695545","0.021594968","0.010080229","0.005238875","-0.10320679","0.06669058","-0.03065136","0.02051558","0.07088533","-0.09987906","0.028019695","-0.081106946","0.05764361","0.05041114","0.016017023","-0.011798413","0.01926331","0.0074437996","0.0068109306","0.09608869","0.021193579","0.04437181","0.04672176","0.052489176","-0.05306716","0.10320577","-0.1878697","-0.033118192","-0.020140965","0.034935523","0.08323863","-0.028826255","0.02166527","-0.0058878586","0.051240362","-0.011179638","0.004151852","0.10415212","-0.08391988","0.02493364","0.048387345"]</t>
+  </si>
+  <si>
+    <t>NK-4puqpbCnvgtESpFgGvacHZ</t>
+  </si>
+  <si>
+    <t>Haejin Ship Management Company Limited</t>
+  </si>
+  <si>
+    <t>Entity Name: Haejin Ship Management Company Limited | Type: Company | Jurisdiction: kp | Risk Context: Executive Order 13551 (North Korea) | IMO番号：5814866 According to Annex 18 (p. 125) of the UN Panel of Experts February 2015 report, Haejin Ship Management, Jihyesan Shipping and Cholryong Shipping share the same telephone number and email address.</t>
+  </si>
+  <si>
+    <t>["-0.10371643","0.017299403","0.0152228065","0.0049728905","0.008250752","-0.034612685","0.05151516","-0.016697658","-0.045075566","-0.008338741","0.070700176","-0.019249512","-0.04985276","-0.014355921","-0.039983977","-0.014633054","0.011936754","-0.04174616","-0.05365174","-0.059347562","0.028250465","0.014350881","3.842009E-4","-0.011737147","-0.012608043","-0.072164014","-0.0057294127","0.05968277","-0.036701784","-0.054634135","-0.014718127","0.059011668","0.06767597","0.034132693","0.07451955","0.09437878","-0.07367175","-0.08637587","0.033348672","-0.016248142","0.008892506","-0.05736374","0.04390361","0.024290584","0.014661856","-0.050154872","-0.0063490835","-0.024775542","-0.028374169","0.093616374","-0.015772229","0.009729044","0.056790255","0.018852333","0.012292934","0.0388804","-0.03731835","-0.04663976","0.024106128","-0.006215284","-0.0304745","0.060083497","-0.011920817","-0.07146111","-0.03393456","-0.04065209","0.043479733","0.01981405","-0.03874308","-0.014259735","0.10272389","-0.026091857","-0.031564906","0.081370614","-0.021281762","0.021422584","0.034659725","0.029169058","0.033469524","-0.036097262","-0.01907802","0.021636307","0.049666435","0.009590437","-0.08578371","0.049152557","-0.05044589","0.03945885","-0.020105565","0.033110943","0.06199649","-0.028065823","0.088124536","0.014652718","-0.05364275","0.0047998726","-0.0057009407","0.06425506","-0.041303597","0.02546873","0.085618354","0.0936701","-0.01918765","-0.00853454","-0.043587394","-0.03194642","0.0048643677","-0.0814583","0.065995194","-0.050985247","-0.09523544","-0.015370231","-0.03970812","-0.03482158","-0.03933063","0.022532089","-0.07181424","0.033387404","0.07162181","-0.11066714","0.035435766","-0.015940612","0.006558561","-0.04093612","-0.040325202","-0.015385794","0.016563931","2.2519911E-33","0.009585749","-0.0263923","0.05156453","-0.06210682","0.029154653","-0.072685815","-0.058649294","0.00481892","-0.03716733","0.037719503","-0.109886885","-0.040723316","-0.046671867","-0.08339865","-0.085847996","-0.036333896","-0.008323857","0.04150458","0.031659797","0.0552983","-0.022285562","-0.013089541","-0.07484144","0.013392219","0.06544415","0.050494798","-0.016056087","0.03725646","0.043431997","0.06764295","0.018939655","-0.006310912","0.035495784","-0.03827936","-0.088400744","-4.4416683E-4","-0.092890754","-0.03253471","-0.09860736","-0.06495736","0.0038806612","0.017770551","-0.094056934","0.13470976","-0.009149058","0.017965464","-0.0034643745","-0.048730306","0.14498396","-0.035021756","-0.09831038","-0.030100051","0.029673886","-0.02359717","0.09216702","-0.09285999","0.074780464","0.010407072","0.029140353","-0.0774301","0.006912495","-0.0026461233","-0.07148039","0.07306031","0.08747513","-0.03159974","0.018776758","-0.058166213","0.0010671603","-0.064267814","0.074067","0.015421776","0.014343694","0.053139687","0.0036724217","-0.0519099","-0.026087532","0.026884178","0.010267773","0.026451422","-0.08200133","0.038711537","-0.032809872","0.059983086","0.030629924","0.081485845","0.012422626","0.0025563447","-0.0124117425","0.04095533","-0.034697074","0.0060523525","0.0074206586","0.018677091","-0.038965415","-3.325601E-33","-0.071771406","0.04994413","-0.09391552","-0.003794805","-0.03110629","0.019080587","0.09590917","0.07551007","0.01488597","-0.0059822756","0.003716839","-0.052020714","-0.028621001","0.0058536706","0.051988304","0.026172224","0.04983297","0.05041772","-0.034310598","0.058739144","0.036567364","-0.06435961","0.038737673","0.0987889","0.04203535","0.024016477","0.10042611","-0.01841179","-0.049293928","0.016579261","-0.023995163","-0.05210962","-0.06776784","0.0896445","-0.08671828","-0.1357197","0.034991816","0.07241805","-0.0091288425","0.009976856","-0.010831058","0.030101443","0.024753751","0.07110105","-0.10860721","0.044819865","0.03596855","-0.03861318","0.043118753","-0.07030722","-0.043380514","0.064741716","0.040822208","-0.04876225","0.0054461863","0.07116853","-0.04322331","0.04417082","0.04927412","0.013186814","0.030974181","0.0236263","0.021593358","0.11657754","-0.004331771","0.08922103","0.009519034","0.0071302927","0.032484274","-0.10539002","0.017426832","-0.063303694","0.023655161","0.059298113","0.0039367573","-0.06728744","-0.0024575766","0.03450367","-0.03488466","-0.02269724","0.12429812","0.022323772","-0.11103839","0.023655543","-0.05640157","-0.066915415","0.08293033","0.015867865","0.048350252","0.032389797","0.0019563641","0.04105015","-0.09902","-0.00956099","-0.08538255","-3.4640983E-8","0.018976163","-0.1253181","0.0637576","-0.06123927","0.04708209","0.0028653082","-0.060904007","0.010936444","-0.00415637","0.024048144","0.028873477","0.051112745","-0.08825388","-0.03665353","-0.06978308","-0.04983028","0.042289283","0.05697923","0.007188539","-0.014992217","-0.02544797","0.046489343","0.032517117","-0.04955815","0.015629774","0.0365005","-0.04848663","0.027171126","0.08713595","-0.075165264","0.04599724","0.07470528","-0.009487006","0.052040577","-0.03925113","0.018034229","-0.043429866","-0.06632778","0.041939087","-0.020838885","-0.06536144","0.02309022","0.026346121","0.041430697","1.9281716E-4","-0.0057775285","-0.014835373","-0.05488249","0.0033263266","-0.082765155","-0.049893595","-0.051691543","0.08272381","0.017466784","0.0031748675","-0.019732498","0.08802903","-0.02040983","0.036555566","0.014757746","0.052839316","-0.055510566","-0.0062597194","0.07463389"]</t>
+  </si>
+  <si>
+    <t>NK-4sjXgiXRPLpxp2nTMPHQ2s</t>
+  </si>
+  <si>
+    <t>AREFULLAH AREF GHAZI MOHAMMAD</t>
+  </si>
+  <si>
+    <t>. Governor of Ghazni Province under the Taliban regime. Governor of Paktia Province under the Taliban regime. (Date of UN designation: 2001-01-31) (Believed to be in Afghanistan/Pakistan border area. Belongs to Andar tribe. Review pursuant to Security Council Resolution 1822 (2008) was concluded on 27 Jul. 2010. INTERPOL-UN Security Council Special Notice web link: https://www.interpol.int/en/notice/search/un/1427419 () Directs Taliban "front" in Gelan District, Ghazni Province, Afghanistan as of mid-2013. Believed to be in Afghanistan/Pakistan border area. Belongs to Andar tribe. Review pursuant to Security Council resolution 1822 (2008) was concluded on 27 Jul. 2010</t>
+  </si>
+  <si>
+    <t>["-0.13777837","0.10080488","0.0025577866","0.011221261","-0.020970084","-0.10238927","-0.038945694","-0.03573392","-0.044978313","0.020414986","0.049423337","0.034230478","0.047147915","-0.016805705","-9.5200137E-4","-0.013117393","0.022842068","-0.0010705963","0.02675955","-0.03611932","0.0890172","0.059976023","0.12755562","-0.054232635","-0.008075347","-0.040762708","-0.01898753","0.0025739563","0.0123084","-0.004968263","0.020574365","0.013973479","-0.042154115","0.011947622","0.047258403","0.065304585","-0.03588205","0.025821134","0.007878485","-0.04969392","0.09250595","0.0085018035","0.0018322453","0.024296539","0.065253496","-0.08916341","-0.024431838","-0.014189701","-0.097049944","0.019217877","0.08158696","-0.050315414","-0.041353446","-0.004118902","0.067500174","-0.041114688","-0.10637718","-0.009769513","0.027722096","0.06979227","-0.008384439","0.052257188","-0.09997377","-0.030857448","0.00678906","-0.04342473","0.06717602","-0.054345462","0.005396971","-0.037984744","0.08722673","0.0072363806","0.012906458","-0.06266201","-0.03322485","-0.08094836","-0.013671114","0.15302947","-0.018361675","-0.035642132","0.09525037","-0.017341156","0.02984348","0.016011","-0.010486316","-0.069289446","-0.033996567","0.026801048","0.03186477","0.021065958","0.11796386","0.10947903","0.034085132","0.03878049","0.06172859","-0.084004216","0.09765996","0.055808153","-0.0030802207","0.056331594","0.045280077","-0.13259163","-0.04883693","0.0015542225","-0.0658747","0.022237785","0.024026915","-0.039828833","3.1635823E-4","0.0181884","-0.030901859","-0.009826525","-0.042106237","-0.0030066716","0.022079805","-0.027842375","-0.0037381905","0.033153843","0.090878375","-0.10896755","-0.11485241","0.040888585","0.017013887","-0.0067177205","0.07968451","0.0057680467","-0.062318526","-1.1424076E-33","0.026418876","-0.012808499","-0.032577395","0.00890006","-0.13650034","0.07290353","0.012301808","-0.07983671","-0.068672866","0.011510895","0.030946298","-0.0014292165","-0.0012250852","-0.028551018","0.019021612","-0.019665089","-7.245601E-4","0.00557681","0.0057784524","0.058822516","0.06354318","-0.049031578","-0.0402836","-0.0240528","0.03559539","0.0054909587","0.005441405","-0.08910287","-0.04870213","0.024398394","0.004017277","-0.042116955","0.03752753","-0.021562258","0.0052468614","0.034153122","0.0068821115","-0.025957812","-0.040936563","-0.07896924","-0.0065674144","-0.05574986","-0.031233434","-0.0019202171","0.06991554","0.009857037","-0.030660855","0.040124156","-0.0118974475","-0.020936074","0.021640442","0.020921413","-0.05111449","-0.018015094","-0.117097676","0.06581757","-0.022611873","0.016144257","0.05180463","-0.024392975","0.042655595","-0.0053744507","-0.08621046","-0.0421466","0.03560212","-0.03639894","-0.056541346","-0.031020705","0.047541566","0.021605344","0.018846953","-0.012817755","0.0407855","0.103972495","-0.02739731","0.008637652","-0.06396723","0.11262607","-0.06474925","0.093974136","0.019354196","0.072559","0.028563285","-0.01854001","0.02476085","0.012930138","0.038116384","-0.059293576","-0.02604135","0.023343632","0.0072246813","0.015554876","-0.021343505","0.027611695","0.0591323","-1.7525667E-34","0.07458481","0.00588758","0.0060797175","0.0018241084","0.004819499","-0.03966126","0.12074139","-0.010066412","0.0638071","0.010052466","0.03451045","0.011698211","0.09271563","-0.0010206708","0.037649166","0.04578452","-0.063484944","0.02036178","0.0061632567","0.011967552","-0.03043964","-0.032608192","0.03865374","0.020368826","-0.013406477","-0.021119742","0.054427482","-0.021778427","-0.074632205","-0.050257053","-0.002293524","-0.097869","-0.0068793204","-0.0015428165","-0.04240797","-0.045014083","-0.010980879","-0.038131617","-0.062323574","0.01334233","0.0060954504","0.035388187","-0.0021368288","0.022858676","-0.06090512","0.029046597","0.07835309","0.06458493","-0.09190938","-0.072749905","0.032254722","0.12549877","0.012082101","-0.04049594","0.11151616","0.057378754","-0.005630886","0.031841848","0.081709385","-0.021832885","0.07385946","0.0659546","0.019627526","0.019120736","0.06316723","0.013562938","0.010737492","-0.06531945","0.16177699","-0.014181314","-0.02946994","-0.065254964","-0.097111225","-0.04309752","0.07412991","0.05949944","-0.029899519","0.009505312","-0.002193082","-0.024760326","0.01756163","-6.1374914E-4","-0.058002274","0.0037265068","0.019425537","-0.03149874","0.11230971","0.03574425","0.04276259","-1.7154653E-4","-0.030042173","1.0142872E-4","-0.068665445","0.026890974","0.016614715","-4.0373525E-8","-0.04689054","0.0455713","-0.07472354","0.026576528","-0.01791951","0.012029916","0.026368141","-0.03904296","0.02064394","-0.022594798","0.07467172","-0.01026036","-0.094867885","-0.045299925","-0.04426169","-0.046546005","0.017677346","0.06458628","-0.0048675747","-0.06263791","-0.05023367","0.029739678","-0.1148377","-0.0059028985","-0.048681784","0.024885833","-0.07004971","0.042955443","0.0698703","0.0056261253","-0.00300957","-0.015880797","-0.034069177","-0.036393862","0.0026863345","0.061190892","-0.0064324997","0.007338501","0.07810067","-0.06418013","0.0030123584","0.03943185","0.108419836","0.059543345","-0.0714088","-0.070540905","0.043526597","-0.075596765","0.026977543","0.01444595","-0.006405478","0.003734515","-0.028553072","-0.004940494","0.02315255","-0.02516305","0.012608192","-0.04187791","-0.099939756","0.012211034","0.04049464","-0.10599543","-0.059673633","0.030397946"]</t>
+  </si>
+  <si>
+    <t>NK-4uabScaY8xbv6puGwHvRdp</t>
+  </si>
+  <si>
+    <t>SBERBANK INSURANCE BROKER LIMITED LIABILITY COMPANY</t>
+  </si>
+  <si>
+    <t>Entity Name: SBERBANK INSURANCE BROKER LIMITED LIABILITY COMPANY | Type: Company | Jurisdiction: ru | Risk Context: (also LLC INSURANCE BROKER OF SBERBANK, STRAKHOVOI BROKER SBERBANKA, OOO, OBSHCHESTVO S OGRANICHENNOI OTVETSTVENNOSTYU STRAKHOVOI BROKER SBERBANKA, OOO STRAKHOVOI BROKER SBERBANKA) For more information on directives, please visit the following link: http://www.treasury.gov/resource-center/sanctions/Programs/Pages/ukraine.aspx#directives (also SBERBANK INSURANCE BROKER LIMITED LIABILITY COMPANY)</t>
+  </si>
+  <si>
+    <t>["-8.2549715E-4","-0.007922727","-0.16230276","0.011215837","0.006140377","0.022790281","0.076914385","0.019482166","0.05365063","-0.08568745","0.018282807","0.019183137","-0.0019084892","-0.020136494","0.02541816","0.00439188","0.035979006","-0.020199934","-0.034068357","-0.00332879","0.0020217644","0.004211661","-0.03168487","0.016116321","7.4022263E-4","-0.04528755","0.027851272","0.016179109","0.015261182","-0.057413317","0.03346557","-0.040028956","0.056201603","-0.011058286","0.06417165","0.05575455","-0.036601137","-0.029373204","-0.040825557","0.010206535","0.023772152","-0.08668761","-0.06689732","-0.013756325","-0.031459466","-0.034518808","-3.8544688E-4","0.029494178","-0.028610764","0.015867542","-0.07505662","-0.090140566","-0.0017380138","0.020295188","-0.01814932","-0.06374727","-0.018805882","0.02551933","-0.0022364347","-0.020827448","0.020795856","0.07187102","0.0075086206","0.07312524","-0.051368404","0.030766888","0.09353182","0.06683116","-0.036551524","-0.03244763","0.052588098","-0.087738134","-0.0983574","2.739857E-4","-0.045448832","-0.03401378","0.0032397392","0.09654583","0.059281986","-0.090418346","0.028994504","5.8885396E-4","0.023015883","-0.043772344","-0.08578811","0.04725983","-0.03434226","-0.004094634","0.09251969","0.020186314","0.034821533","-0.052700873","0.104033366","-0.045233473","0.0072908183","-0.051414084","-0.013077816","-0.014747534","-0.014083924","0.005259257","-0.041121066","-0.06864294","-0.079103336","0.081498496","-0.071795136","-0.045079328","-0.05270874","0.0045385743","0.012452296","-0.0015075679","0.043119177","0.06799221","-0.01404038","-0.07605595","-0.027441548","-0.03647635","-0.061164677","0.025456049","0.07603837","-0.11695816","0.05659569","0.031775307","-0.044013593","-0.076102905","-0.025757862","0.0633409","-0.025786366","6.29428E-33","0.05694917","0.034266517","-0.031685803","-0.04909682","-0.0013480453","0.039166503","-0.008796916","0.038497463","-0.0763955","0.051091813","0.004241818","-0.044028707","0.045395117","-0.06406105","0.014656861","0.028587686","-0.008193733","0.09260256","0.07005971","0.053972874","0.039770186","0.02960046","-0.0072938967","0.029189456","-0.029029207","0.043848332","0.03101047","-0.10656644","-0.0059194244","0.02520122","0.037480004","-0.020981697","-0.016599525","0.04512017","0.01924024","0.017056543","-0.11102035","-0.049966715","-0.074400544","0.005352683","0.012747682","-0.04077209","-0.049525537","0.069084555","0.017055418","-7.435285E-4","-0.0014003041","-0.00887735","0.063088834","-0.046438497","-0.08838562","0.006408996","0.0024864173","0.040504653","0.09294576","0.032438587","-0.03591051","0.09210114","6.3458184E-4","-0.03925428","0.02471977","-0.024763687","-0.012124093","-0.02029236","0.04696309","-0.020350287","0.04014942","0.06246176","0.011908973","-0.06039645","0.020564307","-0.012911791","0.0837453","0.089988485","-0.06523596","-0.045210343","-0.0150795765","0.013020217","0.05980889","-0.009231398","-0.076687455","0.025240013","0.08941417","0.044754904","-0.018851014","0.070682466","0.045974422","-0.053620074","-0.082811564","-0.0042667487","-0.092954464","-0.001071128","0.017364444","0.07853916","0.025963033","-9.2142315E-33","-0.024239957","-0.06566007","0.012712995","-0.06530458","-0.0847053","-0.027634783","0.06114452","0.02864434","0.031691648","0.03453715","-0.027423307","-0.051617052","0.0025278856","-0.039937526","0.0475743","-0.006606072","-0.009201324","-0.0046349354","-0.06862192","-0.0055526625","-0.0015789471","0.004886019","0.046595912","0.10776048","-0.02240232","-0.06721579","0.088771604","-0.03186651","-0.0016758128","0.023716163","0.012469576","-0.047730505","-0.077215664","0.028862283","-0.11566109","-0.075184084","0.008049494","-0.021905003","-0.03634603","-0.022571746","0.038842022","0.060778033","-0.0069041033","0.05020109","-0.038085822","-0.055541195","-0.0036572344","-0.027500693","0.07363902","-0.09228888","-0.011824795","3.8516845E-4","-0.027239906","0.051616445","-0.039896693","-0.018543886","0.053471267","-0.027033443","0.019739611","-0.020761065","0.032684557","0.06782746","0.059868503","0.16704686","0.050773393","0.0050967024","-0.038729127","-0.061718173","0.04963615","-0.11106829","0.029602414","-0.13071251","-0.073227376","0.052207507","0.060739208","-0.017822215","-0.05010113","-0.08182079","-0.03653649","0.024666134","0.06457197","-0.012362673","-0.030181691","0.065110505","0.061662685","-0.05900551","0.07032202","-0.02057722","0.10679511","0.03681641","-0.035120726","-0.016351322","0.011763592","0.05143592","-0.008101047","-5.0099764E-8","-0.0036749311","-0.038830962","0.018743992","-0.024216833","0.0158943","-0.08788128","-0.0070437323","-0.03297978","-0.11234813","0.043765318","0.010709398","0.009731867","-0.08320417","-0.037793346","-0.02718147","-0.047863327","0.019882387","0.103464134","-0.0038609472","0.029409196","0.031587783","-0.02513165","0.025525982","-0.12983562","-0.0140976645","-0.04337456","0.018624669","0.022331817","0.16791175","-0.05271122","-0.043693326","0.07186114","0.048752617","-0.010577661","-0.056837764","0.051747344","0.034929298","0.040684827","0.0119678285","0.041986607","-0.07333399","-0.051714018","0.07184936","0.02897479","-0.023909554","0.03712218","-0.11209493","0.003647387","0.07067906","-0.042495895","0.011217167","-0.06570655","0.058849793","0.103187874","-0.0025096226","-0.020662824","-0.021894483","-0.0044355066","0.023987899","0.0105534755","0.018597478","-0.062578745","0.06848466","-0.04878021"]</t>
+  </si>
+  <si>
+    <t>NK-4x5TD2PVDtPZZpfZ7DB5Z5</t>
+  </si>
+  <si>
+    <t>Jefferson Medical Industrial Clinic P.C.</t>
+  </si>
+  <si>
+    <t>Entity Name: Jefferson Medical Industrial Clinic P.C. | Type: Company | Jurisdiction: us | Risk Context: Summary Suspension Terminated</t>
+  </si>
+  <si>
+    <t>["-0.04990549","0.016927041","-0.020875037","-0.0071560633","0.01824539","0.04048314","0.008888982","0.04839787","0.011208285","-0.07127506","0.041234624","0.009302335","-0.020504527","-0.034527853","-0.09116256","-0.02662997","0.03983017","0.028791638","0.017849363","0.017335672","0.045800857","0.10838101","-0.009225645","0.052145157","-0.02259836","0.01932426","-0.03712478","3.4631975E-4","0.0072008003","-0.03406219","-0.013816817","-0.02535582","-0.016116796","-0.0520526","0.121810876","0.002165786","-0.060394466","0.101066835","0.06297903","-0.009263885","0.01313857","-0.041612387","0.034873065","0.04849454","-0.04548035","0.031483855","-0.04485454","-0.03837376","0.044792753","0.078779586","-0.08128032","-0.050852243","0.033126045","0.06823954","-0.022583043","-0.035452954","-0.048952036","-0.028528782","-0.0646398","6.0284056E-4","-0.032159902","-4.948157E-4","0.02111826","0.07030731","-0.020497886","0.038354777","0.06270048","-0.07276299","0.026261982","-0.07610433","-0.034662884","-0.07384859","-0.06305162","0.07113249","-0.027049737","0.12780048","0.033440243","0.00989089","0.06673999","-0.04811115","0.06483002","-0.036017586","0.020995583","0.01302783","-0.11589941","0.03768101","0.03246911","-0.015542245","0.0042750547","-0.05718575","0.047589753","-0.0069461972","0.08126189","-0.035612654","-0.0520009","0.0071701696","-0.025627894","-0.04307479","0.013647236","0.08002063","-0.032875743","-0.0012852614","-0.0012643358","0.0049451934","-0.043341506","-0.0702551","-0.07252739","-0.004695362","-0.027523424","0.04841873","0.04423553","0.06455763","-0.036774714","-0.055967044","0.030210936","0.067131795","-0.0068723243","-0.02182253","0.047575694","-0.06825642","-0.019915186","0.032379042","-0.065015465","-0.07544654","-0.07533348","8.987914E-4","0.001667154","-2.2579711E-33","-0.0030260156","-0.02248464","-0.020887563","0.03031816","0.041105166","-0.005838193","0.049650915","0.02699837","-0.0016244827","0.031024724","-0.06886198","0.0049938946","0.061807863","-0.07235923","-0.11036751","-0.003054661","0.025394857","0.06570279","-0.060891986","0.03818034","-0.037479114","-0.031563025","-7.7836233E-4","0.1292189","-0.055008758","0.05061678","-0.061679356","-0.0116414","0.048092794","0.0073349304","0.028843509","0.07070043","0.049660288","-0.029323978","0.084559396","0.03270638","-0.047356706","-0.03303982","0.008337817","-0.03401758","-0.029282736","0.05882935","0.032181527","0.073252566","0.021628482","-0.032877386","-0.049130633","0.016216153","-0.046888668","-0.04226674","0.0030542987","0.026552413","0.046748627","-0.011408644","0.06523354","-0.0144805685","-0.04408205","0.13224576","0.015672414","-0.009116498","0.06022901","0.12616843","-0.06141262","0.0205667","-0.0066239894","-0.05144962","-0.033912335","-0.042469252","-0.006550408","-0.077009015","0.08533051","0.03980197","0.077167876","0.066651754","-7.248421E-4","-0.007769016","-0.053805992","-0.034468208","-1.3015285E-5","-0.02812648","-0.04937312","-0.005649467","-0.02396495","0.05477297","0.046801414","-0.032573868","0.03521752","-0.012729135","-0.12174732","-0.022700373","-0.086131364","0.06551359","0.023865841","0.17859583","0.03356213","-3.3319695E-34","0.03638611","-0.033295188","-0.036446802","-0.06621084","0.051708348","-0.033414744","0.05593121","0.022668457","-2.0501074E-4","-0.015401963","0.10059873","-0.06484497","-0.039141595","0.08420078","-0.007400105","0.032826595","-0.0050936122","-0.020241555","-0.12896447","0.1016798","0.0027971794","0.030082738","-0.047140405","0.02251988","-0.036103148","0.031774055","-0.002182816","0.04364488","-0.026526218","-0.025949247","-0.042048894","0.029661201","-0.032796092","0.10291169","-0.054460146","-0.08013859","0.020374706","-0.11956211","0.027873944","-0.0950944","0.06243367","0.042149898","-0.049790364","0.06079028","0.07643038","-0.020618351","0.004711392","-0.054426216","0.11437549","-0.025666865","-0.09663744","0.0016833479","0.017105408","0.04703908","-0.01817554","0.01708875","0.08202963","-0.08522525","-0.10717845","0.009682148","0.004342158","-0.02186091","-0.029095078","0.12922624","0.08664391","0.009960406","0.01199573","-0.06319686","-0.0088800965","-0.034353983","-0.017465407","-0.0056166905","-0.0023108106","-0.054367587","0.027029313","0.0041003153","0.02941708","-0.084150665","-0.08912665","-8.175887E-4","0.068939485","-0.049298417","-0.015669072","0.091118164","-0.029009871","0.03770494","0.029043779","-0.052876916","-0.0035881852","0.017662702","-0.008868397","-0.07822066","-0.07074807","0.001403325","-0.035343215","-2.5978627E-8","0.00616375","0.023413","0.025463268","-0.031235255","0.05122111","-0.0067809285","-0.044202898","-0.0028019783","-0.012443477","0.008739592","-0.03725247","0.06093372","-0.06688182","0.03913729","0.0071342695","-0.054862972","-0.09365366","0.104638845","0.0028843547","-0.0264015","-0.08708849","-0.04461486","0.034319274","-0.060442988","-0.019953683","-0.009446326","0.032784417","0.008417874","0.01506597","-0.057034165","-0.008307635","0.07682105","0.0394783","-0.023828803","-0.07186338","-0.016500302","0.024022596","-0.026153974","0.006815991","-0.015054251","0.030527141","0.076388076","-0.05202829","0.013258278","0.12276524","-0.008034283","-0.060957428","0.053092364","0.0026313914","-0.003425124","-0.030389283","-0.022226118","0.052907042","-0.01973161","-0.06561244","0.020118462","0.014637566","0.020948645","-0.11946579","-0.019555809","0.015473647","-0.041193068","0.096046925","-0.034063723"]</t>
+  </si>
+  <si>
+    <t>NK-52ZuKZJUnSsncuQujL69xh</t>
+  </si>
+  <si>
+    <t>CENTER FOR GEOPOLITICAL EXPERTISE</t>
+  </si>
+  <si>
+    <t>Entity Name: CENTER FOR GEOPOLITICAL EXPERTISE | Type: Company | Jurisdiction: ru</t>
+  </si>
+  <si>
+    <t>["0.0446679","-0.07336","-0.0696601","0.034562547","-0.02017692","0.0017596794","0.04903663","-0.0046806773","0.020964822","-0.046591327","-0.043542597","-0.03648408","-0.0062276395","0.05770686","-2.1587161E-4","0.01422557","0.013139159","0.0208528","-0.0143829435","-0.08088214","0.03365907","-0.06337505","0.049894873","0.016152265","0.001248692","0.013802112","0.02301662","0.0017491623","0.006178951","-0.07159086","0.0112637775","0.010529353","0.038318478","0.02610184","0.05444909","0.075112484","-0.06244843","-0.00675998","0.030003594","0.023073604","0.012401683","-0.0777335","0.016348148","-0.030827828","-0.020790016","0.011995373","0.020222997","0.016502758","0.009870603","-0.04934824","-0.0012951201","-0.089202814","-0.017915497","0.056855764","0.010504791","0.007573338","-0.021294579","0.00664711","-0.010296539","-0.03903241","0.0073513757","0.01527036","-0.016328478","0.013186692","-0.0014127948","-0.009974823","0.04602517","0.06758874","-0.04032198","-0.06786179","0.06512757","-0.025059829","-0.06962854","0.011801598","-0.01660637","-0.06887535","-0.005400839","0.08260302","0.014401787","-0.041870218","0.07761727","0.10684155","-0.0016968718","-0.012382523","-0.074539006","0.036283128","0.08461409","-0.029304923","0.061227407","-0.017010596","-0.011009076","-0.063094884","0.18013525","-0.04079393","-0.018244872","0.042664018","0.043599445","-0.0050521283","0.0107255075","0.017335363","0.021733306","-0.035186134","-0.1020925","0.043844935","-0.052733988","-0.045192964","-0.13457507","0.05978645","-0.008280681","0.07582624","-0.080738015","0.088054426","-0.08794256","-0.011845104","-0.0048682205","-0.02767787","-0.0441954","0.032233972","0.07200726","-0.10272051","-0.02109668","0.016405972","-0.125348","-0.070491344","-0.046321057","-0.0011877712","-0.040780295","-1.717016E-33","0.014975141","0.07257841","-0.015593884","0.070794016","-0.11482809","0.062406614","-0.059800792","0.036261447","-0.070746414","-0.018205855","-0.021096263","0.048867125","0.023369556","-0.06535445","0.038722575","0.050850473","0.0012784258","0.06327955","0.009500176","0.01740761","-0.024262125","0.04372575","-0.04375027","0.050448","-0.0013753433","-0.01489084","0.038026765","-0.072532065","-0.028348465","0.033522025","0.050537273","-0.011638407","0.0040736324","0.07080339","0.042388972","0.09281625","-0.04900008","-0.036848117","-0.022997731","0.02636319","-0.019014802","0.0035054723","-0.08554152","0.078181006","0.087745324","0.019283433","0.06966721","-2.9968377E-4","0.09406431","0.010885738","-0.043657888","0.02427728","0.005681905","-5.6379614E-4","0.06758691","0.05809009","0.010429891","0.049028873","0.012865756","-0.042555436","-0.009582723","0.0142136235","-0.030848442","0.008111306","0.05634977","-0.0358609","-0.054584287","0.014093454","0.06973177","-0.043072063","0.029657407","0.011149982","0.11577463","0.13511086","-0.11435162","0.0044598696","-0.042674094","0.0116494745","-0.045801517","0.07077515","-0.12017044","0.012246231","-0.005779339","0.058641363","0.010841515","-0.022974117","0.055860505","-0.06853718","-0.022931393","0.0076399436","-0.1142769","-0.020704538","-0.062053356","0.07818509","-0.017061777","1.5749105E-34","0.069438025","-0.12817717","-0.07107684","0.04122781","0.0148194395","-0.014234244","0.028988171","0.0038866035","-0.016111681","0.054957304","-0.014753369","-0.09201155","7.359998E-4","0.062872924","0.02954414","0.017278146","0.042376697","-0.028980928","-0.09863241","0.12114074","0.0039718044","-0.06480107","-0.08893307","0.08419237","0.02289554","0.012959267","0.045527197","-0.10787074","-0.052546307","-0.024273865","-0.023104208","-0.028338237","-0.09824211","0.09267356","-0.12971708","-0.022642074","0.0134025905","-0.056760523","-0.038319517","-0.04234819","-0.0089722555","0.05393092","0.02075745","0.026870115","-0.055887215","-0.07231754","5.1872997E-4","0.030197145","0.06475333","-0.0910235","-0.049576674","0.015625315","-0.019763224","-0.03152913","0.0055980985","-0.007198326","-0.0063810027","0.02570812","0.018480135","0.0072468566","0.05585423","0.12255176","0.024935251","0.10698622","-0.041224223","-0.021946017","-0.021802025","-0.008503336","0.039821927","-0.07633473","0.015928848","-0.051835615","-0.06259871","-0.04644193","0.0048879106","0.006237284","0.0051340973","-0.05332406","-0.025759112","-0.0024688256","0.096568115","0.034262173","-0.014519707","0.029733976","0.044559374","0.08289959","0.0047097052","-0.0079139015","0.096861005","-0.020959739","-0.0067955228","-0.033794094","-0.0949577","-0.0023147697","-0.008094738","-2.1902537E-8","-0.019278863","-0.016195314","-0.0045502214","0.05512903","0.011246792","-0.07532941","-0.0017335808","-0.030304909","-0.069187336","0.062955774","-0.05785466","-0.044962525","-0.11126986","-0.01108134","0.017824661","-0.006814837","6.292035E-5","0.15816076","0.013056912","0.038464893","0.009551679","0.0074572726","0.0020526124","-0.09452505","0.040938806","-0.016175503","0.0346322","-0.020002674","0.115125306","-0.019857675","0.033021633","0.034796342","-0.020101752","0.026602732","0.0024525952","-0.0032305256","0.07257382","0.053161","-0.030199861","0.003452335","-0.021703873","0.05173538","0.03110304","0.025838958","0.010914332","0.052609112","-0.019278163","-0.0059260284","0.06404095","-0.048259508","-0.041174553","-0.04652553","-0.0018340253","0.065499134","-0.024558432","0.04929922","0.023469778","-0.033763148","-0.038161006","-0.004336617","-0.041528564","-0.056325372","0.026019625","0.028961785"]</t>
+  </si>
+  <si>
+    <t>NK-54i6qBQiP5GWNvE28KK7pG</t>
+  </si>
+  <si>
+    <t>GS CARE CORP</t>
+  </si>
+  <si>
+    <t>Entity Name: GS CARE CORP | Type: Company | Jurisdiction: us | Risk Context: 1128a1</t>
+  </si>
+  <si>
+    <t>["-0.07772615","9.771995E-4","-0.04653314","-0.03393565","-0.04831998","0.042488705","0.03156458","0.003009462","0.009578689","-0.06732655","0.0139157055","-0.038550206","0.004830932","-0.09551539","-0.023880133","-0.022391493","0.05928821","0.013095929","-0.064003065","-0.032533377","0.08635312","0.051841516","0.009225742","-0.03574797","-0.009336263","-0.054976597","-0.05498261","-0.013072443","0.03604861","-0.006171289","0.014355573","0.052528143","0.036980994","0.058085397","0.07493187","0.090938896","-0.05677219","0.028325854","0.0064559234","0.0015656679","0.013524977","-0.026855653","0.055910695","0.025411576","0.006128585","-0.0227422","-0.06828792","-0.046343382","0.020762743","0.075419575","-0.048422072","-0.02817309","-0.019052451","0.04539882","-0.019137345","0.036866713","-0.08199005","-0.0126440255","-0.056598853","0.019912565","0.001790068","0.0029936556","0.02833055","0.03213681","-0.016652154","0.0072262865","0.04492165","0.0015064825","0.0017836634","-0.11612607","0.06434098","-0.02679052","-0.07140325","0.07320031","-0.045986246","0.06140243","0.0036813936","0.038802605","0.07270047","-0.08174898","0.0383211","0.03654157","0.072301686","0.06734963","-0.12460357","-0.003730547","0.013376065","0.028272707","0.033851147","0.022919009","0.02648029","-0.020028224","0.08983002","0.0012771697","-0.037417885","-0.0033442758","0.005973174","-0.06217011","-0.05242345","0.035080716","-0.0014528198","-0.014716711","0.02631189","0.0858611","-0.07881871","-0.01747531","-0.12327354","0.045949057","0.01817942","0.03178622","-0.023839518","0.12065401","-0.062901124","-0.03856523","-0.06004997","-0.06605948","-0.041578077","-0.026277732","0.07913714","-0.07025","0.007291008","0.017525615","-0.11702042","-0.11944567","-0.06413606","-0.010856535","0.009014507","-2.2038188E-33","0.071733974","0.043915015","0.11548299","0.0028710302","-0.038485974","0.016081179","0.0039560036","0.027121639","-0.047910556","0.044513617","-0.078986146","0.04106908","-0.015888851","-0.101996325","-0.071847886","0.023809418","-0.044070214","0.03992935","0.022953575","-0.011997404","-0.0649653","-0.01121856","-0.033029716","0.018583346","-0.01132496","0.03447088","-2.1106697E-4","-0.0898032","0.030335272","0.06752393","0.062347107","-0.005815555","0.036596518","0.0098335985","0.039870292","0.05243105","-0.046593875","-0.07393882","-0.009513163","-0.059471667","0.0013265603","0.027163131","0.006848316","0.089250244","0.028577086","0.012231832","0.05680168","-0.045806784","0.056519534","0.05238557","-0.02040714","-0.0042169695","-0.065536596","-0.001076686","0.009587647","0.022999253","0.0508431","0.08823508","-0.039904203","-0.02582813","0.038027667","0.019155685","-0.06233673","0.012922026","0.012454485","-0.08503208","-0.0061784927","-0.08162974","0.0063615898","-0.021655098","0.033427082","0.03218289","0.054418985","0.07068345","-0.028549844","-0.01427409","0.014297019","0.038528536","-0.051098246","0.0371842","-0.07979219","0.009609602","-0.041370764","0.072976746","0.0082394555","0.017838128","0.033486716","-0.046895918","-0.10434584","-0.008546971","-0.08989608","0.07154793","0.04132038","0.10581628","-6.457821E-4","-1.3860419E-33","-0.043070484","-0.08367616","0.017755188","-0.045948844","0.050549217","-0.08605352","0.04377995","0.021990897","0.040426053","0.07593354","-0.020508442","-5.0306384E-4","0.032728188","0.0073938826","0.030337194","0.015678342","-0.017879011","-0.023334445","-0.09985572","0.09677192","-0.0017099839","0.031263344","0.00911792","0.12548415","0.050978992","-0.006882616","0.0011724889","0.0038282673","0.019393662","-0.061088532","0.03438959","0.029484022","-0.04228761","0.10807314","-0.10652641","-0.13582474","0.043802354","-0.060066715","-0.015017548","-0.04949105","-0.0029183202","0.04305852","-0.01506793","0.053381294","-0.018875804","-0.021661744","0.10463754","-0.05593624","0.039983086","-0.05362849","-0.041610926","0.0024586","-0.041471463","0.03955673","7.901681E-4","0.045724224","0.049075264","-0.08911964","-0.040072247","-0.0655602","0.07293757","0.06988762","-0.05660966","0.10189847","0.032354437","0.012367947","-0.0010443995","-0.042619623","0.017778233","-0.085840456","0.023537304","-0.03395113","-0.045067415","-0.03620852","0.0077162","-0.053643942","-0.014533212","-0.071873136","-0.06331081","-0.006589444","0.12900591","0.0059573585","-0.008278193","0.06915532","-0.00525974","-0.007485105","0.08942657","0.056144","-0.0030261518","0.05271854","-0.105357446","0.021369392","-0.06485624","0.010906004","-0.07541387","-2.3796282E-8","0.007175994","0.032673113","0.021044929","-0.048841387","0.023524864","-0.064278476","-0.07113328","0.056195345","0.0019915267","0.021368494","-0.051453125","0.0643696","-0.08960586","-0.012260287","-0.023630487","-0.064088225","-0.07572702","0.090147786","0.011946703","0.11366517","-0.025314938","0.011108332","0.009119644","-0.084744625","-0.028114129","-0.0051953425","-0.0016933128","0.0016939378","0.07378666","-0.0142226275","0.02116491","0.070595786","-0.0243056","-0.0010166581","-0.10684072","-0.039093405","0.10459257","-0.04127192","0.053904515","-0.023159727","0.054697268","0.048871","0.0051183864","0.044894613","0.0148134045","0.008314942","2.6542644E-4","-0.005170877","0.03326606","-0.011746756","-0.059751276","-0.08846902","-0.038971763","0.008355181","-0.06742709","-0.07866817","-0.010385895","0.019533562","-0.022621168","0.002045385","0.027267262","-0.04819144","0.06134863","0.003782367"]</t>
+  </si>
+  <si>
+    <t>NK-59wrEkptjhztRnZyN5zFhD</t>
+  </si>
+  <si>
+    <t>Sergeev Andrey Fyodorovich</t>
+  </si>
+  <si>
+    <t>Entity Name: Sergeev Andrey Fyodorovich | Type: Person | Jurisdiction: ru | Risk Context: 1, Part 1.1 | Former head of the Ministry for Internal Affairs of North Ossetia-Alania, a federal state body that carried out political persecution in the territory under its jurisdiction against citizens and organizations that opposed Russia's aggressive war against Ukraine and were in opposition to the current political regime in Russia.</t>
+  </si>
+  <si>
+    <t>["0.018073117","0.022665216","-0.07493255","-0.02084954","-0.001423868","-0.07683584","0.077912055","0.0072575845","0.025536714","0.019903708","-0.0816178","-0.0074557634","0.03091463","0.016708864","-0.031437635","0.010099643","-0.023254072","0.031428397","-0.025886724","0.073797256","-0.012575515","-0.042684905","0.045867458","-0.0122803245","0.04686207","0.015612518","-0.020708121","0.039984357","-0.01475986","0.016972354","0.080761395","-0.051510558","0.024412468","-0.01794744","0.056122966","0.061918687","0.0012591106","-0.058805913","-0.092273","0.0059585036","-0.016346663","0.019206656","-0.013847649","0.054444436","-0.05111092","-0.053014413","-0.023676919","0.03132151","0.022387832","0.011161661","-0.06950517","-0.076425634","-0.0104269665","0.051043544","-0.0033446325","-0.02865023","0.015114129","0.00947454","-0.058356825","0.028265344","0.06586799","-0.014856809","-0.03737783","0.012528387","-0.07221288","0.0059929243","-0.011054187","-0.040663246","0.0133590475","0.021285482","0.109994575","-0.045336243","-0.03727522","-0.058248702","0.020144207","-0.09166356","-0.0064530987","0.0501109","0.05546152","-0.04012622","0.08834898","0.027175216","0.007261825","-0.008679912","-0.04313228","-0.028456654","0.040290326","-0.05296645","0.06411065","0.09768728","0.02644555","0.03354265","0.23264799","-0.10253975","0.09979639","-0.03914808","0.07886754","0.009309156","0.00281683","0.1065704","-0.059884634","-0.08196753","-0.036061432","0.030138403","-0.060814075","0.025182249","-0.08898085","-0.019169025","-0.13648377","-3.1376345E-4","0.0010445209","-0.0374631","-0.0013948296","0.006012723","0.049305618","0.015510827","0.050553083","0.049316995","-0.048769113","-0.005276206","-0.007869696","-0.02560724","-0.0766494","0.016748799","0.065060176","0.04968669","-0.06073341","-1.1836571E-34","0.07058791","0.005828199","-0.03797128","-0.033904523","-0.06082872","0.0388634","0.037753113","-0.033041857","-0.039934352","0.03705631","-0.006184179","0.05702551","0.008975712","-0.09862448","0.04379113","0.045334727","0.0052023795","0.10159827","0.019932924","0.1279922","0.104836255","0.008169362","-0.014866327","-0.023756523","-0.06655018","0.035240356","7.8858563E-4","-0.066939615","0.043207135","0.017398862","-0.0960391","-0.004659025","-0.040664822","0.004690686","0.038706306","-0.001987978","-0.06716504","-0.06972757","0.01731194","0.011053666","0.02209333","-0.0014640563","0.03471318","0.02622623","-0.009725235","8.264185E-5","0.035234004","-0.01002894","0.03473889","0.011272724","0.0037658054","0.017944131","0.009557682","0.017182285","-0.049002465","0.002068552","-0.06471193","0.12419767","0.049245346","-0.015941612","0.060117505","-0.06196756","0.03567468","0.071724966","0.009667733","-0.12250537","0.05142445","0.037097435","0.045418546","-0.023911271","-0.026462508","0.014630528","-0.015865818","0.11863723","-0.06874555","-0.011899325","-0.012788652","-0.021509174","-0.13905744","0.038023025","-0.07858662","0.011011921","0.009306331","0.009879494","-0.024393635","0.08568863","0.032969907","-0.03297268","-0.058579694","0.0032390747","-0.051411614","-0.06909137","-0.0030196882","0.059444338","-0.08355912","-1.787545E-33","0.017515218","-0.12939133","-0.019017676","-0.029242743","-0.02691978","0.03381649","-0.02825623","0.03104412","-0.039652534","0.0727052","0.046030257","-0.09434211","0.06860333","0.049372703","-0.034032572","-0.03172309","0.07696297","0.0154489","-0.09828589","-0.048383936","-0.08664239","-0.017535625","0.004222212","0.009290925","-0.028911136","-0.028433068","0.08239108","-0.050796423","-0.115733616","0.064170346","-0.011047671","0.03625285","-0.09666831","0.005054745","0.014037372","0.043769464","0.068194844","-0.06928187","-0.0020883686","0.04872637","0.022720702","0.068588614","0.06201739","0.09812483","-0.027905641","0.006854707","-0.070330374","0.08140563","0.053277157","-0.106857836","-0.06309199","0.011466455","-0.007987326","0.03186805","0.021508284","-0.027029077","-0.034968086","0.013713406","-0.024534239","0.052565783","-0.023101848","-0.050837077","-0.022908667","0.05916806","0.010109033","0.086918205","-0.035498172","-0.03400269","0.0596239","0.010641413","0.09365149","-0.06348638","-0.0062980196","0.096684724","0.016471185","0.08263309","0.03846284","0.0032320837","-0.012284784","4.115426E-5","0.11273194","-0.0712749","-0.07558173","0.0052891406","-0.018729666","-0.02502524","0.06421224","-0.001228222","-0.005283952","-0.006490472","-0.016380887","-0.0017078881","-0.05067086","0.04355733","0.04716786","-4.036233E-8","0.0740275","-0.03361036","-0.0016301583","0.04586344","-0.04784845","0.016644802","-0.04568382","-0.06997808","-0.06708896","0.020698206","0.004623106","-0.032051425","-0.017073743","-0.051794022","-0.0046789646","0.008827582","0.025641806","0.119098864","-0.019954352","-0.023203857","-0.012766408","-0.033712916","7.0457853E-4","-0.059337266","-0.024168512","-0.040055145","0.044951737","-0.010721261","0.065785035","-0.013219266","-0.023985507","0.029354015","-0.033466045","-0.009501804","-0.05508113","0.049730547","-0.0107700415","0.005992981","-0.027003393","-0.052726947","0.0132196015","0.015147061","-0.0013270436","-0.019208603","-0.078854874","0.039930828","-0.017234394","-0.029406255","0.050875016","-0.057241134","0.030922152","0.05928143","0.029004846","0.11754535","-0.025498543","0.036880594","0.004107242","-0.01637218","-0.04797532","0.012821342","-0.053889427","-0.053318355","0.03627248","-0.08036217"]</t>
+  </si>
+  <si>
+    <t>NK-5F8VcgoWKRJZLzZe9AbNS4</t>
+  </si>
+  <si>
+    <t>Kantemir Kaparbekovich CHALBAYEV</t>
+  </si>
+  <si>
+    <t>Entity Name: Kantemir Kaparbekovich CHALBAYEV | Type: Person | Jurisdiction: Unknown</t>
+  </si>
+  <si>
+    <t>["-0.07340351","0.010181877","-0.08181963","-0.051342614","-0.077713855","-0.0038922029","0.075787336","8.063649E-4","0.027124077","-0.0059850942","0.045682855","-0.13475631","0.005466534","-0.02996512","-0.07230588","0.019612895","-1.833311E-4","0.042481765","-0.017798861","-0.082577534","-0.04327109","-0.026769424","0.036329884","-0.009021986","0.06273258","-0.049155682","0.0027499637","-0.0047504944","-0.0046363734","-0.014033035","0.06846318","0.034659576","-0.031325284","0.09137341","0.08403185","0.037638478","-0.114170104","0.0592203","0.0525323","-0.010188121","0.005224106","-0.046885736","0.022418778","0.07339001","-0.0033631194","0.02817989","-0.028482106","0.055773623","-0.029541075","0.016299449","-0.044713944","-0.01026648","0.03037653","0.06667415","0.016151175","-0.050330598","-0.032786403","0.059396993","-0.044215992","-0.0025500252","-0.009866683","0.07238389","-0.0065658707","-0.0069086156","-0.10332766","0.011089652","0.018412858","-0.024424752","0.0446188","-0.08139603","0.1140878","-0.012142237","-0.053214513","2.7537264E-4","-0.020892983","-0.083730325","-0.014772336","0.086606376","-0.021646582","-0.034195725","0.0034739254","-0.0034338576","0.043886494","0.0033500989","-0.054844677","0.008946589","0.07918311","-0.031855613","0.0711716","0.04608378","-0.0032650325","0.012153368","0.12985119","-0.05926322","-0.045914948","-0.008580788","0.038486272","0.008884334","-0.007613687","0.089849815","-0.030643497","0.030258993","0.0039070565","0.048309933","-0.106304556","-0.012667352","-0.030502183","-0.014354309","-0.05071467","0.011253892","-0.017309114","-0.020315604","-0.03325946","-0.011384141","0.122242704","-0.010407477","0.051133316","0.03838059","-0.0100878365","-0.08269128","-0.03174915","0.011653508","-0.12380238","-0.058378816","-0.06390562","0.009951889","0.0014468366","2.4249266E-33","0.053873993","0.03554989","0.020402696","0.052869868","-0.09542463","-0.022424743","-0.05200507","0.030803466","-0.13074207","0.042871412","0.032473393","-0.07045042","-0.004779076","-0.121285304","-0.009152824","0.0947468","-0.04417008","0.04893014","0.0217524","0.08692763","0.018700695","0.012368376","-0.0064052166","-9.3016156E-4","0.0035991073","0.008597799","0.055477437","-0.09298047","0.02654871","0.03599974","0.009377954","-0.0475353","0.02809474","0.010351434","0.0038607812","0.029523958","-0.04007387","-0.072442144","-0.040919255","0.034231853","-0.009162755","0.027071211","0.011123773","0.046114415","0.006964573","-0.008634566","0.08679893","-0.010217621","0.083511464","0.044386175","-0.048646376","0.024451165","0.010562495","0.013236444","-0.0034905435","0.038055927","-0.037907023","0.07000819","0.083591565","-0.046290465","0.074721016","-0.027278887","-0.12074012","-0.0056578442","0.048822228","-0.13796748","-0.0012516418","-0.022584893","0.019027675","-0.102272786","0.034283362","-0.035501525","-2.682465E-4","0.1034902","-0.025260605","0.011421989","-0.020644862","-0.03765628","-0.099658","0.06470428","-0.12673366","0.02819955","-0.0058690626","0.02441174","-0.028894784","0.063808374","0.033856865","-0.047595005","-0.041871242","0.05487701","-0.08201872","0.027404882","-0.027191268","0.047586672","0.011667612","-3.1022824E-33","0.012257344","-0.15171908","-0.049238384","-0.01781198","0.06256441","-0.03608941","-0.03187305","0.034081925","0.027135871","-0.0027577789","0.018420113","-0.0366937","0.03176443","-0.01016091","0.03159257","0.08524658","0.06192828","0.0387659","-0.08590778","0.107031874","0.008230525","0.036311142","-0.04310701","0.022657145","-0.056773685","0.03676006","0.07911598","-0.011469389","-0.04406275","0.012746498","-0.009689124","-0.050532755","-0.0966514","0.0070761098","-0.120705105","-0.08066155","0.07808551","-0.030976884","-0.046597097","0.02215784","-3.1548954E-4","0.108239904","-0.010310535","0.016281694","-0.009985131","-0.061625488","-0.008862178","0.054530576","0.06764979","-0.08157278","0.008165728","0.01573936","-0.0321402","-0.042955495","0.06615246","0.067681","-0.01822812","0.0012006473","0.09678655","-0.02666785","-0.02120538","0.014698353","-0.0073735504","0.11088494","-0.0069701564","0.03637138","-0.0284649","0.030628368","0.005142105","-0.104223795","0.01869011","-0.1206311","-0.06832512","-9.846715E-4","0.02843209","0.027610052","-0.013747575","0.060424138","0.024347672","-0.00427896","0.07525859","0.011315309","-0.048461426","-0.014514227","0.079058","-0.018432168","-0.0056923465","-0.04083989","0.06260338","-0.082638465","-0.0115355905","-0.013199859","-0.016186152","-0.012725514","-0.015694","-2.5843024E-8","0.015177683","6.794564E-4","-0.050329287","0.02730235","-0.03675783","-0.043276027","-0.0019833683","-0.006771729","-0.061684098","0.019602804","0.005828795","-0.006567917","0.023355147","0.012032294","0.08374883","-0.03792201","0.011440716","0.057410248","-0.016863558","-0.0013353942","3.6681144E-4","-0.0116937235","0.020807931","-0.10623619","-0.01894248","0.043955836","-0.021161279","-0.05954082","0.0077971905","-0.017084697","0.00777427","0.12514076","0.0076887854","0.008574041","0.07578484","0.07922711","0.026013616","-0.040069446","-0.028209157","-0.0018199593","0.017548297","0.040117614","-0.020293158","0.048153076","0.05673884","0.054452978","0.083934456","-0.05195238","0.046094723","-0.043950632","0.01070411","-0.031945717","0.08598283","0.078384936","-0.035853572","0.015647095","0.06351895","-0.02883353","-0.041421883","-0.07228661","0.045580845","-0.0634722","-0.018127577","-0.020932259"]</t>
+  </si>
+  <si>
+    <t>NK-5HTmA74tCGz4WvAd4y2wKu</t>
+  </si>
+  <si>
+    <t>TALIA</t>
+  </si>
+  <si>
+    <t>Entity Name: TALIA | Type: Vessel | Jurisdiction: Unknown | Risk Context: 03112 - WATER/WEATHERTIGHT CONDITIONS - Scuppers, inlets and discharges (DNV GL AS (DNVGL))</t>
+  </si>
+  <si>
+    <t>["-0.10061111","0.032730818","0.0040260344","0.027600747","0.0015448097","-0.0833276","0.035464708","-0.009862598","-0.050515484","-0.07550576","0.039385673","-0.108023666","-0.074056","0.011309243","-0.08353039","0.019016344","0.016167797","-0.008208521","-0.07331904","0.007933081","0.03832635","0.12186865","-0.041106813","-0.011380648","-0.06707051","0.0034040965","-0.024345051","0.049717445","0.030037593","-0.076484814","-0.05610534","0.12564518","-0.03425543","0.013630746","0.112372674","0.058719464","-0.06385439","0.07478702","-0.0037011486","0.0030430455","0.08698974","-0.08640687","0.037175227","0.0013819436","-0.068176866","-0.018074602","-0.014743786","0.043864366","-0.006211614","0.052794885","-0.05953387","-0.06734061","-0.029627401","0.040817346","-0.047550917","-0.059805647","-0.04902923","-0.043435436","-0.0463841","-0.054279022","0.05436161","0.07928595","-0.054733932","0.026521476","0.07702504","-0.038346287","0.025721883","0.038459588","0.03134725","-0.049568832","0.047521353","0.023655737","-0.05039838","0.023844479","-0.07825354","-0.014410397","0.05676401","-9.80055E-4","0.08276422","-0.02752366","-0.032669604","0.06167609","0.04806156","-0.014403148","-0.018052896","0.063650765","-0.0056640427","0.024706293","0.05540723","-0.02377957","-0.055907197","-0.065077044","0.11646144","0.0062535354","-0.022060351","0.071513504","0.08014598","-0.033612557","0.0055375756","0.073003486","8.3726534E-4","-0.030197017","-0.023114","0.042959157","-0.06802635","-0.025026223","-0.001834191","0.02853704","0.016746849","-0.042026784","-0.02435115","0.10542477","-0.04356285","-0.05572465","-0.0775243","-0.023301644","-0.112794","-0.007871962","0.101878434","-0.07749148","-0.026645094","-0.04213099","-0.052884407","-0.017831048","0.030105237","0.0125025315","0.03204338","-2.0617078E-34","0.051038306","-0.040612094","-0.0031816089","0.058695752","0.055147916","-0.019731821","-0.025902819","-0.034193274","-0.08190596","0.053100474","-0.12361125","-0.0076024453","-0.08813349","-0.07638452","0.0322569","0.022533046","-0.019792521","0.0114250025","-0.018992305","0.0074746865","0.045083918","-0.003935767","-0.042522594","-0.05433801","0.008932092","0.051401727","-0.00971934","-0.07284092","-0.009660731","0.06485139","0.09605509","-0.010986597","0.10440763","0.023867028","0.042279154","0.019540844","-0.06547623","-0.075238355","-0.07864207","-0.038170017","-0.012840738","-0.002193252","0.004262485","0.07531709","-0.053227995","-0.024836453","0.0259388","-0.02802159","-0.0076741176","0.0030293248","0.007968155","0.021235552","0.0018488889","-0.030237915","-0.007639556","0.023187716","0.044767458","0.057796367","-0.001048614","0.003856686","-0.042350322","0.07339249","-0.0059238793","-0.014357727","0.1107749","-0.017341334","0.032037545","-0.03703009","0.101089455","-0.11656418","-0.05411621","0.05265519","0.04519674","0.1271504","0.043654658","-0.021683637","0.094884485","-0.04669662","-0.0060738362","0.010261239","-0.11851768","0.025238317","-0.016287344","0.08196648","-0.028051557","-0.014656375","0.0019231561","-0.03155503","-0.06554906","-0.009393015","-0.05194808","0.05801852","-0.044741344","-0.029277112","0.0325723","-1.4470623E-33","0.04338755","-0.048995476","-0.049541947","-0.052363563","0.041193217","-0.035620745","0.013361928","0.012961619","0.013260951","0.027873445","-0.0399858","0.013779928","-0.022101292","0.04228617","0.045309115","0.049287494","0.018244494","-0.05012047","-0.07401048","-0.0032188992","-0.0027399124","-0.016642975","-0.036896687","0.04473607","-0.016300587","-0.039296363","0.03965434","-0.020017546","-0.09990182","-0.019168124","0.01230767","0.033572935","9.515887E-5","0.06292892","-0.074682645","-0.078492835","0.054605592","-0.045799945","-0.04413114","-0.04707621","0.022665596","-0.0043099606","0.03045853","0.03812011","-0.057320878","0.008886518","0.051519644","-0.017163854","0.054946985","-0.0017280031","0.029354982","-0.031826627","0.0023937463","0.064524","0.101522245","0.029569814","0.050585646","-0.077557646","-0.043990493","0.011766224","0.08539869","0.054148186","-0.047621705","0.082705125","0.0515781","0.007906036","-0.13195397","-0.0077211694","-0.015815383","-0.048025392","0.051519167","-0.0817901","-0.062966004","-0.00847849","0.006529931","-0.08786957","-0.050066214","-0.017916549","-0.03313234","-0.015008137","0.042129938","-0.041286923","-0.035938866","0.074693054","0.11935531","-0.012827838","0.107498504","0.032865338","0.09447291","0.04681335","-0.01764685","-0.0031359468","-0.12746967","0.011451906","-0.07155009","-3.4178623E-8","-0.008523097","0.04513521","-0.004315882","0.020699853","-0.038424414","-0.016367719","0.01090905","0.04826254","0.024592908","0.0024278886","-0.0051845973","-8.513191E-4","-0.054797515","-0.041995723","0.029632878","-0.014159298","-0.06677071","0.045836207","-0.04524012","-0.05968462","0.024916884","0.0014464584","-0.023444457","-0.030846769","-0.046140242","-0.032054245","0.057102","0.012923446","0.10109659","-0.06848121","0.017547926","0.08833808","0.03165088","0.021659223","-0.030782392","0.07031734","0.019324495","-8.3715393E-4","0.0028495234","0.011721509","0.0139282085","0.056454867","0.024825398","0.013556035","0.06820459","0.11851357","-0.034822166","0.008795596","0.033867743","-0.037218206","-0.035385158","-0.009865047","0.045702737","0.13525148","-0.04716182","0.02658722","0.048767347","0.037858456","-0.013819279","-0.015231081","0.05970262","0.020785559","0.0023424732","0.042978536"]</t>
+  </si>
+  <si>
+    <t>NK-5LXJagsZHPj2GrxmGxxbTT</t>
+  </si>
+  <si>
+    <t>Joint Stock Company Ascon</t>
+  </si>
+  <si>
+    <t>. 7809009923 (fiscalcode-National Fiscal Code) (on 2002-09-12)(Tax Identification Number) Principal établissement: Fédération de Russie - Askon JSC est une société informatique russe qui met au point des logiciels de conception, d’ingénierie et de gestion de la production pour le complexe militaro-industriel russe. En particulier, Askon JSC met au point des logiciels de modélisation numérique pour JSC United Shipbuilding Corporation, JSC Research and Production Corporation URALVAGONZAVOD, JSC Tactical Missiles Corporation (KTRV) et JSC Almaz-Antey Air and Space Defense Corporation</t>
+  </si>
+  <si>
+    <t>["-0.08893866","0.0012371964","-0.036341462","-0.09594623","-0.019608254","0.034217414","0.026112061","0.0734049","-0.039383788","0.009223262","-0.016299747","0.05902613","0.0049954066","-0.040671263","-0.12178383","-0.095441364","-0.0808758","-0.03806888","-0.006514515","-0.017272945","0.0796677","0.02179647","-0.018954698","0.0052710418","0.08728247","-0.018661946","0.0024823963","0.032531165","-0.025968965","-0.015123324","-0.021167997","0.052098047","0.0066391598","0.028353535","0.11507428","-0.01595276","0.07294944","-0.04938235","-0.053869065","0.061229777","-0.057304054","-0.036495157","-0.05163727","0.049330946","-0.021279927","0.013610647","-0.011425212","-0.04764612","-0.039147492","0.11848103","-0.042025037","0.08418936","0.028007654","0.013365493","0.092920564","-0.12738453","-0.03421924","-0.0040474855","-0.05637798","-8.620502E-4","-0.048846755","-0.054242507","0.033619538","-0.07888722","0.015438689","0.02854032","-0.012454351","-0.06161955","-0.078317896","-0.072963014","0.019156603","0.031577952","-0.08630369","-0.0017178836","-0.09102566","-0.015301811","0.02056333","0.08422917","0.05398942","-0.10131901","0.06379375","-0.008297976","-0.12011082","-7.5880997E-4","-0.044468828","-3.618957E-4","-0.014960467","0.04080206","0.15343244","0.095775224","0.026222488","-0.011252128","0.101160966","-0.037015237","-0.055364173","0.024322318","0.020258576","-0.020865817","-0.0026543434","0.08270166","0.031030104","0.032792848","0.04240113","-0.024916817","-0.100896575","0.025407014","-0.057248212","0.05652012","-0.0019512412","-0.10223797","-0.0029883625","0.024548512","-0.083571196","-0.10182184","-0.06334086","-0.028137548","-0.01481655","-0.06107899","0.032446258","-0.13004583","0.04856524","-0.024752336","-0.0394225","-0.0063221953","-0.018976629","-0.029108055","-0.0846376","8.985935E-33","-0.04711092","0.068772554","0.041587383","-0.032721866","-0.14406596","-0.021037987","-0.07331423","0.011913135","-0.037604507","-0.005734955","-0.072860256","0.019904127","-0.041094042","-0.04073983","0.06897476","-0.050076924","-0.006678194","0.07620674","0.0418708","0.065398045","0.083395205","-0.014029545","0.04296391","-0.016753927","0.07452444","0.09629442","-0.043428104","-0.013319663","-0.03375023","0.04933783","0.059680935","0.056838326","0.032931402","-0.03183166","0.0070037097","-0.014673643","-0.008273211","-0.036562655","-0.018331647","-0.06370338","0.025270019","0.015406157","-0.014697101","0.053548735","1.5415905E-4","0.004350782","0.067055635","0.019073557","0.08844425","-0.036955357","-0.037716806","0.013696121","0.037836537","-0.07824385","0.03540026","-0.0063824262","0.050332103","-0.05475499","-0.051817235","-0.0015289156","0.006845593","0.0073725176","-0.014886404","-0.01436292","-0.038503032","-0.0011786876","-0.0013942528","0.04349845","0.06861726","0.06725149","0.011995057","-0.019788735","0.059811313","0.050564967","0.038655728","-0.0053949985","-0.00445283","0.04538485","-0.015479232","0.036065847","-0.08337969","0.033204388","-0.044243827","0.015086802","0.059131157","0.051384896","0.051852472","0.07226423","0.004783684","-0.018634563","-0.016495697","-0.006107498","0.007786075","0.037080806","-0.007207812","-1.1646277E-32","-0.018089278","0.0502822","-0.04686445","-0.028273517","-0.0937799","-0.006689488","0.046093475","0.013206614","-0.07134395","0.02533418","0.019667258","-0.06254446","-0.008938629","-4.0265245E-4","0.047703397","-0.024560284","0.05595122","0.0069993017","-0.02143257","-0.001187991","0.03521189","0.03414833","0.012773737","0.021797141","-0.02311994","-0.00893852","0.014616803","0.019702122","-0.00871007","0.007184821","0.020242957","-0.051919952","-0.02616236","0.065013506","-0.003934417","-0.047769476","0.083265305","6.4064324E-4","-0.015886102","-0.022717055","-0.0028600788","0.039464682","-0.015607697","0.11024259","-0.018118223","-0.07171927","-0.016492601","0.016102634","0.044570386","-0.118741155","0.02950968","0.018566968","-0.018340545","-0.004286609","-0.02741899","0.11077958","-0.020735262","0.039949134","-0.022222819","0.05853404","0.05154541","0.0014524773","0.026871607","0.02576601","-0.027796","-0.111722246","0.02945923","-0.009510461","0.052286413","-0.112039976","0.035457402","-0.060777057","-0.00632829","0.0571794","0.02847787","-0.031950608","-0.038274117","0.065341234","0.009854745","0.075300924","-0.003732259","0.02889911","-0.048436288","0.05527094","-0.0012248664","-0.050988663","0.05630846","0.03556137","0.015286614","-0.074301","-0.08876642","0.019806165","-0.01564478","0.056784604","-0.06852309","-5.8225577E-8","0.018445427","-0.04426444","-0.046746984","0.003118236","-0.049150195","-0.08304904","-0.05030451","-0.03626457","-0.04280335","-0.016563127","0.042746905","0.022977479","-0.1197938","-0.011835906","-0.030707996","-0.03638039","-0.075155675","0.12955725","-0.040465962","0.047341138","0.025784856","-0.01163264","-0.042852204","-0.045082938","-0.08124053","-0.0076931757","0.0034144376","0.023957912","0.06867298","0.024045607","0.02739262","0.045890626","-0.09341875","-0.052822087","-0.033467993","0.004048649","0.0028197889","0.063519165","0.078702666","0.008593175","-0.007927521","0.0023680185","-0.081577815","0.03564246","0.0065381","0.036559775","-0.123475984","-0.12115998","-0.07072171","-0.023797398","0.041381925","0.047948156","-3.003269E-4","0.020886274","-0.025521643","-0.018272115","-0.0049632033","-0.06327425","-0.0718731","-0.0022118485","0.084707804","-0.061805658","-8.36235E-4","0.037351646"]</t>
+  </si>
+  <si>
+    <t>NK-5MdHUAUdYQwLe3k8xCiHW3</t>
+  </si>
+  <si>
+    <t>Richard V Utarnachitt</t>
+  </si>
+  <si>
+    <t>Entity Name: Richard V Utarnachitt | Type: Person | Jurisdiction: us | Risk Context: 1128a1</t>
+  </si>
+  <si>
+    <t>["-0.04908029","0.07651832","-0.046980463","-0.040009424","-0.029020205","0.055436913","0.027240107","-0.0171062","0.006552237","0.0076122032","0.040185288","-0.03742533","0.003952061","-0.011921159","0.017638672","0.0421036","0.027659543","0.063907534","-0.03214111","0.009615294","0.03118757","0.0646792","0.046734136","-0.09077536","0.02734817","-0.058369454","-0.02183843","0.035680946","0.029323574","-0.027037084","0.0253647","-0.0028988076","0.04268005","0.106644","0.061838675","0.016383206","-0.07948396","0.05572122","-0.06039535","0.004033881","-0.0154533535","-0.072504476","0.06105657","9.063621E-4","-0.039691076","-0.018830907","-0.036167298","-0.07572814","-0.0152066825","0.083807334","-0.040440284","-0.013846697","0.041301586","0.053570442","0.013545261","-0.004931974","-0.011085583","0.02720871","-0.10045173","-0.0032754831","0.040186297","0.03762215","-0.035005774","-0.027399091","0.033106368","0.019650145","0.01577709","-0.005493535","0.071324036","-0.13829651","0.08840213","-0.0203762","-0.13290362","0.051621575","-0.013654336","-0.022768801","0.022188477","0.076812424","0.089718096","-0.043532494","-0.0038397196","0.021244723","7.9567166E-4","-0.022631388","-0.056976125","0.05615345","-0.032825","-0.02147852","-0.021846196","0.06632666","-0.035409074","-0.05062859","0.15305148","-0.008133753","0.04006126","-0.023224546","-0.028611507","-0.014919267","-0.07548775","0.07297069","-0.048064224","0.05042216","-0.06284521","0.033733487","0.0015183896","0.0034656243","-0.0063627088","-0.01115312","-0.025074484","-0.0021691942","-0.0021587512","0.06638598","-0.05946485","-0.027440008","0.036461465","-0.05735791","-0.10694183","0.08213473","0.059875693","-0.13172705","-0.0106591545","0.0071568266","-0.103315644","-0.034037925","-0.091704816","-0.05400562","0.040097587","-1.9894285E-34","0.07865463","0.046062507","0.020278685","0.043971457","-0.048427533","0.061956145","-0.024652574","-0.007988832","-0.042249005","0.001144564","-0.030051608","0.012751467","0.024763122","-0.07855593","-0.095409565","0.010953027","-0.0065297675","0.083152026","0.02528366","-0.005196069","0.016515898","0.039803855","0.0017547858","0.013837935","-0.037317075","-0.05675141","-0.031374343","-0.046573568","0.036904402","0.06442941","-0.01685329","0.038642757","0.030776506","0.009854045","0.06882791","0.08939117","-0.031010715","-0.06052103","-9.890746E-4","-0.0036235305","-0.0063051246","0.04819549","-0.022679642","0.06728398","-0.0458839","-0.0078218505","0.099900275","-0.003982121","0.042066388","0.033440277","-0.076698355","0.03668085","-0.061109528","-0.041828007","-0.050328378","-0.070068836","0.04890491","0.07109164","-0.04365137","-0.05635116","0.034495704","0.030386107","-0.028733484","0.0011349841","-0.012891578","-0.12501127","0.014563312","-0.10794449","0.03054822","-0.035387818","0.05565652","0.044775803","0.0022942817","-0.005632354","-0.033346083","-0.03322056","-0.02195159","0.015419377","-0.020432705","0.08216839","-0.09707785","0.033624154","-0.04540165","0.01600059","-0.008443214","0.0348591","0.028681148","-0.06848952","-0.011099362","0.054491214","0.0062788185","0.015197929","0.007794953","0.048527762","0.014374556","-1.715864E-33","-0.077490285","-0.10706002","-0.00989129","-0.059442014","0.077342525","-0.123604834","0.0168379","0.033313114","-0.03230885","0.0032049122","-0.016180264","-0.119774975","0.02641156","-0.013142963","0.06602868","0.023275455","-0.0064971293","0.0070933","-0.008165547","0.082696564","0.07079631","0.037036918","-0.022571957","0.0944317","0.012382404","-0.051105533","0.07889258","-0.031027135","-0.027353514","-0.05632412","-0.0113645205","0.01442791","-0.11180719","0.063216224","-0.078229055","-0.068480775","0.09452851","-0.055062048","-0.03885468","-0.057117485","0.026664907","0.06571381","-0.0653031","0.020907592","0.005153339","-0.004955178","1.09025306E-4","-0.026915861","0.069160834","-0.032139577","0.06019757","0.02400372","0.049588837","-0.012444772","0.016212463","0.010321429","0.022824604","-0.038509365","0.07096953","-0.017997589","0.0048117405","0.0792883","-0.041228443","0.17755052","-0.021203369","0.0075111226","-0.042101137","-0.018449761","-0.038093165","-0.0872153","0.021474779","-0.13790253","0.009443965","-0.08196163","1.5854137E-4","-0.05537435","0.0011397339","-0.0037665362","-0.052785367","-0.018449472","0.041494146","0.028070327","0.0104903905","0.0027271472","0.015539405","0.081646726","0.09094684","0.03704455","-5.8359517E-5","0.071718164","-0.028635833","-0.029910011","-0.08459198","0.01834226","-0.06381116","-2.8469492E-8","0.002318565","0.007963662","-0.0021829144","0.0035714735","0.0062795915","0.06447196","-0.006801451","0.026655901","-0.016202679","0.07914243","-0.01133058","0.052109234","-0.039478775","-0.05422811","0.08257186","-0.107819386","-0.0026808833","0.08322782","0.019855019","0.073495865","-0.002056089","0.031610213","0.004525557","-0.08545995","-0.015962414","0.0747755","0.0134388795","0.004391484","0.015070588","-0.045107532","0.038476955","0.071501575","-0.06256266","-0.0099059595","-0.041439053","-0.024419878","0.06954893","-0.016656792","0.0068045678","-0.02852791","0.02714861","0.022969961","0.055076174","0.08435048","0.05664987","0.03019174","0.027317699","-0.04011217","0.0045407815","-0.05842359","-0.056964643","-0.12921555","0.011809066","0.0037449861","-0.038577206","-0.041686732","0.04243667","0.03772691","-0.05888331","-0.030431703","0.08787427","-0.0363186","-0.004084094","-0.028587854"]</t>
+  </si>
+  <si>
+    <t>NK-5MmRbaDmzf7YV5sxGoXe75</t>
+  </si>
+  <si>
+    <t>Luckson Elan</t>
+  </si>
+  <si>
+    <t>des viols, des recrutements d'enfants, des vols, des destructions de biens, des enlèvements et des détournements de camions</t>
+  </si>
+  <si>
+    <t>["-0.027194655","0.0624591","0.028600296","-0.033793185","-0.01036084","0.0037618591","0.036017764","0.077488534","0.04624681","0.02855958","0.08934341","-0.07105787","0.0012575845","-0.034545228","-0.06504469","-0.1056677","-0.06832381","0.082064286","-0.07345969","0.12325355","-0.05288883","-0.019303836","-0.02970537","0.09400459","-0.01977907","0.04021259","-0.079757586","0.095875606","0.024534442","-0.06527779","3.1850254E-4","0.019731814","0.025606196","-0.013494534","0.036313858","0.014766556","0.015309696","-0.029684985","-0.046800204","0.0396079","-0.16347662","0.076442786","-0.06302652","0.02769796","-0.048859265","0.025545685","0.014496189","-0.0045824912","-0.10633845","-0.071167335","-0.004531281","0.003089273","-0.05039344","0.0821798","0.017233169","-0.028065022","-0.028256513","-0.104286455","0.003167275","0.0018511491","0.045432325","0.093291044","-0.013828862","-0.009972077","-0.025837893","-0.012516356","0.0810812","-0.021500899","-0.018295161","0.08827769","0.026090754","-0.021135373","-0.049430307","-0.01883661","0.010431202","0.048140872","-0.044137627","-0.0168728","-0.021263078","-0.12080111","0.041916985","-0.0032984924","-0.012802779","-0.017453684","-0.02290859","-0.021652255","0.051763453","-0.08055844","0.10398839","-0.010033602","-0.0565","6.774949E-4","-0.020391516","-0.035552647","-0.0021139015","0.011774008","-8.304197E-4","-0.058075882","0.0683451","0.033181865","-0.027201267","-0.027902067","0.00764854","0.063078515","-0.013129403","-0.022513475","-0.06294622","-0.01789636","-0.057104647","-0.031422123","-0.017432563","-0.05447782","0.025231075","0.02274936","0.015108698","-0.0051623844","-0.008550667","-0.056377772","-0.01771081","0.006664015","0.116394594","-0.033324674","-0.024257164","0.0044585993","-0.040314715","-0.05164339","0.052347433","-2.2192575E-33","-0.028502971","-0.071079284","-0.019652167","0.057313416","0.01070011","-0.010905429","-0.055756286","-0.039187234","-0.009412014","-0.0391524","-0.040777363","0.009539048","0.024370166","0.020907748","0.04610906","0.0120105175","0.016182795","-0.009881126","-1.6890507E-4","-0.067291744","-0.052798536","0.106498145","0.028702082","0.04257067","0.016224444","-0.012516959","-0.031187803","-0.045370534","-0.08721174","0.006046781","0.02634638","0.053974226","-0.057103932","0.045953687","0.058489725","0.0300797","-0.016094355","0.05355007","0.029031686","6.478219E-4","0.004828131","0.01929689","-0.039810244","-0.03688838","0.099259555","0.041756187","0.026010178","0.033607814","-0.08670199","-0.023302944","-0.04108996","0.078185745","-0.063855916","-0.11116594","-0.058674857","0.0775191","-0.021642417","0.056598824","-0.122669935","-0.0018608712","-0.014277288","0.044733252","0.037282884","-0.037286177","-0.025143776","-0.080037825","0.0022896046","0.027222179","0.034192495","0.023491181","-0.12156353","0.04679315","0.017317224","-0.062406704","0.036312126","0.02009614","-0.018616727","-0.024111588","-0.049737178","-0.031392273","-0.11809344","0.022356452","-0.03839761","-0.024768177","0.031369016","-0.08773228","0.052290823","-0.030256791","0.011346179","0.041682627","-0.04129638","0.0102831805","0.045306765","-0.09841096","-0.0032464622","-3.3045134E-33","-0.05117906","0.047650505","-0.101950884","0.062031657","-0.09360619","0.02207527","-0.06809287","0.1182851","-0.073286526","-0.07304248","-0.09483177","0.003141832","-0.045971334","-0.030068832","-0.040077258","0.029591894","-0.004786432","-0.07245922","-0.06819397","-0.017438097","0.013189058","0.0612557","0.030605724","-0.033607688","-0.013033292","-0.016606158","-0.010204496","0.01904118","-0.036517665","0.04936624","0.09196775","-0.027924297","0.023569992","0.059375133","-0.007728801","-0.0115994755","0.110721186","0.0052140662","0.005618627","0.029853154","-0.01649451","0.031173363","0.10706031","0.0068490645","0.0027833711","0.015885187","-0.026811363","-0.005219294","-0.04084979","-0.06939226","0.07977966","0.02620668","-0.003129946","0.02351509","0.025475385","-0.021515073","-0.011021302","-0.03210596","-0.029200712","0.091156326","0.015247719","0.035453066","0.0013563246","-0.012031963","-0.015745997","-0.0752072","-0.07429901","-0.01229649","-0.025264747","-0.053238407","0.09421075","-0.002681779","0.02459313","-0.06911174","-0.02971999","-0.04696479","-0.028762175","-0.012202981","-0.023100214","0.017043587","-0.1328732","-0.06281328","0.016714415","0.022477271","-0.06517837","-0.04006163","-0.025247019","-0.0034630345","0.04555094","-0.06237426","-0.007449248","-0.0895322","-0.0011160191","-0.047978707","0.064082175","-3.7004376E-8","0.03999252","0.013835324","-0.10588824","0.06056259","0.03315905","-0.050639737","-1.8839123E-4","0.15849084","-0.0026664308","0.08639267","-0.0050464775","0.052287888","-0.017817833","0.10721862","0.018576035","0.013112538","0.045080986","0.04722318","-0.06181927","-0.01606948","0.048400532","-0.0064314017","-0.026733384","-0.028406914","-0.059632458","-0.032071196","-0.020216137","-0.15211114","-0.06784533","0.0024577635","0.086032495","0.06503477","0.050528843","-0.018746741","0.03787443","0.012905606","-0.0709182","0.0502132","-0.013936109","0.033770803","0.027915578","-0.0030711263","-0.010799494","0.04498753","0.05379534","-0.02713345","0.038939107","0.104312025","0.012468599","0.004543944","-0.011810604","0.050536633","-5.122454E-4","0.03967852","-0.0035205043","-0.022823505","0.089539774","0.058438588","-0.06361214","0.011880697","0.07274892","0.041007217","0.048626274","-0.017510593"]</t>
+  </si>
+  <si>
+    <t>NK-5NgqbKQ3EjzdKppdjTRzpw</t>
+  </si>
+  <si>
+    <t>Bobrakov Anatoly Yuryevich</t>
+  </si>
+  <si>
+    <t>Entity Name: Bobrakov Anatoly Yuryevich | Type: Person | Jurisdiction: Unknown | Risk Context: Former Deputy Minister of the Russian Federation for the Development of the Far East and the Arctic. Managed a state body of the Russian Federation, which supported or implemented actions or policies that undermined or threatened the territorial integrity, sovereignty and independence of Ukraine.</t>
+  </si>
+  <si>
+    <t>["-8.986709E-4","0.03025001","-0.044893656","-0.012878395","-0.051867686","-0.03522996","0.099256635","0.011092937","-0.007868145","-0.0040763807","-0.095807396","-0.015682118","0.017804122","0.04822135","-0.0019808658","0.057508413","0.021943001","0.060035434","-0.040294454","-0.022812646","-0.030714395","-0.041811854","0.06454507","-0.032787852","-0.004135007","-0.019056994","-0.004952837","0.009414409","-0.0221906","-0.04924091","0.025738921","-0.039053053","-0.019468533","0.0014333919","0.076984234","0.11264301","0.014279845","0.024430035","-0.025154702","0.054834496","0.02066644","-0.00831907","0.0048958785","0.083887324","-3.9644653E-4","0.038045097","-0.046137307","-0.009331351","0.024075303","-0.019875081","-0.044365127","-0.026240744","-0.041642904","-0.013674984","-0.019450879","-0.060083464","0.027295899","-0.031131737","-0.05762512","-0.05547899","0.0055259485","-0.012499061","0.03558362","0.039844904","-0.08819024","-0.04455101","-0.0112695005","-0.014262812","-0.055437446","0.01612907","0.035094563","-0.0643831","-0.11996939","-0.03565531","-0.022133015","-0.15439168","0.025962012","0.11271036","0.052004058","0.04887797","0.044391666","0.07308809","0.05700786","-0.027180348","-0.04792683","-0.043423843","0.02787795","-0.062703066","0.020043457","-0.012376342","0.020168997","-0.019755024","0.21675913","-0.011786824","0.020775503","-0.020404149","0.048648424","-0.026179343","-0.049492426","0.06545841","-0.029789807","-0.06713797","-0.013778609","0.04626284","-0.08301574","-0.0050869905","-0.123621866","-0.009283599","-0.03826767","-0.033770945","0.0075672567","-0.026355265","-0.013482248","0.026412124","0.12987614","-0.02387215","-0.058595173","0.038456496","-0.004768451","-0.09075081","-0.002889297","-0.046143536","0.012677844","0.029363794","-0.0040695034","0.034148056","-0.0074861883","-1.1524588E-33","0.09080899","0.01922004","-0.005331324","-0.03152413","-0.12272157","0.039432053","0.039698828","0.022341868","-0.08758918","0.051964495","0.070287004","0.08180796","0.018492462","-0.046562586","-0.040877074","0.02037223","-0.029276492","0.10095755","0.008201751","0.07358826","0.04898874","0.09442154","-0.019333657","0.0010550342","0.03547095","-0.018859977","0.004911731","-0.026386093","0.008017299","0.01760135","-8.208826E-4","-0.009754051","-0.04430851","0.08806149","-0.023919052","-0.065958574","-0.060038537","-0.022822468","-0.04571016","0.0027251204","0.0067254347","-0.05126079","0.034882072","0.0016947974","0.004922511","-0.018129488","0.10208289","-0.0068681156","0.011416051","-0.035567418","-0.016197296","0.013447586","0.05480372","0.042599633","-0.03272522","-0.026869219","-0.01217523","0.074071735","-0.023031214","-0.040713906","-0.01237777","-0.045940787","-0.009366774","-0.029040638","0.061686505","-0.12786852","0.08109747","0.041510966","0.02031039","0.021556532","0.07200933","0.0012565032","0.050550573","0.069171265","0.00927814","-0.058437694","-0.020856574","-0.012675365","-0.09416169","0.015514809","-0.07170252","0.02119162","0.044046473","0.046447802","-0.026798138","0.019581815","0.02795738","0.009796965","-0.07103957","0.009651945","-0.12523402","-0.003197872","-0.024523202","0.057775743","-0.0602683","-8.979382E-34","0.05306546","-0.08204168","-0.107258454","0.050631635","0.015256404","-0.06138973","0.08345222","0.071220316","-0.029635413","-0.03327187","-0.010796474","-0.070915855","0.065027714","0.0477654","0.039551504","-0.012286712","-0.001653341","0.012083923","-0.10040842","-0.013957905","-0.058102164","-0.06581682","-0.021335606","0.042188417","-0.027631113","0.039360087","0.09501514","-0.0955051","-0.058297668","0.020908277","-0.040147807","0.04742598","-0.07005443","-0.0100583965","-0.09254291","0.008398984","-0.02622324","-0.0579218","-0.09945793","0.038354658","0.023180397","0.102725655","0.011351928","0.044049043","0.017351218","-0.019642044","-0.07784358","0.103473574","0.07992536","-0.048634123","-0.09828049","0.020938316","0.025151968","0.042642","-0.019704679","-0.0017620855","-0.048438106","0.06227041","0.04906844","0.081028245","-0.036747202","-0.037986442","0.0648048","0.017856225","0.0313136","0.053435538","-0.09139851","-0.0116649745","0.08351544","-0.002539537","0.06942401","-0.07994888","-0.038812943","0.04207242","0.050298262","0.0031395615","-0.044677705","-0.015845815","0.056082796","0.059418958","0.03715249","-0.022480115","-0.055131003","0.03459061","0.025035998","-0.040503066","0.0013796672","-0.04742843","0.035253823","0.009961818","0.04499468","-0.052427184","-0.06336603","0.101899505","-0.032672435","-3.840243E-8","0.12589581","-0.015664134","0.048166353","0.012574817","-0.020541392","-0.0059506805","0.001965793","-0.10466282","-0.07882559","0.019020658","0.033119697","-0.0038492149","0.021051725","0.011458684","0.032194354","0.0210159","0.004629913","0.03989844","-0.035774555","-0.00931487","0.042609066","-0.045842748","-0.048441466","-0.013556678","-0.018743694","0.005561641","0.038089722","-0.03540988","0.12802891","0.0376779","-0.06553477","0.05006724","-0.0053653265","0.04366313","-0.005207977","0.017649703","0.0074892733","-0.02223113","0.06572934","-0.0058717593","-0.06521961","0.042757","0.0468882","0.047649432","-0.0585239","0.045028023","-0.029013319","-0.075426355","0.035088632","-0.056287043","7.911142E-4","0.053626686","-0.034439366","0.08739234","-0.045992088","0.04822725","-0.022804381","-0.01876716","-0.010001524","-0.008013775","-0.08321447","-0.051387794","0.056407142","-0.06854364"]</t>
+  </si>
+  <si>
+    <t>NK-5QCNmih2Tig4JiM5DAbefP</t>
+  </si>
+  <si>
+    <t>Karlo Omar Herrera Sanchez</t>
+  </si>
+  <si>
+    <t>Entity Name: Karlo Omar Herrera Sanchez | Type: Person | Jurisdiction: mx | Risk Context: Executive Order 13224 (Terrorism) | Executive Order 14059 (Illicit Drugs) | (also KARLO OMAR HERRERA SANCHEZ) (also CARLO OMAR HERRERA SANCHEZ)</t>
+  </si>
+  <si>
+    <t>["-0.02972519","0.0071694227","-0.040377606","0.034664735","0.025700388","0.029701214","0.068450995","0.0048117023","0.06662546","0.0053758784","0.086467385","0.029136952","0.04581541","-1.5874348E-4","-0.005801799","0.09970476","0.02996152","0.03153023","0.002283222","-0.0026515895","0.04710929","0.007261982","-0.03656173","-0.01766965","-0.053886097","0.01775883","-0.018164018","-0.016854884","-0.0741882","-0.03904182","0.054137263","0.044550378","0.057553872","0.050454486","0.06546942","0.009380345","0.043074537","-0.06292528","0.074837856","-0.005924206","0.017974608","-0.05479583","0.09529749","0.059132732","-0.015728423","-0.032227844","-0.015267779","-0.011333698","0.01229042","0.025757344","-0.06160625","-0.051589817","0.021360897","0.110738255","0.017900508","-0.04126702","0.025420932","0.0073398273","-0.036664855","0.040694598","0.015524957","0.049438976","-1.01187565E-4","0.0068437294","-0.0441112","0.0018649776","0.05715372","-0.063648604","-0.0044413726","-0.05051339","0.0814819","0.001886107","-0.014256255","0.043244656","-0.0454908","-0.03190241","-0.0036049958","0.02515423","-0.05151465","-0.09008485","-0.047586575","0.053503588","-0.01613333","-0.0910345","-0.009507777","0.07606575","-0.07171725","0.012844387","-0.031952858","0.044836592","0.0075166407","-0.0018172676","0.036329806","-0.0014270253","0.033633713","-0.088900365","0.12171413","-0.039908525","-0.08789491","0.05382943","-0.003022429","0.0413509","-0.033582922","-0.03369901","0.008059011","-0.025777267","0.016230522","0.015400182","-0.08422825","-0.0030645528","-0.08726425","0.061748657","-0.068027765","-0.05680789","0.005277472","-0.034926895","-0.02855998","0.051067155","0.009937451","-0.060910407","0.059493065","-0.008635358","-0.102267526","0.03723498","-0.055837266","0.0010993641","0.01766586","4.3957423E-34","0.053237252","0.052329402","-0.05461419","0.033884235","-0.051344894","0.031414688","-0.024470154","-0.026734445","-0.07498938","0.088629976","-0.047916587","-0.03159747","0.042698752","0.03717304","-0.035325583","0.022048926","-0.03819775","0.030057829","0.059112273","0.034990873","0.036414202","-0.013603163","-0.05032257","0.024503633","0.007707148","0.08842827","-0.04252814","-0.08272891","0.027519884","0.02960741","-0.011869338","0.09384845","0.043195006","-0.030071719","0.040001385","0.01638152","1.4729863E-4","-0.051119257","-0.06943393","-0.059229944","0.028787378","0.09340947","-0.0044500357","0.057624977","-0.0097244205","-0.039943956","-0.016166843","0.010951809","0.13032079","-0.11438457","-0.023332888","0.024805484","-0.02709565","-0.028963415","-0.064915024","-0.07705089","-0.0370103","0.08495766","-0.0037557373","-0.02031825","0.08255409","0.002453073","-0.09931719","0.05819144","0.0078713065","-0.13940369","0.019385023","-0.032718778","0.03596756","-0.015568463","-6.0248916E-4","0.038395766","0.030582078","0.032213133","-0.10964703","-0.07663618","-0.009276701","-0.002375915","0.026603002","0.054043125","-0.102182634","-0.008372139","0.09553897","0.03254585","-0.0054942435","0.13063195","0.013312349","0.04595677","-0.11243268","0.07479347","-0.011873683","0.020338897","-0.008995625","0.0037757966","0.035282392","-3.0739234E-33","-0.02916803","-0.06691779","0.037152622","-0.097828396","0.07998053","-0.027437182","-0.021188205","-0.0050406842","0.001537237","-0.040078275","0.03597666","-0.07752386","0.00921822","-0.024699332","0.077515826","-0.018817073","-0.060698725","0.005840324","-0.028066026","0.08185588","-0.0022560747","0.021070726","0.017110726","0.021690257","-0.024788368","-0.039285038","0.056120142","0.030769788","-0.06921598","-0.021270823","-0.068338215","-0.027924895","-0.049708284","0.05060385","-0.06512375","-0.019232586","-0.08706176","0.0012817193","-0.017718296","0.007647652","-0.014305972","0.120314114","0.0017682852","0.015777184","-0.02274268","0.02747266","-0.015468243","-0.013561997","0.021586651","-0.029763516","-0.037511304","0.03155223","-0.104480535","-0.044053886","0.091868475","-0.0019621607","-0.09322383","-0.07804153","0.096902","-0.06587895","-0.050433505","0.1440582","0.017210972","0.07749653","0.022316119","0.019096294","-0.09247513","-0.059309486","0.074338295","-0.035703924","0.05186339","-0.08127687","-0.061960213","0.047224656","-0.007446176","-0.07822903","-0.0928107","0.06589922","-0.06558156","0.01769662","0.107797176","-7.1582105E-4","-0.08101359","0.07795831","0.023393702","0.047557414","0.0481858","0.012151564","0.038114585","0.013486224","-0.0030538836","-0.061343897","-0.03552127","-0.058047462","-0.08969611","-3.4830595E-8","-0.013712592","-0.0017331322","0.060212113","0.009559624","0.007067361","0.059194405","0.020364698","-0.045411374","0.0046389485","0.0068656015","0.062255323","0.058195982","0.007063018","-0.07346286","-0.020295313","-0.09407697","-0.03859974","0.026405696","0.037458155","0.081653155","-0.06770381","-0.009915165","0.032212637","-0.05670916","0.06574699","0.045331094","-0.055178717","-0.0058014942","0.07029755","-0.0058559235","0.0017135894","0.042322025","-0.06317402","0.002919148","0.021047147","0.08360475","0.008362477","-0.03899004","-0.0021850257","-0.03220593","0.038151436","-0.04010409","-0.009054501","0.04488677","0.05472723","-0.033553094","-0.053728938","-0.09678756","0.04964444","-0.048438884","-0.016104594","-0.086678706","0.035519887","0.03525549","-0.011525313","-0.0060066534","0.059017137","0.043166734","-0.028467186","-0.04819947","0.05878697","-0.087249875","0.004573324","-0.00437662"]</t>
+  </si>
+  <si>
+    <t>NK-5SbE2xBrgHjuKwGFCVvjQM</t>
+  </si>
+  <si>
+    <t>Peleng JSC</t>
+  </si>
+  <si>
+    <t>Entity Name: Peleng JSC | Type: Company | Jurisdiction: by</t>
+  </si>
+  <si>
+    <t>["0.0073917094","0.044538546","6.12515E-4","-0.090435155","-8.8682387E-4","-0.013911066","0.057335515","0.0029359611","0.03626855","-0.034054127","0.049816463","-0.06601723","0.030386094","-0.030806413","-0.045155913","-0.011379722","-0.030037342","0.051098716","0.035268188","-0.09854999","0.05297325","-0.0019653097","0.010989322","-0.045252044","-0.030765506","0.016519299","0.040794816","0.06859155","-0.004378988","-0.08130472","-0.04609226","0.017253693","0.034010656","0.061769303","0.062467214","0.03044016","-0.0359767","0.007145401","0.049193077","-0.055552166","-0.01151684","-0.010744971","0.0570467","0.0014121156","-0.027191646","0.025997186","-0.02249497","0.021892717","-0.041171357","0.040064506","-0.033776645","-0.06209805","0.035740662","0.030411698","-0.034221042","0.040373817","-0.050232377","0.055605277","-0.10637387","-0.016636824","-0.048491664","0.022926062","-0.02121978","0.0056548277","0.002785158","0.005989652","0.030846784","0.022809992","-0.07788877","-0.121449664","0.050494663","-0.06379218","-0.08220448","0.004699372","-0.05015519","0.061530072","-0.006227812","0.05945933","0.018097287","-0.032249495","-0.012847879","0.026810357","-0.05597381","-0.006065798","-0.04809281","-0.016827635","0.06156662","0.006009346","0.05805227","0.05794486","0.069530785","-0.056754883","0.066241704","0.0118097095","-0.046191607","0.044348508","0.011192623","-0.053337634","0.06707586","0.042666458","-0.025437858","0.05035256","-0.008696537","0.029630724","-0.04518511","0.025569528","-0.0605835","0.06944973","0.036976025","0.055163994","-0.06336834","0.11499744","-0.07451595","-0.03575681","-0.014378286","-0.033890888","-0.05091336","0.03324966","0.112584464","-0.1752693","-0.019627616","0.019575547","-0.128373","-0.053332187","-0.09958329","0.06931788","-0.051165957","-8.426921E-34","-3.9373655E-4","0.057140313","0.08718674","0.03972355","-0.11015228","0.03421127","0.011615016","0.015107412","-0.053541917","-0.0015565716","-0.09175436","-0.011880926","0.018752921","-0.096374154","0.01775809","-0.048182197","-0.00489321","0.047518868","0.044914387","0.05237168","0.008119941","0.029077657","-0.05428823","0.04260511","0.07051355","0.014121493","0.028065437","-0.019185346","-0.016599385","0.058706325","0.12693182","-0.040872566","-0.029960241","0.014925556","0.064764544","0.082448035","-0.0012451804","-0.003011216","0.013416165","-0.025703486","0.015747502","-0.019120187","0.00968937","0.064886704","0.013733671","-0.032119006","-0.027618414","0.031619966","0.049897898","0.06385126","-0.030199952","-0.018429639","0.015066788","0.0031003652","0.102296956","0.041897018","0.0045367368","0.06183025","-0.051231798","-0.018248271","0.002083271","0.10649091","-0.06340369","0.011632896","0.027157493","-0.019636318","-0.047234908","-0.0824349","0.013791955","0.012556067","0.050811972","0.0872116","0.084859155","0.1063597","-0.028751288","-0.03237372","-0.06332317","0.091413036","-0.06768253","0.048549496","-0.07607994","0.029010715","-0.056425333","0.040511858","0.07046771","-0.004338276","0.042269573","-0.033188477","-0.013924923","0.02610944","-0.03252127","0.038298763","-0.055436898","0.10828575","-0.0060456055","-4.38023E-34","0.0032572662","-0.104843564","0.059031755","-0.038222007","0.00879425","-0.06911359","0.01908052","0.020788658","-0.043065146","-0.00771891","-0.060741752","-0.05812568","0.019690674","0.008336131","0.024775943","0.046237327","-0.022894721","-0.04457519","-0.057838615","0.129651","-0.051905885","-0.012918381","0.026859589","0.093619056","0.063422084","-2.5752152E-4","-0.006308288","-0.010243126","-0.06438344","-0.07311683","0.0056670797","-0.0509583","-0.062379252","0.09509679","-0.14283396","-0.106058516","0.016092397","-0.039193794","0.03608243","-0.020860655","-0.038379796","0.07330578","-0.030133825","0.097111054","-0.051302887","-0.06307715","0.01160753","4.679121E-4","0.06629469","-0.039154124","-0.060491197","0.037486922","0.0051267385","-0.053532436","0.029960422","0.031750128","0.006716066","0.039243694","-0.0068598995","0.0035089373","0.05063912","0.049978483","0.005848639","0.13315523","0.05734378","-0.040556762","-0.025539313","0.03042949","-0.022570727","-0.11149966","-0.012708819","-0.03805165","-0.07214862","-0.059433263","0.061978895","-0.0060055936","0.011193912","0.008010716","-0.047515772","-0.03529836","0.1076506","0.04520599","-0.028704211","0.067579955","6.0163345E-4","0.008610407","0.041261036","-0.036017973","-0.016603196","-9.225664E-4","-0.05739968","0.029219283","-0.05837789","0.015283143","-0.015706295","-1.9881503E-8","-0.0019317651","-0.05310183","-0.03023977","0.009065538","0.0012801432","-0.047559306","0.00991637","-0.0012219977","-0.047947545","0.012986768","-0.02588824","0.029572096","-0.094665244","0.0464329","0.018559555","-0.055718377","-0.049740084","0.09617534","-0.018410375","0.07369027","-0.05663313","0.0013868113","0.0076310677","-0.035593238","0.036914475","-0.0024579535","0.026369473","-0.07222994","0.11786744","0.047906186","0.0035620471","0.036486108","-0.05259555","-0.026590763","-0.03600701","-0.014800898","0.057659358","-0.014606022","-0.0130099","0.04087205","-0.011317756","0.038899206","-0.036754318","0.04115144","0.04090414","0.011079402","8.981732E-4","-0.008141088","0.017814847","-0.038400453","-0.07845527","-0.042678073","0.0409907","-0.021045081","-0.15187256","0.028219732","0.056167934","-0.009057378","0.0012705885","-0.04840676","0.03254368","-0.04273919","0.08358603","0.0627157"]</t>
+  </si>
+  <si>
+    <t>NK-5Vc7GuxNyzMB9yQXBeCaL2</t>
+  </si>
+  <si>
+    <t>Olga Pismenskaya</t>
+  </si>
+  <si>
+    <t>Entity Name: Olga Pismenskaya | Type: Person | Jurisdiction: Unknown | Risk Context: 2022/2476 (OJ L322-I)</t>
+  </si>
+  <si>
+    <t>["-0.03606221","0.0270041","-0.07394882","-0.041682642","0.0129974745","0.03128619","0.055377647","0.044915006","0.031590566","-0.012601931","0.056324426","-0.028008018","-0.016948372","-0.058613434","-0.06924384","0.058419876","0.02351893","0.030598646","-0.027059708","0.025820378","0.014786335","-0.029068453","0.08528324","-0.039915092","0.03287968","-0.017670961","-0.0054765227","0.04501466","0.046082005","-0.03524664","0.054762874","0.10797199","-0.011653738","0.027853033","0.09062055","0.06287964","-0.02083774","-0.044677757","0.005127706","0.014957829","0.04539004","-0.039432246","0.015113334","0.023341896","-0.03205233","-0.020301048","-0.0736437","-0.026749948","0.0042458335","-0.02951159","-0.118723065","-0.055913195","0.02794802","0.018628545","-5.601997E-4","-0.05330529","-0.0299911","0.023592697","-0.05551131","-0.014534713","0.020591429","-0.01661541","-0.0116071645","0.016321925","-0.04604484","-0.02258925","-0.025363555","0.004070381","-0.027912578","-0.028001655","0.058007546","-0.015082983","-0.11493851","-5.478324E-4","-0.028493999","-0.007834245","0.0060083065","0.01159106","-0.003665838","-0.02327382","0.02214987","0.004828384","0.020571643","-0.04106824","-0.06329893","0.02654725","0.021220958","-0.0025247075","0.050744858","0.04005066","-0.008438317","-0.03714909","0.16904628","-0.004976238","-0.059224736","-0.026482396","0.07835077","0.014352046","-0.007962681","0.075742796","-0.0134991715","0.011289574","0.02297518","0.052076094","-0.06890523","-0.016577221","-0.04328698","-0.0015661926","-0.02164251","-0.044752322","-0.011850207","-0.042545576","-0.04250461","-0.06984145","0.042333916","0.004290743","-0.030082399","0.04045558","0.045755696","-0.08111161","0.026282787","-0.007578213","-0.08913132","-0.0022906845","-0.10372859","0.05864662","-0.075460024","2.0385533E-34","0.091300614","0.03893473","0.03636968","0.06921673","-0.07265203","0.035307884","-0.05854449","-0.022957724","-0.015744759","0.048705794","-0.07049898","-0.006084395","0.0076545794","-0.13682172","-0.04612265","0.059526864","0.022820838","0.04658604","-0.028915107","0.082046874","0.12081044","-0.010704778","-0.065899104","-8.1958226E-4","0.02960781","0.040474035","0.06798244","-0.16653892","0.040758263","0.04842707","0.0027141361","2.1136433E-4","-0.008468526","-0.020442354","0.05465372","0.014727629","-0.029459083","-0.05155533","-0.012244567","-0.06248605","0.0033913008","-0.038325794","0.025099259","0.078005195","-0.0050722747","-0.025055617","0.10583038","0.009952483","0.102834895","0.01911797","-0.0684606","0.01008647","-0.048608318","0.045080442","-0.05915075","0.018131897","-0.013414283","0.071158856","-0.0029463652","-0.03477988","0.042516977","0.005446167","-0.04002107","-0.024363782","0.057978895","-0.079385035","0.03647752","-0.07592","0.027051855","-0.0067583653","-0.026362114","0.007860365","0.038458165","0.059735466","0.029433077","-0.048980556","0.007734369","0.008202001","-0.032510277","0.04942128","-0.1282904","0.047222856","-0.008775","0.033628635","-0.016705284","-0.0016294201","0.025053931","-0.03418536","-0.08585182","0.036852755","-0.021014208","-0.010184228","0.0656154","0.06251172","-0.082797125","-2.162313E-33","-0.009926459","-0.0965095","-0.031809516","-0.05325464","0.092695765","-0.07077673","-0.035835966","0.10640116","-0.02395354","0.017394148","-0.009581461","-0.102314554","0.080417186","0.024250247","0.05497186","0.02262925","-0.07065443","0.02209196","-0.103049345","6.926311E-4","-0.06967605","0.01493522","5.490984E-4","0.082574815","-0.025838846","0.04240053","0.11284646","-0.08841225","-0.075671725","0.03754029","-0.09527199","0.004686504","-0.12634349","0.08278568","-0.043347206","-9.8106466E-5","0.061817262","-0.10032046","-0.08174474","0.019760195","-0.025354343","0.08359528","-0.008811352","0.013661151","-0.039508887","-0.059282895","0.05113636","0.06300461","0.08707597","-0.09427076","-0.0011732981","0.08381929","-0.027602047","0.05253269","0.046439905","0.013722391","0.010336201","-0.048725635","0.025347972","0.03473753","-0.013734458","0.03327342","-0.048056137","0.13240385","0.05951376","-0.03774481","-0.050080657","-0.0023718323","-0.013941311","-0.0725886","0.054878894","-0.092331916","-0.07153529","0.023993349","0.075412996","-0.015428613","-0.04860388","0.0058888583","-0.022564756","6.4681063E-4","0.052621014","-0.013700128","-0.032169398","0.06664975","0.0772549","1.2752006E-5","0.08093844","-0.03321023","-0.0122541","-0.018592643","-0.011562866","0.012376552","-0.03949721","0.05273372","-0.062561914","-3.023769E-8","0.023962134","0.074026704","0.0016396189","-0.0035529116","0.043300122","-0.014072919","-0.043743543","0.023917591","-0.07685684","0.070520595","-0.060800422","0.063671164","0.026157094","-0.0689999","0.038977493","-0.032849293","-0.040204763","0.08239237","0.0026496947","0.040496435","0.06796042","-0.05169732","0.0011853873","-0.1028196","-0.038897756","0.014961674","0.019816305","0.057931818","0.06794816","-0.0013246158","-0.0395211","0.074733354","-0.052510735","0.011654968","-0.013775429","0.026809001","0.052336324","-0.034073528","-0.048515197","0.032532938","-0.0064395084","0.032940257","0.013504512","0.076647244","0.005411217","0.045124933","0.030940559","-0.09562499","0.058788203","-0.027193759","-0.07528206","-0.040820297","0.020626398","0.06341028","-0.06519798","-0.038604416","0.030766167","0.046865076","-0.01849231","-0.049365874","0.04833819","-0.030992746","-0.023541246","0.017380295"]</t>
+  </si>
+  <si>
+    <t>NK-5Y3EFsrUxg7EMVfhAs2ekj</t>
+  </si>
+  <si>
+    <t>SEAPRIDE</t>
+  </si>
+  <si>
+    <t>Entity Name: SEAPRIDE | Type: Vessel | Jurisdiction: Unknown | Risk Context: (also ALERT) (also ASTANEH, NEPTUNE, SEAPRIDE, NEPTUNE, SEAPRIDE)</t>
+  </si>
+  <si>
+    <t>["-0.026192075","0.04716794","-0.0760015","0.013241277","0.05320539","-0.033229858","0.029953895","0.049431026","-0.003113903","-0.07329257","0.021354407","-0.121934086","0.04074947","-0.01727913","-0.06290223","-1.3801316E-4","0.025822299","-0.054547146","-0.013398353","0.043226916","0.0011539856","0.076485604","-0.011512303","-0.032377232","-0.072411604","-0.048861764","-0.03288848","0.026001519","0.042390384","-0.03224281","-0.010665166","0.08105458","0.016241718","0.07094319","0.062488478","0.07776149","-0.08664894","0.024886103","-0.047779746","0.037191153","0.043477602","-0.05330759","0.010966632","0.080816604","-0.024024403","-0.037584785","-0.024067804","-0.014311936","-0.0027447823","0.081574485","-0.028081326","-0.08780366","-0.044165354","0.044848274","-0.027340496","-0.012301941","-0.13654053","-0.050275993","0.008798617","-0.0979524","0.030376667","0.055970132","0.0039424347","6.719342E-4","0.015770815","0.04075563","-0.032875612","0.036668416","-0.0149597265","-0.041623864","0.055178277","-0.046622057","0.0019525139","0.16208504","-0.03695248","-0.024261544","0.058282584","0.0011349093","0.021270493","-0.051836524","-0.024545847","0.011074434","-0.039414093","-0.026113318","0.0511348","0.07013697","0.0045426874","-0.036260456","0.034133345","0.04187184","-0.04396995","-0.13295287","0.13496377","-0.01581105","-0.041563787","0.01624857","-0.03101652","-0.029228436","-0.060947765","0.01814559","0.016910113","0.041070387","-0.07152317","0.025519833","-0.07257482","-0.043118518","-0.02321198","-0.006486601","0.011565154","-0.026081072","-0.08833998","0.06415466","-0.055136587","-0.07925574","0.0037268745","0.037390698","-0.11831881","-0.040763136","0.035006024","-0.13244016","0.034286633","-0.010114956","-0.01884996","-0.005226834","-0.018091774","0.035297945","-0.001517614","-2.0347036E-33","0.05064787","0.047859583","0.075906545","0.011068999","-0.015983276","-0.043195322","-0.053406134","-0.0022495268","-0.056541763","0.033858508","-0.08711817","-0.013887512","-0.018751903","-0.053553894","-0.00551064","-0.0139397485","0.05567528","0.012679052","0.0020087129","-0.04252839","-0.019100746","0.051004868","-0.018091854","-0.030032882","0.0065784752","-0.040927697","-0.0027959398","-0.060726874","0.0477133","0.06717119","-0.012327968","-0.0013209106","-0.024347542","0.035998825","0.044188004","0.007917832","-0.045809757","-0.080922574","-0.050662115","-0.022345144","-0.02676038","-0.023571039","-0.03051047","0.1028847","0.0148792","-0.063692674","0.025056114","-0.017185533","0.08059218","0.008482754","-0.02762587","0.0034031332","-0.034880985","0.025929535","-0.039864358","0.06925729","-0.012652361","0.05250038","-0.07267309","0.041051857","-0.01610429","0.018537398","0.0019055476","-0.005760588","0.043741513","0.07586552","0.018998424","-0.04086508","-0.0041516665","-0.06982484","-0.028007519","0.0143466955","0.0713004","0.09315896","0.026249357","0.037826117","-0.0148008","0.023850959","-0.025745543","0.027872076","-0.15434846","0.01998901","0.015589641","0.14364724","-0.07445354","0.061932564","0.08267995","-0.050187483","-0.009621167","0.014260507","-0.029362971","-0.03203849","0.016567273","-0.037951738","-0.06922043","-2.2125938E-34","-0.056554932","-0.07394897","-0.1027317","-0.06841619","0.01480875","-0.05136798","0.055182412","0.020803565","-0.028521983","-0.010530709","-0.07050645","-5.8574695E-4","0.003237485","-0.047167793","0.057891537","0.07500046","-0.01051847","0.077728264","-0.014239779","0.0035134319","0.034437478","-0.07334382","0.013784561","0.07486904","-0.031211574","0.05277165","0.095235825","-0.032680355","-0.038614284","-0.037194557","-0.015518545","0.10242449","-0.022164581","0.012810533","-0.12800595","-0.04660005","-0.018664995","-0.069729","-0.0806652","-0.028052516","-0.06362373","0.02147404","-0.013190418","-0.005995739","-0.03337158","0.032953765","0.05260986","0.037433706","0.10132104","-0.026367152","-0.021952383","0.008938101","0.06271005","0.0133563755","0.016955497","0.03503488","-0.04423325","-0.029205922","0.08250062","0.011347484","0.07486926","0.06788108","-0.04653873","0.09425407","0.054220125","-0.08247435","-0.0350562","0.026572077","-0.05388242","-0.016479563","0.06361406","-0.04051767","-0.07173113","-0.015072204","0.017066583","-0.08934633","-0.02249656","-0.011937488","-0.043790016","0.044793095","0.024956297","0.020018378","0.0034488798","0.046310782","-0.01991847","0.023051595","0.08761315","0.03728485","0.031293068","0.0022611986","-0.04335876","0.0043606698","-0.10412483","0.035246912","-0.03911721","-2.7955716E-8","0.07652007","0.028191948","0.0401381","0.020223266","-0.008116704","-0.046510518","-0.019411867","0.01839743","-0.0485059","-0.049329244","-0.011280675","-0.009045772","0.024178548","-0.109725215","0.012443416","-0.048050683","0.016435977","0.09838938","-0.012339785","-0.018261662","0.032624938","0.028777096","-0.04711262","-0.10609447","-0.0093838805","0.028385054","0.0859621","0.0082295835","0.072530605","-0.02278952","-0.0015307483","0.027123166","0.004759032","0.016374465","0.061716385","0.09537193","0.00987476","-0.019741965","0.044907488","0.10757117","-0.055979986","0.09487287","0.03026098","0.09955029","0.052353952","0.12856032","0.034930702","0.0032188362","0.060357954","-0.061675094","-0.039563354","-0.018417958","0.010869236","0.03526035","0.004706908","0.039752584","-0.036751606","-0.019312467","-0.04500575","0.018491153","0.023308467","-0.009442862","0.0055815573","0.11801812"]</t>
+  </si>
+  <si>
+    <t>NK-5aw3P5qi7EaMCSRxGYJquB</t>
+  </si>
+  <si>
+    <t>Prince Global Group Limited</t>
+  </si>
+  <si>
+    <t>| There are reasonable grounds to suspect that PRINCE GLOBAL GROUP LIMITED (“PRINCE GROUP”) is an involved person under Global Human Rights Sanctions Regulations 2020 on the basis of the following grounds: (1) PRINCE GROUP is or has been responsible for, engaging in, facilitating or providing support for human rights abuses; (2) PRINCE GROUP is or has been involved in providing financial services or making available funds, economic resources, goods or technology, knowing or having reasonable cause to suspect that those financial services or funds will or may contribute to a human rights abuse; (3) PRINCE GROUP is or has been involved in profiting financially from human rights abuses</t>
+  </si>
+  <si>
+    <t>["-0.048937604","0.030838085","0.037653163","0.047608986","0.064530455","0.06896023","0.04543328","-0.057179436","-0.015046784","0.0141568445","0.037007995","-0.0028690998","-0.06530865","-0.004086629","-9.160483E-4","-0.02210633","-0.009070436","0.035629593","-0.09806883","-0.0056302412","-0.012185638","-0.11393055","-0.011574774","-0.002774358","-0.14292768","0.004592326","0.028152421","-0.041624825","0.025311166","0.044084188","-0.024434868","-0.036256015","0.054507438","0.09105065","0.012886455","0.07379582","-0.0028534667","-0.046277236","-0.055796463","0.005060841","0.09514098","-0.01907031","0.028084671","0.020944668","0.034165163","-0.004451206","-0.0070369323","-0.014568054","-0.12318388","-0.013062426","0.015600227","0.05174394","0.07926556","-0.004971441","-0.049193706","-0.038634434","0.0056044143","-0.09135303","0.062084947","-0.023406373","0.038704097","-0.02749771","0.0018182934","0.0021237906","-0.01508805","0.07188109","0.02711054","0.04955943","0.0062882314","0.016381597","0.055805527","-0.026038622","0.010501071","-0.055462696","-0.056623336","3.9713166E-4","0.02953662","-0.035277586","0.032959536","-0.0342697","0.07680898","0.04457708","0.04484023","-0.010360868","-0.060364638","0.017425716","0.021596212","-0.030976754","-0.009764333","0.073397234","0.01063087","0.04638618","0.09791613","0.012328423","-0.06311789","0.011987156","0.09726048","0.00714516","-0.05062962","-0.0029763835","-9.7622664E-4","0.04788048","-0.023917226","-0.043429475","-0.04173252","-0.02797265","0.012963955","-0.019515442","-0.014326042","0.03950965","-0.09925243","-0.01123928","-0.061552934","-0.07367525","0.05565091","-0.05048822","-0.0067994483","0.0581257","0.03455977","-0.027469423","0.029287258","0.058532465","0.015375605","-0.030546494","0.073805764","-0.030756883","-0.18967253","1.7289239E-33","-0.049145333","-0.02513497","0.026629388","-0.0349695","-0.044056334","0.031695906","-0.064419694","0.061501086","-0.022451269","0.084212705","0.026232721","-0.009928431","-0.0073505887","-0.023081016","-0.03888367","0.028806347","-0.0026406185","0.015178665","0.041569903","0.050108913","0.018718334","0.067051634","0.05475242","0.053875346","-0.06514872","-0.036401305","-0.024481205","-0.055061765","0.06992275","0.027296217","-0.009893572","-0.01782409","-0.01562894","0.0063189017","-0.020055551","0.039218143","-0.08596629","-0.018869625","-0.014437294","-0.029960673","3.676982E-4","0.0011565103","0.018075425","-0.030383693","0.039273355","-0.004469093","0.002410668","-0.06849872","-0.0137466425","0.023913287","-0.05549719","0.03462009","-0.06512534","-0.06932321","-0.0067873374","-0.10839401","-0.08667974","0.07110679","0.038131226","-0.06925281","0.08479352","-0.021500649","-0.06270082","0.09192136","0.034561068","-0.036417335","-0.028005593","0.04450454","-3.701771E-5","-0.021846853","0.031524368","0.11404746","0.08233378","0.09616733","-0.023835704","-0.055607744","-0.029528584","0.069672965","-0.0381609","0.0825988","-0.095553994","-0.007617812","0.110323876","-1.8270889E-4","-0.046573427","0.010811236","0.0019842319","-0.012294703","0.064970694","0.09302286","-0.091137566","-0.03961531","-0.06949944","0.07166181","-0.07088039","-4.493468E-33","-0.014782152","-0.03910532","0.02796278","-0.03271096","0.06609082","-0.02072039","-0.015946567","0.0117730405","0.043460082","0.04103115","-0.04129737","-0.01760846","0.07348625","-0.008838447","-0.009200035","-0.077676915","0.03047153","-0.053645507","-0.0047334465","-0.0051476336","0.021802431","-0.05662026","0.06396922","0.06416758","0.059538756","0.01815107","0.025461812","-0.04457967","-0.052325964","0.08033113","0.03303431","0.1447652","-0.05669341","0.07879564","-0.071796656","-0.067787886","-0.057330526","0.008271944","0.0021531826","-0.018170962","-0.003978733","3.744417E-5","-0.040048085","-0.02250511","-0.0055237156","0.05284798","0.10585276","0.00498208","0.08590862","-0.029226294","-0.036785897","0.0014385866","-0.041894164","-0.013239065","0.043014802","0.08269889","-0.028096294","-0.11596091","0.02650048","-8.5745973E-4","0.06407781","0.044357527","-0.010336726","0.032910354","-0.030455759","0.07224961","0.046210233","-0.014064902","0.09854957","-0.028035745","0.08617248","-0.039782807","-0.089932725","-0.0070599196","-0.0043347236","0.040854797","-0.03755368","-0.087788895","-0.09806059","-0.078048825","0.08382384","-0.1217603","-0.0075749834","0.012085272","0.015892684","-0.029571885","0.0348565","0.051786643","-0.059298236","0.011007416","-0.07026533","-0.04217958","-0.13334094","0.04587117","-0.04283498","-4.4945434E-8","-0.017823348","-0.005831545","0.02785108","-0.029052801","-0.0022789729","0.018839343","-0.06446538","-0.06917743","0.014149948","0.065516286","0.050384503","-0.06625552","-0.043688368","-0.0067819115","9.273244E-5","-0.039047077","-0.025581641","-0.05423788","-0.034214593","-0.012897565","-0.053039122","-0.026739499","-0.020870531","-0.043859255","-0.054462794","-0.03867385","-0.06844853","0.01797589","-0.0011884047","-0.05990715","0.048481695","-7.04112E-4","-0.043927696","0.058344204","0.04096122","0.03340046","-0.07374191","1.5951067E-4","0.059559602","-0.029209355","-0.01311354","0.035246745","0.026706276","0.09205486","0.0020365715","-0.044264816","-0.08234348","-0.013106973","4.2714993E-4","-0.035614926","-0.027452083","-0.021458576","0.011280158","0.036486786","0.07880312","0.08400061","0.082542844","0.057804503","-0.10963049","0.0068161213","0.039520804","-0.11067561","0.022331364","0.0126519725"]</t>
+  </si>
+  <si>
+    <t>NK-5daSWmCzJdq9HpQADAQiJZ</t>
+  </si>
+  <si>
+    <t>Alexander Maksimtsev</t>
+  </si>
+  <si>
+    <t>Entity Name: Alexander Maksimtsev | Type: Person | Jurisdiction: kg | Risk Context: 2022/1270 (OJ L193)</t>
+  </si>
+  <si>
+    <t>["-0.07887429","0.07442399","-0.07337082","-0.029730476","-0.022196153","-0.007844715","0.0422513","0.03487815","0.035185743","3.0290827E-4","0.020019338","-0.10458292","0.039088547","-0.026813569","-0.07103693","0.073527694","0.011524896","0.06922857","-0.0066232146","0.020469481","0.09536759","0.024026193","0.04900219","-0.068891","0.018286351","-0.023841724","-0.020796554","0.0875686","0.0038261316","-0.03781452","0.044497285","0.062296905","0.058280118","0.06565438","0.04819948","0.07913743","-0.05803518","0.027476162","-0.015172557","-0.01085488","0.09022012","-0.051603846","0.09883374","0.06040111","-0.039039087","-0.014586088","-0.053230982","-0.03579786","-0.030497143","0.12452154","-0.11662489","-0.0480649","0.020094957","0.027744574","0.02046027","-0.039456766","-0.054975584","0.06961474","-0.05043931","-0.0315377","0.05791201","0.021917071","-0.04081549","0.023823261","0.0037728334","-0.030722149","0.0065104784","-0.007870032","-0.0119370865","-0.07569029","0.083192565","-0.023389334","-0.092602246","-0.011604556","-0.026844058","0.075187996","0.03213372","0.0188618","0.03757247","-0.056408983","0.011856649","-0.045042343","-0.02077422","-0.020382704","-0.08104291","0.026485732","9.814479E-4","-2.1736693E-4","0.042717062","0.054561418","-0.0019655307","-0.06064478","0.16029252","0.01645792","0.01678301","0.023727655","0.0019436653","0.008456685","-0.076308735","0.08492419","-0.020650933","0.027560841","0.015671242","0.08886969","-0.063311316","-0.070833534","-0.068804994","-0.0048535406","-0.041021828","-0.02525367","-0.017025877","0.034710944","-0.0433328","-0.028926238","0.08370128","-3.924184E-4","-0.069985665","0.0094711585","0.06578819","-0.107037276","-0.008801868","-0.016551698","-0.13809074","-0.032905646","-0.08137337","0.07634709","-0.0074467645","1.6359553E-33","0.073442966","0.0408649","0.067515686","0.040210903","-0.09343982","-0.033073902","-0.0053529106","-0.029406257","-0.045389857","0.040563818","-0.040755156","-0.002827345","0.008353851","-0.08650151","-0.02871275","-0.008696337","0.019798402","0.01852909","-0.0011049706","0.08546954","0.028336149","0.001640084","-0.06266822","0.024449576","0.034125768","0.02381158","0.018111853","-0.12814407","0.026992528","0.06911216","0.027210161","0.019377725","-0.031890962","0.0033109568","0.039230626","0.018223379","-0.07816736","-0.08526857","-0.026180554","-0.086779535","-0.013563736","-0.0034391393","-5.4712134E-4","0.08928243","-0.01842198","-0.039847128","0.044982515","0.031193852","0.104862206","0.031417005","-0.06922298","0.042638104","-0.052153826","-0.0334562","-0.034852426","-0.03646164","-0.027736882","0.10343107","-0.0473193","-0.016557705","0.005672637","-0.001966658","-0.035906307","0.08685644","0.012792813","-0.1162924","0.0043053827","-0.074962966","0.03001422","-0.04012301","0.06462406","0.08454787","0.04063605","0.042256232","-0.03778347","0.009175515","0.00870594","-0.012244341","-0.049432922","0.053712822","-0.1105676","0.013706002","-0.0346569","0.01419611","-0.011761459","0.040046234","0.02596655","-0.028589198","-0.008937647","0.07110994","-0.016248653","-0.01962457","-0.002408038","0.042295195","-0.081434265","-2.7810968E-33","-0.038366858","-0.057037685","-0.017516542","-0.010637662","0.05011355","-0.08397655","0.036736835","0.1302771","-0.008356613","0.00205323","0.008120326","-0.063258395","0.08737268","-0.04481848","0.05896944","0.0011484777","-0.032499965","0.008673114","-0.03469613","0.06687295","0.0050059287","0.027811917","-0.05921832","0.06661323","-0.008110126","0.010942604","0.019483814","-0.05847347","-0.12766612","-0.015601962","-0.03343141","0.038910795","-0.07928382","0.09641057","-0.08826836","-0.07752585","0.102977015","-0.066641614","-0.031882174","-0.009800423","-0.025671097","0.097103454","-0.010131446","0.0452465","0.013812613","-0.010147176","0.03270994","0.014542596","0.11085079","-0.067092545","-0.019845843","0.06341105","-0.020642955","0.018813852","0.055611964","0.04756048","0.00945336","-0.04247475","0.027686382","0.008752138","-0.04390768","0.013835433","0.0035610707","0.10539947","0.009754422","-0.009646767","-0.050456837","-0.0052431445","-0.03341182","-0.07585651","0.0659479","-0.09934984","-0.07364052","-0.028053297","0.05129868","-0.032576475","-0.020492831","0.026065731","-0.027735239","-0.044456895","0.03531641","0.04721602","-0.022336561","0.022912772","0.105500385","0.027527982","0.07739345","-0.017118357","0.021351771","0.0061223907","-0.07714842","-0.022935675","-0.09219348","-0.019490162","-0.05104198","-3.2395032E-8","-0.0029693057","0.024852142","-0.010799171","-0.0052350946","0.030928493","0.047250528","-0.030764803","0.024925595","-0.0056213504","0.06942843","-0.0062792525","0.024617344","0.014458259","-0.06348744","0.05302626","-0.10407251","-0.024312228","0.054229088","-0.030570004","0.02438918","-0.011336437","-0.028838042","0.013233448","-0.049103133","0.0028046428","0.034058098","0.0047904206","0.025995614","0.06532315","-0.005899672","-0.03789888","0.08051467","-0.03488835","-0.018633576","-0.041920546","0.06804989","0.06801641","-0.013130798","0.033212665","0.015402618","-0.01680735","-4.7151683E-4","0.00808954","0.0845129","0.061786838","0.026735","-0.02430792","-0.06277119","0.009037984","-0.06859908","-0.09178142","-0.056816682","0.016775345","0.034456823","-0.02662494","-0.042869337","0.02733771","0.023631694","-0.024548698","-0.038939707","0.08926679","-0.050261077","-0.040927548","-0.030614374"]</t>
+  </si>
+  <si>
+    <t>NK-5giGuXZXRiCrMuX4Dck28D</t>
+  </si>
+  <si>
+    <t>LINGLONG TRADING GROUP FZE</t>
+  </si>
+  <si>
+    <t>| Transport sanctions: where transport sanctions apply, a ship owned, controlled, chartered or operated by a designated person is prohibited from entering a port in the UK, may be given a movement or a port entry direction, can be detained, and will be refused permission to register on the UK Ship Register or have its existing registration terminated. Similarly, an aircraft owned, chartered or operated by a designated person is prohibited from overflying or landing in the UK, may be given a movement direction, can be detained or moved to a specified airport, and will be refused permission to register on the CAA Aircraft Register or have its existing registration terminated</t>
+  </si>
+  <si>
+    <t>["0.04092075","-0.045831926","-0.0026798118","-0.030285532","3.3920186E-4","0.037981555","0.05911577","-0.08496334","-0.03077921","-0.049736828","0.053627416","0.07161742","-0.056992915","0.11514563","-0.03350818","-0.02887788","0.012183298","-0.09931619","-0.013052276","0.04445791","0.051691633","0.049703956","-0.0835129","0.05593096","-0.12622619","-0.012189041","0.06493643","0.07173407","0.075845756","0.0017848929","-0.095963694","0.016875396","-0.06767671","0.095512815","-0.016272021","-0.009240887","0.006692242","-0.07661558","-0.046210617","-0.09308961","0.050046213","-0.09275774","-0.040789187","0.082535625","0.044719063","-0.0016157234","0.029482177","-0.039589245","-0.099151924","-0.028522171","-0.004842246","-0.0016824726","0.023558524","0.024723127","-0.045836996","-0.087369554","-0.009028649","0.003132743","0.02747703","0.0014917982","0.010061213","0.043170065","-0.06142868","-0.030992413","-0.009929089","-0.023769286","-0.049103346","-0.035703965","0.023721283","0.08223454","-0.04684572","-0.09054461","-0.0017904408","0.08630082","0.036070243","-0.049796175","-1.8309541E-4","0.0052868985","0.046452917","-0.054972593","-0.0046319054","-0.04484215","-0.010821151","-0.026207188","-0.010783122","-0.025581265","-0.04528023","0.019871203","0.083676554","0.07097034","-0.01521585","0.003346451","0.16179505","-0.018807748","-0.006200627","-0.009798683","-0.0015491578","-0.011228395","-0.010268749","-0.030159999","0.025341196","0.07595424","-0.11421829","0.1063403","-0.038834713","-0.042780116","0.0017949373","-0.06500393","-0.0014071832","-0.0063559376","-8.761797E-4","0.086216204","0.018426873","-0.031999677","-0.09713071","0.034432117","-0.10150725","-0.007571492","0.010659391","-0.071117215","-0.04599873","0.017475672","0.12306325","-0.058353107","-0.01615913","-0.01645449","-0.051262986","-1.3745627E-33","-0.059958316","0.016525017","-0.083979666","-0.012224896","0.039556548","-0.029171033","-0.09091204","0.06834738","0.0228788","0.08330483","0.001374006","-0.035556257","0.014052752","0.005176121","0.11151715","0.049322613","0.070389904","0.007850419","0.025022928","0.047315843","0.08388876","-0.046221495","0.033572204","-0.035189517","-0.036048856","-0.0018626743","-0.12409596","-0.04738535","0.07145678","0.022858799","0.0010216411","0.050191734","0.037323397","0.01827247","0.017382907","-0.04779832","-0.056228388","-0.019629182","0.014309551","0.025182514","-0.061225563","-0.071349785","-0.06691928","0.05239039","0.013891809","-0.027305184","0.029458184","-0.06664413","0.025857745","0.06992282","-0.010719525","-0.027439756","-0.07744563","-0.082943894","0.0024677317","-0.05425675","0.0068447916","0.079723805","-0.035968196","-0.09683498","-0.0058525405","0.041456096","0.01022723","0.04649946","0.08344457","-0.06968946","-0.0020884804","-0.013098237","-0.08363166","-0.042952772","-0.03126844","0.02417858","0.04326985","0.0062277177","-0.005891368","-0.05662888","-0.029537965","0.01096551","0.016712045","-0.02621259","-0.0384972","0.055010825","0.05157906","0.0025723153","0.020571591","-0.011696086","-0.049013916","0.018654024","0.0193924","0.014139739","-0.04564078","-0.02129385","-7.7374594E-4","0.02890416","0.04032131","-2.6658011E-33","-0.004766719","-0.0038097282","-0.046235472","-0.07595522","-0.027687533","0.010026383","0.10152268","-0.07164258","0.015073611","-0.023461133","-0.13085523","-0.008723964","0.09004448","0.029833306","0.025367614","-0.065349594","-0.041427217","0.101399325","-0.025936764","0.026717959","0.01043057","-0.025321094","0.034295842","0.05604607","-0.058860946","-0.03862683","0.077311","0.0045172097","-0.02142518","-0.035447016","0.01418807","0.051547542","0.024915054","0.04042875","-0.0924842","-0.07129574","-0.022943707","0.068922736","-0.017869638","0.02865108","-0.018242378","0.022624318","0.01446029","0.056868862","-0.038602944","-0.024541924","0.03240274","-0.013280297","0.03390439","0.001396279","0.028575392","0.038976397","0.046203397","-0.014923139","0.014536821","0.052745238","-5.13595E-4","-0.09520865","0.1669032","-8.41892E-4","0.069086425","-0.005962566","-0.016825391","0.014511679","0.037101407","0.040875707","-0.024892097","0.048957385","0.048897978","0.021751078","0.090594776","-0.15039413","-0.02619073","-0.0068554194","0.025087802","-0.05864216","0.030053271","-0.0121424245","-0.07397643","-0.022570489","0.02194341","-0.029399103","0.010380266","0.044545185","0.052770127","-0.030327044","0.028804777","-0.042096857","0.017030098","-0.06869305","0.020075727","-0.037791375","-0.036116157","-0.06174271","-0.012662986","-4.408841E-8","-0.028213177","-0.091600105","-0.022718245","0.013892537","0.0012935847","0.038420245","0.019545754","-0.02912505","-0.006932924","0.0189193","0.012893935","-0.022058548","-0.082649626","0.009311957","-0.03784633","0.05299331","-0.004889137","0.042533003","-0.05476113","0.025358772","-0.098258235","-0.018932948","-0.0062229144","0.069953136","-0.072091125","-0.030890478","-0.015154109","0.0013211413","0.082658105","0.025797457","2.064226E-4","0.046100087","0.054407056","0.10223093","-0.024315836","0.0055519994","-0.014619677","0.015433663","-0.02757836","0.01837385","0.011639197","0.06928678","-0.025675304","0.09028442","-0.0065202336","0.042490818","-0.073285036","-0.019852763","-0.0069823437","0.030061286","0.06824973","-0.05664657","0.061328527","0.095264845","0.039637122","0.09425243","0.0012840186","-0.019712407","-0.053278007","0.08606198","-0.017065758","0.06738823","0.095789686","-0.054446064"]</t>
+  </si>
+  <si>
+    <t>NK-5k2Z3BD3KX698e6mT7oQaD</t>
+  </si>
+  <si>
+    <t>ALI MOHAMMAD SALEH</t>
+  </si>
+  <si>
+    <t>MUHAMMAD SALIH, ALI MUHAMMAD ABD-AL-AMIR SALIH, ALI MOHAMMAD SALAH, ALI MOHAMED SALEH, ALI MOHAMMAD SALEH, ALI ABD-AL-AMIR MUHAMMAD SALIH, ALI MUHAMMAD SALIH, ALI MUHAMMAD ABD-AL-AMIR SALIH, ALI MOHAMAD SALEH) (also ALI MOHAMED SALEH, ALI MUHAMMAD SALIH, ALI MOHAMMAD SALEH, ALI MOHAMMAD SALAH, ALI ABD-AL-AMIR MUHAMMAD SALIH, ALI MOHAMMAD SALAH, ALI MOHAMED SALEH, ALI MOHAMMAD SALEH, ALI ABD-AL-AMIR MUHAMMAD SALIH, ALI MUHAMMAD SALIH, ALI MUHAMMAD ABD-AL-AMIR SALIH, ALI MOHAMAD SALEH) (also ALI MOHAMED SALEH, ALI MUHAMMAD SALIH, ALI MOHAMMAD SALEH, ALI MOHAMMAD SALAH, ALI ABD-AL-AMIR MUHAMMAD SALIH, ALI MUHAMMAD ABD-AL-AMIR SALIH, ALI MOHAMMAD SALAH, ALI MOHAMED SALEH, ALI MOHAMMAD SALEH, ALI ABD-AL-AMIR MUHAMMAD SALIH, ALI MUHAMMAD ABD-AL-AMIR SALIH, ALI MOHAMAD SALEH) (also ALI MOHAMED</t>
+  </si>
+  <si>
+    <t>["-0.008661884","0.06488852","-0.01619047","-0.06730953","-0.013854683","0.068088405","0.01050985","-0.0067804363","0.061987218","-0.006873894","0.05213712","-0.02066917","0.07298968","-0.06659036","-0.00195849","0.038346242","-0.09074687","0.10711118","-0.059440363","-0.08735711","-0.08397674","-0.007131181","0.0070511443","-0.008484105","-0.07683631","0.03413307","-0.0673483","0.041951068","-0.0106822755","-0.08219546","-0.03831832","-0.002279011","0.11658104","-0.0034646515","-0.0534077","0.0071285563","-0.0035764184","0.06213565","0.0673443","0.0677601","0.12573734","-0.05658445","-0.06580995","-0.057809424","0.05924751","-0.043942455","-0.02521019","-0.048867054","0.0628912","0.005158556","-0.049558204","0.0019366235","-0.024438271","0.063893855","0.056930233","-0.06357806","-0.045358412","-0.009769733","-0.008188176","-0.055776183","0.04958125","0.07228682","-0.038244173","0.0013010424","-0.028154714","-0.058608267","-0.0036454373","-0.06766129","0.040837694","-0.006721605","0.016115855","-0.0013295267","-0.024500275","0.029330706","-0.104752414","0.06086033","0.026381144","-0.091762684","-0.11296534","-0.03550073","-0.03191753","-0.05571337","-0.06352644","-0.115273334","0.055145968","0.04310441","0.00607565","0.015626164","-0.008597457","-0.05636165","-0.0038635838","0.03777262","-0.037421625","-0.002710281","0.0034064995","-0.12305102","0.014000558","0.037784304","-0.13851263","0.048273653","0.017579557","0.046587747","0.038932327","-0.07287288","-0.014065164","0.031018622","-0.056588598","-0.027585708","-0.07459769","-0.021298535","-0.036559425","0.04107447","-0.0044912305","-0.04836113","0.010431652","0.08882813","-0.06487458","0.020819666","-0.06795089","0.018517077","0.0039341217","0.010567015","-0.0013437255","0.05126713","0.021899762","-0.012403575","-0.051042628","6.348257E-33","-0.065238446","-0.015464795","0.024545658","-0.011725583","-0.047065597","-0.043941896","-0.053603332","0.014019313","-0.102880985","0.059704766","-0.008544761","0.020022884","0.01762125","-0.004327811","0.03885446","-0.001824206","0.03332146","-0.035420902","0.03181056","0.042612042","0.0024391133","0.04913755","-0.03613503","0.0015141948","-0.04395793","0.04461761","0.039171696","0.0019754136","0.09402928","0.022430234","0.09020425","0.047593016","-0.08129401","0.011854501","-0.10594162","-0.0071780346","-0.026888864","-0.034093205","-0.013413414","0.008939338","0.006898246","-0.01614776","0.02686557","-0.020157889","-0.0086964825","0.020610051","-0.042899814","-0.06384838","0.1334981","-0.05258486","-0.011147029","0.0025574816","-0.025361054","0.025983391","-0.016318649","-0.09312799","-0.053362954","0.07093303","-0.06766454","0.09115229","-0.031561576","-0.023596026","-0.106953606","0.0029666878","-0.07552084","-0.01945466","0.0036814732","-0.0010976075","0.007954914","-0.01086787","0.02308989","0.02190614","0.041930415","0.027267156","2.2184754E-4","-0.0314068","0.0060182707","1.2317464E-4","0.061105084","0.046569563","0.019551434","0.011985078","-0.0035792824","0.036461107","-0.08559677","0.02247068","-0.030412259","0.023514772","-0.09330882","0.006202787","-0.048040092","0.02140936","0.09313424","-0.027553221","0.012201262","-7.250375E-33","0.020811124","0.09788295","-0.054681905","-0.042530477","0.04923501","0.04201906","0.08064384","0.036378805","-0.04470659","-0.05638059","0.050005704","-0.03941116","-0.011170944","-0.073747665","0.010798906","0.00979479","-0.028110635","0.011994623","-0.018364592","-0.014377574","0.022975877","0.10768222","0.046247892","0.002198111","-0.018743517","0.045817453","0.0805112","0.072530866","0.054134298","0.04367451","0.02302468","-0.032784894","-0.100359425","0.0014650082","-0.022179414","0.0027845015","-0.034637835","0.06138939","-0.021499401","0.037779223","-0.022397827","0.016428921","0.08813227","-0.04321444","0.047496818","0.027231751","0.019144576","-0.031892937","-0.022397038","-0.07939262","-0.031167058","0.11121581","-0.095982246","-0.01160131","0.041854758","0.07264243","0.0017799278","-0.0084891785","0.037671987","-0.06217408","-0.0742799","0.03317812","0.07844983","-0.010358683","0.00910672","-0.011106654","0.0060268277","-0.042435396","-0.06135757","0.0026883935","-0.054524865","-0.0818017","-0.10411261","-0.069965854","-0.029336799","0.019633593","-0.10529442","0.037826918","-0.01922249","-0.011543398","-0.0025889813","-0.012622736","-0.061303597","0.09992285","0.034875493","0.09218672","-0.012891534","-0.04806896","0.059247997","0.0037095682","0.029955652","0.0057658367","0.12312878","-0.088673815","-0.05099944","-3.9120433E-8","0.017845523","-0.06258109","0.045672476","0.05925994","0.006229514","0.019010201","0.0033961192","0.06157077","-0.012123452","0.030553987","0.11981621","0.03645911","-0.0054346686","-0.019642772","0.07581566","-0.04418242","-0.041522548","0.008157169","0.07546078","-0.059486188","-0.0303812","-0.0011715023","0.0127630625","-0.014018625","-0.03340638","0.05923337","0.031036256","-0.06264678","-6.048768E-4","0.05504528","0.05141281","-0.060240354","0.09558571","-0.031759672","0.13494718","0.034553334","-0.040083513","0.00949474","-0.015255149","0.085978694","0.018301707","-0.065411285","-0.0021028388","0.1029985","0.08839212","-0.028770108","0.04567397","-0.020967526","0.015122682","-0.044423733","0.017650148","-0.003520238","-0.020277526","-0.062491022","-0.042719394","0.04953228","-0.03750367","-0.059897136","0.060622226","0.012293254","0.101656504","-0.040607095","-0.016015558","0.02572192"]</t>
+  </si>
+  <si>
+    <t>NK-5nmtFRWLNm8PPsojYDZGda</t>
+  </si>
+  <si>
+    <t>Троодос Лімітед</t>
+  </si>
+  <si>
+    <t>Entity Name: Троодос Лімітед | Type: Organization | Jurisdiction: gi | Risk Context: Malta corporate registry data is current through 2016</t>
+  </si>
+  <si>
+    <t>["0.0052461447","0.032602884","-0.02936319","-0.024946155","-0.06101364","0.020067548","0.002791684","-0.0065148226","0.00618435","-0.02475396","0.047720123","-0.05744891","0.032666974","0.0062871594","-0.055005312","-0.003904871","-0.07015117","0.030768959","-0.03489484","-0.020278776","0.043178905","0.037981592","0.05024043","0.01211601","0.0074945404","-0.00436588","-0.005928343","0.037247583","0.03944406","0.030662999","-0.038363956","0.08875563","0.07944147","7.3815556E-4","0.12506442","0.05224718","-0.022861587","-0.009510612","0.029792467","0.04934164","0.004916325","-0.10294904","-0.015382747","0.019520197","-7.7740056E-4","0.058722798","0.039984524","-0.030479318","-0.022022381","0.10139564","-0.060539715","-0.011905955","0.07329356","0.029985853","-0.010709721","-0.030179601","-0.081431","0.0038650604","-0.08454983","-0.07533928","0.03146178","0.012189753","-0.050155204","0.0127665885","-0.07448103","0.04943146","0.044939123","0.06678527","0.0026402872","-0.098242365","0.059591003","-0.08065249","-0.12201454","0.03690689","-0.06119723","-0.031272143","0.04300512","0.015160058","-0.007318997","-0.06931825","0.0733334","0.03588396","0.0074384604","0.023665767","-0.05055236","0.055829845","0.05812845","0.035529945","0.0148102045","0.04533779","-0.057968903","-0.043581832","0.12679835","-0.052877985","0.028383384","-0.015879245","0.016200043","-0.0034952674","0.037935093","0.033910472","-0.033119254","0.021198072","-0.06573296","0.118130825","-0.10370071","-0.027120603","-0.056477737","0.01557824","-0.0024047336","8.841492E-4","-0.03475947","0.043537527","-0.080909066","-0.1210147","-0.036878273","-0.0074663037","-0.05134295","-0.0027840042","0.02934437","-0.023929749","0.071410075","-0.06925166","-0.054010373","-0.034822516","-0.014865326","0.027081598","-0.014281462","1.4981326E-33","0.05087919","0.020847473","0.020598728","0.017233703","-0.031693667","-0.03157486","-0.055061165","-0.029306637","-0.09294784","0.016346073","-0.024512349","0.023457918","-0.0420166","-0.0775197","0.010825389","0.09310774","0.06608277","0.049509987","-0.017042134","0.056534644","-0.0068329237","0.04078974","0.010268965","0.020001097","0.062684335","0.044833317","-0.008156098","-0.038274914","0.027606554","0.0061475155","0.06395162","-0.012293957","-0.0029766608","-0.04234022","-0.009757475","0.07518741","-0.11146544","-0.04649514","0.011018317","-0.041825876","-0.0038451713","-0.048855755","-0.0013721774","0.08315846","0.02116303","-0.0110976165","-0.024574561","-0.106992","0.047263354","-0.015622433","0.067105","0.039217804","-0.090587474","0.042209662","0.012961995","-0.02897102","-0.051121645","0.04116218","-0.06594896","0.006522581","0.06438867","-0.018640148","-0.0036035322","0.06299208","0.040987425","-0.07714492","0.0076849107","0.04095385","0.015475395","0.0026267045","0.008651035","0.014974732","0.06732646","0.07530331","-0.02921444","0.011874168","-0.028726231","-0.014571268","-0.06968177","0.08373126","-0.080853134","-0.007202331","0.02032567","0.048070155","-0.02817219","0.08160812","0.13304062","-0.051827807","-0.032011032","0.028277729","-0.13104837","0.0067753172","-0.037830614","0.103155315","-0.06834598","-4.219124E-33","-0.0022012505","-0.076547526","-0.021221146","-0.05704674","-0.04176282","-0.030876353","-0.019116504","-0.0028326125","0.020427879","0.059731353","0.007046343","-0.088255785","-0.037155524","0.011624867","0.014384026","0.053753983","0.039780773","-0.015810477","-0.06507285","0.054488216","-0.0028244713","-0.00889284","-0.035359178","0.11876853","-0.044097655","-0.01150494","0.02616531","-0.06011123","-0.029278487","-0.06760322","-0.037329856","8.9188997E-4","-0.057654217","0.10342466","-0.049960308","-0.037644554","0.047511674","-0.093295485","-0.0049712155","0.03666581","0.012796864","0.048424806","-0.04498612","0.068965375","-0.021325747","-0.027754894","-0.005634215","-0.023213789","0.1252187","-0.11417676","0.083592445","0.06580678","-0.05749264","0.018462788","0.0768859","0.019734558","-0.060260385","-0.043989144","-0.012262153","-0.012115681","0.023735844","0.028819839","-0.085393585","0.095368445","-0.012217103","-0.025663247","-0.076219894","-0.048148364","-0.0068523716","-0.04056708","0.042903673","-0.070910096","-0.04362685","-0.0096021285","-0.0035552257","-0.036019504","-0.046189416","-0.03953254","-0.034454938","0.021381255","0.08689628","-0.04449334","-0.034418374","0.1020669","0.009879092","-0.009229328","0.12413274","-0.010305988","-0.008391333","-0.029684646","-0.06543172","-0.03331403","-0.109013386","0.046959624","-0.037317064","-3.164576E-8","0.053467907","-0.031991642","-0.02965363","0.032435056","0.023727063","-0.06124842","0.01117091","0.08186949","-0.016720096","0.030450992","-0.059235897","0.0032333396","-0.10206028","-0.04275003","-0.012770751","-0.0018751866","-0.05586799","0.12439102","0.035791166","0.06290873","0.01862297","0.030606432","-0.010376128","-0.09631034","-0.09445015","-0.038974475","0.07882117","0.05228244","0.056641914","-0.051774748","0.024807865","0.014650468","0.009026379","0.006032779","-0.029331354","-0.009338198","0.042258255","-0.0035442542","-0.0032923396","-0.007938601","-0.013736511","0.004308255","-0.008220937","0.08182822","-0.042858552","0.032802414","-0.0650912","-0.024729311","0.043799844","-0.115571074","0.043272294","0.011447041","0.08633733","0.078561515","-0.041918945","0.028123777","0.06148988","0.038848355","-0.022993784","-0.011246833","0.0031170407","-0.07375956","0.0259494","-0.00545692"]</t>
+  </si>
+  <si>
+    <t>NK-5qLCNS3yRjtq4t9CB59fGf</t>
+  </si>
+  <si>
+    <t>MINNIE UGO NDEM</t>
+  </si>
+  <si>
+    <t>Entity Name: MINNIE UGO NDEM | Type: Person | Jurisdiction: us | Risk Context: 1128a4</t>
+  </si>
+  <si>
+    <t>["-0.020345878","0.044806127","-0.02681172","-0.009762944","-0.009959309","0.017356131","0.0584089","-0.06315334","-0.041806363","-0.01618903","0.058629982","-0.12584364","-0.035416543","-0.027102327","-0.025566623","0.057819966","0.03168174","0.06678799","-0.013688552","0.043049082","0.066384636","-0.03234196","0.023665663","-0.019724628","-0.023955224","-0.08790634","-0.0017246039","0.034436747","0.032468896","-0.10874759","0.010601662","0.06763133","0.04416213","0.0880815","0.091931306","0.036508292","-0.02812838","-0.03804555","-0.033027522","-0.03016339","0.014665662","-0.059284054","0.073938824","0.03373802","-0.047165163","-0.025252687","-0.059959993","-0.0016989717","-0.009412487","0.049404554","-0.077325106","-0.016919412","-0.021858612","0.029587654","0.035250872","0.05111002","0.04534398","0.01894994","-0.08266786","-0.01760299","-0.004451991","0.03658765","0.0033074783","0.010530859","0.013729858","-0.033465356","0.019925527","0.03971312","-0.040145367","-0.05926797","0.09358973","-0.040752668","-0.067245305","0.02004261","-0.04547693","-0.02762131","-0.013197601","0.0452328","0.08005712","-0.009320205","0.02713065","0.07397005","0.10375161","-0.06678474","0.0051408336","0.03540204","-0.047292557","-0.026291616","-0.0017693351","0.022208177","-0.04612727","-0.082629964","0.08813029","0.084208496","-0.01969966","-0.013854455","0.054456666","0.013481512","-0.014633187","0.03687035","-0.0012520128","0.07363511","0.0049793725","0.03185431","-0.0062010773","0.0153512405","-0.017836265","0.017774481","0.028993413","0.069698006","-0.048870333","0.061357874","-0.12197234","-0.038251292","-0.0056211455","-0.06821652","-0.08284679","-0.057183016","0.03835361","-0.12926273","-0.00592008","0.022489136","-0.08967981","-0.0152152","-0.08821835","0.012212421","0.011744658","1.147114E-34","0.07552545","0.026259726","0.045801505","0.07539968","-0.016191244","0.046886478","-0.031817343","-0.005041777","-0.08448068","-0.0047933618","-0.021059025","0.0031162233","-0.053063337","-0.018062254","-0.005536369","0.023653904","-0.011500112","0.015852073","0.03454333","0.06571859","0.03739769","2.576688E-4","-0.08105887","-0.055496998","-0.03717944","0.023532897","-0.057352975","-0.06881428","0.016279673","0.058962625","0.04041102","-0.019121347","0.02973134","-0.010448342","0.05682771","0.009048471","-0.021272417","-0.06078822","-0.06730949","-0.04115002","0.023207692","0.012370442","0.0034771983","0.058301233","-0.038244374","-0.028494874","0.04735278","-0.051831964","0.04279538","0.034637667","-0.04294365","0.0056834617","-0.082387395","-0.055424575","0.010985516","-7.627039E-4","0.019832293","0.07447066","-0.046237975","-0.075315736","-0.02818362","0.0282046","-0.014477874","-0.0012509185","0.041387487","-0.050246734","0.048045877","-0.020869501","0.017180162","-0.06629036","0.015856385","0.02558819","0.0624272","0.0422476","-0.042728275","0.021592442","0.04920745","0.044732817","-0.0444543","0.044095393","-0.058729522","0.046658773","-0.056022655","0.045386706","0.010912794","-7.066468E-4","0.04606652","-0.058669757","-0.06830054","0.07995608","-0.011161063","0.01586273","-0.005742675","0.012360081","-0.0452337","-3.8955266E-33","-0.07210874","-0.063758865","-0.0028073743","-0.027795596","0.06463974","-0.11242042","-3.890614E-4","0.10514663","-0.0041937437","-0.022100387","-0.089576975","-0.08586197","0.069008775","0.013524125","0.08304826","0.05730217","-0.017023547","0.012940132","-0.04000319","0.05199475","0.027313633","0.0020941289","-0.07967921","0.09111111","-0.023857344","-0.003989151","0.058979027","-0.07309394","-0.031192781","-0.07497806","0.024160985","0.036415312","-0.10829201","0.09746745","-0.08868884","-0.09818337","0.031933747","-0.0358886","-0.02715265","-0.024726635","0.0038216459","0.06737988","-0.067033805","0.026232587","-0.055326585","-0.01702582","-0.007773804","-0.038172252","0.07324692","0.01844334","-0.026931018","0.0014021366","-0.029316032","0.0010229549","-0.016574016","-0.015054896","0.013811478","-0.08611638","0.10761465","0.042474233","-0.0036163863","0.12453843","-0.10122235","0.13681036","0.01100565","-0.027698232","-0.11337704","-0.007270959","-0.057606976","-0.092573434","0.041539628","9.9421464E-5","-0.035602283","0.0028433278","-0.00738967","-0.056041192","0.011682593","-0.05373958","-0.01329755","-0.052401297","0.06716631","-3.010252E-4","-0.020543218","0.030415816","0.043434214","0.014172811","0.070608824","0.03646268","-0.011285914","-0.0044904463","0.029402366","0.01396241","-0.11458415","-0.019694442","-0.07860504","-2.8572519E-8","-0.03125689","-0.013928979","0.032008387","-0.045741588","0.053375777","0.012178072","-0.021420328","2.3194328E-4","-0.009626511","0.037352797","0.016430868","0.05920724","-0.05068803","-0.02016524","0.034053132","-0.09831943","0.0067817667","0.082838885","0.012478058","0.08526749","-0.033482693","0.019110456","0.0011079393","-0.09470798","0.004574453","0.022285214","0.07427406","0.018399248","0.023925118","-0.031404786","-0.039538745","0.12870759","-0.06896998","0.07072331","-0.027592635","0.00227682","0.0761981","-0.06769937","-0.038994335","-0.034751676","0.07089853","-0.0015742858","0.05330737","0.04815432","0.04356763","0.032824915","0.04658953","-0.069270805","0.07199435","-0.009456518","-0.12765983","-0.09549646","0.020797817","0.014980543","-0.04874199","-0.055176254","0.05208602","0.09413699","0.059214346","-0.039883077","0.07749033","-0.086454585","0.022954473","0.053400367"]</t>
+  </si>
+  <si>
+    <t>NK-5vHsZhcsq8HWkJytNjcbxh</t>
+  </si>
+  <si>
+    <t>CONSUELO A RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>Entity Name: CONSUELO A RODRIGUEZ | Type: Person | Jurisdiction: us | Risk Context: 1128b14</t>
+  </si>
+  <si>
+    <t>["-0.032763906","0.026077988","-0.072069","0.0054299603","0.0110118445","-0.0037835485","0.046306558","0.003871267","-0.016370187","0.016583499","0.073593944","-0.111278474","-0.021325205","0.004699311","-0.047343843","0.10933364","0.06990431","0.029552508","-0.0060830684","0.0026426308","0.035640176","0.05002879","0.005353141","-0.018955823","0.0014120612","-0.044883806","-0.06945529","0.044115562","0.021382146","-0.0439049","-0.017107114","0.056385834","0.080658","0.08795334","0.04868157","0.017070143","-0.07034872","0.03752797","0.05865982","0.0044428017","0.043001793","-0.01828678","0.05521729","0.05319916","-0.10523577","-0.017626774","-0.046146832","0.04384113","0.023435427","0.00576064","-0.12665197","-0.07645067","0.038151205","0.053285338","0.0065004784","0.04688228","-0.042029377","-0.0027733787","-0.0042121094","0.027709173","0.041350935","0.030538203","-0.029513333","0.01759088","0.0043899952","-0.011580594","-0.011021541","0.057239298","0.0026417167","-0.05807108","0.15705551","0.029991565","-0.046073936","0.04354747","-0.063510485","0.0409903","-0.01783174","0.053763885","0.003786627","-0.052653763","-0.052658662","0.032439735","0.020626519","-0.10517804","0.03216806","0.03822555","0.033565167","-0.005969361","-0.022254016","0.045860585","-0.055800747","0.012594504","0.12623718","0.0019869108","-0.06497376","0.031199606","0.06082182","-0.0068913167","-0.073039085","0.06312419","-0.007894631","0.029614996","0.011537047","0.024759056","-0.09074286","-0.0634951","-0.021825667","0.013038787","-0.019022623","0.037774876","-0.04581045","0.05223033","-0.042131502","-0.0019263659","0.033579968","-0.05119459","-0.015353634","0.029587286","0.05836251","-0.13495845","-0.008524902","-0.012053701","-0.065668344","-0.09873015","-0.06235199","-0.005800757","0.030858332","-2.8697468E-34","0.101886265","0.03649784","-0.019858852","0.10106918","0.014547545","0.03951784","-0.054441392","0.034146406","-0.10909034","0.036861464","-0.030522665","-0.011404928","-0.016136777","-0.06458916","-0.036920182","0.0029325539","-0.006542677","0.05792768","0.025787275","0.014092046","0.00912468","0.007542032","-0.08160599","0.006741663","-0.09280459","-0.022316718","-0.01521608","-0.13041818","-0.0046243626","0.07738004","0.019675113","0.04135075","0.061310057","-0.0019236283","0.038766228","-0.01999525","-0.023064194","-0.08625147","-0.09572436","-0.03856772","0.013607052","0.03886397","-0.0090922555","0.118379965","-0.026764477","-0.068670094","0.08540141","-0.001901796","0.035411075","0.024324968","-0.010456583","-0.018371958","-0.018219788","-0.0536222","-0.0126525685","0.009120797","0.016098578","0.12174365","0.015596056","-0.051349793","0.018567314","0.015314522","-0.08929352","0.015046226","-0.02392991","-0.11091448","-0.011128595","-0.08812225","0.09233715","-0.06636201","0.020465797","0.035643615","-0.0041836076","0.070930846","0.0032693679","0.00875581","0.013641298","-0.0019178968","-0.043328006","0.05668063","-0.122131504","0.015194656","-0.014335488","0.08392142","-0.0016659618","0.042496","0.041916944","-0.04363838","-0.059275713","0.021946067","0.028000502","0.027053831","0.0044269385","-0.0034783615","0.0748682","-9.922084E-34","-0.05280532","-0.092669204","9.143462E-4","-0.03887374","0.03541163","-0.116582684","-0.016575227","0.024724359","5.4171E-4","-0.09940072","-0.056978017","-0.10595018","0.072625466","-0.013282461","0.0419548","0.019941896","-0.02194245","-0.055760518","-0.07675317","0.024537284","-0.030851299","0.0014041498","0.04589538","0.01672226","0.009599016","0.049715914","0.020876395","-0.008992261","-0.05267443","-0.029897029","-0.020507375","0.088547505","-0.07290285","0.07853095","-0.17333658","-0.06768555","0.012151807","-0.11038953","0.0027463464","-0.026753701","-0.031020269","0.09112725","-0.024365","0.025645912","-0.06612096","-0.029063215","0.073834285","-0.023424411","0.07834184","-0.0045082048","-0.014116992","0.046718113","-0.06157386","0.006735921","0.059521426","-0.04021394","-0.01819436","-0.08582272","0.008030976","0.0067494735","-0.0140529955","0.07459617","-0.0345962","0.14541785","0.063321866","0.028023252","-0.073984765","0.054101843","0.015623308","-0.06322489","0.011677793","-0.041019388","-0.032134086","-7.4638723E-4","0.039546013","-0.067323335","-0.01107714","0.0026847865","-0.05166935","0.022420624","-0.0019342006","0.032284714","-0.049949452","0.0035407927","0.056861002","-0.035555325","0.06761486","-0.0011024924","0.03865843","0.072707616","-0.03953797","0.02763687","-0.029406903","-0.027133083","-0.021818986","-2.6192094E-8","-0.018135611","0.04457156","0.023866586","0.0031301517","0.08883138","0.021142839","-0.06346392","0.022074802","0.0144585855","0.07409183","-0.0120688025","0.036937606","-0.0052830568","-0.011044282","0.024442153","-0.04934601","0.019101188","0.013574995","-0.01141275","0.041252565","-0.022491427","-0.011152368","-0.018544925","-0.055932473","-0.011466756","-0.002944587","-0.04801423","-0.031265743","0.03319446","-0.013395181","-0.008218047","0.09632597","0.015153903","0.04411042","-0.034342386","0.066246055","0.058776625","-0.033745464","-0.06635705","-0.044431537","0.096980035","0.05502374","-0.056806013","0.074309155","0.02840723","0.029301163","-0.048059467","0.021352664","0.033149723","-0.019234514","-0.076730266","-0.101912536","0.068150796","0.028244626","-0.050378315","-0.062361944","0.06564571","0.05621207","0.020599486","-0.0010285177","0.0013477423","-0.037579674","0.0141346855","0.024696026"]</t>
+  </si>
+  <si>
+    <t>NK-5zgGs38RB4uBtBDCom7VtL</t>
+  </si>
+  <si>
+    <t>Lottery BG OOD</t>
+  </si>
+  <si>
+    <t>Entity Name: Lottery BG OOD | Type: Organization | Jurisdiction: bg | Risk Context: (also LOTTERY BG LTD.) (also LOTTERY BG OOD)</t>
+  </si>
+  <si>
+    <t>["-0.029653661","0.011946498","-0.04853611","-0.008307782","-0.043087564","-0.00888664","0.13295624","-0.028231177","0.060501616","-0.07895892","-0.005186491","-0.07638498","0.046933748","-0.063619465","0.024625843","0.066100515","0.054697115","0.007900478","-0.059422202","-0.020600595","0.06418885","-0.021609202","-0.018480597","-0.0025310018","0.02783726","-0.073635586","-0.06783287","0.13414015","0.037596777","-0.06992453","0.013957969","0.14734468","-0.02455824","0.048619326","0.06546724","0.019710617","-0.066204436","-0.020409018","-0.07952571","-0.042282037","0.02784987","-0.03841633","0.039231263","0.061754454","-0.036208313","0.05111181","-0.008419192","-0.02091363","-0.014578913","0.04285354","-0.010116558","-0.07313286","0.005999444","0.04096863","0.023158198","0.048189603","-0.03783219","-0.009718361","-0.038720995","-0.086679034","-0.07058388","0.048279334","-0.006155027","0.0321469","-0.02301806","0.011458404","0.023895094","0.030478064","-0.030448325","-0.11094106","0.14076792","-0.07497778","0.0022196604","0.037436716","0.013909738","0.044432145","0.018829197","0.031309135","0.03249102","-0.032794144","-0.03395057","0.0032101504","0.014511588","-0.04193313","-0.025314257","0.05218701","-0.014949345","-0.017735237","0.034517862","0.0194648","-0.048975453","-0.05782298","0.1377425","0.046671685","0.02508018","0.018092839","0.07584252","-0.10972037","-0.005255739","0.03269388","-0.03977678","0.059925888","-0.042456362","0.10111683","-0.034919724","-0.03645606","-0.07527419","0.02716577","0.083796516","-0.08587075","-0.05535481","0.074767694","0.067157924","-0.008979595","-0.07955249","-0.007071763","-0.14343837","0.015441895","0.023434797","-0.07712878","-0.003231852","0.021892283","-0.09674478","-0.08709624","-0.0717419","0.0071278326","0.008936865","8.6069035E-34","0.08043086","0.009674292","0.055537343","0.026367446","-0.02978333","6.716516E-4","0.022926476","0.048869237","-0.079027474","0.01729928","-0.075456016","0.030139986","0.004167777","-0.011717384","0.059833553","0.0028707404","-0.04880351","0.047902595","0.085012935","0.043821327","-0.008647293","0.03572107","-0.055538263","-0.016460326","0.023735048","0.024982626","0.021689856","-0.08041196","0.03790356","0.07274052","0.06868762","-0.0016936791","-0.043231472","-0.02486584","0.037592147","-0.041207343","-0.056733087","-0.05941192","-0.06044372","-0.046187364","-0.025326056","-0.043601617","-0.082137704","0.07803659","-0.016528547","0.024171522","0.012145495","-0.016492074","0.08506398","0.017179536","-0.01811672","-0.011789508","0.01395139","0.0028888802","0.029402407","-0.023936378","-0.021595087","0.0570832","-0.055191062","-0.002451763","0.032123633","0.03716476","-0.02398473","0.05547696","-0.0056783995","-0.03789475","0.0032793107","-0.10027651","0.07853101","-0.103850245","0.10350212","0.029115431","0.02472314","0.09667501","-0.033936035","-0.026667237","0.060427926","0.0819723","-0.043015976","0.017143259","0.012936906","-0.0019779026","0.0017161295","0.0025206169","-0.010988736","0.072526954","0.044202656","-0.10026448","-0.0554802","-0.002333932","-0.032938633","-0.039082374","0.02113087","0.0014590444","-0.04478905","-9.280961E-34","-0.079709895","-0.06132261","-0.010729136","-0.0073684915","0.04508794","-0.04481309","0.07640905","-0.012227454","0.019997815","0.051426586","-0.08552991","-0.005353434","0.07679327","-0.0623742","0.0062742927","-0.07088126","-0.032778446","-0.00828363","-0.03490359","0.12364815","0.0032021492","-0.07730379","-0.033788048","0.06050437","0.025716145","0.024252094","-0.035082076","-0.0806107","-0.011623305","-0.020960968","0.04763225","0.051316284","-0.061971266","0.034811303","-4.690754E-5","-0.11669102","0.12572393","-0.13113366","-0.045589667","-0.020659333","-0.08581447","0.03155013","0.006661386","-0.012917332","-0.006870338","0.025277529","-0.0540255","-0.0051673525","0.11416846","-0.06867295","-0.004710471","0.0626866","-0.06625713","-0.0024392102","0.032582704","-0.0018423784","-0.021787519","-0.06303852","0.05347436","0.02548254","0.043353133","0.040345352","0.031606548","0.17430754","0.019278996","0.0036527964","-0.041405577","-0.017057206","-0.0062372326","-0.07887528","-0.013847737","-0.040413816","0.00208958","0.022141816","0.028824404","-0.0031276487","0.03780135","0.023343956","0.0037249466","-0.033872448","0.05474313","-0.00724428","0.0060871392","0.060514566","-0.011209978","-0.022832032","0.087371856","2.8545855E-4","0.0094059855","0.017692726","-0.04739842","-0.040005054","0.0200149","0.047057986","0.040657673","-2.7011072E-8","0.024485568","-0.03165783","0.040771894","4.9270777E-4","0.028024971","-0.028787073","0.026132567","0.04062452","-0.036846932","-0.016340593","-0.016310513","0.012134163","-0.07583496","-0.083219","0.006384713","-0.021778166","-0.06580149","0.03692701","0.023914555","0.08005022","0.08244743","0.007162421","0.018741628","-0.07354603","0.018622622","-0.008036574","0.0060220915","0.007423088","0.10424826","-0.04284682","0.011251888","0.011966978","0.0076701096","-0.017977398","-0.07576854","0.051525928","0.0621084","0.009897871","0.00956831","0.03428819","0.020734582","-0.01583023","0.0438848","0.04269454","0.04593821","0.028793365","-0.018445065","-0.019497879","0.03441399","-0.08653073","-0.05770763","-0.06992255","-0.0034822377","0.024437174","-0.04795006","-0.03917309","0.007439089","-0.02358926","0.10843617","-0.01884535","0.036344383","-0.029685797","-0.010221668","0.061073445"]</t>
+  </si>
+  <si>
+    <t>NK-65Xg5n7HPdAMmF5dd8F37R</t>
+  </si>
+  <si>
+    <t>Aliaksandr Yauhenavich Shatrou</t>
+  </si>
+  <si>
+    <t>. He remains a shareholder of Synesis LLC. Personal ID: 3091178A002VF5 (Date of UN designation: 2021-06-21) En tant qu’ancien chef et ancien actionnaire majoritaire de Synesis LLC, Alexandre Chatrov a été responsable de la décision de cette entreprise de fournir aux autorités biélorusses une plateforme de surveillance, Kipod, qui permet d’analyser les enregistrements vidéo et d’y effectuer des recherches et qui recourt à des logiciels de reconnaissance faciale. Il participe donc à la répression de la société civile et de l’opposition démocratique menée par l’appareil d’État. Synesis affirme avoir cessé de fournir aux autorités biélorusses la plateforme Kipod, mais selon des rapports de ByPOL, Kipod est toujours utilisée par les services de sûreté de l’État</t>
+  </si>
+  <si>
+    <t>["-0.052808434","0.070389286","0.029424785","-0.10973231","-0.05738734","0.0206366","0.040224552","0.041727416","0.04349064","0.07148575","0.014132673","-0.04827827","-0.02339405","1.1202094E-4","-0.047829818","-0.03868343","-0.035253923","-0.011887541","-0.038576152","0.10193496","-0.05484909","-0.114766575","-0.021771943","0.019666295","-0.030789416","0.016127186","-0.087123305","-0.0017593744","-0.015114724","-0.087387","-0.016393654","0.09115332","0.0095764175","-0.004427629","0.047151495","0.0134100225","-0.02525194","-0.021231271","-0.06959193","0.111615315","0.022714596","-0.038750138","-0.07733088","-0.06310974","-0.07053191","0.11736092","-0.046839148","0.053712204","-0.03107563","0.045430876","-0.058794986","-0.078039065","0.1304871","-0.1122628","0.030318229","-0.073870555","-0.047048047","0.024763","0.10322529","0.018465914","0.14663404","0.007331524","0.012166319","0.0014135209","0.011980205","-0.052087463","-0.008726401","-0.029968858","-8.3732906E-5","0.0024666078","0.17712113","-0.05680228","-0.05321606","-0.065570876","-0.10035599","0.03179543","0.09218863","-1.5043822E-4","-0.0051053674","-0.14655334","0.07796807","0.07758663","0.025763955","-0.019861793","0.008318775","0.042232554","0.0128238425","0.026640773","0.0048239436","0.025057308","-0.030732512","0.0063072587","0.05711727","-0.09859171","-0.02868375","-6.97589E-4","-0.021435823","-0.005646374","-0.0050456873","0.07901764","0.068471596","-0.0033894412","-0.010355899","-0.018774774","-0.020463623","-0.056624956","0.008279948","0.03516804","0.01480993","0.041075293","-0.06686411","0.019137753","-0.016591202","0.02014058","-0.005036772","-0.016512776","-0.106881164","-0.029636422","0.0141989775","-0.043748844","0.07279241","0.036177814","-0.04729293","-0.05177017","0.041675862","0.07632467","-0.015119658","1.0219987E-32","-0.007153447","0.013456086","-0.02836573","0.0065303836","0.011561944","-0.013665929","-0.051625747","0.016224118","-0.071945176","0.010543014","-0.055250242","0.034819722","0.04425341","0.0100053465","-0.032470163","-0.05364788","3.686528E-4","-0.027177902","0.08865549","-0.0069075515","-0.04720033","-0.010042711","-0.0143239675","0.07830703","-0.0049953065","4.6814358E-4","-0.011774837","-0.062137265","-0.01984656","0.03377271","0.032029517","-0.0035326756","-0.025818055","-0.028656587","0.012971485","-0.101621315","-0.0553153","-0.07796049","-0.10825233","0.022015546","0.07014968","-0.03728959","-0.071790114","-0.0037855613","-0.0056331777","-0.0071155597","0.0078083407","0.04104774","0.09598268","-0.047742482","0.03745284","0.06786013","0.018105317","-0.07001892","-0.013276819","0.0064393943","-0.12029518","0.005392207","-0.029943528","-0.113927945","0.040892817","0.060155712","-0.04936215","0.052168775","-4.729502E-4","-0.034569334","-0.0019434767","-0.038717594","0.033576716","-0.086134896","0.005091803","-0.043917127","0.05152844","0.01431611","0.004702865","0.010035479","-0.018057391","0.07468575","-0.06136303","0.085484944","-0.09584701","0.015146345","0.06332053","0.029217986","-2.577213E-4","-0.011110139","0.111382514","-0.0355054","-0.010091876","0.09989593","-0.097123034","-0.025195586","-0.10197651","0.02319408","-0.050263133","-1.1792859E-32","-0.032644186","0.029908419","-0.0068593267","-0.019161403","-0.02452106","0.017609792","0.012283274","0.023812862","-0.07266286","-0.052135535","0.049949937","4.446035E-4","-0.002236863","-0.057195075","0.004656361","0.02711453","-0.0025893943","-7.3007174E-4","-0.027577583","-0.06274898","-0.031634226","-0.017567674","0.048715796","0.074437454","-0.0031842703","0.063861296","0.12136302","-0.037020735","-0.082199596","-0.042692736","0.019016879","0.044740036","-0.061406743","0.07941662","-6.9365645E-4","-0.017249454","0.026930861","-0.03220006","-0.01997684","-0.029202389","-0.014255786","0.06981016","0.057867754","0.07692277","-0.013854379","-0.020430204","-0.0061987927","-0.01620989","-0.011011734","-0.020356005","0.022854874","0.05026622","0.050345216","-0.04662568","0.018069081","0.01117236","0.02074497","-0.062300604","0.0036133283","0.039491247","0.08114454","0.04625573","-0.008674911","0.018384712","0.05855554","0.06280609","-0.051764376","0.08317047","0.05302338","-0.031304147","0.07150651","-0.039327305","-0.004837422","0.011047048","-0.022720175","0.016699541","-0.026459567","-0.037006386","0.0099816965","-0.026523318","-0.091189675","-0.10295211","-0.0055210334","0.06035858","0.01859842","0.003381494","-0.031065525","-0.055829298","0.003300259","0.0332502","-0.022973152","-0.08693748","-0.053103164","0.07395593","0.0818764","-6.723343E-8","0.12425133","0.01527861","-0.0042274473","-0.04374955","-7.778741E-4","-0.091213964","-0.03810242","-0.02806807","7.504613E-4","0.08087545","-0.027126031","-0.018893374","-0.07689899","-2.50093E-4","0.002164717","-0.011805524","0.014448884","0.016981672","-0.09165855","-0.032635048","0.029615195","-0.039412208","-0.025439944","-0.071942285","-0.05578329","-0.04201605","-0.029635658","-0.064107396","-0.0030837497","-0.027751654","-0.012932038","0.0892462","0.0153860105","-0.06991729","0.060475692","0.024777314","-0.03936633","-0.048259966","-0.0131024355","-0.027405724","0.014990317","0.08210847","-0.019854184","0.027477097","-0.039405767","-0.07356516","-0.0017912289","1.9150843E-4","0.029988546","-0.06406971","-0.023538472","0.046616744","0.040287398","0.10649025","-0.051993027","0.035851054","0.05870359","-0.016533019","0.0064692604","0.011787565","0.015146782","0.0126787005","-0.0036847468","-0.056147113"]</t>
+  </si>
+  <si>
+    <t>NK-66tRApALEgHNpx62AbdyiE</t>
+  </si>
+  <si>
+    <t>Aleksandr Borisovich LIVSHITS</t>
+  </si>
+  <si>
+    <t>Entity Name: Aleksandr Borisovich LIVSHITS | Type: Person | Jurisdiction: ru | Risk Context: 2024/753 (OJ L23022024)</t>
+  </si>
+  <si>
+    <t>["-0.05227325","-0.012416459","-0.044665597","-0.04161705","-0.024878832","0.0023722409","0.06767207","0.026012238","0.0020081257","-0.03842521","0.016643183","-0.040414426","-0.026007436","0.03783182","-0.04907814","0.021563785","0.005174225","0.06965845","-0.007204969","-0.0011510825","0.024745416","-0.05337035","0.062126346","0.026583482","0.025542224","-0.035830777","0.04304018","-0.0061014127","-0.021054024","0.030337643","0.08439285","-0.0073682996","0.029489942","-0.016934656","0.05923814","0.06633639","-0.030438403","-0.015460252","0.030032165","0.03808372","-0.0068734596","-0.06302104","0.018045643","0.08931488","0.0051879757","-0.015195541","-0.08551425","-0.02699429","5.1438296E-4","-3.1337145E-4","-0.12427149","-0.0034103892","-0.0020062306","0.03376645","0.031480484","-0.046474293","0.003130241","0.05846661","-0.05889762","-0.03457403","0.039404333","-0.005322631","-0.02587194","0.011500732","-0.07338202","0.036616407","0.08693629","0.0030462113","0.009867287","0.01168037","0.05231544","-0.031053552","-0.08224469","0.002776711","-0.042722788","-0.07223438","-0.0067382194","0.035430245","-0.029563377","-0.023111463","0.048140995","0.011013393","2.521175E-4","-0.04082209","-0.1096426","-0.01214258","0.036235","-0.07358488","0.0670104","0.07272199","0.0056701005","6.1261473E-4","0.14033476","-0.065583535","-0.011306965","-0.04139067","-0.029071223","0.005385115","-0.032278467","0.043358166","-0.06989904","1.5718584E-4","-0.018974695","0.09142718","-0.07825345","-0.03480088","-0.07755308","-0.02186881","-0.044224683","-0.0047582146","-0.0147383725","0.004439187","-0.0057126037","-0.035119236","0.052147437","-0.0039506014","-0.065937966","0.006538819","0.019079756","-0.016840396","0.05536026","-0.0028061585","-0.08849432","-0.027834715","-0.08037659","0.0019388329","-0.021569688","1.4146663E-33","0.09633971","-0.002186807","0.02885739","0.07348948","-0.16235794","0.008470074","-0.082454175","-0.043947313","-0.052360564","1.9215302E-5","-0.0064696805","0.012880995","-0.01315032","-0.111834005","-0.011047745","0.0663029","-0.015316391","0.102716655","-0.011389651","0.10525329","0.048064154","0.044022277","-0.028930599","-0.040730868","0.014865643","0.032963447","0.019644916","-0.091427974","0.023496043","0.03260242","-0.036451016","-0.027791431","-0.010900313","0.0061800582","5.763182E-4","0.034801994","-0.08863199","-0.11310603","0.0029388573","0.010192928","0.03922777","-0.024444092","0.012347561","0.09173142","0.023464097","0.028972385","0.05983805","-0.018010806","0.12133286","0.012778777","-0.06195822","-0.0029092946","-0.06523702","0.014072814","-0.05570306","-0.007762082","-0.061120346","0.069539696","0.041099165","-0.04163045","0.060813583","-0.016139181","-0.030705081","0.04013042","0.074802816","-0.13274367","0.008226555","0.027573692","0.02610513","-0.09153387","0.020142455","0.004148073","0.045013748","0.051055074","-0.060008425","-0.042766668","-0.01792493","-4.7535362E-4","-0.04090367","0.077995226","-0.10699538","-0.0066401702","0.022961836","3.248654E-4","0.0031787641","0.08985812","0.04726","-0.014732361","-0.037670612","0.0402489","-0.0881174","-0.06886955","0.022004379","0.056697328","-0.03825578","-4.3590934E-33","-0.0022405316","-0.117981575","-0.029748589","0.024780953","0.04222269","0.0070982683","-0.016716","0.089126766","-0.0038379193","0.07882514","-0.01601307","-0.083969645","0.04334924","-0.015697973","0.015918523","0.003925033","0.044876758","-0.024625458","-0.12419894","0.051079094","-0.017289583","0.0019065395","-0.039083745","0.1085153","-0.03584142","0.046652123","0.122356914","-0.052275635","-0.108046114","0.043511536","-0.010669459","0.039820466","-0.1184946","0.094595864","0.013667463","-0.018717607","0.069615714","-0.057524286","-0.058588114","0.034114797","-0.008213629","0.06903866","0.015649252","0.020680167","0.007159145","-0.028692763","-0.018802853","0.021164853","0.096803755","-0.13727784","-0.02063924","0.09637382","-0.063015215","-0.019362222","0.03528969","-0.022311289","-0.0054397066","-0.02615417","0.09036836","0.038159523","-0.051870394","0.011639464","0.021854326","0.10633124","-0.046811108","0.028846027","-0.030582517","-0.026965003","0.029418672","-0.08389882","0.026057916","-0.13024676","-0.004730241","3.140273E-4","-0.018996168","0.0256409","-0.021294488","0.0021036936","-0.0066310787","0.015047348","0.1095103","-0.06956966","-0.033071566","0.025087312","0.05054562","-0.048544582","0.0116894385","-0.039484907","0.03754113","-0.062469047","-0.009661846","-0.0323296","-0.039144877","0.00831409","-0.045286626","-3.144154E-8","0.07893074","0.016105887","0.051626086","0.05650873","-0.02368731","0.003846554","-0.004604744","-0.017520767","-0.07022113","0.052776597","-0.035269797","-0.024296423","-0.02865327","-0.020409262","0.05582357","-0.053126607","-0.04074779","0.08135839","-0.0014397185","0.06495229","0.021977333","-0.0643656","0.024992503","-0.1261445","-0.03349129","0.049829304","0.04845451","0.035836574","0.07618484","-0.012861997","0.031310283","0.03669936","-0.07842729","0.087093264","0.0026250167","0.03410411","0.10900165","0.017484706","-0.024970632","0.021223914","-0.07024488","-0.069159016","-0.007201476","0.06493381","0.0070729232","0.08692171","-0.016199106","-0.018711941","0.05166104","-0.0103748655","0.0030304228","-0.015479469","0.01843824","0.07931991","-0.047979485","-0.0064636595","0.057831444","0.003230628","-0.06014434","-0.037262205","0.02680542","-0.046901107","-0.0036192","0.0012053298"]</t>
+  </si>
+  <si>
+    <t>NK-67jG6GpBuUH6iFqDgnGopo</t>
+  </si>
+  <si>
+    <t>JURDAN MARTITEGUI</t>
+  </si>
+  <si>
+    <t>Entity Name: JURDAN MARTITEGUI | Type: Person | Jurisdiction: es | Risk Context: (also JURDAN MARTITEGUI LIZASO) (also JURDAN MARTITEGUI)</t>
+  </si>
+  <si>
+    <t>["-0.028683156","0.049413674","-0.047512144","9.487875E-4","-0.010942576","0.03727758","0.10646951","0.0014672421","0.038298763","-0.03498062","0.029871423","-0.057472363","0.010657315","-0.04162837","0.006894303","0.0908307","0.01619174","0.114000335","-0.04300307","0.039805893","0.029096004","-0.042517893","0.04654974","-0.046918586","0.034827296","-0.05522495","-0.023293793","0.076863706","-0.0022973916","-0.0035679224","0.004113869","0.041866474","0.05377132","0.08058857","0.04873616","0.036421318","-0.025269125","-6.7548524E-4","-0.028523382","-0.0016209669","0.022479424","0.005165901","-0.006934093","0.011142357","-0.05592793","-0.10665008","-0.035421245","-0.02999805","-0.02893699","0.026585482","-0.1452349","-0.09287161","0.014517282","-0.005446838","-0.009051843","0.06172397","0.004250198","0.049750324","-0.023553416","-0.029495362","0.008843358","0.015406463","-0.0163204","0.012327691","-0.028067036","0.00763089","0.0011102398","0.056781344","-0.022207825","-0.06079109","0.09174308","-0.041122027","-0.1149748","0.00775942","-0.03206954","-0.020211816","0.00921497","-0.034611266","0.04688741","-0.018443223","-0.04568527","0.047271248","-0.029030373","-0.1000813","0.0079256985","0.08274852","0.010116349","-0.038142946","0.032073677","0.019274997","0.0045140623","-0.016587637","0.117169484","0.015387918","0.023956256","-0.02084124","0.12724128","0.022655005","-0.04078057","0.066239655","0.015961617","0.008763263","0.02503673","0.03387807","-0.017345786","-0.011777114","-0.039182868","-0.02982723","-0.044008903","-0.051527858","-0.045674294","0.038307004","-0.06996404","-0.05577732","0.043650012","0.0035841647","-0.051009323","0.07098459","0.09908035","-0.08252553","0.027311614","0.04843257","-0.118607216","-0.036141668","-0.01753973","0.063138016","-0.0106513435","2.0454625E-33","0.052844927","0.043966394","0.04719168","0.0634336","0.01017493","0.02460032","-0.032501724","0.003151977","-0.07927805","0.028044704","-0.06828662","-0.022297192","-0.023398492","-0.12508826","-0.044682942","0.020071115","-0.011842503","0.009889634","0.06052742","0.024147594","-0.007012403","0.015395435","-0.06421791","-0.0036185246","-0.07202337","-0.06611668","0.080287755","-0.09813767","0.0132644465","0.06790488","-0.008100253","0.028786663","0.03575798","0.02553611","0.047842316","0.047586635","-0.025090631","-0.05286471","-0.056391273","0.008159715","-0.003088257","-0.006135358","0.02117137","0.062026355","-0.07037089","-0.08134798","0.0098966425","0.021470783","0.06944779","0.008237733","-0.023063751","0.0031681077","0.025611654","0.022762561","-0.036844272","0.044016466","-0.001183603","0.14605291","-0.0049049607","-0.027523233","0.054600064","0.002236263","0.022798447","0.042924017","0.08359343","-0.017963395","-0.0077637467","-0.022557465","0.10145619","-0.02744693","0.028350636","0.060080957","0.04725475","0.09129667","-0.021224875","-0.0035568252","-0.08501552","0.009818623","-0.035366856","0.03159893","-0.13512063","0.024570871","-0.04032008","0.071097985","-0.056290098","0.016472341","0.019191016","-0.06138769","-0.03799578","0.0401469","0.036966216","-0.0012427941","-0.015057715","0.0058307988","-0.048380256","-2.9355277E-33","-0.05093668","-0.077395104","-0.03611524","-0.031146744","0.016386982","-0.112276964","0.016385762","-0.0028889957","-0.03887424","-0.016370768","-0.023862854","-0.15963693","0.06375303","-0.06833797","0.04875663","0.10282459","-0.041414548","0.018119104","-0.034833875","0.047514305","-0.037323248","-0.1040811","-0.006949829","0.09236869","0.01219101","-0.05113087","0.042057876","-0.07848849","-0.073035516","-0.030771032","0.02647081","0.03769203","-0.09238012","0.010760169","-0.07758065","-0.04320311","0.022910498","-0.10848816","0.03398689","0.022339847","-0.007986147","0.074115","0.005051422","0.09714775","-0.010636998","-0.00854246","0.045252454","-0.034372933","0.08002163","-0.061911717","-0.026793452","0.0419672","-0.05726138","-0.0069187693","0.04736258","-3.199882E-4","0.008062887","-0.043490186","-0.030500952","0.032853395","-0.035382085","0.07665888","-0.04445544","0.112575345","0.13079745","-0.010012422","-0.1505326","0.02389671","-0.016614007","-0.10867326","0.11666535","-0.061439525","-0.038508095","0.0043459074","-0.0018534058","-0.06637356","0.009268605","-0.014911101","-0.07431393","-0.012824541","0.09281419","-0.06265847","-0.0055809137","0.026969953","-0.011735852","-0.037573572","0.06773404","0.042314142","-6.041147E-4","0.04659198","-0.0056536635","-0.010962002","-0.059519067","0.022128884","-0.034594912","-2.9207179E-8","-0.051043637","0.014707077","-0.007717129","-0.014123463","0.03227025","0.021235343","-0.03157352","0.029202782","-0.018331025","0.04713817","-0.056328226","0.011763571","-0.024441002","-0.056589607","0.022792814","-0.01535083","0.016335983","0.09279325","0.007677411","0.05818919","0.012797086","0.0055310973","-0.012068462","-0.079585336","-0.015327632","0.0076808776","-0.042564783","0.04019199","0.113805234","-0.038455203","-0.03836794","0.053477865","-0.03641607","0.010272942","-0.06078067","0.0898148","0.0250615","-0.028744271","0.024399033","0.03992018","-0.007151701","-0.043620445","-0.035837237","0.038877167","0.055833593","0.024570161","-0.034699667","-0.008954841","0.053289317","-0.028706029","-0.05923135","-0.0616366","0.06345258","0.05645312","-0.01141654","0.0058947797","0.064843","0.1354903","0.027384557","-0.017359737","-0.0064345472","-0.011102071","0.042879265","-0.0046659387"]</t>
+  </si>
+  <si>
+    <t>NK-6ATSSYUnqkb6YTSUk7mczB</t>
+  </si>
+  <si>
+    <t>ORLANDO LIMITED PARTNERSHIP</t>
+  </si>
+  <si>
+    <t>Entity Name: ORLANDO LIMITED PARTNERSHIP | Type: Company | Jurisdiction: us | Risk Context: (also MAZZIOTTA-D'AGOSTINO, MAZZIOTTA ENTERPRISES, YANKEE TRUCKING, INC., DOMINICK D'AGOSTINO) (also ORLANDO LIMITED PARTNERSHIP, MAZZIOTTA-D'AGOSTINO, MAZZIOTTA ENTERPRISES, DOMINICK D'AGOSTINO)</t>
+  </si>
+  <si>
+    <t>["-0.030633798","0.017214231","-0.06415945","0.03312859","-0.030653594","0.011014265","-0.019023532","-0.02302797","-0.001864569","-0.07000694","0.044118542","0.009143877","-0.042014025","0.025297156","-0.025962474","0.081907295","0.02036225","0.069332935","0.009669851","-0.01295879","0.006445574","4.958852E-5","-0.01758344","0.0066703134","0.00959683","0.011766011","0.0255799","0.11816318","-0.073186204","-0.10327305","-0.038036887","0.042376038","0.03771259","0.016574582","0.10879738","0.095520034","-0.15296477","-0.049689133","0.031507898","-0.038073946","0.064758174","-0.08898052","0.062803864","0.04033085","-0.07918784","-0.076306574","-0.007995631","0.07072762","0.07018178","0.08259258","-0.0813253","-0.06453694","-0.004277917","-0.07968611","0.018648837","0.056215197","-0.027662316","0.0500158","-0.04028898","-0.054370046","0.07394153","0.01909661","0.033296812","0.049431283","0.012699457","-0.0056014513","-0.037599847","0.032745384","-0.05891022","-0.11059757","0.10677224","-0.053229164","-0.029082045","0.033713095","-0.04015833","0.04826141","-0.009473918","0.07045512","0.077819","-0.02078367","0.008937318","0.04071064","-0.040409084","-0.048325572","-0.07239422","0.06124249","0.005706225","0.039184943","0.07218129","0.033797294","-0.030054267","-0.047392055","0.033671003","0.063101105","-0.03858912","-0.0048143016","-0.002046641","0.033869755","-0.094646715","0.05398413","-0.025360476","0.053955324","0.0140148355","0.01168404","-0.043510728","-0.040526796","-0.012950205","-0.01941935","0.0055828164","0.014738234","-0.06724583","0.0038165578","-0.06486073","-0.043547906","0.0065584723","-0.0453499","-0.072929464","0.068812765","0.08546327","-0.14360896","0.02097802","0.015920417","-0.005417908","-0.08507941","0.004849587","-0.013330844","-0.0012808121","2.5096913E-33","0.027877426","-0.0038362218","-0.018680334","0.052471716","0.06451056","-3.3979982E-4","-0.015677068","-0.0033150637","-0.07394072","0.04347127","-0.050859597","0.0341102","-0.018065762","-0.09653681","-0.038827043","-0.025190316","0.014030086","0.0033886917","0.075698406","-0.011143961","-0.03936541","0.068302765","-4.4708513E-4","0.10684675","-0.08477397","0.0064303093","-0.04978681","-0.059433423","0.010556531","0.07176007","0.012843568","0.03294208","-0.009864521","-0.032947805","0.003850209","0.010704413","-0.15395664","-0.098713875","-0.087572075","0.023756089","-0.046559814","-0.038643952","-0.049587034","0.072243944","-0.07492517","-0.017283212","-0.033406537","0.0674767","0.09687961","0.01742353","4.3353287E-4","-0.04953892","-0.044454075","-0.05274337","0.014382617","-0.032122288","-0.037555303","0.08443669","0.021257656","-0.058532264","-0.041119125","-0.0028868194","0.022044657","-0.0067682853","0.011520693","-0.019476214","0.06983146","0.01655492","0.10866734","-0.05167982","0.06383677","0.024768293","0.03815674","0.07619605","0.01303375","-0.057873465","-0.015399312","0.08600584","0.06249277","0.009064774","-0.061189823","0.014656367","0.058408234","-0.004725204","0.012343387","0.078616716","0.028937506","-8.3480554E-4","-0.027836205","0.109977715","-0.06712808","0.08841271","-0.06519835","0.05410974","0.11887339","-3.7262183E-33","-0.015647653","-0.05733945","0.029630378","-0.0045785154","0.009480647","-0.07196431","0.010828442","-0.0032283699","-0.022418274","0.03875491","-0.033461004","-0.05636146","-0.0048765996","-0.068326615","0.063420296","0.03251093","0.030704722","-0.0567247","-0.003640528","0.011322571","0.034147266","-0.06306255","-0.028716085","0.05514771","0.015726453","0.016480993","-0.025604224","-0.08056728","-0.0576255","0.02442898","0.03197868","0.07970236","-0.077478305","0.07181345","-0.07429717","-0.04139972","-0.0051780837","0.028445283","0.001290203","-0.064021125","0.059140023","0.015449187","-0.0042868215","0.030372495","-0.02952321","0.0013831652","0.05278608","-0.033250343","0.087900564","0.010331254","-0.017412562","0.039335083","-0.04312259","-0.004305304","-0.0030103023","0.08234669","0.028268103","-0.0018135232","-0.0063549513","0.024624227","0.016325012","0.060209956","-0.02598189","0.08581156","0.041467834","0.045017146","-0.06513581","-0.011498081","0.011581309","-0.049261454","0.056852326","-0.031533353","-0.031943083","-0.032843843","0.03335066","-0.03291353","-0.0011830606","-0.02975002","-0.05039213","-0.017301844","0.059210896","0.042111408","-0.005756065","0.07131939","0.005926875","0.0048968676","0.05708929","-0.030481806","0.022975706","0.06114425","-0.007133185","0.047579788","-0.08969256","-0.05250978","-0.06053775","-4.250959E-8","-0.028645344","0.02113427","0.00841104","-0.04374518","0.12041136","-0.036514774","-0.04661614","0.14025998","0.008281935","0.040723424","0.05463921","-0.042015675","-0.01849134","0.033263426","-0.031556435","-0.041502938","0.019603105","0.07737363","-0.039304912","0.029441854","-0.04170247","0.0035120698","-0.01731249","-0.060654096","-0.050772358","-0.025365194","-0.022300404","0.015129164","0.04008941","-0.045193177","0.026673384","0.070518225","-0.027881997","-0.03349123","-0.09218064","-0.025120737","0.07717342","-0.050727658","-0.021418167","-0.0070490213","-0.08625672","0.023525354","0.03360744","0.0289743","0.018370118","7.931189E-4","-0.0865275","0.008083002","-0.020778349","-0.0022421393","-0.061444264","-0.04731464","0.030787142","0.01142793","-0.013196535","-0.045660716","0.06870452","0.06836098","-0.023972593","-0.0378836","-0.0678765","-0.13923708","0.10687786","-1.1449104E-4"]</t>
+  </si>
+  <si>
+    <t>NK-6D36iTr7h8DgBE4xTEwYah</t>
+  </si>
+  <si>
+    <t>Aleksey Konstantinovich KAKHIDZE</t>
+  </si>
+  <si>
+    <t>| Risk Context: (Date of UN designation: 2024-12-16) Aleksey Kakhidze is the Chairman of the Board of Directors of Gazprom LNG Technologies LLC, a leading company in the Russian energy sector. Among the company’s activities are liquefaction and enrichment of natural gas, as well as construction of cryogenic filling stations. The energy sector, especially oil, provides substantial revenues to the Government of the Russian Federation. Therefore, Aleksey Kakhidze is associated with an entity which is involved in an economic sector providing a substantial source of revenue to the Government of the Russian Federation, which is responsible for the illegal annexation of Crimea and the destabilisation of Ukraine</t>
+  </si>
+  <si>
+    <t>["-0.089326404","0.038249128","-0.038829654","0.011476466","0.007594674","0.016691655","0.10242349","0.02524322","-0.014062221","-0.044142786","-0.08182736","0.013168907","-0.009534055","-0.006728141","-0.076531485","-0.008865014","-0.023283549","-0.025198733","-0.07508547","-0.04298843","0.03608647","-0.06833887","0.038806487","-0.0046360027","0.043625724","-0.0024135567","0.02405734","0.01051094","0.03463436","-1.1469051E-4","0.029195191","-0.0010320924","-0.021581093","-0.018126175","0.070121765","0.13089533","-0.044271898","-0.020433601","0.0071523706","0.006195945","0.011158869","-0.106510326","-0.05100509","0.016570622","-0.064006485","0.06635837","-0.005238527","-0.046155237","-0.076190256","0.033531934","-0.022826105","-0.052572273","-0.017411284","0.031589627","0.051764276","-0.07060114","-0.040148832","-0.018320888","-0.035876658","0.011036846","0.07685649","0.021806452","-0.03317497","0.027176403","-0.0335165","-0.0077866865","0.008205956","0.035235047","-0.052032877","-0.024557047","0.10254876","-0.066433035","-0.08611023","0.003892726","-0.035142716","-0.0580788","0.043193225","0.0977386","0.01944882","-0.05141773","0.086941585","-0.05298445","0.014706316","-0.05186307","-0.07320794","-0.049510024","0.025309082","0.007993744","0.07804068","0.061871342","0.049029704","0.015249002","0.16416848","0.0148787545","0.069822475","0.06205618","-0.010599534","-0.039096657","-0.041634377","-0.0038156582","-0.04494821","0.043830384","0.011151383","0.009233569","-0.06093454","-0.05904043","-0.07138399","-0.027579127","0.0028227197","-0.040765192","-0.025479056","-0.020429796","0.00851756","0.015574379","0.0064866166","0.0032221482","-0.06855145","-0.085928105","-0.033694953","-0.07501415","0.010248372","0.027099583","-0.034288265","0.03681903","-0.039140735","0.0578654","-0.03335971","-3.3249898E-34","0.009380995","-0.0031235279","-0.023003928","-0.009871504","-0.106087506","0.06262274","-0.021151554","-0.040886495","-0.08080793","0.042992055","-0.040317293","0.092673905","-0.0111633465","0.010343194","0.034481417","0.009677499","-0.0683593","0.07365377","0.021315431","0.065973446","0.04437571","0.029203136","-0.0121094305","0.02888925","0.028726904","0.029578643","0.042183537","-0.045910582","-0.01011941","0.030188782","-0.031814512","-0.001004292","-0.07916804","-0.009410749","-0.073795475","-0.01575118","-0.13917083","-0.0074347225","-0.026436275","-0.019187644","4.4200785E-4","-0.06712636","0.011440585","0.061382692","-0.027298609","0.03062249","0.05690763","-0.02214409","0.062075906","-0.047747273","0.0026291092","0.02650953","-0.005317806","0.005523152","-3.1110537E-4","0.028409254","-0.019958917","-0.02488861","0.015645444","-0.08946706","-0.019853637","0.02526468","0.03458281","0.10389737","0.042037457","-0.01949345","0.04583811","0.013111991","-0.043806154","0.017003842","0.017983967","-0.063894026","0.09007681","0.059784386","-0.060600463","-0.017024381","-0.021258572","0.03695392","-0.11936896","0.09999128","-0.029934622","0.020324437","0.08017162","-0.012596635","-0.04655642","-0.017937968","0.026939396","-0.0038159417","-0.007846617","0.08243418","-0.12052708","-0.0054539987","-0.002213288","0.07333872","-0.04325557","-3.6984524E-33","0.08542195","-0.046196528","-0.031226538","-0.03274604","0.015333008","0.028521849","0.08816692","-0.042540252","0.013960407","0.064670876","0.027322344","-0.0035184906","0.016556935","0.022582473","9.930076E-4","-0.030786857","0.07453304","0.0025046794","-0.05610453","-0.12128179","-0.022784691","0.06061577","0.006252847","0.0615618","-0.09439771","0.0037198","0.035668667","-0.072423115","-0.06532965","0.08338249","0.033491924","0.005845143","-0.08817422","0.047260232","-0.04398126","0.0103352135","0.06717428","-0.04799883","-0.096228406","-0.064049415","0.050074883","0.03391679","-0.009038941","0.045223095","0.010390234","-0.023050265","-6.967868E-4","-0.043616243","-0.0026577832","-0.08953454","0.027574966","0.05092724","-0.00727506","0.0106143085","-0.011931174","0.08726807","-0.026911562","0.040625658","-0.006087115","0.016607383","0.07611484","0.016898315","0.09324524","-0.043207522","-0.05682877","0.006675909","0.0030183315","0.0061464086","0.091913804","-0.032876436","0.09378513","-0.014023072","-0.066409886","0.058467913","0.018832419","0.09273714","-0.03346367","0.039925385","-0.05034281","-0.083612695","0.07814307","0.004569871","-0.010959277","0.03061073","0.035193183","-0.09149668","0.031330526","-0.104813226","0.07946466","-0.066495135","-0.08716448","-0.05841214","-0.09725604","0.12155506","0.0050520753","-4.920569E-8","-0.004927075","0.032868512","-0.0015042821","0.00879164","-0.051230434","-0.08687014","-0.06700789","0.024332166","-0.058640074","-0.022096947","0.011859266","-0.03001791","-0.0269617","0.09022482","-0.033160497","-0.024099026","-0.05193696","0.07178004","-0.012546979","0.012291519","0.053958394","-0.023977507","-0.0195118","-0.08995268","0.01365115","0.046909235","0.064556696","0.035803597","0.112433836","0.018785696","-0.011119434","0.00708152","-0.029509852","0.058328506","0.05534051","0.034929283","-0.0013314564","-0.017747734","9.2435133E-4","8.783297E-5","-0.066554226","0.05105142","0.029706912","0.067198716","-0.12989427","-0.02054914","-0.08755587","-0.0779115","0.08109409","0.06272763","0.00815214","0.03902418","-0.013339519","0.054479633","0.047788","-0.02532644","-0.06369827","-0.016937582","-0.045777693","-0.07357505","-0.00295073","-0.09332293","0.023639366","-0.0015674072"]</t>
+  </si>
+  <si>
+    <t>NK-6EDCjwnwEQbVvNjHBPKLRk</t>
+  </si>
+  <si>
+    <t>CHERE A HOLMAN ADAMS</t>
+  </si>
+  <si>
+    <t>Entity Name: CHERE A HOLMAN ADAMS | Type: Person | Jurisdiction: us | Risk Context: 1128b4</t>
+  </si>
+  <si>
+    <t>["-0.047804803","0.07665338","-0.004335133","0.0092434","-0.024103332","0.016305337","0.096268825","0.014063836","0.0011215064","0.0055049863","0.04344643","-0.0896923","-0.0022277308","-0.045560855","-0.040578723","0.089955494","-0.021882137","0.11651472","-0.023851143","-0.0026271138","-0.01787047","0.043908566","0.020410834","0.038668334","-0.019771527","-0.057726625","0.008951395","0.022054695","-0.014047221","-0.056361422","0.044845324","0.004340609","0.0480059","0.045640863","0.052231964","0.067196265","0.033630997","-0.020804508","-0.015196655","0.011385407","0.061039895","-0.04051744","0.043889046","0.029277502","-0.042196516","0.0025175957","-0.056712437","0.022289379","0.057117607","-0.045297388","-0.027141789","-0.06655758","0.03665446","-0.009741111","-0.023824086","0.023215398","-0.010394679","0.028352652","-0.016213525","0.0046814806","0.04981966","0.014285126","0.05713674","0.023226429","-0.0055434466","0.036284383","-0.012991112","-0.013156971","-0.021448392","-0.14166738","0.09097974","-0.019436784","-0.13013439","0.07300766","-0.034390505","0.03398804","0.02827686","0.051282138","-0.0402393","0.0043170163","-0.0529416","-0.017247679","0.06276545","-0.05554304","-0.012938104","0.02735792","-0.004684083","-0.067402944","0.007918854","0.009191478","-0.07243343","-0.0881032","0.10367282","-0.029316861","0.050048504","0.015620709","-0.0118914535","-0.017477972","-0.04326301","0.061406393","-0.047278214","0.027514687","-0.021744106","0.08367614","-0.04187732","-0.034469154","-0.060562372","-0.03433245","-0.02041806","-0.009163501","0.018450998","0.036749955","-0.062044587","-0.045246925","0.040477928","-0.0072761765","-0.08133068","-0.016489321","0.062435","-0.14283276","0.0200788","0.059574492","-0.10515921","-0.01910924","-0.0735307","0.007592944","0.022770759","-7.782689E-34","0.03719821","0.07717307","0.020155316","0.026961679","-0.0525993","0.0033095088","-0.015025104","-0.009675292","-0.03620617","-0.035347722","-0.058185782","-0.03873591","0.015460338","-0.15974948","-0.043836083","0.043136712","0.021210985","0.08253437","0.007656954","5.277046E-4","0.009100522","0.007179975","-0.055821095","0.003778559","-0.03577007","-0.0019596275","0.03133348","-0.096165","0.057146482","0.018618837","0.018261092","-0.006482775","0.08615782","-0.0027784824","0.075250834","0.020280542","-0.050576534","-0.028757725","-0.012000013","0.042457018","0.002404377","0.026176613","0.06301013","0.11888717","-0.020730695","-0.08129861","0.052020688","0.001922441","0.12265881","-0.023385497","-0.04965296","0.025643954","-0.080987036","0.052668724","-0.040071413","0.016793795","0.021836927","0.07170565","-0.032165576","-0.058583304","0.042145096","0.040115535","-0.06460604","-0.040865358","0.006064164","-0.045145825","0.0018300685","-0.025097333","0.0021361588","-0.039308358","-7.5492106E-4","0.032915123","0.031529296","0.04308395","-0.002560768","0.014839312","0.07116306","-0.0053274315","-0.028333472","0.04942621","-0.12927623","0.04883562","-0.011397672","0.089477725","-0.038869325","-0.014561893","-0.011871797","-0.0344068","-0.049785253","0.039728444","0.04404836","0.06616313","-0.02572155","-0.041411936","-0.017370112","-1.810154E-33","-0.031711634","-0.07793431","0.005460299","-0.038014412","0.07772198","-0.11039726","-0.040121634","0.036489848","0.002315324","-0.09508537","-0.031918615","-0.093104176","0.06300062","-0.019113103","0.029104775","0.056241643","0.016458262","0.0047786003","-0.053705737","0.06264727","-0.032997824","0.058765497","-0.02969385","-0.007856008","0.025727982","-0.03038424","0.055968843","-0.066109724","0.018904457","-0.05696945","-7.877612E-4","0.045560308","-0.06973459","0.09488912","-0.092533454","-0.06034262","0.019697737","-0.041898742","-0.014765311","-0.004462447","-0.020340906","0.022403855","-0.010742851","0.06563819","0.032742977","0.034862496","-0.0025252956","0.05350813","0.025159216","0.055272926","-0.0018076182","0.07738513","-0.037102688","-0.011107493","0.0038714488","-0.037616163","0.0128273135","-0.057934865","0.03234402","0.021609662","0.03808878","0.03332228","-0.01603821","0.114806496","-0.020326639","-0.04336713","-0.18585749","-0.051317852","-0.055923574","-0.083100654","0.029206688","-0.06731424","-0.043467905","-0.044542175","0.02577284","-0.023927826","-0.04815477","-0.02769378","0.008638931","-0.013283823","-0.05130893","0.09097747","-0.020829577","-0.022702059","0.111794226","0.036530383","0.026455807","0.015783599","0.044450752","-0.03827238","-0.05039479","-0.03923304","-0.08171942","-0.025081597","-0.070050664","-2.9341455E-8","0.021062095","0.019313239","-0.0355619","0.0016486907","0.034145966","0.015655605","0.027887706","-0.013133475","-0.06289388","0.018114652","-0.07769794","0.0759066","-0.024257625","-0.06958486","0.06980089","-0.080139406","0.0086057205","0.04471285","0.0070875357","0.043863006","0.038536392","0.016898917","-0.038393028","-0.114626415","-0.041405722","0.030535756","0.054081663","0.047181748","0.032133166","-0.062991545","0.09674721","0.08830034","-0.05361409","0.049399525","0.047423303","0.074211456","0.0077550625","0.07460443","-0.032894414","0.015897935","1.8321058E-4","0.061916836","0.023688724","0.09660788","0.010623987","0.035083838","0.051261965","0.011628517","0.07228887","-0.034703393","-0.035739373","-0.119810134","0.058209844","0.016417976","-0.039923124","-0.011629864","0.093795955","-0.048470143","-0.05676805","-0.0055345087","0.030775432","-0.14365703","0.040890645","0.06685536"]</t>
+  </si>
+  <si>
+    <t>NK-6HuYYEVHWQAfiBpPppSd9y</t>
+  </si>
+  <si>
+    <t>Farahnaz Meshkat</t>
+  </si>
+  <si>
+    <t>Entity Name: Farahnaz Meshkat | Type: Person | Jurisdiction: ir | Risk Context: Executive Order 13902 (Iran)</t>
+  </si>
+  <si>
+    <t>["0.020127885","0.14235365","-0.04155071","0.005883445","-0.020347826","0.0054509556","-0.0059466204","-0.033608854","0.001245229","0.019680645","0.005537006","-0.044900868","0.05051732","-0.026956504","0.010970247","0.02400488","0.035061784","0.013222127","-0.061025195","0.022936989","0.04258652","0.027464833","0.07734879","-0.022098571","-0.021755923","-0.025858043","-0.04105022","0.011614255","0.019928055","-0.08777114","0.019674342","0.0073558483","-0.005584559","0.09820931","-6.2773307E-4","0.028057355","0.016051166","-0.05937111","0.025166342","-0.008211447","0.07818568","-0.03137503","0.03785643","0.05425453","-0.031663045","-0.019638885","-0.060042217","-0.0033774383","-0.040379696","0.06893262","-0.10592095","-0.070401244","-0.012300213","0.050644137","0.032825146","-0.0633066","0.02038388","-0.013018419","-0.05179405","-0.02701749","0.057113703","0.009963333","-0.025246812","-0.03640386","-0.020390198","-0.04951958","0.06642281","-0.063034505","0.03229201","-0.103031136","0.0047548967","0.00452145","-0.06961656","0.060808826","-0.10105297","-0.0740056","0.085393496","0.07317591","-0.0325521","-0.10451151","0.010634828","0.050076656","0.048416235","-0.062475517","-0.02346554","0.049742997","-0.07622865","-0.0017224811","-0.011123206","0.072970495","4.5901802E-4","-0.055536363","0.14926937","0.019979784","0.031826247","-0.01463026","0.0897511","-0.039652407","-0.08875434","0.08138903","0.075537376","-0.029732011","-0.015266242","0.0332464","-0.06234184","0.0013129202","-0.08972862","-0.077789605","-0.087808244","0.0017343296","-0.07752589","0.029403819","-0.026974076","-0.09490198","-0.021687517","-0.008122245","-0.045124296","0.04108487","0.026604526","-0.08175832","-0.05695362","0.009632672","-0.046770517","-0.005385004","-0.0057749692","-0.028993312","-0.06286416","-3.2157067E-34","0.009738754","0.032162707","0.002421333","0.023559313","-0.052497767","0.02054776","-0.031107817","-0.01217596","-0.058990844","0.054204263","-0.0030620433","-0.01537344","0.03369603","-0.07773858","-0.023338363","-0.03109035","-0.012951987","0.039068185","-0.016711818","0.06136087","0.022136578","-0.018023344","-0.015000149","0.0074778423","0.023511086","0.04466034","-0.007948998","-0.04344439","-0.0144898575","0.05549443","0.06039106","-0.0030648333","0.042757053","-0.028013187","0.02183364","-0.009355354","-0.051768787","-0.06265214","-0.0023882305","-0.089544274","0.018835517","-0.0077165184","-0.006511457","0.13127114","0.016877742","-0.056575198","-0.005011921","0.073953815","0.082797356","-0.015281113","-0.03714358","0.024228286","-0.06381152","-0.021516388","-0.12224871","-0.036763284","-0.030992707","0.075262435","-0.028975898","-0.034769394","0.019243576","-0.012603041","-0.068438195","0.08575183","-0.02161557","-0.122789696","-0.0372753","0.02610092","0.07764776","-0.029020783","0.057615366","0.0358442","0.08567484","0.07289172","-0.07275216","-0.02616532","0.040588412","-0.043221306","0.03256801","0.04307445","-0.08705523","0.10157328","0.06670499","0.019903274","-0.015336609","0.08989077","0.010014867","-0.022127647","-0.031314","0.048887473","0.033287764","-0.013560016","0.05507686","-0.032200307","0.034494225","-1.4581952E-33","-0.0292041","-0.032842178","-0.065439396","-0.08873076","0.14005208","-0.049573284","-0.00718248","0.004172817","-0.06363603","0.019027427","0.058499083","-0.06995412","0.05714551","-0.0013720328","0.117789745","0.0123084355","0.047880244","-0.03637665","-0.01620767","0.03128661","-0.01799644","-0.010167617","-0.026329985","0.07428563","-0.0016715202","-0.03432714","0.049345456","-0.025326686","-0.05221355","0.0047146645","0.003210662","-0.03293574","-0.11029277","0.10789889","-0.01211217","-0.12086389","-0.0032024416","-0.048737485","-0.05077179","-0.010153695","-0.015605168","0.072144814","-0.030857626","0.07249086","-0.06633766","0.07140889","0.014630783","-0.023355126","0.0027394362","-0.0529591","0.016866568","0.04285548","-1.2270325E-4","-0.01947627","0.01410728","0.012202264","-0.016834507","-0.001016355","0.07669661","0.03077636","-0.011974279","0.09855103","0.0069955117","0.097432025","0.034707006","-0.033047214","-0.066180445","-0.028741237","0.05812444","-0.02434847","0.029875394","-0.06490824","-0.086794406","0.018580824","0.04160011","0.024099803","0.009070449","0.019821238","-0.09323068","-0.017732363","0.07819331","-0.001615531","-0.09759909","0.05244497","0.08022138","-0.02585631","0.06411762","0.011594796","0.031788766","0.04735474","-0.020407274","-0.03618064","-0.0351732","-0.009743677","-0.007858707","-2.5566615E-8","0.0046019214","-0.031605132","0.006292196","0.0055723996","0.021382738","0.06892408","0.0060973754","-0.019972954","-0.08436837","-0.016420418","0.027886856","0.034927677","0.026301347","-0.068190575","0.042179916","-0.07290248","0.029880611","0.07426514","0.015123787","0.019124473","-0.07722648","0.0027614562","-0.030530997","-0.053676415","-0.0075910795","0.062653065","-0.024820846","0.024640761","0.07104158","-0.011378847","0.018233914","0.055213362","-0.07355838","0.024059378","-0.10473448","0.07619941","0.08261857","-0.02154134","-0.02077039","-0.021824544","0.07111516","0.08273265","0.05638275","0.0784414","-0.04123879","-0.007252339","0.028439663","-0.12846357","0.10207409","-0.05866395","-0.028379776","-0.025877729","0.024231926","0.03880531","-0.008999578","0.038775176","-0.0027326264","0.015744403","-0.044920307","0.028691038","0.10537182","-0.053594485","0.0234041","0.00331128"]</t>
+  </si>
+  <si>
+    <t>NK-6Ma7T7k83whGGSyW4ibBG7</t>
+  </si>
+  <si>
+    <t>Andrei Konstantinovich NEKRASHEVICH</t>
+  </si>
+  <si>
+    <t>. He publicly praised the joint Belarusian-Russian military exercises, which prepared and facilitated the Russian military aggression against Ukraine of 24 February 2022. He is therefore responsible for and actively supporting actions undermining the territorial integrity, sovereignty and independence of Ukraine, as well as stability and security in Ukraine</t>
+  </si>
+  <si>
+    <t>["-0.0016833547","0.06975073","-0.015780963","0.038935736","-0.038176443","0.06915091","0.08382473","-0.053259216","-0.07682448","0.013001324","-0.079937465","0.11648123","0.050827775","0.03854959","-0.023604311","0.04679769","-0.048933443","-0.047883876","-0.09513639","-0.020185912","-0.04002983","-0.022300946","0.120087035","0.032696605","-0.013671306","-0.033767767","0.017450934","0.017398594","0.045396045","0.0018192917","0.10210052","-0.06455678","-0.016465046","-0.047888972","-0.052444186","0.1077851","0.07098575","-0.048288703","-0.122736864","0.01688128","-0.037338052","-0.05172656","-0.033430837","0.091147564","0.016761104","0.01937488","0.033167455","-0.07901224","-0.057600167","0.019251784","-0.013989055","-0.039828815","0.042927153","-0.07670163","-0.0129864635","-0.022599185","0.010199489","0.035392463","5.194321E-4","-0.051754497","0.047639426","-0.055333804","-0.07637048","-0.015616706","-0.012845956","-0.021630608","0.027587688","-0.015283879","-0.07477293","0.055536468","0.0790317","-0.010100471","0.005786891","-0.07995075","0.028831197","-0.062462576","0.011887889","0.07572071","0.014070345","-0.06383498","0.068583764","0.015943615","-0.012354648","-0.026368449","-0.0066135577","-0.049396127","0.050777797","-0.04825557","0.045686994","0.04962017","0.06050434","-6.5691833E-4","0.091499284","-0.036783956","-0.04484148","-0.0026333202","0.014755197","-0.0071047903","-0.031850964","0.045309473","0.052653056","0.022551026","-0.0419804","0.044571806","-0.06293559","-0.002431657","-0.04835911","0.044686053","5.257326E-4","-0.0076774512","0.024950635","-0.030662214","-0.037519507","0.020052375","0.058624517","0.07215123","-0.0031648672","0.0035741946","0.012986607","-0.06321943","0.056223337","0.014563596","-0.0013638005","0.05378603","-2.1852518E-4","0.0038999266","-0.05395326","-1.8945586E-33","0.09246158","-0.057710618","-0.013121899","0.09398153","-0.10305834","0.06785327","-0.0038577567","-0.02903269","-0.0534123","0.009907137","0.030360365","0.094695054","0.054520726","0.015025535","-0.008658423","0.020953642","-0.04909898","0.14749877","0.071199074","0.058501255","0.072012864","-0.011296438","-0.047614176","-0.028122524","0.08414282","-0.0062017995","0.03328067","-0.024559868","-0.08417405","0.021677345","-0.089201234","-0.042419553","-0.069625884","-0.004045218","0.027684681","-0.017705265","-0.1567496","0.0031514245","0.0116740465","0.048318967","0.13251694","-0.027421208","-0.01018441","0.008332502","0.0777231","-0.048936874","0.035175536","0.025972042","0.0392864","-0.045559086","0.011143402","0.043325596","-0.04106034","-0.0398287","-0.01940447","0.029091243","-0.01272974","0.06155213","0.022043152","0.027093405","0.065083474","-0.022369526","-0.06640906","8.5697044E-4","-0.029510744","-0.070415825","-0.05746248","0.084306724","-0.058486454","0.021075048","-0.037793726","-0.0049741818","0.008136939","-0.019251585","-0.105926506","-0.046156798","-0.05394408","-0.049819138","0.00445866","0.07696621","-0.03853512","-0.042689163","0.07093099","0.05317664","-0.12880747","0.030399116","0.048105694","-0.058537677","-0.033284456","0.04741097","-0.10537285","-0.0021838294","-0.0056341453","0.015126063","-0.042887352","-1.6204825E-33","0.054163035","0.009528538","0.0011343996","0.041065987","-0.04529","-0.0018827021","-0.059891265","-0.006826488","-0.02665282","0.036342498","0.04634338","-0.06861979","-0.0272076","0.018770631","-0.043158453","-0.010465819","0.01918011","-0.012778125","-0.05161131","-0.06176364","-0.06813312","0.04952041","0.06471836","0.01838635","-0.038296837","-0.03772277","0.15894105","-0.06732598","0.03116567","0.1227916","9.5202494E-4","-0.10786169","-0.04616994","-0.03379975","0.071536474","0.0031253872","0.027859444","-0.019362373","-0.03904689","0.031047003","0.066042125","0.08030062","0.015760992","0.052742258","-0.029125847","0.010691847","-0.047323316","0.036836483","-0.043303374","-0.047736604","-0.010194452","0.0043640477","-0.050307572","0.08360215","-0.0025804762","0.026812606","-0.10634318","0.035574842","0.04695708","-0.020957157","-0.027771197","0.04152008","0.024813352","-0.024558458","0.02492898","0.05703955","-0.010185359","0.035276856","0.035658877","0.06104619","-0.018169641","-0.06301517","-0.0013399129","0.059078768","-0.016600609","0.03710644","-0.04973401","-0.022640552","0.004514816","-0.024341986","0.05186925","-0.08500917","-0.015361268","-0.03933977","-0.03981403","0.034840483","0.018737152","0.009418996","0.0068974574","-4.1002786E-4","-0.019587848","-0.018353296","-0.06352484","0.08384955","0.053245544","-3.8122817E-8","-0.0023538724","-0.018393794","-0.058474306","0.044177398","-0.10817508","0.026627656","-0.009003289","-0.11370344","-0.041262273","0.07121213","0.01396658","0.0011452019","-0.047411885","-0.013590157","0.014001921","-0.01906556","0.036924634","-0.022885572","-0.08240359","-0.0030156078","0.014644902","-0.05636661","-0.008038397","-0.032166183","-0.015918188","0.007093339","0.0075066844","0.03175717","0.09407061","-0.013123182","0.023321599","-0.03490917","-0.07584466","-0.040920988","0.030677484","0.08161831","0.00904177","-0.022857754","0.046762284","-0.012401984","-0.07432456","0.061927237","0.01584054","0.04606163","6.5918296E-4","-0.04057526","-0.081950895","-0.07427303","-0.049215138","-0.011937289","-0.055862937","0.029311493","0.04010435","0.111870915","0.07495721","0.034580305","-0.025567172","-0.09261808","-0.030892046","0.035206076","-0.049673565","0.020300534","0.045172166","-0.10869178"]</t>
+  </si>
+  <si>
+    <t>NK-6PxQsdBriyC4jYHpBFDhHH</t>
+  </si>
+  <si>
+    <t>Gorshenin Oleg Vladimirovich</t>
+  </si>
+  <si>
+    <t>. (Date of UN designation: 2023-06-23) Head of the Russian National Defence Control Center Function: Member of the “working group special military operation” established per decree by President Putin; Head of the National Defense Control Center of the Russian Federation, Major General. Russian military official. Head of the National Defense Control Center of the Russian Federation. In his position, he participates in strengthening the combat capability of the Russian army during the invasion of Ukraine. Russian military official. Head of the National Defense Control Center of the Russian Federation</t>
+  </si>
+  <si>
+    <t>["-0.07566352","-0.004323049","-0.015865706","0.034648094","-0.020119509","0.06032828","0.06410743","7.259302E-4","-0.0015878556","0.0033715004","-0.065774515","0.00864949","-0.008954959","0.076320134","-0.038540475","-0.05361766","-0.030014155","-0.017676508","-0.04373548","-0.019394103","-0.012647137","0.0017882759","0.11562138","-0.044103663","-0.05205223","-0.014436679","-0.067934416","0.032691643","-0.027264882","-0.019094875","0.06961134","-0.035291545","0.013754102","-0.03245779","-0.048432924","0.044129804","-0.005202872","0.019623721","0.062888704","0.051839694","-0.08565132","-0.05048004","-0.06259172","0.103033535","0.024043791","0.10477546","-0.03265998","-0.007473534","0.03201332","-0.015531174","0.060744196","-0.0022441247","0.0035001994","0.021678094","0.09787405","-0.005708595","0.043989696","-0.09050847","0.002394422","-0.022681586","-0.06075113","-0.07840601","0.028890727","-0.00791425","-0.015884863","0.005532588","6.092424E-4","4.4456671E-4","-0.053240463","0.014984707","0.024095137","0.03708578","-0.015191631","-0.05589651","0.048230994","-0.06615776","0.009419089","0.086960614","-0.01761294","-0.025323346","0.13880736","0.07206514","0.02616389","0.018216996","0.0033945125","0.013274109","-0.0027344557","-0.019514907","0.04092651","0.12723535","0.021250451","0.00884863","0.15046683","-0.0636421","0.0025898279","-0.0010976831","-0.048701376","0.004100853","-0.041453924","-0.0025871026","0.039063618","-0.07293891","-0.029316708","-0.0315789","-0.033623334","0.056340463","-0.041657154","0.00967835","-0.019809287","-0.03849053","0.0073613278","-0.03866463","-0.09574885","-0.06810376","-0.042447153","0.022049585","-0.026996683","-0.02752464","0.0018980214","-0.07959897","0.039401434","0.0035090835","-0.020024084","-0.0153389545","-0.011892199","0.07598867","-0.021224936","-2.413551E-33","0.026729204","-0.023917489","-0.03006679","0.040154606","-0.116491504","0.09557162","-0.033389024","-0.027743079","-0.0031325647","0.035709422","-0.021131242","0.047010396","-0.045279194","-0.019692762","9.6025376E-4","0.034658708","0.0899864","0.047350243","-0.023979826","0.097850606","0.08804293","0.044668727","-0.03297489","-0.017627764","0.06583865","0.03797936","-0.048474915","0.0074100443","-0.033703595","-0.03444556","-0.079836614","-0.037147287","-0.04846677","0.03658042","0.026468243","-0.021553542","-0.0541686","-0.013633836","0.033168655","0.056550216","0.037094843","-0.019653928","-0.017856628","0.040972814","0.040077657","-0.044907484","0.025576398","0.06464775","0.05677014","-0.00974834","-0.03306001","0.013433137","-0.014387925","0.009827156","0.034027103","-0.019716613","-0.013093304","0.03789539","0.0347204","-0.015086601","0.031337965","-0.059581883","-0.060082644","0.02168765","0.03666229","-0.08955633","-5.8556657E-4","0.042788398","-0.013004242","0.02058514","-0.0110994","0.02402163","-0.009515664","0.07122771","-0.07405607","-0.009900824","-0.01832133","0.0063066604","-0.05631332","0.058861103","-0.02019843","0.07021918","0.06709047","0.056724504","-0.007832047","0.02718817","0.020641223","0.021729833","-0.09366476","-0.0055702403","-0.119486876","-0.05115677","0.02666267","0.12043243","-0.030452058","-1.9171907E-33","0.040587947","0.012650154","0.0040551363","-0.010905078","-0.04922456","0.040790826","0.041355263","-0.05915846","-0.09172319","0.08039518","0.04333845","-0.020727344","-0.0017033673","-0.04550571","0.023271695","-0.04384829","-0.054651882","-0.0017415582","-0.11265648","-0.07301635","-0.03294342","0.0120712565","0.044246353","0.033765163","-0.063877285","-0.039809383","0.112126596","0.017137857","-0.03461993","0.0720245","-0.068206266","-0.08557395","-0.053325817","0.090355806","0.037118685","-0.008842792","0.0400008","-0.06987785","-0.07889183","0.06051949","0.005615173","0.12381546","0.035321165","0.0036869238","-0.024255158","0.015230784","-0.083862744","0.043865502","-0.016395036","-0.03263895","-0.07741038","0.012914054","-0.022747422","-0.0023722795","0.0012262248","0.08492221","-0.02615385","-0.033684086","0.10472357","-0.009500146","0.052144412","-0.063627206","0.065045156","0.017723616","-0.09420179","0.024407998","0.040772673","0.095829755","0.042357564","0.05288335","0.03692249","-0.06303643","-0.013223988","-0.0020484992","-0.038734365","-0.0060211187","-0.043075733","-0.010857239","0.03994718","0.08130685","0.030594254","-0.034843966","-0.06453205","-0.0036201053","-0.010026225","0.019824628","0.031860635","-0.01482231","0.06533617","-0.1093886","-0.018988462","-0.019553365","-0.10713714","0.05833987","-0.04962571","-4.220716E-8","0.026172403","-0.020108096","0.04133973","-0.0070557804","-0.024795296","-0.08816621","-0.0150845125","-0.20592749","-0.043386173","0.024576237","0.034155708","-0.007559434","-0.03258894","-0.12339452","0.062116113","-0.039030477","0.013126828","0.09988811","-0.014001247","-0.0054759323","-0.012302189","-0.021919252","-0.027177604","-0.031750854","-0.018624656","-0.018555002","0.010003012","0.062231563","0.010288735","0.04387932","0.0018490687","-0.029908849","-0.050804496","-0.010567664","0.06015113","0.0747319","-0.005432746","-0.016102107","0.053034347","0.005761724","-0.044028927","0.0011432018","0.0432629","0.0577702","-0.11021657","0.005810062","-0.0021941352","-0.06536308","-0.017246097","-0.0038235672","0.05814394","0.086609825","-0.005267034","0.10996278","-0.032099344","0.09124527","0.04091188","-0.10913058","-0.09578104","-0.0025204802","-0.12236899","-0.022914713","-0.0035611368","-0.01626888"]</t>
+  </si>
+  <si>
+    <t>NK-6SmuUFKBZfVpUMXrSmJf4h</t>
+  </si>
+  <si>
+    <t>Behrouz Kamalian</t>
+  </si>
+  <si>
+    <t>. Kamalian’s “Ashiyaneh” organisation’s work has assisted the regime’s crackdown against the opposition, which has involved numerous serious human rights violations.</t>
+  </si>
+  <si>
+    <t>["-0.08657417","0.07669684","-0.075445056","0.015441699","-0.023227334","0.051820986","-0.017821442","-0.07092822","-0.10545142","0.012411143","0.0017524316","0.06959546","0.05717346","-0.035136234","0.040291447","0.04119747","-0.034416325","0.0630254","-0.011370749","-0.03246024","-0.047772616","0.017623058","0.08135627","0.017931677","-0.1091739","-0.021136243","0.012374224","-0.046035144","0.040608678","-0.055470694","0.019187076","0.042509515","-0.024518287","0.0043454478","0.0018641815","0.04640087","-0.031681884","0.007775517","-0.01055981","-0.06673919","0.08146373","-0.055199806","0.010996416","-0.090654634","0.011505221","-0.04270374","-0.0044330647","0.07455478","0.03934903","-0.026143346","-0.0069226753","0.0040558856","0.0044619604","0.02499591","-0.018859109","-0.15290307","0.0024830722","-0.004856253","0.043001685","-0.037952192","0.07425176","0.055826444","-0.052647505","-0.0044291127","0.018826306","-0.05112948","0.05706381","-0.034445062","-0.029056516","0.06868305","0.02158948","-0.051070996","0.055801284","0.021957897","-0.06997387","-0.050675534","0.024202785","0.008456215","0.0144228935","-0.05698706","0.09105204","-0.03667073","0.04677537","0.0664068","0.027663885","0.059571616","-0.012597803","0.03650645","0.09654802","-0.01906991","0.005897132","0.022345915","0.15577656","-0.031467162","0.058257557","-0.06667013","0.062463522","0.045009553","-0.09593986","0.07250842","-0.006935403","-0.002941925","-0.10658232","-0.06926992","-0.017017353","-0.04724525","0.011136336","-0.081062384","-0.09995781","0.025682976","-0.025841393","-0.025448287","-0.04162513","-0.078616336","0.04851924","-0.017369507","0.02831319","-0.032047372","-0.10801801","0.021969985","-0.045835257","0.058555167","-0.017094994","0.0059667816","0.07015348","-0.03464641","-0.12892005","-4.3510585E-33","-0.020797025","-0.0047668694","0.047030095","-0.020953393","-0.06185453","0.017095894","-0.08820136","-0.043407824","0.009376484","0.051882938","0.022077905","-0.009387461","0.049041476","-0.03455158","0.014359474","-0.007388567","-0.038565315","0.01968238","-0.014375149","0.06813026","0.02349205","0.0033179177","-0.042906705","0.082602136","0.0026216926","0.0515854","0.011987342","-0.0030111603","0.0049350085","0.031916812","0.017781325","0.032628953","-0.095501","-0.025946416","0.013315251","0.026092086","-0.03583842","-0.020654237","-0.0063662967","0.00726446","-0.07232099","0.030400263","0.034362365","-0.045417078","0.053686455","0.06140625","-0.05098851","-0.017532662","0.0292246","0.02791029","-0.009877664","0.050216947","-0.039086964","-0.06086824","-0.054455865","-0.024079112","-0.007757104","0.025624104","0.07685352","0.0033754662","-0.016353736","-0.07953104","-0.106890544","0.07489272","-0.024006266","0.009101544","-0.041966107","-0.023821346","0.034555417","-0.031339515","-0.011632841","-0.027965266","0.0014134677","0.07401974","-0.084445715","-0.0074017933","0.024511019","0.009608917","-0.031893574","0.08389834","-0.01942105","-0.01742521","0.073376656","-0.037988033","0.0023167026","-0.009165496","-0.032582704","-0.101056665","0.06775984","0.02106278","-0.035748415","-0.011497638","0.015057574","0.060019553","-0.027779078","1.15526575E-33","-0.0028599976","-0.041971684","-0.0753439","-0.0010174185","0.13041441","0.024689618","-0.039459668","0.063858315","0.0046488424","0.016618462","0.031472657","-0.031510778","-0.021150986","0.089669","0.035365913","-0.043550733","0.09738383","-0.022459384","0.025424145","0.0644912","-0.09604897","0.02858294","-0.008613681","-0.001135651","0.00560934","0.05155425","0.057723902","-0.051818494","0.039320476","0.087160625","-0.0038640136","-0.015017195","-0.11974312","0.100378476","0.03759379","0.001441856","0.008177119","0.053634502","0.015914688","-0.025216475","-0.011345349","0.009414938","-0.04866757","0.031406","-0.03190011","0.006950458","-0.005854934","0.028991062","-0.068571806","-0.15618055","0.065311536","0.021228928","0.09153482","0.02123127","0.03970252","0.028481534","-0.076531366","-0.04033701","0.056989845","0.030443534","0.011352568","-0.0016264254","-0.09046406","0.07636021","-0.031333324","0.017765203","0.0213086","-0.111089215","0.07846479","-0.0065698004","-0.024285553","-0.091875985","-0.016620282","0.06768078","0.0324023","0.03435045","-0.061858907","-7.000986E-4","-0.029514654","-0.0043619587","0.067525804","-0.096713334","-0.08512952","0.0021835892","0.037361164","0.07236188","0.018350145","-0.04230407","0.05605532","-0.057663973","-0.02928602","-0.018480577","-0.04412603","0.07638078","0.055483367","-2.9358443E-8","0.012599902","-0.038286973","0.018723939","0.016840119","-0.010202568","-0.011221858","-0.06769534","-0.05014574","0.03194022","0.06701261","0.05792114","0.025061276","0.034429993","0.02044045","-0.04674076","-0.020480508","0.04282876","-0.010635599","-0.0011776098","-0.036297373","-0.011649603","-0.004627506","0.031251706","-0.14010203","-0.026946276","0.035622768","-0.06424708","-0.06290646","-0.07445538","0.06549284","0.013184934","0.046616234","-0.05264532","-0.01874286","-0.017644065","0.0581969","0.042985868","-0.04799384","0.07527316","-0.10808303","0.025431523","0.097788595","0.07988339","0.01823579","-0.007379705","-0.04176564","0.028105285","-0.022288086","0.03425222","-0.13348217","-0.0015316868","0.026920393","0.04294333","-0.005379926","0.05632714","0.034020085","0.025558049","0.0015440353","-0.067113385","0.030468686","0.08973004","-0.07443082","0.06096027","-0.005548921"]</t>
+  </si>
+  <si>
+    <t>NK-6VnYSbttwkF7pUvd8v4ieb</t>
+  </si>
+  <si>
+    <t>Igor Grigoryan</t>
+  </si>
+  <si>
+    <t>Entity Name: Igor Grigoryan | Type: Person | Jurisdiction: us | Risk Context: 1128a4</t>
+  </si>
+  <si>
+    <t>["-0.07077071","0.00811173","-0.09824126","-0.04213452","-0.0021710533","0.017113786","0.1222802","0.031722873","-0.008355722","-0.044805475","-0.05823989","-0.07025264","-0.045514066","0.055500012","-0.043287225","0.075193696","0.013621859","0.026358621","-0.0070005544","-0.024796339","0.02172581","-0.024987321","0.07496611","-0.027427966","0.028281897","-0.09430328","-0.006879764","0.015238748","0.022636192","-0.017726863","0.04636135","0.059149552","0.047882866","0.08172089","0.054648116","0.104798965","-0.057988368","0.025712516","-0.027841317","0.01591672","2.7851426E-4","0.033456","-0.02004582","0.07388613","-0.019267386","-0.031377714","-0.026718693","-0.0037463128","-0.046979364","0.07137696","-0.107678175","-0.078331314","-0.0019843716","-0.014197878","0.06817294","0.0048030373","-0.024895113","-0.01766513","-0.045590818","-0.0016135903","0.10431822","-0.045257464","-0.045666575","-0.008556394","-0.014794249","0.023279138","0.04643165","0.00549558","-0.027552335","-0.057907112","0.13161129","-0.021498429","-0.14784522","0.003610093","-0.048959654","-0.045731805","0.02073042","0.068032645","0.06472946","-0.046219457","0.015903952","0.042068075","0.09526424","-0.015215996","-0.035004426","0.06967041","0.035889193","-0.009476192","0.033394407","0.027993437","-0.0072546406","-0.06226007","0.20342825","0.0195866","-0.0152775375","0.04805628","0.058469363","-0.046174403","-0.028387336","0.089860275","-0.021318948","-0.0625674","-0.019873738","0.051708687","-0.06045639","0.0010556914","-0.027552538","0.056511674","-0.054585226","0.026515769","-0.042364474","0.09856471","-0.020961585","0.047094565","0.0012456727","-0.0031522955","-0.09606484","0.068917826","0.07557439","-0.011571693","0.016372558","0.062399935","-0.14250204","-0.017831918","-0.07252727","0.035951253","0.011075072","-2.4795207E-34","0.09883641","0.011745406","0.034017503","0.036080133","-0.031828944","0.02382777","0.0059560654","0.030857686","-0.07021411","0.006804396","-0.033150125","-0.0032195149","-0.0032103679","-0.03675869","-0.060404804","0.059437294","-0.030419722","0.05361191","0.041126978","0.01737226","0.03717009","-0.0028650947","-0.08256341","-0.023526823","-0.017918356","0.011101723","-0.041308895","-0.0539432","0.021755453","0.04551034","-0.034746736","4.94915E-4","0.030277856","0.048118792","0.08217796","0.009475667","-0.028980682","-0.082441784","-0.0555723","0.029079197","0.03515578","0.056519732","-0.060315847","0.04370158","0.025364079","-0.03707642","0.06092775","-0.020478455","0.0449732","0.012450994","-0.09056454","0.08544707","-0.04130397","-0.0041465256","-0.045779735","0.04017215","0.021789256","0.07112742","0.010269654","-0.100438386","0.021539835","0.017142102","-0.0047789975","0.009019256","0.062680274","-0.103077605","0.032328017","-0.025128758","0.059719346","-0.0637632","0.021116644","0.005897069","0.029059991","0.054176114","-0.042679578","-0.038098883","-0.048745647","-0.019427853","-0.06011941","0.055811517","-0.1602879","0.014332056","-0.041132126","0.0029695574","-0.031429347","0.045923356","0.014249774","-0.049337976","-0.050723996","0.06756003","-0.08376392","-0.015908694","-0.03457974","0.026619723","-0.041318916","-1.6862044E-33","-0.051824704","-0.0958881","-0.008452771","-0.047786422","0.03652437","-0.06031778","-0.025661869","0.045695465","0.017770719","0.07070091","0.0033717996","-0.047962412","0.048423305","-0.0051695816","-0.002549675","0.058760066","-0.044747297","-0.0061294795","-0.08805915","-0.020151721","0.0010247775","0.0076477644","-0.056996934","0.076006","-0.02335765","-0.013348809","0.04963372","-0.025688812","-0.03981239","-0.00426008","-0.054342743","-0.050200507","-0.13017035","0.08655528","-0.072675206","-0.057027794","0.07695799","-0.08273203","-0.046545617","-0.014289774","-0.013763932","0.06983526","-0.0066057495","0.086341016","-0.00644792","-0.021449594","0.02509659","-0.013400033","0.06686839","-0.075532414","0.0033517077","0.05566125","-0.01322258","-0.033067316","0.033314403","-0.03622863","0.085322365","-0.07392583","0.02254824","0.070424914","-0.006891428","0.07579118","-0.043954987","0.10189179","0.050562344","0.034548074","-0.12916005","0.051509958","0.015740441","-0.08862147","0.042753085","-0.07431783","-0.029329581","0.018555133","-0.052762967","-0.0060508116","0.01187401","0.018392274","-0.007803154","-0.03842522","0.108818896","-0.03911156","-0.008487691","0.060305625","0.057735763","-0.021731481","0.08391949","0.021752914","0.06559484","0.0320564","-0.0042547844","0.018707654","-0.06675785","-0.002328606","-0.03693181","-2.7951826E-8","-0.0058154236","0.041683","-0.01343848","0.0019489352","0.018607643","-0.00937871","-0.025166824","0.016432732","-0.03990224","0.0056278273","-0.03681572","0.02238688","-0.02242635","0.022388242","0.07883146","-0.08329243","-0.0076920167","0.07009362","-0.014135967","0.025554882","0.0037312694","0.019159852","0.0023432395","-0.08597043","-0.008801044","-0.02429821","0.0070173545","0.005891238","0.030271903","0.03108677","-0.074418895","0.09318427","-0.0027104262","0.061524827","0.012347255","0.07188783","0.077549614","-0.021469926","-0.010491998","-0.03739322","-0.006349669","0.019738149","0.02232051","0.038677257","-0.005985551","0.029601693","-0.017830145","-0.078551486","0.09475083","-0.021615172","-0.029399194","-0.09310249","0.011386422","0.080109976","-0.051912673","-0.0070743193","-0.027101394","-0.014722806","-0.03326565","-0.045623124","0.02149905","-0.054960433","-0.0114692105","-0.033531174"]</t>
+  </si>
+  <si>
+    <t>NK-6YsZ3to4zu3yK6KYZrxAGX</t>
+  </si>
+  <si>
+    <t>Sandra Milena HERNANDEZ ARBOLEDA</t>
+  </si>
+  <si>
+    <t>Entity Name: Sandra Milena HERNANDEZ ARBOLEDA | Type: Person | Jurisdiction: co | Risk Context: Unknown</t>
+  </si>
+  <si>
+    <t>["-0.03140795","0.0075956923","-0.08754027","0.011814601","-0.0059171994","0.031588938","0.03357537","-0.008121302","0.031027334","-0.020474143","0.079530984","-0.10423262","-0.019101791","-0.02429749","-0.03722124","0.103934996","0.016391814","0.02583452","-0.015540728","0.051173124","0.014493922","0.00844767","-0.047383472","0.0031316876","-6.2234595E-4","0.010971436","0.01206533","0.051641848","-0.026150791","9.855888E-4","-0.033734415","0.030869385","0.017010279","0.09661645","0.049295336","-0.014234902","-0.028007513","0.019880068","0.042169765","-0.015723933","-0.04906968","-0.105280675","0.0055192825","0.032635506","-0.05980787","-0.059031896","-0.0074588056","0.014909361","0.012742779","-0.008376664","-0.06971955","-0.079003125","-0.015402193","0.015969282","-0.026574848","-0.027844347","-0.016360117","0.064022064","-0.07160924","0.018474173","0.0874691","0.02165048","-0.042240165","0.019093342","-0.045653407","-0.042959787","0.037386","0.023114072","0.07514695","-0.0828894","0.1340958","-0.006224482","-0.10098968","0.062017985","0.018996295","0.015509073","0.06768397","0.04627139","0.046835385","-0.035912294","-0.0065863123","0.011702266","0.02227619","-0.057432692","-0.029670538","0.072446674","-0.041288108","-0.019773403","0.030920213","0.019323662","-0.07557112","-0.06772868","0.13129577","-0.04368053","0.0127268415","-0.022203736","0.0025205547","-0.062278185","-0.028758377","0.07889351","-0.062315565","0.07214221","-0.02919689","0.01764082","-0.007506377","0.004513121","0.023232648","0.005231576","-0.048191622","0.076611266","-0.026791226","0.061883472","-0.06872724","-0.011631316","0.01927859","0.005274459","-0.03718611","-0.001096342","0.02002178","-0.056490656","-0.013956915","-0.01753676","-0.13729726","-0.058344204","-0.046777323","0.01119911","0.01777511","-1.1451687E-33","0.06043298","0.054388452","0.034516398","0.054963514","-0.018917738","0.054411244","-0.033678606","-0.00908077","-0.030214727","0.015885776","-0.049984805","-0.0039336756","0.024749776","-0.09604525","-0.019884504","0.06375403","-0.02778824","0.030788109","0.0030281937","0.09202954","0.05251079","-0.030176222","-0.035401475","0.01131189","-0.022219786","-0.0283042","0.03776803","-0.049536984","0.00822597","0.057756744","-0.0835071","0.020739378","0.060359694","-0.034983847","0.13138054","0.03842593","0.005750063","-0.03747294","-0.0330917","-0.003302453","-0.008932819","0.028630268","-0.0017627814","0.09045044","-0.056377552","2.3858565E-5","0.041687317","0.0058006477","-0.0021985967","-0.02619475","-0.07630038","0.03311962","-0.045802608","0.025566775","-0.02018509","-0.014575339","-0.012501885","0.06329529","-0.009203025","-0.09061122","0.047395702","0.02273812","-0.034647673","0.041204285","-0.0017969807","-0.090108514","0.04567715","-0.036663625","0.08660304","-0.06602228","0.015744928","0.048641946","0.065644026","0.0517683","-0.06731247","0.017550768","0.050823133","-0.0138267875","-0.0033604722","0.064700104","-0.07509023","-0.01691731","0.020777427","0.06213573","-0.045879073","0.05242162","0.054026548","-0.046229016","-0.09928604","0.024872003","0.012542828","0.0835632","0.024760716","-0.002048244","-0.023599118","-1.3746175E-33","-0.02573056","-0.10241973","0.0060310387","-0.119930536","0.07592629","-0.037369348","-0.02048222","-0.030458497","-0.03190301","-0.034131594","-0.033090867","-0.16472095","0.02151404","-0.019872054","0.047401696","0.07032276","-0.027166499","-0.026654469","-0.06399865","0.042104464","-0.004591279","-0.024766147","-0.049009357","0.068233594","0.02191751","-0.049081583","0.033284627","-0.004018155","-0.10631321","-0.026521143","0.030730698","-0.019254517","-0.042957537","0.024340045","-0.10150945","0.009418402","0.06524687","-0.06722436","-0.0052151773","-0.028093372","0.0039876485","0.056997802","-0.06142073","0.036889095","-0.060746767","0.03558298","0.05292106","-0.066123895","0.041966505","-0.11683702","0.041980132","0.0036936277","-0.061102696","0.014429771","0.057703495","-2.0367425E-4","0.04914408","-0.05397691","0.04757651","0.054419782","-0.011829121","0.050390802","-0.112480275","0.12480352","0.055399783","-0.060595","-0.061470456","-0.0034252945","-0.06402851","-0.056291394","0.03243768","-0.0657657","-0.060326025","0.04973646","-0.05003111","-0.0692437","0.0069756443","-0.045106266","-0.06013871","0.012384529","0.07500119","-0.051795136","-0.04139719","0.049066648","0.070540614","0.0483075","0.052300304","0.012736455","0.016009474","0.061234385","-0.033878796","0.0038262666","-0.10744665","-0.041898973","-0.08160289","-2.4809195E-8","0.04970748","0.023549648","-0.011821945","-0.002556153","0.0013144375","0.053490028","-0.0113628665","0.05364624","-0.020329062","0.02420035","-0.051213223","0.045816205","0.0075048925","-0.018769037","0.04482291","-0.0838597","0.028579492","0.1404459","0.018814797","0.080096476","-0.003540125","0.029374542","-0.06259206","-0.13827704","0.02824584","-0.006274993","-0.02382177","0.044322215","0.051944043","-0.03545557","-0.03049754","0.08711487","0.010780541","0.010257266","-0.026434746","0.06701146","0.13263267","-0.02064787","-0.11433347","-0.01323215","0.034121867","0.07709064","-0.05909909","0.05256762","0.06215172","0.032048345","0.039079327","-0.055824902","0.068777084","-0.048921946","-0.011825121","-0.041384477","0.07288227","0.07241301","-0.003536486","-0.0057189073","-0.009856895","0.050703175","-0.0027138407","-0.021988744","0.052644834","-0.032704674","-0.0062428047","0.01667462"]</t>
+  </si>
+  <si>
+    <t>NK-6buiRsQBLAfzYAaPjQQ3qp</t>
+  </si>
+  <si>
+    <t>Limited Liability Company responsibility "Market Special Depository"</t>
+  </si>
+  <si>
+    <t>Entity Name: Limited Liability Company responsibility "Market Special Depository" | Type: Company | Jurisdiction: ru | Risk Context: (also SBERBANK FUND ADMINISTRATION LIMITED LIABILITY COMPANY) Disqualified (also LIMITED LIABILITY COMPANY MARKET FUND ADMINISTRATION)</t>
+  </si>
+  <si>
+    <t>["0.011015033","-0.062664285","-0.109242015","0.04859616","0.047566805","0.018424336","0.09616475","0.028229894","0.05803326","-0.06372869","-0.0037617844","-0.025106894","0.0024960004","0.015943963","9.0151705E-4","-0.025634462","0.019934699","0.0023639086","0.016630588","-0.004350879","0.009148829","-0.012887214","0.009295912","0.026451446","-0.018973192","-0.0614077","-0.014591377","0.06217308","-0.0031054728","-0.08375742","0.012756238","0.017958663","0.052463602","-0.027472608","0.09680007","0.063103236","-0.11305175","0.03406993","-0.031637818","-0.014898656","-0.025224708","-0.071182184","-0.011504093","-0.049936038","-0.024376428","-0.023400813","-0.00381034","0.022495195","0.030542372","0.03851291","0.0051824395","-0.05972092","-0.006414759","0.045846913","-0.03119816","-0.018405218","-0.027672436","-0.022158895","-0.032246046","-0.019874861","0.0040360643","0.04420312","0.053944807","0.03436189","-0.014703206","0.033321247","-0.043716494","0.08800343","0.008594022","-0.09761057","0.07922638","-0.062676065","-0.11223464","0.0038977414","-0.034398135","-0.0157684","-0.02086195","0.111502625","0.05394172","-0.0515994","0.013434037","2.770799E-4","0.021861412","-0.041683387","-0.08672914","0.039086312","0.033749823","-0.013583477","0.07368887","0.025362521","-0.015478322","-0.022772156","0.11224738","-0.0110027045","-0.021108398","-0.041000802","0.016236061","-0.031761494","-0.019017592","0.03554297","0.033820137","-0.020597039","-0.04759197","0.053325128","-0.030324921","-0.037630383","-0.020654356","0.0057850764","0.030531708","-0.04163009","0.018062716","0.10115827","-0.010456095","-0.03691601","-0.021247426","-0.041744705","-0.1342221","0.005769942","0.060415402","-0.08571651","0.038313493","0.094292395","-0.06592319","-0.11888141","-0.07823639","0.009880863","-0.036489956","1.5666452E-33","0.015368386","0.06426933","0.024148298","-0.028133716","-0.017477248","0.0296876","0.0036887894","0.031015918","-0.08858687","0.035353243","0.041668437","-0.04351122","0.027227178","-0.06376505","0.00988879","0.033592","0.0021890418","0.06698508","0.10901168","0.0012866615","0.0065147886","0.048442654","-0.03450653","-0.011837895","0.032668825","-0.013043945","0.036385898","-0.0647139","0.014218267","0.03617005","0.061057817","-0.033498082","0.0447593","0.038061455","0.06347894","-0.025168983","-0.035925735","-0.050005108","-0.085083395","-0.006671187","0.005081433","-0.004255841","-0.01522931","0.088804714","-0.02158781","0.026124625","0.051784687","0.039419267","0.038451824","0.048857965","-0.06366822","-0.03270135","-0.06985918","0.010033588","0.05275598","0.021897357","-0.028251989","0.011525211","-0.059035096","-0.015545659","0.055385053","-0.0035895675","-0.115546405","-0.02765311","-0.0028184266","-0.011285757","0.034537025","-0.05527501","0.051129445","-0.016096475","-0.014935561","0.015196772","0.121895336","0.09611862","-0.028070644","-0.06076611","-0.01554773","0.07732526","-0.011589273","0.033650976","-0.12241929","-0.01535934","-0.005586469","0.093426235","-0.06704727","0.034929667","0.051152956","-0.051120624","-0.058019467","-0.052985754","-0.027464312","0.011461449","-0.015960457","0.08100017","-0.054035112","-2.7245452E-33","-0.025092658","-0.08415113","-0.0043690335","-0.03065274","-0.0029938137","-0.028257977","0.071395345","-0.012444193","0.047096457","0.07146962","-0.057927605","-0.0148351025","0.012560649","-0.01951786","-0.036491048","-0.024520142","0.009733029","0.0038391203","-0.05790919","0.055272684","0.02703943","0.039329663","0.0686383","0.04240114","0.0011852222","-0.018728238","0.012611933","-0.01252545","-0.070225924","0.03562942","0.019678323","0.010765881","-0.05851214","0.032769836","-0.14327483","-0.117762536","0.040733296","-0.08189793","-0.07865523","-0.010381911","0.011893217","0.05203152","-0.02303491","0.051018104","0.022794848","-0.045400612","-0.012401509","-0.029204627","0.14736255","-0.088478684","-0.109640665","-0.077548005","5.3722726E-4","0.044999752","0.0055112005","-0.00444043","0.029478153","-0.004983908","0.019288639","0.019537188","0.09557688","0.08743606","0.062227823","0.13956556","0.035939727","-0.02306189","-0.067621514","-0.040599547","0.021073468","-0.09170387","0.09037216","-0.055987053","0.039970208","0.037238143","0.027120858","-0.01412712","-0.03818413","-0.051810183","-0.050628304","-0.008166003","0.06607779","0.022693763","-0.020164626","0.042840403","0.055434145","-0.03548901","0.06748344","-0.05672462","0.042650715","-0.03696524","0.01854201","-0.015527849","0.0054900534","0.071087345","-0.011130162","-2.9700644E-8","-0.043878734","0.005259645","-0.032363698","-0.04741876","0.06298973","-0.10351136","-0.012361425","-0.057143223","-0.0039962665","0.06447939","-0.02273085","-0.027124556","-0.07441617","-0.04436132","0.007076082","-0.025463523","-0.02501774","0.11751661","0.0046354006","0.04691583","0.031970926","0.023297679","-0.004318533","-0.08685247","0.012455919","-0.06464456","0.052150737","-0.026976397","0.13248964","-0.048261475","-0.017324388","0.07991594","0.053640097","-0.033376288","-0.027938187","0.08467142","0.043130603","0.057997815","-0.008552578","0.0989956","-0.09250976","-0.0488556","0.054301307","2.9587364E-4","0.022385232","0.05292098","-0.09794088","0.049176347","0.07570653","-0.06172118","0.012743422","-0.0612417","0.047298595","0.07904218","-0.02896476","-0.005481706","-0.033983544","-0.011481109","-0.033651248","-0.0452292","0.0674401","-0.009029085","0.062489636","0.03351767"]</t>
+  </si>
+  <si>
+    <t>NK-6eTqRYWz5x8kszhPbu74fc</t>
+  </si>
+  <si>
+    <t>OLUWAFEMI CHARLES IGBERASE</t>
+  </si>
+  <si>
+    <t>Entity Name: OLUWAFEMI CHARLES IGBERASE | Type: Person | Jurisdiction: us | Risk Context: 1128a3</t>
+  </si>
+  <si>
+    <t>["-0.037491232","0.04313853","-0.034260906","0.02603824","0.014244231","0.020755466","0.089017846","0.020606281","0.036498275","-0.015112795","0.004506533","-0.09740327","0.012877036","-0.05200828","-0.06533711","0.11851212","0.030951407","0.043654475","-0.038604382","-0.012796549","0.037413884","0.045898713","0.0205739","-0.06829861","-0.034844436","-0.08704403","-0.036314584","-0.0115544405","-0.011600882","-0.071546465","0.09005746","-0.015171259","0.040614035","0.061457083","0.076466165","0.020252671","-0.036050823","0.0033271094","0.010871722","0.026410444","0.020695196","-0.058583975","0.03514309","0.05076367","-0.0068347785","-0.017997477","-0.030432208","-0.0034318962","0.0024961333","0.011062615","-0.108946726","-0.06751866","-0.04425125","0.038913634","0.011789082","-0.016467929","-0.016810559","0.019547544","-0.0027571502","0.019556658","0.064161904","0.069098935","0.049716003","0.03428078","0.015311206","-0.0021463397","0.041085687","0.04677843","6.92145E-4","-0.062255494","0.09469845","0.0012671485","-0.14384785","0.06484772","-0.0016618313","0.009178724","-0.023845365","0.09965414","0.0497803","-0.0377224","-0.0272348","-0.038057208","0.072323605","-0.052941937","-0.0409336","-0.0018702849","-0.042862933","-0.0066165724","0.030582262","0.027985416","-0.003246429","-0.06774671","0.097886056","0.018921737","0.03327058","-0.077457","0.03852295","0.023702784","-0.044943843","0.060203817","-0.048986103","0.007006122","-0.0052046413","0.07248905","-0.1006309","-0.048430007","5.516083E-4","0.02223893","0.0054005906","0.014252328","-0.01143028","-0.0060589244","-0.04437486","-0.014461154","0.017434474","-0.019210398","-0.07763365","0.040345408","0.06678626","-0.08808256","-0.0065717874","0.030444553","-0.07145531","-0.052761555","-0.21132106","0.052561887","0.047661666","1.5967238E-33","0.07314919","0.061739553","0.027493097","0.04901169","-0.041013066","0.011059486","-0.013672279","-0.004784951","-0.087386735","0.02527076","-0.04653286","-0.01323317","-0.018019129","-0.04212545","-0.028266478","0.07222918","-0.071498446","0.02931269","0.0042430726","0.030462371","0.07614769","0.017922318","-0.03920344","0.018430576","0.02251513","-0.011368803","-0.01265646","-0.08403404","0.027710186","0.06307265","0.0472282","0.017878102","-0.027243035","-0.07313955","0.04336045","-3.6770225E-4","-0.015618978","-0.08359777","-0.048363008","-0.05101909","0.011342436","0.032597225","0.01971081","0.058486283","-0.00436936","0.016315524","0.07586283","0.013865587","0.09065175","-0.009683257","-0.048963003","-0.0030531224","-0.07983877","-0.030885734","-0.0035456344","0.014291054","0.011463358","0.12928341","0.053217914","-0.032299325","0.037100106","0.058327626","-0.031575248","0.016456742","-0.0081671225","-0.09220125","0.044749863","-0.017175497","-0.034723453","-0.10769734","-2.8610858E-4","0.002464412","0.01775386","0.017575445","-0.056006566","-0.0072268136","-0.066085346","-0.038438756","-0.051909443","-0.023740992","-0.0774144","0.0054479158","0.0018675383","0.019775726","0.031357836","0.046196908","0.02866545","-0.03092278","-0.06304288","0.094485804","-0.01971833","0.032300852","-0.030716797","0.04383703","-0.038273256","-3.0753691E-33","-0.09517406","-0.08951637","-0.017459432","-0.0018742313","0.03968966","-0.07493569","0.029675769","0.059619937","0.058199577","-0.0108544985","0.010731797","-0.07357972","0.07093454","0.04325077","0.016110253","-0.013907372","-0.05919772","0.0043209004","-0.07155487","0.043116063","-0.0061419653","-0.05305269","-0.0077575524","0.015545188","-0.030442499","0.061298776","0.045122772","-0.035412397","-0.019431371","-0.012161721","-0.0152091235","0.07380021","-0.10596912","0.07203566","-0.110058956","-0.046292473","0.053605955","-0.12747514","-0.0024161525","-0.014497226","-0.031200953","0.104321785","-0.03866533","-0.002555275","-0.025521878","0.038932633","-0.03127117","0.025052762","0.09013209","-0.0054042153","0.010504437","0.047473073","-0.034011178","0.01762816","0.03560717","-0.015867706","0.033212204","-0.08541946","0.03224778","-0.016466519","-0.006844109","0.098601915","0.017361049","0.06705787","0.060012076","0.050986715","-0.069727264","0.032521848","0.030586338","-0.103819646","0.049224317","-0.14369087","-0.046334293","-0.04360394","0.018618912","0.007566157","-0.0053186417","0.0041764984","-0.041306697","-0.033643804","0.043444525","0.0096489005","0.046960294","-0.020803297","0.04821767","0.0062114536","0.06559188","0.018076729","0.07461185","0.04978119","-0.04611913","0.016931063","-0.072948754","-0.005284363","-0.07492102","-2.881337E-8","-0.028988205","-0.009794225","0.06242962","0.011775095","0.006976031","-0.05072483","-0.022933772","0.011876059","-0.043063752","0.07951597","-0.022829931","0.027554657","-0.0036546923","-0.045661855","0.024402095","-0.080107406","0.003951868","0.03238688","0.044237718","0.055995453","-0.0030835122","-0.0036050791","0.07340945","-0.09177561","0.05352977","-0.03273719","0.0029456164","-0.009140203","0.05574135","-0.03960185","-0.046369836","0.10611245","-0.010817923","0.047741655","-0.07803887","0.038395934","0.03616595","-0.030695569","-0.044414543","-0.06172283","0.029210405","0.03634383","0.026793022","0.017229399","0.09635279","0.04315199","0.019877197","0.017283542","0.019570403","-0.048777632","-0.14614333","-0.12774184","0.06433874","0.09092023","-0.047649357","-0.05606675","-0.014091564","0.06879985","0.033647537","-0.057822663","0.033235885","-0.11106091","0.038331248","-0.015594172"]</t>
+  </si>
+  <si>
+    <t>NK-6j8MMQRaDrzFm4jSdFmqzU</t>
+  </si>
+  <si>
+    <t>ERSİN KARAOĞLAN</t>
+  </si>
+  <si>
+    <t>Entity Name: ERSİN KARAOĞLAN | Type: Person | Jurisdiction: tr | Risk Context: FETÖ/PDY</t>
+  </si>
+  <si>
+    <t>["-0.022533594","0.021388864","-0.1060253","0.01578684","-0.006305818","-0.02835726","0.12908906","0.04018843","0.042931776","-0.039027575","0.0868128","-0.0748121","0.02075748","-0.022737809","0.016249152","0.021885257","-0.0075244303","0.05836178","-0.019823097","-3.303912E-4","0.057337362","0.04039912","0.046741784","-0.012125618","-0.056520026","-0.070202954","0.014480011","0.033251077","-5.823365E-4","-0.10501638","-0.005145009","0.059828203","0.07730191","0.08952975","0.022499187","0.05586165","-0.05483406","0.044520386","-0.009530995","0.0017491244","-0.007087087","-0.071180716","0.024174472","-0.01238161","-0.053030994","-0.077775545","-0.050512675","0.015981687","-0.04229131","0.034335654","-0.050221786","-0.01855459","-0.01949966","0.063948065","-0.014435887","0.019484704","-0.012679326","-0.008836565","-0.056266516","-0.020865515","0.030007733","0.07047216","-0.038884003","-0.019458743","-0.037038844","0.031065544","0.035610676","-0.016275879","0.012766683","-0.02440425","0.032265406","-0.096657656","-0.093890734","0.053742968","0.024435915","-0.0070057395","0.051350277","0.028531209","0.068665825","-0.08198115","-0.016499754","0.079794765","0.07047094","-0.05596808","-0.0017345287","0.112673864","-0.035274934","-0.044645168","-0.018034633","0.0038099047","0.01168392","-0.11214786","0.12219853","0.009449716","0.016591903","-0.008809119","0.04065682","-0.06472978","0.024891067","0.07229775","-0.026921265","0.02176597","-0.011553966","0.033651404","-0.04849034","-0.031029478","-0.008577972","-0.026999388","-0.04028162","-0.03123083","0.0010477065","0.07364105","-0.032677338","-0.06547369","0.017394174","-0.03830025","-0.09958589","0.019777022","0.08510425","-0.055022825","-0.019830452","0.027250618","-0.109484546","-0.013649651","-0.076928966","0.0022058554","-0.0029862896","-5.3749865E-34","0.06146341","0.09072584","0.034457676","0.0037442562","-0.054233827","0.048422307","-0.040536053","-0.07819523","-0.01702429","0.036035378","-0.06154358","-0.0112933","-0.030687502","-0.06904871","-5.075987E-5","0.061922055","-0.045421127","0.06543457","0.009621854","0.023086194","0.02746898","0.057205364","-0.03468598","-0.09454809","0.041345086","0.06947338","-0.006541653","-0.0538759","0.01119692","0.08361492","0.008949932","-0.0064300834","0.038249157","0.024915209","0.04490991","0.03130676","-0.029221583","-0.029429968","-0.07039076","-0.0720725","-0.0075064464","0.060913216","-0.06990071","0.06474974","-0.04691056","-0.04240473","0.047684472","0.022747982","0.035089992","0.01355221","-0.06280491","-0.011927606","0.0024197726","0.011281114","0.030735426","0.021460777","0.039107583","0.0693073","0.07436769","-0.0022170444","0.052956924","0.031713694","0.012834157","-0.013476095","0.07875083","-0.06158482","-0.005617612","-0.035034955","0.080357775","-0.06774493","-0.0066936165","0.041147448","0.081198975","0.08936367","-0.027245117","-0.008752313","-0.02918773","-0.011241493","-0.054236557","0.07326879","-0.12501645","0.02675047","-0.046785563","0.057428353","0.0074148756","0.05418524","-0.0048528","-0.109825835","-0.121633984","0.035363022","-0.0387875","0.03752881","-0.041370567","0.052622903","0.0046611535","-1.1527853E-33","-0.0073906532","-0.06226997","-0.04156944","-0.036080804","0.029486336","-0.13753669","0.03143784","0.023380041","-0.01978942","0.044411365","-0.04830484","-0.114579","0.013819919","-0.04907548","0.08481863","0.03004502","-0.04393872","0.028074399","-0.03055652","0.14046524","-0.063917145","-0.023955295","-0.07218778","0.10942435","0.0012158501","0.024085933","0.0036183356","-0.053494003","-0.10313721","-0.069363706","-0.005859839","0.005244873","-0.07938969","0.015934298","-0.13923259","-0.107630074","0.00375912","-0.07587261","0.017956577","-0.034327686","0.040736154","0.097813606","0.0036012083","0.036081385","0.0062227957","-0.007933947","0.035404887","-0.02379317","0.051800065","-0.089291565","0.035359144","0.01379229","-0.039826173","0.0027992656","0.0013609543","0.0063456246","0.06050435","-0.031615514","-0.027915495","0.027811155","-0.026073398","0.07095504","-0.0049375547","0.13547689","0.08094715","-0.0485332","-0.048217937","-0.0015452057","-7.313278E-4","-0.09753209","0.04499699","-0.062027868","-0.050346006","0.020244941","0.022097318","-0.069854975","-0.056960076","-0.057159126","-0.029507663","-0.01976848","0.04071426","-0.023448298","-0.04499911","0.061144117","0.032357574","0.036912676","0.0338576","0.025958378","0.030619023","0.04354785","4.910747E-4","0.019510875","-0.073721394","0.022090623","-0.02852086","-2.8120311E-8","-0.035645742","0.029669568","0.0018179776","-0.033820823","-8.46794E-5","-0.027662843","-0.030757593","0.010403626","-0.018381001","0.026143687","-0.034545783","0.0754082","-0.05752146","-0.03977732","0.06504948","-0.03846056","-0.009235392","0.1348458","0.0133797815","0.015105713","0.030544458","0.025895165","0.017619105","-0.10988212","0.03315181","0.0017957767","0.0041368557","0.0217958","0.08484976","-0.037386592","0.04114135","0.05258505","-0.03953713","0.03799848","-0.0037037968","0.06645582","0.03897933","-0.054755826","-0.03561833","0.046369385","0.045018252","0.02841989","0.024979768","0.045938212","0.0030439245","0.05659193","-0.002368139","-0.02030701","0.060192753","-0.05309413","-0.10392122","-0.10932935","0.019982075","0.029863345","-0.038427144","0.006558228","0.079121344","0.032572884","0.03589969","-0.018612515","0.04964428","-0.030916283","0.010431867","0.026325151"]</t>
+  </si>
+  <si>
+    <t>NK-6o3bsh9Dkaz42s835LJNos</t>
+  </si>
+  <si>
+    <t>Dmitrii Pakhandrin</t>
+  </si>
+  <si>
+    <t>. National ID number: Ф-620770 Dmitrii Viktorovich Pakhandrin est lieutenant-colonel de la 64e brigade de fusiliers motorisés de la 35e armée interarmes de la Fédération de Russie, qui a tué, violé et torturé des civils à Boutcha, Ukraine. Ces atrocités constituent des crimes contre l’humanité et des crimes de guerre. Il a dirigé les opérations de son unité militaire. Il est donc responsable de soutenir ou de mettre en œuvre des actions ou des politiques qui compromettent ou menacent l’intégrité territoriale, la souveraineté et l’indépendance de l’Ukraine, ou la stabilité ou la sécurité en Ukraine</t>
+  </si>
+  <si>
+    <t>["-0.11016007","0.019113112","-0.091080405","-0.03825281","0.007902923","0.038818132","0.053757545","0.031221664","0.011292327","0.0013176379","-0.034367044","0.010507292","0.051693164","0.01137635","-0.11464474","-0.08302579","-0.09196295","-0.010700293","-0.054940607","-0.007531995","-0.0687329","-0.011798239","0.11727302","0.01524183","-0.037443936","-0.015675977","0.021418791","0.015361333","-0.028822735","0.037689984","0.042264264","-0.0022387377","-0.052808","-0.03476696","0.04659114","0.057472587","0.04038557","-0.047603026","-0.064391516","0.08616454","-0.024293214","-0.07376085","-0.057711095","0.062799215","-0.0066818967","0.042266864","-0.06932987","0.029820269","-0.021556912","0.009941568","0.00198425","0.041906957","0.010518939","0.015067313","0.0027390383","-0.14214225","0.008769673","0.0036738275","0.006854747","0.024243921","0.033725433","0.020242628","0.06916239","-0.02451194","-0.10197589","-0.055667277","0.11908588","-0.058555134","-0.008890835","-0.0029818523","0.08024011","0.00775377","-0.03774513","-0.037118625","-0.015663147","0.005974839","-0.052268","0.08721354","0.02759123","-0.13913134","0.09857996","0.002010164","0.022821428","-0.012788069","-0.044625673","-0.0382157","0.028120993","0.040501747","0.059120577","0.09452481","0.049490094","0.096655555","0.040917445","-0.07611917","0.011669407","0.018443735","0.07743267","0.0755126","-0.058962848","0.028444104","0.010196767","-0.04316111","-0.11417929","0.06217915","-0.038357586","-0.022782238","-0.049424194","-0.03297715","-0.065614484","-0.080531165","0.04966511","-0.018522471","-0.03612248","-0.01266067","0.045777615","0.016574848","-0.0066046054","0.0028532238","-0.015999159","-0.015141211","0.052544933","-0.061354186","-0.06512433","0.021068899","0.016118571","0.06440183","0.0025233782","3.5554105E-33","0.07678289","-0.015126363","-0.030762091","0.021880416","-0.13821416","-0.061648488","-0.08460119","-0.042518716","-0.009340509","0.085545704","-0.05721091","-0.0035400186","0.05131841","-0.010358442","0.0445302","-0.0013967183","0.02285649","0.032050017","-0.0015626157","0.017272985","0.023151485","0.028305314","-0.021228185","0.0038093554","0.076785594","0.10213576","-0.07721083","-0.013538433","0.04280244","-0.012396406","-0.03419349","-0.07029538","-0.032444544","-0.011912706","0.015624464","-0.04975909","-0.068503395","0.0023986318","-0.022908047","-0.017355958","0.031075263","-0.020068442","-0.054410804","0.0079745045","0.0717297","-0.018222986","0.013864194","0.008103709","0.015589042","-0.09379403","-0.062147584","0.016157001","0.017128117","-0.040719707","-0.017889071","-0.014678667","-0.022393074","0.07535669","-0.048579387","6.177171E-4","0.11513169","-0.024559505","-0.03896742","0.016368838","0.07564124","-0.15885593","0.008082565","0.09128507","0.028172584","-0.02435273","-0.008874031","-0.014643228","0.04827315","0.07811813","-0.051558573","0.0388597","0.07451303","0.04967575","-0.11896525","0.0117447525","-0.11835509","0.003916179","0.0044212076","0.01966555","0.03032507","0.044325624","0.03859238","-0.05562468","-0.07328961","0.031535108","-0.10003719","-0.00509274","-3.1202883E-4","0.040933404","-0.081303604","-8.153525E-33","-0.026637511","0.013952676","-0.021104958","-0.03451379","-0.027505755","0.076182656","0.018737158","-0.0010506737","-0.0758489","0.03336376","0.015978875","-0.073035106","-0.0011141358","0.006987957","0.031862304","0.029560141","-0.00832558","0.05601124","-0.05987017","-0.003976612","-0.0721263","6.6234573E-4","0.076644205","0.029519737","-0.0037866342","0.0065240795","0.09084978","-0.027117234","-0.108664684","0.07235137","0.054856643","-0.10336858","-0.03055325","0.06923387","0.045132697","-0.013119033","0.107427455","-0.046693068","-0.049721476","0.073107824","-0.018170262","0.083090074","0.012249598","0.105741784","-0.04371089","-0.06538058","-0.10616299","-0.039740637","-0.02867721","-0.09467698","0.03555551","0.09339788","-0.013239851","-0.02057825","0.015466905","0.0046534995","0.004840389","-0.0010295335","0.04662254","0.016030846","0.059051756","0.031971786","-0.027072841","0.042927153","0.026375","-0.007110999","-0.041629534","0.00904956","-0.025670156","-0.042827174","0.052580446","-0.09265787","0.018644193","0.051606797","-0.010123807","-0.034808494","-0.03586462","0.029198281","-0.021255683","0.05074548","0.052244198","-0.064127535","-0.09259157","0.015302161","-0.08544813","0.0011793787","0.110018544","0.07396203","0.028459573","-0.08079721","-0.010381714","-0.045983948","-0.029333845","-0.009063709","-0.031141594","-5.9805224E-8","0.0745519","-0.013366839","-0.0022527575","0.010636054","-0.049194183","-0.019624295","-0.06839902","-0.056896277","-0.1040731","0.019724011","-0.00340093","-0.036325373","-0.05630786","-0.060850788","-0.033518843","-0.050584607","-0.033171993","0.019158507","-0.02317946","-0.0060419734","0.025094125","-0.06641538","-0.042771365","-0.086088724","-0.014630754","-0.009036977","-0.0040592933","-0.045433734","1.9712516E-4","-0.025057634","0.0109895095","-0.021426398","-0.0462652","-0.01714475","0.03197635","0.095217496","0.020357838","-0.0071422486","-0.0035235856","0.014947598","-0.055580493","0.014600444","0.0138396965","0.007599039","0.015282212","-0.003056277","-0.065585285","-0.065867625","0.023461841","0.029305624","0.028661013","-0.02565297","0.039405983","0.10358228","-0.024200082","-0.010553557","0.027339455","0.018651692","-0.019956727","0.04741898","-0.024298437","0.04008234","0.035918742","-0.06588755"]</t>
+  </si>
+  <si>
+    <t>NK-6pe3A3UzgMBo5uQ6qEiUye</t>
+  </si>
+  <si>
+    <t>MUTHANNA HARITH SALMAN AL-DARI</t>
+  </si>
+  <si>
+    <t>. Father’s name: Harith bin Salman Al-Dari bin Mahmud al-Shammari. (also MUTHANNA HARITH AL-DARI, MUTHANNA HARITH SULAYMAN AL-DARI AL-ZAWBA'I, MUTHANNA HARITH SULAYMAN AL-DARI AL-ZOBAI, DOCTOR MUTHANNA HARITH SULAYMAN AL DARI AL-ZAWBA, MUTHANNA HARETH AL-DHARI, MUTHANNA HARITH SULAYMAN AL-DHARI, MUTHANNA HARITH SULAYMAN AL-DARI, MUTHANA HARITH AL DARI, DR. MUTHANNA AL DARI) Mother’s name: Heba Khamis Dari. Father’s name: Harith bin Salman Al-Dari bin Mahmud al-Shammari Provided operational guidance financial support and other services to or in support of Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115). He is the head of the political department of the Association of Muslim Scholars in Iraq. Involved in oil smuggling. Wanted by the Iraqi security forces</t>
+  </si>
+  <si>
+    <t>["-0.046058036","0.052105952","-0.009297808","-0.059273","-0.051237255","-0.02236069","0.03693773","-0.06882871","0.04127219","-0.057247356","0.068021074","-0.079234436","0.061956003","-0.047592096","-0.04443478","0.07250114","-0.013186408","0.013631198","-0.09049673","-0.062172584","-0.02984037","0.023933524","0.06117609","-0.059915412","-0.0577651","0.055553146","-0.04719271","0.011980288","-0.02888461","-0.0012394768","0.08516541","0.04702626","-0.017719956","-0.0033187075","-0.065883785","0.030612044","-0.016158674","0.06770754","0.07535656","0.002181312","0.08235136","-0.07095394","0.021039763","-0.068108365","0.030005863","-0.061917115","0.024973352","0.013743395","0.07978358","0.058699153","-0.033978615","-0.006707617","0.039979395","0.06747112","0.052545026","-0.10554779","0.007339492","-0.0076299314","-0.038537085","-0.014741144","-0.081859164","0.091797456","0.012904954","-0.010855549","-0.065095514","-0.07317224","0.13492219","-0.11735765","-0.008940182","-0.05719556","0.0020216473","0.013137797","0.037857514","0.026827004","-0.060008902","0.016793082","0.016444273","0.07475356","-0.05683073","-0.077590145","-0.010296898","0.0761599","0.054521024","-0.019959792","-0.041964225","-0.022005511","-0.05699763","-0.013481502","-0.024371317","-0.0016439349","-0.003024073","0.0023815574","-0.013440967","-0.049704995","0.11252673","-0.040592823","0.096113406","0.05991398","-0.10876054","0.03315807","-0.03456125","-0.047993116","-0.079675585","-0.031273082","-0.08531101","0.0026916014","-0.029901616","-0.0023003935","-0.09885939","0.0071977815","-0.04551224","-0.010449096","-0.08428037","-0.060218453","-0.011398787","0.017496668","-0.042248383","-0.0025682328","-0.073197536","8.1311126E-5","-0.055110093","0.03846218","-0.014588873","0.06954786","0.029237943","-0.050566606","-0.053287286","6.459606E-33","-0.014652548","6.114353E-4","0.023156745","-0.012978168","-0.03471889","0.03074705","-0.04415338","0.094010025","-0.04400435","-0.005733497","-0.030582495","-0.031748842","0.01357779","-0.050785754","-0.03396489","0.015512587","-0.011351642","-0.04570867","0.039077006","-0.0827357","-0.008395211","-0.04144143","0.031836625","-0.02989024","0.049326606","0.058925394","0.08085162","-0.042455535","0.053843517","0.03789689","-0.029863168","-0.029495614","-6.853963E-4","-0.14547504","-0.02758564","0.018712906","-0.08239761","-0.018616317","-0.082681425","-0.0057853875","-0.037666343","0.04200095","0.08571459","-0.0172127","-0.051318645","0.052670542","0.03792818","-0.005445969","0.053112708","0.010009077","0.011359319","-0.034623884","-0.017351318","-0.06572175","-0.048778888","-0.023770554","-0.020800812","0.012508925","-0.033952456","0.07073199","0.00927341","-0.020005465","-0.11328372","0.08387359","-0.05777725","-0.05468202","0.025824072","0.04833882","0.022091752","0.020625448","-0.002782005","0.024646675","0.039431218","0.06988798","-0.07574803","0.026582887","0.034886762","0.009119021","-0.020961268","0.025378969","-0.005463675","0.054104082","0.08099919","-0.05150422","-0.1184065","0.039522424","-0.05643767","0.022953313","-0.09204707","-0.017882489","-0.0301603","0.01632565","0.033520777","0.009552351","0.047627963","-9.758513E-33","0.034110196","-0.0026190914","0.029520683","-0.096037686","0.08439557","0.017318085","0.070549086","0.04235727","0.025404043","0.0143605005","0.04871735","0.03970639","0.005099365","-0.03672577","-0.0044129454","0.04941992","-0.06295917","0.017114863","-0.0086778365","-0.0026614654","0.0036905524","0.08496862","-0.015290895","-0.06860874","-0.012855287","-0.014028659","0.07692475","0.042864513","-0.011138185","0.07189573","0.032393016","-0.06893627","-0.11744653","-0.01918253","0.02300383","-0.0027939705","-0.054857004","0.014484381","-0.016944211","0.09007616","0.03403487","0.07568312","0.07526539","-0.010488249","-0.040003892","0.06726095","-0.033431225","0.016009385","0.04561136","-0.109270364","-0.008874992","0.023804652","-0.0043305997","-0.020371942","0.09590882","0.15143834","-0.0484831","-0.026780026","0.019555692","-0.08202477","-0.013286004","0.035517454","0.07116824","0.013272092","-0.108813554","0.021356495","-0.04444369","-0.07709798","0.05707202","-1.786983E-4","0.022288078","-0.15976273","-0.055030677","-0.0599559","-0.013957341","0.033744995","-0.052224956","0.027515003","-0.03815076","0.036730286","0.14971782","-0.07147244","-0.06231273","-3.513813E-4","0.05713752","-0.02223106","0.08311588","0.024450166","0.07420285","-0.04365919","0.007959142","-0.039676595","-0.012284465","-0.030329874","-0.064365186","-5.615556E-8","-0.0066898763","-0.0890566","0.019260168","0.030832367","-0.026713826","0.027991943","-0.040494297","0.015259297","-0.060179483","0.0159752","0.06670679","-0.0045389687","-0.10085688","-0.027158171","0.041708168","-0.054248206","-0.035415314","0.011344549","0.044953864","-0.05631786","0.025478203","-0.030913174","-0.017579682","0.036047567","0.028023848","0.043814395","0.018726535","-0.054348007","0.008281034","0.06884796","0.0274238","0.07913755","-0.032613993","-0.024898462","0.0054694125","0.026588835","-0.058949374","0.03466801","0.0012981652","0.023209767","0.012262442","0.052302428","0.020951943","-0.001123283","0.068732284","0.028002728","0.030984355","0.037676856","-0.005924997","-0.006110858","-0.0127787525","-0.01939235","0.05732181","0.07395105","0.024236385","-0.024626296","-0.026875898","-0.06584618","0.0055492837","0.0029558528","0.079670765","-0.067078546","0.055204026","0.04568573"]</t>
+  </si>
+  <si>
+    <t>. MUTHANNA AL DARI) (also MUTHANNA HARITH AL-DARI, MUTHANNA HARITH SULAYMAN AL-DARI AL-ZAWBA'I, MUTHANNA HARITH SULAYMAN AL-DARI AL-ZOBAI, DOCTOR MUTHANNA HARITH SULAYMAN AL DARI AL-ZAWBA, MUTHANA HARIS AL-DHARI, MUTHANNA HARETH AL-DHARI, MUTHANNA HARITH SULAYMAN AL-DHARI, MUTHANNA HARITH SULAYMAN AL-DARI, MUTHANA HARITH AL DARI) previous Mother’s name: Heba Khamis Dari. Father’s name: Harith bin Salman Al-Dari bin Mahmud al-Shammari. Provided operational guidance financial support and other services to or in support of Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115). He is the head of the political department of the Association of Muslim Scholars in Iraq. Involved in oil smuggling. Wanted by the Iraqi security forces</t>
+  </si>
+  <si>
+    <t>["-0.04985316","0.052443888","-0.004292685","-0.067005575","-0.063004196","-0.036540516","0.027692953","-0.074140064","0.046470203","-0.052103873","0.061170675","-0.07386292","0.089217156","-0.048749123","-0.07208651","0.072096534","-0.019513676","0.0041251867","-0.10478552","-0.025976324","-0.018974176","0.027055643","0.06893665","-0.038284283","-0.078232214","0.068539545","-0.024642259","0.008615538","-0.014906619","0.009759869","0.09057287","0.05266309","-0.026731724","-0.008337959","-0.05828043","0.04500458","-0.040951584","0.042163264","0.09885321","0.019841181","0.0985649","-0.08075609","0.012585204","-0.073194005","0.008190334","-0.06930583","0.034660883","-0.004928555","0.062998995","0.044661757","-0.016613325","8.5342315E-4","0.005374853","0.060053263","0.042319335","-0.1386134","-0.014095663","-0.008440204","-0.022887139","-0.028902754","-0.07630294","0.08501463","0.05567156","0.005258421","-0.07602514","-0.079732366","0.10347301","-0.120308094","-0.028465766","-0.058591474","5.659659E-4","0.0057904236","0.03230849","0.025901046","-0.04931491","0.006882377","0.058699492","0.07593583","-0.041765608","-0.07302387","-0.016184568","0.05631571","0.05431942","-0.018768728","-0.022082444","-0.015058096","-0.066482335","-0.0071074665","-0.0010450953","-0.021919996","-0.022310713","0.025204053","-0.02221203","-0.03689103","0.11262304","-0.028222565","0.0813991","0.05460998","-0.115652494","0.041182905","-0.05182219","-0.056215268","-0.09769542","-0.053257164","-0.10651271","-0.01641752","-0.011311478","-0.02801834","-0.12786193","-0.016604519","-0.044688057","-0.016228294","-0.09719377","-0.052994873","-0.010710396","0.028774725","-0.04755441","-0.0049844994","-0.043294296","-0.02255164","-0.0700527","0.010249227","7.125562E-4","0.059161734","0.043879647","-0.041264754","-0.04623459","6.0075762E-33","-0.012400127","-0.036048952","-0.012351074","-0.018948065","-0.03496637","0.0146745145","-0.04738661","0.0764917","-0.02524015","-0.010939066","-0.028145794","-0.0028164885","-0.0047858846","-0.058279395","-0.033169","0.020897463","0.011240584","-0.049026087","0.023956396","-0.091112584","0.027430674","-0.053825628","0.05317572","-0.014732772","0.038704064","0.05100921","0.07142633","-0.05514855","0.0513702","0.028378623","-0.038619366","-0.036417693","-0.0024973825","-0.13809624","-0.031581216","0.022265207","-0.094904535","0.012303541","-0.09743984","1.0589426E-4","-0.051686537","0.029634057","0.09945792","-0.02827397","-0.032234702","0.06322635","0.04260348","-0.012878435","0.048889305","0.005448492","0.023480613","-0.036930196","0.0022207333","-0.05724831","-0.06678212","-0.026872855","-0.014620752","0.0048001073","-0.013804356","0.057002317","-0.02213096","-0.004843328","-0.09923381","0.057387613","-0.04217842","-0.027370654","0.010280956","0.07012606","0.040688742","0.024706975","0.013404793","0.028322415","0.04419696","0.072217435","-0.06700858","0.013564565","0.027738845","-0.0011543225","0.0058933375","0.038545016","0.025540069","0.04140097","0.073291495","-0.03967473","-0.09505234","0.0359054","-0.052053824","0.017831957","-0.08691299","-0.032988824","-0.012859317","0.03261759","0.046599302","-0.008766909","0.046482965","-9.212415E-33","0.033628985","-7.3391234E-4","0.028808752","-0.078894526","0.10219977","0.019414952","0.064289786","0.051065747","0.03318459","0.020306382","0.052609343","0.02301881","-0.013181888","-0.0345305","0.0035174906","0.064241685","-0.034120545","0.017751906","-0.015416007","-0.05356364","0.011884724","0.08217279","-0.03345721","-0.06823315","-0.020692967","-0.0058003566","0.080756076","0.04774454","-0.015734065","0.052107982","0.03161676","-0.06024495","-0.12378823","-0.015363154","0.016575212","-0.0147118205","-0.042880356","0.01666316","-0.035996232","0.046860162","0.050764587","0.064759046","0.076207","0.042260878","-0.028081948","0.068319894","-0.043696303","-0.0020757313","0.042810343","-0.09834381","0.004479168","0.018922202","0.018995902","-0.03315298","0.09891654","0.1504209","-0.032095905","-0.03540207","0.030834759","-0.08313453","0.0036309203","9.9922E-4","0.07685696","0.017546589","-0.11139165","0.02786805","-0.022882529","-0.08578715","0.030747522","0.035011932","0.038107794","-0.13959974","-0.09143161","-0.07785954","-0.0055233813","0.033160754","-0.05907633","0.03320596","-0.021213327","0.035961624","0.12646322","-0.083736435","-0.066593945","0.0066458816","0.07200936","-0.0144869685","0.06528686","0.0106079215","0.08195533","-0.036547944","-0.0076320427","-0.031698674","-0.018302431","-0.02189132","-0.057810526","-5.5292077E-8","-0.0273184","-0.07313013","-0.002327493","0.035315823","-0.01070468","0.04086237","-0.045243032","0.026002407","-0.028054198","-0.021091085","0.069989845","-0.0030862307","-0.078323096","-0.019425366","0.04421721","-0.020965198","-0.0118077835","0.012921625","0.055667702","-0.069585","0.035762936","-0.03061118","-0.028169222","0.050428957","0.02417467","0.05267374","-0.014800626","-0.042929586","-0.0072632763","0.05958309","0.011834373","0.07367952","-6.590976E-4","-0.008890832","3.353455E-4","0.029743109","-0.041650992","0.021951387","-0.033692315","0.016177917","0.020496938","0.07259737","0.031927444","-0.012522571","0.06900014","0.042590022","0.02948337","0.03816283","-0.0030525592","-0.016814595","0.001382449","-0.007849679","0.038219973","0.09645996","0.016374236","-0.025449695","-0.02503593","-0.069155626","0.006786148","-0.008970983","0.084351","-0.04621985","0.044605024","0.0641092"]</t>
+  </si>
+  <si>
+    <t>MUTHANNA HARITH SULAYMAN AL-DHARI, MUTHANNA HARITH SULAYMAN AL-DARI, MUTHANA HARITH AL DARI, DR</t>
+  </si>
+  <si>
+    <t>["-0.05224103","0.051498353","0.030167317","-0.0129128555","-0.098892584","-0.00560497","0.023606693","-0.03643964","0.0026277173","-0.043167196","0.075113766","-0.008644094","0.04750266","-0.07450912","-0.11633077","0.051957693","0.0024722286","0.071630485","-0.037306417","-0.006508395","-0.015294107","0.077302516","0.04386562","0.036540195","-0.053383674","0.06786425","-0.014978964","-0.0086507285","0.05716582","-0.0147381155","5.88112E-4","0.06183245","0.02150234","-0.021358846","-0.10588592","-0.037345298","-0.071828805","0.04887442","0.10349915","0.05346672","0.077019","-0.048482638","0.008529832","-0.047374606","-0.010251835","-0.08469769","-0.046968497","-0.0016573326","0.04354656","0.090750635","-0.05519321","-0.030370016","-0.03569724","0.0851032","0.020155312","-0.19929665","-0.06436978","-0.018794538","-0.035063136","-0.043851096","-0.023998672","0.039630778","-0.014941218","0.020405909","0.007957692","-0.03487601","0.03081869","-0.10080115","-0.037694577","-0.033844262","-0.028604131","-0.065444924","0.07007295","0.011568577","-0.0720517","0.02967018","0.03818821","-0.04724984","-0.050602905","-0.052677184","-0.018262442","0.035747837","0.07489604","0.01974115","-6.5727375E-4","0.04625998","-0.04622886","-0.00904411","-0.07249536","-0.09973884","0.057613727","0.0016270707","-0.04947554","0.0015190991","-0.002418372","0.03115997","-0.036785446","0.0010559427","-0.072886586","0.08040031","-0.04187311","-0.04350888","-0.08752488","-0.054421887","-0.14671394","-0.0899253","-0.06165031","-0.10124706","-0.081852674","-0.02783554","-0.02204627","-0.017001616","-0.06404614","-0.048786655","-0.0046825744","0.025916012","0.012091537","-0.001302503","0.058731064","-0.030826988","-0.07379136","-0.011800303","-0.0014570499","-0.009643474","-0.009198448","-0.05877899","-0.0011307253","7.9444926E-33","-0.008791939","-0.056871995","0.047628533","0.008697901","0.03594591","-0.06833895","-0.029495172","-0.008292438","-0.0058999113","-0.053248048","0.009755778","-0.002794611","-0.01271294","-0.10277084","-0.03986838","-0.03791392","0.058473937","-0.09270329","0.054605983","-0.09202987","0.009023592","0.0019011318","0.058046587","0.0438764","-0.009694968","0.012944724","0.082416035","-9.6524064E-4","0.033998955","0.020413686","0.07531085","-0.0133810975","-0.014412497","-0.1082927","-0.09386918","0.04472185","-0.11251812","0.00482782","-0.024275871","-0.017280228","-0.04175409","0.021151416","0.09583343","0.021509824","0.051838633","0.09506409","-0.045994196","0.070468575","0.054654058","0.06603006","-0.032371912","0.0058200336","-0.04851386","-0.045194976","-0.051167026","-0.032798763","-0.040621877","0.0029579191","-0.0020337894","0.071572095","-0.033569206","-0.023854995","-0.055557754","-0.041508183","-0.05205772","-0.04008776","-0.05131611","-0.03997969","-0.0030507648","0.0060362895","-0.027201999","-0.026517363","0.072815605","0.08075255","-0.00869597","0.024602674","0.069389395","0.0040601925","0.033253893","-0.0075275707","-0.027306033","0.06957067","0.0104398765","0.046641167","-0.07820587","0.003982805","-0.08016899","-0.006703113","0.012223398","0.03111102","-0.03442686","0.022143472","0.042234287","6.219367E-4","-0.013603506","-9.240306E-33","0.045330193","-0.0433775","-0.03938052","0.017239403","0.061778165","0.034662675","-0.027291836","0.046200007","0.079147995","0.06347479","0.08017668","0.012802969","0.012647129","-0.02272142","-0.015051918","0.06884874","0.038759172","0.053721484","-0.019333404","-0.022763167","0.051679153","0.13319269","-0.06415184","-0.07828734","-0.014562925","0.037709836","0.058144275","0.029076977","0.040062834","0.046462234","0.036520798","-0.06035142","-0.10799514","-0.0017280931","-0.07093986","-0.046573654","0.05963745","0.016216408","-0.05588169","0.040639024","0.006430121","0.06895084","0.08155233","0.099470116","0.07927078","-0.018116405","-0.021351226","-0.0023998583","-0.025751295","-0.050173465","0.017690133","0.00638566","0.05001971","-0.05342154","0.08300118","0.08956714","0.008052497","-0.06648292","-0.016580429","-0.049089476","0.0015606943","0.038100883","0.005379246","0.011574083","-0.06954438","0.030357212","0.010003791","-0.047521006","0.017120713","0.0011112313","-0.025188955","-0.09223954","-0.09737312","-0.07420187","-0.007134722","0.025059182","-0.021213626","0.01585123","-0.052465227","-0.0024647254","0.06406243","-0.027668864","-0.077762336","0.06980655","0.053578213","0.039437275","0.079135716","-0.0028449716","0.051351767","0.026927447","-0.023317937","0.016773714","-0.0274405","-0.015466969","0.02264586","-3.296908E-8","-0.009320412","-0.108591884","-0.03249535","-0.008298219","0.022066396","-0.0055408785","0.022335732","0.04939426","-0.023625668","0.039965384","0.031451236","0.06555461","-0.048723307","0.0087885875","0.060405333","0.00834901","0.028322078","0.020414464","-4.9124175E-4","-0.070436984","0.033660185","-0.002594788","0.068162724","-0.022921458","0.02680715","0.06821548","0.007009745","-0.0639421","-0.062737584","0.07953696","0.04762781","0.12400257","0.044455566","-0.09474686","0.003565547","-0.015202407","0.021531744","0.01505502","-0.0034274207","-0.01255874","-0.008301042","0.0059719966","0.059621338","0.02590021","0.075295106","-0.048789877","0.037430584","0.06146749","0.023494622","-0.018869262","0.01789652","-0.0013767385","0.07389251","0.0023641246","-0.037473615","-0.014200052","0.043591406","-0.034001872","0.014200761","-0.051994156","0.12246322","-0.06126545","0.057804335","0.06051127"]</t>
+  </si>
+  <si>
+    <t>NK-6t9HRDJWGteMCs3mPgkN4e</t>
+  </si>
+  <si>
+    <t>GREGORY DONALD CHANEY</t>
+  </si>
+  <si>
+    <t>Entity Name: GREGORY DONALD CHANEY | Type: Person | Jurisdiction: us | Risk Context: 1128a4</t>
+  </si>
+  <si>
+    <t>["-0.04383389","0.0031650183","-0.04763282","-0.040780835","-0.03941273","0.0030845143","0.061488148","0.029148124","0.0040728287","-0.040654846","0.02875069","-0.05929153","-0.017365348","0.0018978127","-0.021888435","0.03381261","-0.060413163","0.06456571","-0.086167574","-0.06647488","0.0073580937","0.07010291","0.012346926","-0.049484514","-0.016420415","-0.117736235","-0.022888225","0.033054255","-0.0024048008","0.037757665","0.102413975","0.051159054","0.011441082","0.060917832","0.025190385","0.03540127","-0.07355565","0.017723761","0.07331888","-0.008056472","-0.027387923","-0.015900945","0.11766252","0.038382825","-0.08262958","-0.0060173185","-0.012860554","-0.033836663","0.038089033","-0.015830677","-0.057844803","0.010417063","0.07602424","0.06788543","-0.019715589","0.05708282","0.016758608","-0.017723856","-0.0573563","0.008983712","-0.01635516","0.052570593","0.004351818","0.019050967","-0.018040324","0.048555918","-4.8195443E-4","-0.061689984","0.099884376","-0.12085455","0.029766617","-0.041006636","-0.060244277","0.053180046","0.015844844","-0.041943822","0.028117973","0.022418812","0.10297378","-0.08438526","-0.024271348","-0.0050267316","0.044473507","-0.024035238","-0.043385155","0.004143174","0.018508466","0.024863895","0.017456757","0.04113192","0.010321765","-0.042166166","0.11008199","-0.0024954716","-0.059762605","0.020314487","0.05209657","-0.019658713","-0.13080043","0.09418122","-0.0254134","-0.017636724","-0.03341707","0.049030457","-0.050861184","-0.06629939","0.00198953","0.0018214121","-0.05661775","-3.0720586E-4","-0.016830713","0.030381333","-0.044806097","-0.0034454972","0.06264023","-0.052977853","-0.04094495","0.066513404","0.01841014","-0.113813855","-3.8746273E-4","0.019572305","-0.09850606","-0.009894457","-0.11714112","0.017033739","0.073339306","-1.118771E-33","0.073735505","0.08899363","0.05151872","-0.0047144704","-0.038157888","-0.01655459","-0.029067384","0.022548838","-0.009769113","0.011694878","0.06593928","0.029669544","-0.019980446","-0.07358098","-0.049156446","0.028623277","-0.03487707","0.07121038","0.0152455475","0.007262513","-0.0069962116","-0.007387217","0.01311177","-0.007844225","0.054831695","-0.027031936","0.0016885933","-0.022965502","0.03078459","0.06731639","-0.00805837","0.007970384","0.0365111","-0.018848049","0.11355681","0.042367995","-0.058332823","-0.06397471","-0.022699717","0.0041753524","-0.017079227","0.082485706","-0.04919164","0.08944876","-0.023928408","0.01409958","0.05210375","0.0012941468","0.041333072","0.0010116999","-0.042941075","0.034020163","-0.038802702","-0.010145833","0.013105973","-0.06316466","0.03216868","0.041302975","0.0048600542","-0.09106213","0.039280053","0.0018710195","-0.054998524","0.0088383835","0.029135823","-0.12352493","0.022411996","-0.05982823","-0.051123124","-0.09063951","0.019269917","-4.960809E-4","-0.05476961","0.011948729","-0.0721139","0.006324505","0.010794031","0.04228906","-0.06759311","0.04836057","-0.16623779","0.015122946","0.012185037","0.009063535","0.0014510078","0.016575666","0.021010308","-0.018419249","-0.057674248","0.019237423","-0.027306305","0.014260538","0.00826712","0.083943576","3.821654E-5","-1.5897915E-33","-0.10445529","-0.09979144","-0.018909674","-0.08383704","0.08604911","-0.11859428","0.00223046","0.046170074","0.074530534","-0.068362705","-0.033003654","-0.047577254","0.018725092","-0.0039799074","0.032802977","0.023828493","-0.01385043","0.05742809","-0.038076654","0.06658566","0.13089086","0.036515433","-0.0962056","0.058179006","9.3537016E-4","-0.014458996","0.07792934","-0.0035635906","-0.049879387","-0.051299836","0.051729944","0.07026809","-0.041803706","0.044668257","-0.10693285","-0.038492907","0.12931697","-0.042131513","-0.05387964","0.0016501265","0.037275583","0.06965418","0.0061821933","0.04535885","-0.041838765","-0.05319865","0.018499944","0.027568342","0.07109456","-0.009204667","-0.028193576","-0.014321014","-0.005846781","-0.033855338","0.017676458","0.07674713","0.07633449","-0.038351174","0.034299016","-0.054793373","-0.05690295","0.080857635","-0.03320989","0.12821794","0.0021709476","-0.049919758","-0.068830855","-0.02458116","0.025842613","-0.15354411","0.06996496","-0.11331697","0.0010144508","-0.02968636","0.003167913","-0.013781635","-0.001984646","-0.012144256","0.008485692","0.03239242","0.06847846","0.03993066","-0.028490823","0.064783685","0.0035624001","0.017019965","0.06340606","-0.034634724","-0.01996645","-0.03273111","-0.024025215","5.0775905E-4","-0.082074076","0.008845439","-0.014481565","-2.8862413E-8","0.06935477","0.012923009","-0.05140102","-0.0064732903","-0.018368717","0.048897836","-0.0054867133","-0.028779298","-0.03593819","0.004251088","-0.014180796","0.10298705","0.031477727","-0.036483534","-0.0027791068","-0.110617585","-0.05704651","0.039186385","-0.04514089","0.056900695","0.025157891","-0.026693095","0.015405221","-0.06719353","-0.021848299","0.03892224","0.021601843","-0.01778313","-0.026472934","0.01638497","0.0094618825","0.07822631","-0.028204286","0.08266798","0.062028784","0.06624469","-0.012026124","-0.06771958","-0.013479652","0.0034012944","0.015747322","0.009582098","0.07180982","0.07154061","0.056091707","0.020254467","-0.016586285","0.025172362","0.09875907","-0.011849562","-0.02713795","-0.11209598","0.016060652","0.015370553","-0.03551997","-0.014571933","0.04103585","0.016884247","-0.04711688","-0.050755486","0.06269956","-0.08816527","0.015182229","-6.019429E-4"]</t>
+  </si>
+  <si>
+    <t>NK-6vJwP2iR5wHfJq3Eq626EH</t>
+  </si>
+  <si>
+    <t>JOINT STOCK COMPANY RUSSIAN NATIONAL REINSURANCE COMPANY</t>
+  </si>
+  <si>
+    <t>| Risk Context: Informations complémentaires: La Compagnie nationale russe de réassurance S.A. est une filiale de la Banque de Russie. La Compagnie nationale russe de réassurance (RNRC) est une société par actions contrôlée par l’État russe et une filiale de la Banque de Russie. À l’heure actuelle, la RNRC constitue le principal réassureur de navires russes responsables de l’exportation de pétrole russe, y compris la flotte de Sovcomflot, depuis que les compagnies d’assurance occidentales ont cessé de couvrir les armateurs russes, à la suite des sanctions occidentales imposées en raison de à la guerre d’agression menée par la Russie enUkraine</t>
+  </si>
+  <si>
+    <t>["0.020702455","0.03645001","-0.04447816","0.033539444","0.05184324","0.085258976","0.07795518","0.048084877","0.0184575","-0.0060961396","-0.032360744","-0.047539562","0.113136865","0.0048075304","-0.07770197","-0.089351565","-0.080829345","-0.026064027","-0.05242845","0.03092355","-0.021742567","-0.046523437","0.035476856","0.061947167","0.0017695611","-0.10590524","-0.030622382","-0.0076317484","-0.02353223","0.0124875605","-0.046273064","-0.058590766","-4.5543732E-4","0.02248248","-0.024863962","0.033417773","0.006570505","-0.039590433","-0.07822818","0.02948321","-0.015867779","-0.029283715","-0.11557379","0.0149393715","-0.094955176","0.039519142","0.01774055","0.0036400366","-0.046122108","0.007168651","-0.031780437","-0.03709838","0.003637661","-0.06720736","0.088687606","-0.10658116","-0.034740373","-0.06559471","-0.0018004028","0.020201616","0.0011932484","-0.027437085","0.019161303","0.03076134","-0.07471366","-0.011348104","-0.045936007","0.0696626","-0.064631306","4.362326E-4","0.051712632","-0.07866688","-0.11740167","0.011883346","0.0022103505","-0.02483098","-0.054842886","0.005734492","0.011849651","-0.11364932","0.06923552","0.05239591","-0.017253255","0.047265165","-0.055160526","-0.0481847","0.019371398","-0.079620056","0.1280664","0.06921648","0.009378279","-0.09705802","0.07169662","-0.015262295","0.027113779","-0.06460747","0.030370638","-0.017628355","-0.026196375","3.048292E-4","0.011340245","-0.026884716","-0.023214085","0.06626885","-0.16471128","-0.063988715","-0.15016025","-0.09910996","-0.019006973","-0.027816758","0.03028912","0.0015417758","-0.021422023","-0.08420078","-0.002721761","7.717465E-4","-0.08629292","-0.09073124","-0.015520794","-0.050796118","0.020924622","0.057178862","0.009468505","-0.037808105","0.06579945","0.021770487","0.036465585","7.392178E-33","0.020330409","0.030397657","-0.076648645","0.06345362","-0.056647014","-0.028413944","-0.0139513565","-0.021076463","-8.986317E-4","0.03243115","0.009410875","0.071286365","0.004728491","-0.044357043","0.021251747","0.05236489","-0.022602549","0.05170708","0.02517844","0.02240467","-0.0375143","0.0038618387","0.09294975","0.020290537","0.03990488","-0.045116782","-0.004816488","-0.05349179","0.043059513","0.0049007935","0.03838171","0.06469545","0.02727438","0.012921965","0.011498629","0.013103078","-0.06492834","-0.05245305","-0.008241601","0.0064990926","0.024578355","-0.033676106","0.0016041782","0.065458596","0.053056046","0.02108814","0.003815728","-0.039923444","-0.021780265","-0.026566694","0.0025270917","0.03476037","0.03685628","-0.02911881","-0.04191365","0.010668502","-0.06983615","0.030543162","-0.05734348","-0.06419817","0.0122529855","-0.029661","0.01976106","-0.0016214175","0.010403975","0.008364574","-0.077791885","-0.0126367025","0.04398621","0.0042040716","-0.011107476","-0.017458301","0.010800376","0.07008683","0.012107996","0.0523323","-0.049124464","0.036063228","-0.016140727","0.0048528267","-0.13826214","0.016846336","0.06288278","0.054010447","-0.0019850507","0.025854526","0.06580189","-0.0040877876","0.0086463755","0.060024515","-0.08357094","-0.0067502325","0.053126626","0.026626695","-0.0073176417","-1.1413344E-32","-0.02909104","-0.008161411","-0.07147568","0.002093561","9.6146885E-4","-0.01671082","-0.030988999","-0.026236467","0.044520844","0.022624394","-0.040131908","-0.07012995","0.046228062","0.035384703","0.033027165","-0.035289254","0.05815216","0.064437404","-0.07355614","-0.011240924","-0.05049932","-0.035164215","0.023266817","0.07014021","-0.028135912","0.046929564","0.014713706","-0.06765915","-0.020895168","0.0103637185","0.05480178","0.06978313","-0.009028924","0.123286866","0.0041780933","0.029233838","0.02204125","-0.0038594003","-0.06879652","0.04057198","0.0314965","0.019479513","-0.0039664833","0.014223612","0.023091212","-0.024081433","0.059039153","-0.08342895","0.09940853","-0.058458604","0.089609854","0.07709674","-0.05753562","0.01855382","-0.033246983","-0.048376385","-0.017499346","-0.066094205","-4.5190027E-4","-0.03585199","0.021700032","0.077170245","0.0014469977","0.019209024","-0.03997243","-0.018553479","-0.0630768","0.0060083377","0.10710151","-0.07057422","0.02374008","-0.056235213","-0.016225405","-0.045539815","0.052703597","0.026793275","-0.051564917","0.01774996","-0.018860161","0.07014065","-0.016297309","0.007470144","-0.010834679","0.03334768","0.09592383","0.045509987","-0.047745023","-0.03381945","0.05784958","0.011618172","-0.10819927","-0.024590952","-0.034016587","0.004119411","-0.04923755","-6.3182114E-8","0.088759124","0.047950875","-0.0037522726","0.03622352","-0.036007","-0.122466356","-0.053785186","-0.06047238","-0.109867595","0.02975094","-0.0035193341","0.030188432","-0.005516934","-0.08567803","-0.04179078","-0.03210147","-0.03684863","0.111159764","-0.048769657","-0.010573756","0.035016578","-0.04638472","-0.0905559","-0.07584229","-0.058004465","-0.0066514057","-0.015906323","-0.089564554","0.05541395","-0.001195504","0.010704997","0.0043674335","-0.055193245","-0.0066411025","0.022173064","0.02166061","0.06490761","0.064303316","0.07907436","0.032782238","0.0123486295","0.046549726","0.04513002","0.047121335","-0.06488924","-0.025793767","-0.1370986","-0.030844737","0.09970934","0.023024987","0.0030370168","0.013716534","0.053031903","0.14086713","0.031608924","-0.09008317","0.011233306","-0.028530871","-0.09085836","0.0024814568","-0.051329233","0.0039192536","0.09850072","-0.035921287"]</t>
+  </si>
+  <si>
+    <t>NK-6yYfWhQUada8xZR9yLHLru</t>
+  </si>
+  <si>
+    <t>THERESA KPANA LOMBEL</t>
+  </si>
+  <si>
+    <t>Entity Name: THERESA KPANA LOMBEL | Type: Person | Jurisdiction: us | Risk Context: 1128a1</t>
+  </si>
+  <si>
+    <t>["-0.032616884","0.017069492","-0.04956777","-0.028395953","-0.04430376","0.01883856","0.039777048","-0.035174187","0.014719557","0.01985281","0.021184955","-0.14071795","-0.011223513","-0.047644883","-0.06377133","0.09331949","0.030769419","0.04085589","-0.08220892","0.0062481705","0.02298662","0.009775083","0.06987039","0.04153301","-0.00675256","-0.032939725","-0.021049937","0.042838223","0.019332748","-0.027341247","-0.024073849","0.048925877","0.042686936","0.0520626","0.104713954","0.05150137","-0.0528864","0.050677698","0.0042014658","-0.012523574","0.01093953","-0.078163676","0.010095343","0.025400236","-0.046958484","-0.020612042","-0.007571095","-3.6366555E-4","-0.028295437","-0.01872412","-0.047438953","-0.01042552","-0.042346437","0.030285535","-0.021181764","0.0061553367","-0.046567988","0.02850751","-0.0119508905","0.03491019","-0.013303156","0.07693891","-0.009378274","0.029776806","0.024488477","-0.032126382","0.0341672","0.042886395","-0.007846138","-0.097685724","0.091781065","-0.07678891","-0.07154167","0.09772339","0.011924875","-0.038620908","0.057518937","0.06870367","0.034044232","-0.050843656","-0.008616004","0.03256069","0.06920154","-0.005689391","-0.025095325","0.0022811445","-0.08744239","-0.028208852","0.06659078","-0.0050573647","-0.029616361","-0.014773819","0.15133156","0.012106955","0.0065654865","-0.0021466657","0.040614024","-0.025664166","-0.043272343","0.07992832","-0.018782383","0.012153494","-0.029362462","0.04515533","-0.06599528","-0.013491501","-0.018203162","-6.57207E-4","0.0052084","0.014353389","0.011957605","0.06867289","-0.07157056","-0.027851058","0.0455516","-0.08193783","-0.052605685","0.011604135","0.06290669","-0.1469479","-0.02078918","-0.052128933","-0.113800645","-0.09201207","-0.1267405","0.008548517","0.025827864","6.108008E-34","0.09739055","0.021007126","0.08966676","0.059945717","-0.029747808","-0.005471006","5.409939E-4","-0.0064628907","-0.08714363","-0.0025573254","-0.026009044","-0.040551513","-0.0138315195","-0.1513635","-0.039939813","0.05569861","-0.009520084","0.06273317","0.02411279","0.080142796","0.07482538","0.0065790485","-0.018311227","-6.294988E-4","0.019161766","-0.01752253","0.037599567","-0.044914946","-0.03170239","0.06803013","0.025395183","0.0029145468","0.023251375","-0.050776444","0.015929984","0.0065013575","-0.041956797","-0.06643701","-0.03795684","-0.051673263","-0.039081275","-0.0135864485","0.05492183","0.10146997","-0.04484676","0.0052191988","0.07453037","-0.010467171","0.06239384","0.06300257","-0.037765983","-0.00442725","-0.08467342","0.054466963","0.0063070985","0.0725793","0.045005467","0.05583769","0.011481219","-0.06621577","-0.007927661","0.023461856","-0.065964915","0.03440701","0.052474584","-0.11840525","-0.02067307","-0.03456218","0.015130823","-0.08601879","-8.78161E-4","0.0922913","-0.004075689","0.07740169","-0.020755334","-0.009038223","-0.010018105","-0.03411233","-0.053699717","0.10858628","-0.018692568","0.0027436554","8.562884E-4","0.08871778","0.0029764052","0.0384463","0.042217474","-0.040606514","-0.08521874","-0.022134386","1.0673168E-4","-0.017089369","0.08966781","-0.0019428163","-0.03654697","-1.8501188E-33","-0.006331089","-0.10366706","0.015325987","-0.028602606","0.04946343","-0.11585601","0.02998438","0.030596007","-0.028250668","0.044367343","0.018035939","-0.10807238","0.03713497","0.044606414","0.034236416","0.08223138","-0.03970498","7.101753E-4","-0.03234955","-0.006362326","-0.043254673","-0.05241227","-0.0426139","0.039559904","0.008166272","-0.039946184","0.031655412","-0.031950764","-0.032584775","-0.038815115","-0.006275149","0.032772437","-0.118694074","0.06448928","-0.07904699","-0.13907093","0.05154887","-0.13419098","-0.03233624","-0.031945664","-0.014203393","0.11826748","-0.0074200127","0.049510278","-0.041240636","0.025994254","0.031445466","-0.01018207","0.10612646","-0.015393973","0.040094655","0.04587842","-0.016206533","0.030464398","0.06778791","-0.05454443","0.07805105","0.0010828751","0.042120922","-0.033375096","-0.015737817","0.03910107","-0.052798457","0.12697642","0.08079987","-0.007980972","-0.111619495","0.029947214","-0.049044237","-0.076532446","0.054605693","-0.12855813","-0.06436007","-0.027977843","-0.017215997","-0.024089029","0.027902327","-0.026700579","-0.017648028","0.044692773","0.08648817","-0.04043692","-9.471803E-4","-0.0010711746","0.029021075","3.351561E-4","0.11615948","0.041904587","0.026906736","0.056218907","-0.025041074","-0.04131766","-0.024906533","0.03531985","-0.003943509","-2.762571E-8","-0.026260523","0.0021717872","-0.04903761","-0.044203214","0.03014927","0.006982652","0.0064934082","0.008308635","-0.002207564","-0.02102647","-0.034777515","0.057506815","-0.013236372","0.010948441","0.025385825","-0.038749035","-0.0020503025","0.10155549","0.04577342","0.03764523","0.039898705","-0.0052833683","-0.031008674","-0.06416236","-0.015956452","0.015003107","0.011629942","0.029920522","0.07983345","-0.054452617","-0.048934724","0.067647606","-0.021373061","0.02986002","-0.05937297","0.0638038","0.0023887819","-0.065005966","-0.06769404","0.018049741","0.04102173","0.03380657","0.023640165","0.05339415","0.047259726","0.025292782","0.02608478","0.0017725267","0.04906604","-0.07365312","-0.07545042","-0.08176994","0.059369996","0.035488904","-0.042960417","-0.017761825","0.024156725","0.012052319","0.042638652","-0.0012922761","0.039038174","-0.03987636","-0.02010004","0.0014910644"]</t>
   </si>
 </sst>
 </file>
@@ -1043,8 +2235,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1059,9 +2256,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1471,24 +2665,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="5">
+      <c r="A2" s="8">
         <v>1245058</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="8">
         <v>446542</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="8">
         <v>326001</v>
       </c>
     </row>
@@ -1512,98 +2706,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="13">
         <v>1003458</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="13">
         <v>108502</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="13">
         <v>71939</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="13">
         <v>20367</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="13">
         <v>18469</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="13">
         <v>13674</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="13">
         <v>8264</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="13">
         <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="13">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="13">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="13">
         <v>1</v>
       </c>
     </row>
@@ -1626,169 +2820,169 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="10"/>
+      <c r="E1" s="12"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="10"/>
+      <c r="E2" s="12"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="10"/>
+      <c r="E3" s="12"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="10"/>
+      <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="10"/>
+      <c r="E5" s="12"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="10"/>
+      <c r="E6" s="12"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="10"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="10"/>
+      <c r="E8" s="12"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="10"/>
+      <c r="E9" s="12"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="10"/>
+      <c r="E10" s="12"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="10"/>
+      <c r="E11" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1807,18 +3001,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="5">
+      <c r="A2" s="8">
         <v>102</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="8">
         <v>100</v>
       </c>
     </row>
@@ -1846,321 +3040,321 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="2" ht="111" spans="1:9">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="3" ht="380.55" spans="1:9">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="4" ht="380.55" spans="1:9">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" ht="380.55" spans="1:9">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="6" ht="380.55" spans="1:9">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" ht="380.55" spans="1:9">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="8" ht="380.55" spans="1:9">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="9" ht="380.55" spans="1:9">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="10" ht="380.55" spans="1:9">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="11" ht="380.55" spans="1:9">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="6" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2182,24 +3376,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="5">
+      <c r="A2" s="8">
         <v>1520592</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="8">
         <v>224537</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="8">
         <v>570521</v>
       </c>
     </row>
@@ -2221,6 +3415,144 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
+      <c r="A1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" ht="47.55" spans="1:3">
+      <c r="A2" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" ht="47.55" spans="1:3">
+      <c r="A3" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" ht="47.55" spans="1:3">
+      <c r="A4" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" ht="47.55" spans="1:3">
+      <c r="A5" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" ht="31.7" spans="1:3">
+      <c r="A7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" ht="31.7" spans="1:3">
+      <c r="A8" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" ht="31.7" spans="1:3">
+      <c r="A9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" ht="95.15" spans="1:3">
+      <c r="A10" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" ht="95.15" spans="1:3">
+      <c r="A11" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr defaultColWidth="9.1" defaultRowHeight="15.85" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="33.2916666666667" customWidth="1"/>
+    <col min="2" max="2" width="65.125" customWidth="1"/>
+    <col min="3" max="4" width="255.641666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -2230,115 +3562,1408 @@
       <c r="C1" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="2" ht="31.7" spans="1:3">
+      <c r="D1" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" ht="31.7" spans="1:3">
+        <v>120</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" ht="47.55" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" ht="31.7" spans="1:3">
+        <v>124</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" ht="31.7" spans="1:3">
+        <v>128</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>132</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>136</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" ht="47.55" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>140</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" ht="47.55" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>144</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" ht="31.7" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" ht="63.45" spans="1:3">
+        <v>148</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" ht="31.7" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" ht="63.45" spans="1:3">
+        <v>152</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>116</v>
+        <v>156</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="21" ht="31.7" spans="1:4">
+      <c r="A21" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" ht="31.7" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="26" ht="31.7" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="27" ht="31.7" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="29" ht="47.55" spans="1:4">
+      <c r="A29" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="32" ht="47.55" spans="1:4">
+      <c r="A32" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="33" ht="31.7" spans="1:4">
+      <c r="A33" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="34" ht="47.55" spans="1:4">
+      <c r="A34" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="35" ht="47.55" spans="1:4">
+      <c r="A35" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="38" ht="31.7" spans="1:4">
+      <c r="A38" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="39" ht="47.55" spans="1:4">
+      <c r="A39" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="43" ht="31.7" spans="1:4">
+      <c r="A43" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="45" ht="47.55" spans="1:4">
+      <c r="A45" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="46" ht="31.7" spans="1:4">
+      <c r="A46" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="48" ht="47.55" spans="1:4">
+      <c r="A48" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="49" ht="31.7" spans="1:4">
+      <c r="A49" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="50" ht="31.7" spans="1:4">
+      <c r="A50" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="53" ht="47.55" spans="1:4">
+      <c r="A53" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="55" ht="31.7" spans="1:4">
+      <c r="A55" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="56" ht="47.55" spans="1:4">
+      <c r="A56" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="57" ht="31.7" spans="1:4">
+      <c r="A57" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="61" ht="31.7" spans="1:4">
+      <c r="A61" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="64" ht="31.7" spans="1:4">
+      <c r="A64" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="67" ht="31.7" spans="1:4">
+      <c r="A67" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="72" ht="47.55" spans="1:4">
+      <c r="A72" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="74" ht="47.55" spans="1:4">
+      <c r="A74" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="75" ht="63.45" spans="1:4">
+      <c r="A75" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="80" ht="47.55" spans="1:4">
+      <c r="A80" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="83" ht="31.7" spans="1:4">
+      <c r="A83" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="84" ht="47.55" spans="1:4">
+      <c r="A84" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="87" ht="31.7" spans="1:4">
+      <c r="A87" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="88" ht="31.7" spans="1:4">
+      <c r="A88" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="95" ht="31.7" spans="1:4">
+      <c r="A95" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="96" ht="47.55" spans="1:4">
+      <c r="A96" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="97" ht="47.55" spans="1:4">
+      <c r="A97" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="100" ht="47.55" spans="1:4">
+      <c r="A100" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>513</v>
       </c>
     </row>
   </sheetData>
